--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AA$127</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Q$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Q$51</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -1032,23 +1032,79 @@
           <t>University of Edinburgh</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5016434897</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>James R. Hopgood</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Adaptive Kernel Kalman Filter Multi-Sensor Fusion (2021)</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>I98677209</t>
+        </is>
+      </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>9.74</v>
       </c>
       <c r="U7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="4" t="inlineStr"/>
-      <c r="Z7" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>James R. Hopgood; Michael Davies; Mohsen Khadem; Kevin Dhaliwal; Lin Li</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>1. James R. Hopgood | Research=6.1/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.0/10 | Area=State Estimation &amp; Factor Graphs | Paper=Adaptive Kernel Kalman Filter Multi-Sensor Fusion (2021)
+2. Michael Davies | Research=6.1/10 | Activity=8.7/10 | Funding=0.0/10 | Overall=5.7/10 | Area=State Estimation &amp; Factor Graphs | Paper=Adaptive Kernel Kalman Filter Multi-Sensor Fusion (2021)
+3. Mohsen Khadem | Research=3.9/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.5/10 | Area=Visual-Inertial Navigation &amp; SLAM | Paper=Geometry-Aware Visual Odometry for Bronchoscopic Navigation via High-Gain Observer Fusion (2026)
+4. Kevin Dhaliwal | Research=3.9/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.5/10 | Area=Visual-Inertial Navigation &amp; SLAM | Paper=Geometry-Aware Visual Odometry for Bronchoscopic Navigation via High-Gain Observer Fusion (2026)
+5. Lin Li | Research=3.4/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.2/10 | Area=LiDAR &amp; Multimodal Sensor Fusion | Paper=Self-Supervised Cross-Source Point Cloud Registration Framework With Geometric Tree Transformer for  (2026)</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>James R. Hopgood: No homepage/funding evidence available
+Michael Davies: No homepage/funding evidence available
+Mohsen Khadem: No homepage/funding evidence available
+Kevin Dhaliwal: No homepage/funding evidence available
+Lin Li: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -1056,23 +1112,79 @@
           <t>University of Southampton</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5033328008</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Zehor Belkhatir</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Sensor Fusion of Visual Odometry and High-Gain Observer for Application to Vehicle Localization (2025)</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>I43439940</t>
+        </is>
+      </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>9.93</v>
       </c>
       <c r="U8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
-      <c r="Y8" s="4" t="inlineStr"/>
-      <c r="Z8" s="4" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Zehor Belkhatir; Indu Prasad Bodala; Sarvapali D. Ramchurn; Shoaib Ehsan; Blair Thornton</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>1. Zehor Belkhatir | Research=5.6/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.6/10 | Area=Visual-Inertial Navigation &amp; SLAM, State Estimation &amp; Factor Graphs | Paper=Sensor Fusion of Visual Odometry and High-Gain Observer for Application to Vehicle Localization (2025)
+2. Indu Prasad Bodala | Research=4.6/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=4.9/10 | Area=Visual-Inertial Navigation &amp; SLAM, GNSS &amp; Robust Localization, Robotics &amp; Autonomous Navigation | Paper=TAT-VPR: Ternary Adaptive Transformer for Dynamic and Efficient Visual Place Recognition (2025)
+3. Sarvapali D. Ramchurn | Research=4.4/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.9/10 | Area=Visual-Inertial Navigation &amp; SLAM, Robotics &amp; Autonomous Navigation, GNSS &amp; Robust Localization | Paper=TAT-VPR: Ternary Adaptive Transformer for Dynamic and Efficient Visual Place Recognition (2025)
+4. Shoaib Ehsan | Research=4.4/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.8/10 | Area=Visual-Inertial Navigation &amp; SLAM, Robotics &amp; Autonomous Navigation, GNSS &amp; Robust Localization | Paper=TAT-VPR: Ternary Adaptive Transformer for Dynamic and Efficient Visual Place Recognition (2025)
+5. Blair Thornton | Research=4.1/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.7/10 | Area=Robotics &amp; Autonomous Navigation, Visual-Inertial Navigation &amp; SLAM | Paper=Development of a prototype autonomous inspection robot for offshore riser cables (2022)</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
+          <t>Zehor Belkhatir: No homepage/funding evidence available
+Indu Prasad Bodala: No homepage/funding evidence available
+Sarvapali D. Ramchurn: No homepage/funding evidence available
+Shoaib Ehsan: No homepage/funding evidence available
+Blair Thornton: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -1080,23 +1192,79 @@
           <t>Cranfield University</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5015986514</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ivan V. Petrunin</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>A Comparative Analysis of Hybrid Sensor Fusion Schemes for Visual-Inertial Navigation (2025)</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>I82284825</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="4" t="inlineStr"/>
-      <c r="Z9" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Ivan V. Petrunin; Mengwei Sun; Weisi Guo; Hyo‐Sang Shin; Teng Li</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>1. Ivan V. Petrunin | Research=8.1/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.2/10 | Area=Visual-Inertial Navigation &amp; SLAM, GNSS &amp; Robust Localization, State Estimation &amp; Factor Graphs | Paper=A Comparative Analysis of Hybrid Sensor Fusion Schemes for Visual-Inertial Navigation (2025)
+2. Mengwei Sun | Research=6.2/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.0/10 | Area=State Estimation &amp; Factor Graphs, GNSS &amp; Robust Localization | Paper=Machine Learning Enhanced Multi-Sensor Fusion for Air Traffic Surveillance (2025)
+3. Weisi Guo | Research=5.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.7/10 | Area=3D Computer Vision &amp; Geometric Perception, GNSS &amp; Robust Localization, LiDAR &amp; Multimodal Sensor Fusion | Paper=Resilient Multi-Sensor UAV Navigation with a Hybrid Federated Fusion Architecture (2024)
+4. Hyo‐Sang Shin | Research=5.2/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.3/10 | Area=Visual-Inertial Navigation &amp; SLAM, State Estimation &amp; Factor Graphs | Paper=Robust Multi-Sensor Navigation in GNSS Degraded Environments (2023)
+5. Teng Li | Research=4.2/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.7/10 | Area=State Estimation &amp; Factor Graphs, GNSS &amp; Robust Localization | Paper=Comparative Analysis of Factor Graph Models for Carrier Phase-Based Precision Navigation (2026)</t>
+        </is>
+      </c>
+      <c r="Z9" s="4" t="inlineStr">
+        <is>
+          <t>Ivan V. Petrunin: No homepage/funding evidence available
+Mengwei Sun: No homepage/funding evidence available
+Weisi Guo: No homepage/funding evidence available
+Hyo‐Sang Shin: No homepage/funding evidence available
+Teng Li: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -1104,23 +1272,79 @@
           <t>University of Birmingham</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5103116086</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Masoud Bahraini</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Decentralized Cooperative Localization for Multi-Robot Systems with Asynchronous Sensor Fusion (2026)</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>I79619799</t>
+        </is>
+      </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="U10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
-      <c r="Y10" s="4" t="inlineStr"/>
-      <c r="Z10" s="4" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Masoud Bahraini; Mubashir Ali; Naresh Marturi; Beth Jelfs; Rustam Stolkin</t>
+        </is>
+      </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>1. Masoud Bahraini | Research=4.6/10 | Activity=9.0/10 | Funding=0.0/10 | Overall=4.8/10 | Area=Visual-Inertial Navigation &amp; SLAM | Paper=Decentralized Cooperative Localization for Multi-Robot Systems with Asynchronous Sensor Fusion (2026)
+2. Mubashir Ali | Research=3.4/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.2/10 | Area=LiDAR &amp; Multimodal Sensor Fusion | Paper=PLC-Fusion: Perspective-Based Hierarchical and Deep LiDAR Camera Fusion for 3D Object Detection in A (2024)
+3. Naresh Marturi | Research=2.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=3.8/10 | Area=LiDAR &amp; Multimodal Sensor Fusion | Paper=Local Region-to-Region Mapping-based Approach to Classify Articulated Objects (2023)
+4. Beth Jelfs | Research=2.7/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=3.8/10 | Area=GNSS &amp; Robust Localization | Paper=Landmark Management in the Application of Radar SLAM (2022)
+5. Rustam Stolkin | Research=2.6/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=3.7/10 | Area=Robotics &amp; Autonomous Navigation, LiDAR &amp; Multimodal Sensor Fusion, State Estimation &amp; Factor Graphs | Paper=Local Region-to-Region Mapping-based Approach to Classify Articulated Objects (2023)</t>
+        </is>
+      </c>
+      <c r="Z10" s="4" t="inlineStr">
+        <is>
+          <t>Masoud Bahraini: No homepage/funding evidence available
+Mubashir Ali: No homepage/funding evidence available
+Naresh Marturi: No homepage/funding evidence available
+Beth Jelfs: No homepage/funding evidence available
+Rustam Stolkin: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -1128,23 +1352,79 @@
           <t>University of Manchester</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5013721697</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Alexandru Stancu</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Simultaneous Localisation and Mapping with Fiducial Markers Based on Extended Kalman Filter (2023)</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>I28407311</t>
+        </is>
+      </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>9.93</v>
       </c>
       <c r="U11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="4" t="inlineStr"/>
-      <c r="Z11" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Alexandru Stancu; Mikel Luján; Kieran T. Wood; Mostafa R. A. Nabawy; Jyoti Kumar Sinha</t>
+        </is>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>1. Alexandru Stancu | Research=6.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.4/10 | Area=Robotics &amp; Autonomous Navigation, Visual-Inertial Navigation &amp; SLAM | Paper=Simultaneous Localisation and Mapping with Fiducial Markers Based on Extended Kalman Filter (2023)
+2. Mikel Luján | Research=4.1/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.7/10 | Area=Visual-Inertial Navigation &amp; SLAM, Robotics &amp; Autonomous Navigation, LiDAR &amp; Multimodal Sensor Fusion | Paper=NGD-SLAM: Towards Real-Time Dynamic SLAM without GPU (2025)
+3. Kieran T. Wood | Research=4.2/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=4.7/10 | Area=Visual-Inertial Navigation &amp; SLAM | Paper=Dynamic Feature Filtering for Robust Monocular Visual SLAM (2025)
+4. Mostafa R. A. Nabawy | Research=4.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.6/10 | Area=LiDAR &amp; Multimodal Sensor Fusion | Paper=Remote Wind Turbine Inspections: Exploring the Potential of Multimodal Drones (2024)
+5. Jyoti Kumar Sinha | Research=4.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.6/10 | Area=State Estimation &amp; Factor Graphs | Paper=Early Prediction of Remaining Useful Life for Rolling Bearings Based on Envelope Spectral Indicator  (2024)</t>
+        </is>
+      </c>
+      <c r="Z11" s="4" t="inlineStr">
+        <is>
+          <t>Alexandru Stancu: No homepage/funding evidence available
+Mikel Luján: No homepage/funding evidence available
+Kieran T. Wood: No homepage/funding evidence available
+Mostafa R. A. Nabawy: No homepage/funding evidence available
+Jyoti Kumar Sinha: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -3877,12 +4157,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -5636,8 +5916,1658 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>James R. Hopgood</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="F27" t="n">
+        <v>10</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>25</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Adaptive Kernel Kalman Filter Multi-Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>2021</v>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5016434897</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="F28" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Adaptive Kernel Kalman Filter Multi-Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>2021</v>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5113674176</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Mohsen Khadem</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>25</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Geometry-Aware Visual Odometry for Bronchoscopic Navigation via High-Gain Observer Fusion</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5057363853</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Kevin Dhaliwal</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="F30" t="n">
+        <v>10</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>25</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Geometry-Aware Visual Odometry for Bronchoscopic Navigation via High-Gain Observer Fusion</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5053576296</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Lin Li</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="F31" t="n">
+        <v>10</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>13</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Self-Supervised Cross-Source Point Cloud Registration Framework With Geometric Tree Transformer for HMD Six-DoF Pose Estimation</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100624898</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>University of Southampton</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Zehor Belkhatir</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>University of Southampton</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="F32" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>25</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Sensor Fusion of Visual Odometry and High-Gain Observer for Application to Vehicle Localization</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5033328008</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>University of Southampton</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Indu Prasad Bodala</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>University of Southampton</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="F33" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; GNSS &amp; Robust Localization; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>4</v>
+      </c>
+      <c r="K33" t="n">
+        <v>14</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>TAT-VPR: Ternary Adaptive Transformer for Dynamic and Efficient Visual Place Recognition</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5090442030</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>University of Southampton</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sarvapali D. Ramchurn</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>University of Southampton</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="F34" t="n">
+        <v>10</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>7</v>
+      </c>
+      <c r="K34" t="n">
+        <v>25</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>TAT-VPR: Ternary Adaptive Transformer for Dynamic and Efficient Visual Place Recognition</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5065527041</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>University of Southampton</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Shoaib Ehsan</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>University of Southampton</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="F35" t="n">
+        <v>10</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K35" t="n">
+        <v>25</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>TAT-VPR: Ternary Adaptive Transformer for Dynamic and Efficient Visual Place Recognition</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5103245109</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>University of Southampton</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Blair Thornton</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>University of Southampton</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>10</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>25</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Development of a prototype autonomous inspection robot for offshore riser cables</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>2022</v>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5039161868</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ivan V. Petrunin</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="F37" t="n">
+        <v>10</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; GNSS &amp; Robust Localization; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>17</v>
+      </c>
+      <c r="K37" t="n">
+        <v>25</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>A Comparative Analysis of Hybrid Sensor Fusion Schemes for Visual-Inertial Navigation</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5015986514</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Mengwei Sun</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>10</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" t="n">
+        <v>24</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Machine Learning Enhanced Multi-Sensor Fusion for Air Traffic Surveillance</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5078335947</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Weisi Guo</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="F39" t="n">
+        <v>10</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; GNSS &amp; Robust Localization; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" t="n">
+        <v>25</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Resilient Multi-Sensor UAV Navigation with a Hybrid Federated Fusion Architecture</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5062362866</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Hyo‐Sang Shin</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="F40" t="n">
+        <v>10</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>3</v>
+      </c>
+      <c r="K40" t="n">
+        <v>25</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Robust Multi-Sensor Navigation in GNSS Degraded Environments</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>2023</v>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5001666073</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Teng Li</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>10</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>25</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Comparative Analysis of Factor Graph Models for Carrier Phase-Based Precision Navigation</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5020227658</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Masoud Bahraini</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F42" t="n">
+        <v>9</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Decentralized Cooperative Localization for Multi-Robot Systems with Asynchronous Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5103116086</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Mubashir Ali</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="F43" t="n">
+        <v>10</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>2</v>
+      </c>
+      <c r="K43" t="n">
+        <v>25</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>PLC-Fusion: Perspective-Based Hierarchical and Deep LiDAR Camera Fusion for 3D Object Detection in Autonomous Vehicles</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5033406444</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Naresh Marturi</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F44" t="n">
+        <v>10</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>3</v>
+      </c>
+      <c r="K44" t="n">
+        <v>15</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Local Region-to-Region Mapping-based Approach to Classify Articulated Objects</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>2023</v>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5011562571</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Beth Jelfs</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F45" t="n">
+        <v>10</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>25</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Landmark Management in the Application of Radar SLAM</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>2022</v>
+      </c>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5025470623</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Rustam Stolkin</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F46" t="n">
+        <v>10</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; LiDAR &amp; Multimodal Sensor Fusion; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>11</v>
+      </c>
+      <c r="K46" t="n">
+        <v>25</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Local Region-to-Region Mapping-based Approach to Classify Articulated Objects</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>2023</v>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5005183926</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Alexandru Stancu</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="F47" t="n">
+        <v>10</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>3</v>
+      </c>
+      <c r="K47" t="n">
+        <v>18</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Simultaneous Localisation and Mapping with Fiducial Markers Based on Extended Kalman Filter</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>2023</v>
+      </c>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5013721697</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Mikel Luján</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="F48" t="n">
+        <v>10</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>4</v>
+      </c>
+      <c r="K48" t="n">
+        <v>25</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>NGD-SLAM: Towards Real-Time Dynamic SLAM without GPU</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O48" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5026069638</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Kieran T. Wood</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="F49" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>17</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Dynamic Feature Filtering for Robust Monocular Visual SLAM</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O49" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5056402291</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Mostafa R. A. Nabawy</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="F50" t="n">
+        <v>10</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>25</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Remote Wind Turbine Inspections: Exploring the Potential of Multimodal Drones</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O50" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5018262156</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>5</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Jyoti Kumar Sinha</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="F51" t="n">
+        <v>10</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>25</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Early Prediction of Remaining Useful Life for Rolling Bearings Based on Envelope Spectral Indicator and Bayesian Filter</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O51" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5057125584</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q26"/>
+  <autoFilter ref="A1:Q51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Faculty Results" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AA$127</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Q$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AG$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$AA$104</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,13 +457,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA127"/>
+  <dimension ref="A1:AG127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -474,19 +474,25 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="42" customWidth="1" min="17" max="17"/>
     <col width="25" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
     <col width="21" customWidth="1" min="20" max="20"/>
-    <col width="55" customWidth="1" min="21" max="21"/>
+    <col width="58" customWidth="1" min="21" max="21"/>
     <col width="18" customWidth="1" min="22" max="22"/>
     <col width="17" customWidth="1" min="23" max="23"/>
     <col width="42" customWidth="1" min="24" max="24"/>
-    <col width="55" customWidth="1" min="25" max="25"/>
-    <col width="55" customWidth="1" min="26" max="26"/>
+    <col width="58" customWidth="1" min="25" max="25"/>
+    <col width="58" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="21" customWidth="1" min="28" max="28"/>
+    <col width="20" customWidth="1" min="29" max="29"/>
+    <col width="42" customWidth="1" min="30" max="30"/>
+    <col width="42" customWidth="1" min="31" max="31"/>
+    <col width="42" customWidth="1" min="32" max="32"/>
+    <col width="42" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -625,11 +631,51 @@
           <t>Last_Publication</t>
         </is>
       </c>
+      <c r="AB1" s="3" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="AC1" s="3" t="inlineStr">
+        <is>
+          <t>Email_Domain</t>
+        </is>
+      </c>
+      <c r="AD1" s="3" t="inlineStr">
+        <is>
+          <t>PhD_Admission_Type</t>
+        </is>
+      </c>
+      <c r="AE1" s="3" t="inlineStr">
+        <is>
+          <t>PI_Seniority_&amp;_H_Index</t>
+        </is>
+      </c>
+      <c r="AF1" s="3" t="inlineStr">
+        <is>
+          <t>Cold_Email_Keywords</t>
+        </is>
+      </c>
+      <c r="AG1" s="3" t="inlineStr">
+        <is>
+          <t>Email_Search_Link</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
           <t>University of Oxford</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QS #3 | Tier S+ (Global Elite | h=2195)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -705,11 +751,36 @@
           <t>2026-10-01</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Oxford</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>@ox.ac.uk</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
           <t>University of Cambridge</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QS #5 | Tier S+ (Global Elite | h=1966)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -785,11 +856,36 @@
           <t>2026-10-08</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Cambridge</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>@cam.ac.uk</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
           <t>Imperial College London</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>QS #2 | Tier S+ (Global Elite | h=1742)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -865,11 +961,36 @@
           <t>2026-10-09</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>@imperial.ac.uk</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
           <t>University College London</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>QS #9 | Tier S+ (Global Elite | h=2026)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -945,11 +1066,36 @@
           <t>2026-10-08</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
           <t>University of Bristol</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1257)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1025,11 +1171,36 @@
           <t>2026-10-05</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Bristol</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>@bristol.ac.uk</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
           <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>QS #27 | Tier S+ (Global Elite | h=1367)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1105,11 +1276,36 @@
           <t>2026-09-26</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
           <t>University of Southampton</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=937)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1185,11 +1381,36 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>@southampton.ac.uk</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
           <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=469)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1265,11 +1486,36 @@
           <t>2026-09-14</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Cranfield</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>@cranfield.ac.uk</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
           <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=1266)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1345,11 +1591,36 @@
           <t>2026-10-12</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>@birmingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
           <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>QS #34 | Tier S+ (Global Elite | h=1303)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1425,6 +1696,21 @@
           <t>2026-09-01</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>@manchester.ac.uk</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -1432,23 +1718,137 @@
           <t>University of Sheffield</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5077010206</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mathew Hywel Evans</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Assessing the feasibility of monocular visual simultaneous localization and mapping for live sewer pipes: a field robotics study (2021)</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>I91136226</t>
+        </is>
+      </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>9.59</v>
       </c>
       <c r="U12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="4" t="inlineStr"/>
-      <c r="Z12" s="4" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Mathew Hywel Evans; Jonathan M. Aitken; Sean Anderson; Ashutosh Tiwari; Windo Hutabarat; Lyudmila S. Mihaylova; John Anthony Rossiter; Rob Worley; Valentin Radu; Gang Yu; Tony J. Prescott; Sándor M. Veres; Kirill V. Horoshenkov; Yicheng Yu</t>
+        </is>
+      </c>
+      <c r="Y12" s="4" t="inlineStr">
+        <is>
+          <t>1. Mathew Hywel Evans (Associate / Established PI (High Fit), h=14) | Fit=8.2/10 | Activity=7.9/10 | Funding=0.0/10 | Overall=6.9/10 | Keywords=visual slam, visual odometry, loop closure, pose estimation, field robotics | Paper=Assessing the feasibility of monocular visual simultaneous localization and mapping for live se (2021)
+2. Jonathan M. Aitken (Associate / Established PI (High Fit), h=17) | Fit=6.9/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.5/10 | Keywords=visual slam, visual odometry, loop closure, pose estimation, field robotics, robot localization | Paper=Assessing the feasibility of monocular visual simultaneous localization and mapping for live se (2021)
+3. Sean Anderson (Associate / Established PI (High Fit), h=22) | Fit=6.4/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.1/10 | Keywords=visual slam, visual odometry, loop closure, pose estimation, field robotics, robot localization | Paper=Assessing the feasibility of monocular visual simultaneous localization and mapping for live se (2021)
+4. Ashutosh Tiwari (Full / Senior Prof (Large Lab), h=51) | Fit=4.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.6/10 | Keywords=pose estimation, stereo vision, computer vision, ros | Paper=A Lightweight Target Following Architecture for Indoor Mobile Robot (2024)
+5. Windo Hutabarat (Associate / Established PI (High Fit), h=17) | Fit=4.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.6/10 | Keywords=pose estimation, stereo vision, computer vision, ros | Paper=A Lightweight Target Following Architecture for Indoor Mobile Robot (2024)
+6. Lyudmila S. Mihaylova (Full / Senior Prof (Large Lab), h=41) | Fit=4.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.6/10 | Keywords=visual odometry, robot localization, visual inertial odometry, kalman filter, state estimation, extended kalman filter | Paper=A robust method for approximate visual robot localization in feature-sparse sewer pipes (2023)
+7. John Anthony Rossiter (Full / Senior Prof (Large Lab), h=37) | Fit=4.1/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.5/10 | Keywords=pose estimation, robot perception, 3d reconstruction | Paper=Advanced Environment Modelling for Remote Teleoperation to Improve Operator Experience (2021)
+8. Rob Worley (Assistant Prof / Rising Star (Responsive), h=7) | Fit=4.2/10 | Activity=8.6/10 | Funding=0.0/10 | Overall=4.4/10 | Keywords=visual odometry, robot localization, trajectory estimation, loop closure, kalman filter | Paper=A robust method for approximate visual robot localization in feature-sparse sewer pipes (2023)
+9. Valentin Radu (Associate / Established PI (High Fit), h=14) | Fit=3.3/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.1/10 | Keywords=multi-sensor fusion, sensor fusion, sensor calibration | Paper=Multi-Sensor Fusion for Indoor Smartphone Localization with Attention Mechanism (2025)
+10. Gang Yu (Assistant Prof / Rising Star (Responsive), h=5) | Fit=3.3/10 | Activity=9.0/10 | Funding=0.0/10 | Overall=4.0/10 | Keywords=multi-sensor fusion, sensor fusion | Paper=Point Cloud for Wireless Communications: A Comprehensive Survey on Fundamentals, Techniques, an (2026)
+11. Tony J. Prescott (Full / Senior Prof (Large Lab), h=48) | Fit=3.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.0/10 | Keywords=stereo vision, deep learning | Paper=Improving the Robustness of Visual Teach‐and‐Repeat Navigation Using Drift Error Correction and (2025)
+12. Sándor M. Veres (Full / Senior Prof (Large Lab), h=21) | Fit=4.1/10 | Activity=6.3/10 | Funding=0.0/10 | Overall=3.9/10 | Keywords=pose estimation, robot perception, 3d reconstruction | Paper=Advanced Environment Modelling for Remote Teleoperation to Improve Operator Experience (2021)
+13. Kirill V. Horoshenkov (Full / Senior Prof (Large Lab), h=42) | Fit=3.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=3.9/10 | Keywords=robot localization, loop closure, kalman filter, autonomous navigation | Paper=Acoustic Echo Sensing for Robot Localization in Buried Pipe Networks (2023)
+14. Yicheng Yu (Assistant Prof / Rising Star (Responsive), h=6) | Fit=2.7/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=3.6/10 | Keywords=robot localization, kalman filter, autonomous navigation | Paper=Acoustic Echo Sensing for Robot Localization in Buried Pipe Networks (2024)</t>
+        </is>
+      </c>
+      <c r="Z12" s="4" t="inlineStr">
+        <is>
+          <t>Mathew Hywel Evans: No homepage/funding evidence available
+Jonathan M. Aitken: No homepage/funding evidence available
+Sean Anderson: No homepage/funding evidence available
+Ashutosh Tiwari: No homepage/funding evidence available
+Windo Hutabarat: No homepage/funding evidence available
+Lyudmila S. Mihaylova: No homepage/funding evidence available
+John Anthony Rossiter: No homepage/funding evidence available
+Rob Worley: No homepage/funding evidence available
+Valentin Radu: No homepage/funding evidence available
+Gang Yu: No homepage/funding evidence available
+Tony J. Prescott: No homepage/funding evidence available
+Sándor M. Veres: No homepage/funding evidence available
+Kirill V. Horoshenkov: No homepage/funding evidence available
+Yicheng Yu: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit) (h=14)</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>visual slam, visual odometry, loop closure, pose estimation, field robotics</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Mathew%20Hywel%20Evans%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -1456,23 +1856,119 @@
           <t>University of Nottingham</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=876)</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5087034933</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Xin Dong</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Sensors and Sensor Fusion Methodologies for Indoor Odometry: A Review (2022)</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>I142263535</t>
+        </is>
+      </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>8.57</v>
       </c>
       <c r="U13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="4" t="inlineStr"/>
-      <c r="Z13" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Xin Dong; Luis Figueredo; Nicholas Hamm; Keerthy Kusumam; V. Sreeja</t>
+        </is>
+      </c>
+      <c r="Y13" s="4" t="inlineStr">
+        <is>
+          <t>1. Xin Dong (Associate / Established PI (High Fit), h=28) | Fit=3.9/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.6/10 | Keywords=sensor fusion, pose estimation, point cloud registration | Paper=Sensors and Sensor Fusion Methodologies for Indoor Odometry: A Review (2022)
+2. Luis Figueredo (Associate / Established PI (High Fit), h=15) | Fit=3.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.4/10 | Keywords=lidar slam, robust localization, ros2 | Paper=Low-Cost Rapid-Development Air-Ground Robotic Solution for Nuclear Power Plant Inspection (2025)
+3. Nicholas Hamm (Full / Senior Prof (Large Lab), h=27) | Fit=2.6/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=3.7/10 | Keywords=gnss positioning, kalman filter | Paper=Mitigating the Scintillation Effect on GNSS Signals Using MP and ROTI (2022)
+4. Keerthy Kusumam (Assistant Prof / Rising Star (Responsive), h=9) | Fit=3.0/10 | Activity=7.6/10 | Funding=0.0/10 | Overall=3.4/10 | Keywords=mobile robot navigation, deep learning, computer vision | Paper=Self-Supervised Robust Feature Matching Pipeline for Teach and Repeat Navigation (2022)
+5. V. Sreeja (Associate / Established PI (High Fit), h=21) | Fit=2.6/10 | Activity=5.3/10 | Funding=0.0/10 | Overall=2.8/10 | Keywords=gnss positioning, kalman filter | Paper=Mitigating the Scintillation Effect on GNSS Signals Using MP and ROTI (2022)</t>
+        </is>
+      </c>
+      <c r="Z13" s="4" t="inlineStr">
+        <is>
+          <t>Xin Dong: No homepage/funding evidence available
+Luis Figueredo: No homepage/funding evidence available
+Nicholas Hamm: No homepage/funding evidence available
+Keerthy Kusumam: No homepage/funding evidence available
+V. Sreeja: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Nottingham</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>@nottingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit) (h=28)</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>sensor fusion, pose estimation, point cloud registration</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Anottingham.ac.uk%20%22Xin%20Dong%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
@@ -1480,23 +1976,131 @@
           <t>University of Leeds</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=948)</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5057324156</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mounir Ghogho</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Deep Learning Techniques for Visual SLAM: A Survey (2023)</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>I130828816</t>
+        </is>
+      </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>9.93</v>
       </c>
       <c r="U14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="4" t="inlineStr"/>
-      <c r="Z14" s="4" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Mounir Ghogho; Sheng Quan Xie; Mehmet R. Doğar; Richard A. Romano; Sharib Ali; Mahdi Rezaei; Duygu Sarıkaya; Robert C. Richardson; Netta Cohen; George Jackson-Mills; Andrew R. Barber</t>
+        </is>
+      </c>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t>1. Mounir Ghogho (Full / Senior Prof (Large Lab), h=44) | Fit=5.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.6/10 | Keywords=visual slam, robot localization, deep learning | Paper=Deep Learning Techniques for Visual SLAM: A Survey (2023)
+2. Sheng Quan Xie (Full / Senior Prof (Large Lab), h=52) | Fit=3.4/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.2/10 | Keywords=lidar camera fusion, sensor calibration, semantic segmentation, mobile robot navigation | Paper=Object-Based Semantic Fusion Algorithm of Lidar and Camera via Inverse Projection (2025)
+3. Mehmet R. Doğar (Associate / Established PI (High Fit), h=25) | Fit=2.9/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=3.9/10 | Keywords=robot localization, autonomous navigation | Paper=Real-time robot topological localization and mapping with limited visual sampling in simulated  (2023)
+4. Richard A. Romano (Associate / Established PI (High Fit), h=21) | Fit=2.9/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=3.8/10 | Keywords=lidar camera fusion, 3d object detection, object detection | Paper=Multi-level and Multi-modal Feature Fusion for Accurate 3D Object Detection in Connected and Au (2022)
+5. Sharib Ali (Full / Senior Prof (Large Lab), h=24) | Fit=2.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=3.8/10 | Keywords=pose estimation, 3d reconstruction, depth estimation, deep learning | Paper=Self-Supervised Monocular Depth and Pose Estimation for Endoscopy With Latent Priors (2026)
+6. Mahdi Rezaei (Associate / Established PI (High Fit), h=19) | Fit=2.7/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=3.8/10 | Keywords=lidar camera fusion, 3d object detection, object detection, trajectory estimation, computer vision, autonomous vehicles | Paper=Multi-level and multi-modal feature fusion for accurate 3D object detection in Connected and Au (2022)
+7. Duygu Sarıkaya (Assistant Prof / Rising Star (Responsive), h=9) | Fit=2.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=3.7/10 | Keywords=pose estimation, depth estimation, deep learning | Paper=PICO: Projection-Informed Consistency Optimisation for 6DoF surgical tool pose estimation (2026)
+8. Robert C. Richardson (Full / Senior Prof (Large Lab), h=52) | Fit=2.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=3.6/10 | Keywords=autonomous navigation | Paper=Autonomous control for miniaturized mobile robots in unknown pipe networks (2022)
+9. Netta Cohen (Associate / Established PI (High Fit), h=22) | Fit=2.6/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=3.6/10 | Keywords=autonomous navigation | Paper=Autonomous control for miniaturized mobile robots in unknown pipe networks (2022)
+10. George Jackson-Mills (Assistant Prof / Rising Star (Responsive), h=5) | Fit=2.5/10 | Activity=9.3/10 | Funding=0.0/10 | Overall=3.5/10 | Keywords=autonomous navigation | Paper=Autonomous control for miniaturized mobile robots in unknown pipe networks (2022)
+11. Andrew R. Barber (Assistant Prof / Rising Star (Responsive), h=5) | Fit=2.5/10 | Activity=8.7/10 | Funding=0.0/10 | Overall=3.4/10 | Keywords=autonomous navigation | Paper=Autonomous control for miniaturized mobile robots in unknown pipe networks (2022)</t>
+        </is>
+      </c>
+      <c r="Z14" s="4" t="inlineStr">
+        <is>
+          <t>Mounir Ghogho: No homepage/funding evidence available
+Sheng Quan Xie: No homepage/funding evidence available
+Mehmet R. Doğar: No homepage/funding evidence available
+Richard A. Romano: No homepage/funding evidence available
+Sharib Ali: No homepage/funding evidence available
+Mahdi Rezaei: No homepage/funding evidence available
+Duygu Sarıkaya: No homepage/funding evidence available
+Robert C. Richardson: No homepage/funding evidence available
+Netta Cohen: No homepage/funding evidence available
+George Jackson-Mills: No homepage/funding evidence available
+Andrew R. Barber: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=44)</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>visual slam, robot localization, deep learning</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Mounir%20Ghogho%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
@@ -1504,23 +2108,125 @@
           <t>Newcastle University</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=928)</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5028776321</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Xinrun Li</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>ALIVE: Asynchronous Lower Body Pose Estimation with Images, Visual-Inertial Odometry and Electromyography (2025)</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>I84884186</t>
+        </is>
+      </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="U15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="4" t="inlineStr"/>
-      <c r="Z15" s="4" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Xinrun Li; Rosemary A. Norman; Jeffrey A. Neasham; Maryam Haroutunian; Hafiz Husnain Raza Sherazi; Zhizun Xu; Christopher J. Holder; Vladimir V. Terzija</t>
+        </is>
+      </c>
+      <c r="Y15" s="4" t="inlineStr">
+        <is>
+          <t>1. Xinrun Li (Assistant Prof / Rising Star (Responsive), h=4) | Fit=4.4/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.9/10 | Keywords=visual inertial odometry, sensor fusion, pose estimation, 3d reconstruction, computer vision | Paper=ALIVE: Asynchronous Lower Body Pose Estimation with Images, Visual-Inertial Odometry and Electr (2025)
+2. Rosemary A. Norman (Associate / Established PI (High Fit), h=23) | Fit=4.3/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=visual inertial odometry, sensor fusion, visual odometry, pose estimation | Paper=A Low-Cost Visual Inertial Odometry System for Underwater Vehicles (2021)
+3. Jeffrey A. Neasham (Associate / Established PI (High Fit), h=22) | Fit=4.3/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=visual inertial odometry, sensor fusion, visual odometry, pose estimation | Paper=A Low-Cost Visual Inertial Odometry System for Underwater Vehicles (2021)
+4. Maryam Haroutunian (Assistant Prof / Rising Star (Responsive), h=9) | Fit=4.3/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.7/10 | Keywords=visual inertial odometry, sensor fusion, visual odometry, pose estimation | Paper=A Low-Cost Visual Inertial Odometry System for Underwater Vehicles (2021)
+5. Hafiz Husnain Raza Sherazi (Associate / Established PI (High Fit), h=18) | Fit=3.7/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.4/10 | Keywords=lidar camera fusion, autonomous vehicles, 3d object detection, object detection | Paper=PLC-Fusion: Perspective-Based Hierarchical and Deep LiDAR Camera Fusion for 3D Object Detection (2024)
+6. Zhizun Xu (Assistant Prof / Rising Star (Responsive), h=8) | Fit=4.0/10 | Activity=8.6/10 | Funding=0.0/10 | Overall=4.3/10 | Keywords=sensor fusion, kalman filter | Paper=Advancements in Sensor Fusion for Underwater SLAM: A Review on Enhanced Navigation and Environm (2024)
+7. Christopher J. Holder (Assistant Prof / Rising Star (Responsive), h=7) | Fit=3.9/10 | Activity=8.3/10 | Funding=0.0/10 | Overall=4.2/10 | Keywords=visual localization, pose estimation | Paper=On the Application of Efficient Neural Mapping to Real-Time Indoor Localisation for Unmanned Gr (2023)
+8. Vladimir V. Terzija (Full / Senior Prof (Large Lab), h=63) | Fit=3.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.0/10 | Keywords=state estimation, kalman filter | Paper=Variational Bayesian Unscented Kalman Filter for Active Distribution System State Estimation (2024)</t>
+        </is>
+      </c>
+      <c r="Z15" s="4" t="inlineStr">
+        <is>
+          <t>Xinrun Li: No homepage/funding evidence available
+Rosemary A. Norman: No homepage/funding evidence available
+Jeffrey A. Neasham: No homepage/funding evidence available
+Maryam Haroutunian: No homepage/funding evidence available
+Hafiz Husnain Raza Sherazi: No homepage/funding evidence available
+Zhizun Xu: No homepage/funding evidence available
+Christopher J. Holder: No homepage/funding evidence available
+Vladimir V. Terzija: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Newcastle upon Tyne</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>@ncl.ac.uk</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive) (h=4)</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, sensor fusion, pose estimation, 3d reconstruction, computer vision</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ancl.ac.uk%20%22Xinrun%20Li%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
@@ -1528,23 +2234,139 @@
           <t>University of Glasgow</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5103276629</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Zhihao Lin</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>SLAM 2 : Simultaneous Localization and Multimode Mapping for indoor dynamic environments (2024)</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>I7882870</t>
+        </is>
+      </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="4" t="inlineStr"/>
-      <c r="Z16" s="4" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Zhihao Lin; Zhen Tian; Chongfeng Wei; Jianglin Lan; Mahmoud A. Shawky; Prajval Kumar Murali; Anahid Basiri; Shuja Ansari; Lei Zhang; Mark David Butala; Junyin Qiu; Roderick Murray‐Smith; Hang Dai; Chaitanya Kaul; Henrik Hesse</t>
+        </is>
+      </c>
+      <c r="Y16" s="4" t="inlineStr">
+        <is>
+          <t>1. Zhihao Lin (Associate / Established PI (High Fit), h=15) | Fit=4.6/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.0/10 | Keywords=visual slam, pose estimation, deep learning, object detection | Paper=SLAM 2 : Simultaneous Localization and Multimode Mapping for indoor dynamic environments (2024)
+2. Zhen Tian (Associate / Established PI (High Fit), h=11) | Fit=4.6/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.0/10 | Keywords=visual slam, pose estimation, deep learning, object detection | Paper=SLAM 2 : Simultaneous Localization and Multimode Mapping for indoor dynamic environments (2024)
+3. Chongfeng Wei (Full / Senior Prof (Large Lab), h=36) | Fit=4.6/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.0/10 | Keywords=visual odometry, pose estimation, deep learning | Paper=Online Adaptive Keypoint Extraction for Visual Odometry Across Different Scenes (2025)
+4. Jianglin Lan (Associate / Established PI (High Fit), h=21) | Fit=4.4/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.9/10 | Keywords=visual slam, pose estimation, deep learning, object detection, visual inertial odometry | Paper=SLAM 2 : Simultaneous Localization and Multimode Mapping for indoor dynamic environments (2024)
+5. Mahmoud A. Shawky (Associate / Established PI (High Fit), h=12) | Fit=4.2/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=inertial navigation, extended kalman filter, kalman filter, sensor fusion | Paper=Enhanced Navigation Precision Through Interaction Multiple Filtering: Integrating Invariant and (2024)
+6. Prajval Kumar Murali (Assistant Prof / Rising Star (Responsive), h=8) | Fit=4.0/10 | Activity=9.0/10 | Funding=0.0/10 | Overall=4.4/10 | Keywords=point cloud registration, pose estimation, sensor calibration, semantic segmentation | Paper=GMCR: Graph-based Maximum Consensus Estimation for Point Cloud Registration (2023)
+7. Anahid Basiri (Associate / Established PI (High Fit), h=19) | Fit=3.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.3/10 | Keywords=gnss positioning, 3d reconstruction, autonomous vehicles, computer vision, deep learning, semantic segmentation | Paper=Scalable 3D mapping of cities using computer vision and signals of opportunity (2023)
+8. Shuja Ansari (Associate / Established PI (High Fit), h=19) | Fit=3.4/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.2/10 | Keywords=extended kalman filter, kalman filter | Paper=An experimental analysis of outdoor UAV localisation through diverse estimators and crowd-sense (2024)
+9. Lei Zhang (Full / Senior Prof (Large Lab), h=39) | Fit=3.1/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.0/10 | Keywords=visual localization, deep learning, computer vision | Paper=A Fine-Grained Attention Model for High Accuracy Operational Robot Guidance (2022)
+10. Mark David Butala (Associate / Established PI (High Fit), h=20) | Fit=2.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=3.8/10 | Keywords=pose estimation, gaussian splatting | Paper=SCI-Gaussian: Optimizing 3D Gaussian Radiance Fields from a Snapshot Compressive Image (2025)
+11. Junyin Qiu (Assistant Prof / Rising Star (Responsive), h=5) | Fit=2.7/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=3.7/10 | Keywords=visual inertial odometry | Paper=Direct Sparse Initialization for Stereo Visual-Inertial Odometry (2026)
+12. Roderick Murray‐Smith (Full / Senior Prof (Large Lab), h=48) | Fit=2.6/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=3.7/10 | Keywords=sensor fusion, depth estimation | Paper=IGAF: Incremental Guided Attention Fusion for Depth Super-Resolution (2024)
+13. Hang Dai (Associate / Established PI (High Fit), h=18) | Fit=2.8/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=3.7/10 | Keywords=sensor fusion, depth estimation | Paper=IGAF: Incremental Guided Attention Fusion for Depth Super-Resolution (2024)
+14. Chaitanya Kaul (Assistant Prof / Rising Star (Responsive), h=8) | Fit=2.6/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=3.6/10 | Keywords=sensor fusion, depth estimation | Paper=IGAF: Incremental Guided Attention Fusion for Depth Super-Resolution (2024)
+15. Henrik Hesse (Associate / Established PI (High Fit), h=15) | Fit=2.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=3.6/10 | Keywords=autonomous navigation | Paper=Bat-Grid SLAM: Bio-Inspired Active SLAM Approach Using Neural Grid Cells for Autonomous Navigat (2025)</t>
+        </is>
+      </c>
+      <c r="Z16" s="4" t="inlineStr">
+        <is>
+          <t>Zhihao Lin: No homepage/funding evidence available
+Zhen Tian: No homepage/funding evidence available
+Chongfeng Wei: No homepage/funding evidence available
+Jianglin Lan: No homepage/funding evidence available
+Mahmoud A. Shawky: No homepage/funding evidence available
+Prajval Kumar Murali: No homepage/funding evidence available
+Anahid Basiri: No homepage/funding evidence available
+Shuja Ansari: No homepage/funding evidence available
+Lei Zhang: No homepage/funding evidence available
+Mark David Butala: No homepage/funding evidence available
+Junyin Qiu: No homepage/funding evidence available
+Roderick Murray‐Smith: No homepage/funding evidence available
+Hang Dai: No homepage/funding evidence available
+Chaitanya Kaul: No homepage/funding evidence available
+Henrik Hesse: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit) (h=15)</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>visual slam, pose estimation, deep learning, object detection</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Zhihao%20Lin%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
@@ -4146,7 +4968,7 @@
       <c r="Z127" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA127"/>
+  <autoFilter ref="A1:AG127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4157,7 +4979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:AA104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -4166,7 +4988,7 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="42" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
@@ -4174,9 +4996,19 @@
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="42" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="55" customWidth="1" min="15" max="15"/>
+    <col width="58" customWidth="1" min="15" max="15"/>
     <col width="34" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="17" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="26" max="26"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4265,6 +5097,56 @@
           <t>Homepage</t>
         </is>
       </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Ranking</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Email_Domain</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>PhD_Admission_Type</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Seniority_Estimate</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Prof_H_Index</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>Total_Citations</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>Cold_Email_Keywords</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>Email_Search_Link</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7566,8 +8448,5679 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Mathew Hywel Evans</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="F52" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>5</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Assessing the feasibility of monocular visual simultaneous localization and mapping for live sewer pipes: a field robotics study</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>2021</v>
+      </c>
+      <c r="O52" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5077010206</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X52" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>visual slam, visual odometry, loop closure, pose estimation, field robotics</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Mathew%20Hywel%20Evans%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Jonathan M. Aitken</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="F53" t="n">
+        <v>10</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>4</v>
+      </c>
+      <c r="K53" t="n">
+        <v>14</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Assessing the feasibility of monocular visual simultaneous localization and mapping for live sewer pipes: a field robotics study</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>2021</v>
+      </c>
+      <c r="O53" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5080450263</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X53" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>841</v>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>visual slam, visual odometry, loop closure, pose estimation, field robotics, robot localization</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Jonathan%20M.%20Aitken%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>3</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Sean Anderson</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="F54" t="n">
+        <v>10</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>8</v>
+      </c>
+      <c r="K54" t="n">
+        <v>25</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Assessing the feasibility of monocular visual simultaneous localization and mapping for live sewer pipes: a field robotics study</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>2021</v>
+      </c>
+      <c r="O54" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5071097412</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X54" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1795</v>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>visual slam, visual odometry, loop closure, pose estimation, field robotics, robot localization</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Sean%20Anderson%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>4</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ashutosh Tiwari</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="F55" t="n">
+        <v>10</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>25</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>A Lightweight Target Following Architecture for Indoor Mobile Robot</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O55" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5066657755</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="X55" t="n">
+        <v>51</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>12302</v>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>pose estimation, stereo vision, computer vision, ros</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Ashutosh%20Tiwari%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>5</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Windo Hutabarat</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="F56" t="n">
+        <v>10</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>12</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>A Lightweight Target Following Architecture for Indoor Mobile Robot</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O56" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5022038523</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X56" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1643</v>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>pose estimation, stereo vision, computer vision, ros</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Windo%20Hutabarat%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>6</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Lyudmila S. Mihaylova</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="F57" t="n">
+        <v>10</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>8</v>
+      </c>
+      <c r="K57" t="n">
+        <v>25</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>A robust method for approximate visual robot localization in feature-sparse sewer pipes</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>2023</v>
+      </c>
+      <c r="O57" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5006505402</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="X57" t="n">
+        <v>41</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>6475</v>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>visual odometry, robot localization, visual inertial odometry, kalman filter, state estimation, extended kalman filter</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Lyudmila%20S.%20Mihaylova%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>7</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>John Anthony Rossiter</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="F58" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>25</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Advanced Environment Modelling for Remote Teleoperation to Improve Operator Experience</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>2021</v>
+      </c>
+      <c r="O58" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5039249886</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="X58" t="n">
+        <v>37</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>6763</v>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>pose estimation, robot perception, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22John%20Anthony%20Rossiter%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>8</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Rob Worley</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="F59" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; GNSS &amp; Robust Localization; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>6</v>
+      </c>
+      <c r="K59" t="n">
+        <v>8</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>A robust method for approximate visual robot localization in feature-sparse sewer pipes</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>2023</v>
+      </c>
+      <c r="O59" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5034011435</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="X59" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>226</v>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>visual odometry, robot localization, trajectory estimation, loop closure, kalman filter</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Rob%20Worley%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>9</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Valentin Radu</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="F60" t="n">
+        <v>10</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Deep Learning for Navigation &amp; Perception; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>2</v>
+      </c>
+      <c r="K60" t="n">
+        <v>19</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Multi-Sensor Fusion for Indoor Smartphone Localization with Attention Mechanism</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O60" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5007676144</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X60" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1054</v>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, sensor fusion, sensor calibration</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Valentin%20Radu%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>10</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Gang Yu</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="F61" t="n">
+        <v>9</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>7</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Point Cloud for Wireless Communications: A Comprehensive Survey on Fundamentals, Techniques, and Applications</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O61" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5101689085</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="X61" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>82</v>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, sensor fusion</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Gang%20Yu%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>11</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Tony J. Prescott</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="F62" t="n">
+        <v>10</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>25</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Improving the Robustness of Visual Teach‐and‐Repeat Navigation Using Drift Error Correction and Event‐Based Vision for Low‐Light Environments</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O62" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5013009407</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="X62" t="n">
+        <v>48</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>11046</v>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>stereo vision, deep learning</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Tony%20J.%20Prescott%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>12</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Sándor M. Veres</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="F63" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Advanced Environment Modelling for Remote Teleoperation to Improve Operator Experience</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>2021</v>
+      </c>
+      <c r="O63" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5058754653</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="X63" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>1923</v>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>pose estimation, robot perception, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22S%C3%A1ndor%20M.%20Veres%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>13</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Kirill V. Horoshenkov</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F64" t="n">
+        <v>10</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; 3D Computer Vision &amp; Geometric Perception; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>6</v>
+      </c>
+      <c r="K64" t="n">
+        <v>25</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Acoustic Echo Sensing for Robot Localization in Buried Pipe Networks</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>2023</v>
+      </c>
+      <c r="O64" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5035135063</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="X64" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>5221</v>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>robot localization, loop closure, kalman filter, autonomous navigation</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Kirill%20V.%20Horoshenkov%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>14</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Yicheng Yu</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="F65" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>4</v>
+      </c>
+      <c r="K65" t="n">
+        <v>11</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Acoustic Echo Sensing for Robot Localization in Buried Pipe Networks</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O65" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5101194418</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="X65" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>307</v>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>robot localization, kalman filter, autonomous navigation</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Yicheng%20Yu%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>University of Nottingham</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Xin Dong</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="F66" t="n">
+        <v>10</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>2</v>
+      </c>
+      <c r="K66" t="n">
+        <v>25</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Sensors and Sensor Fusion Methodologies for Indoor Odometry: A Review</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>2022</v>
+      </c>
+      <c r="O66" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5087034933</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Nottingham</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=876)</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>@nottingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X66" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>2609</v>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>sensor fusion, pose estimation, point cloud registration</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Anottingham.ac.uk%20%22Xin%20Dong%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>University of Nottingham</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>2</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Luis Figueredo</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F67" t="n">
+        <v>10</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>2</v>
+      </c>
+      <c r="K67" t="n">
+        <v>25</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Low-Cost Rapid-Development Air-Ground Robotic Solution for Nuclear Power Plant Inspection</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O67" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5040790541</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Nottingham</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=876)</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>@nottingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X67" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>822</v>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>lidar slam, robust localization, ros2</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Anottingham.ac.uk%20%22Luis%20Figueredo%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>University of Nottingham</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Nicholas Hamm</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="F68" t="n">
+        <v>10</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>3</v>
+      </c>
+      <c r="K68" t="n">
+        <v>25</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Mitigating the Scintillation Effect on GNSS Signals Using MP and ROTI</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>2022</v>
+      </c>
+      <c r="O68" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5019813634</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Nottingham</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=876)</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>@nottingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="X68" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>4525</v>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>gnss positioning, kalman filter</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Anottingham.ac.uk%20%22Nicholas%20Hamm%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>University of Nottingham</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>4</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Keerthy Kusumam</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="F69" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>2</v>
+      </c>
+      <c r="K69" t="n">
+        <v>6</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Self-Supervised Robust Feature Matching Pipeline for Teach and Repeat Navigation</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>2022</v>
+      </c>
+      <c r="O69" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5066809618</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Nottingham</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=876)</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>@nottingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="X69" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>337</v>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>mobile robot navigation, deep learning, computer vision</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Anottingham.ac.uk%20%22Keerthy%20Kusumam%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>University of Nottingham</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>5</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>V. Sreeja</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F70" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>2</v>
+      </c>
+      <c r="K70" t="n">
+        <v>2</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Mitigating the Scintillation Effect on GNSS Signals Using MP and ROTI</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>2022</v>
+      </c>
+      <c r="O70" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5054153924</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Nottingham</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=876)</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>@nottingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X70" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>1003</v>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>gnss positioning, kalman filter</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Anottingham.ac.uk%20%22V.%20Sreeja%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Mounir Ghogho</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="F71" t="n">
+        <v>10</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" t="n">
+        <v>25</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Deep Learning Techniques for Visual SLAM: A Survey</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>2023</v>
+      </c>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5057324156</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=948)</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="X71" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>8106</v>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>visual slam, robot localization, deep learning</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Mounir%20Ghogho%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Sheng Quan Xie</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="F72" t="n">
+        <v>10</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>2</v>
+      </c>
+      <c r="K72" t="n">
+        <v>25</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Object-Based Semantic Fusion Algorithm of Lidar and Camera via Inverse Projection</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O72" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5035866142</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=948)</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="X72" t="n">
+        <v>52</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>10528</v>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>lidar camera fusion, sensor calibration, semantic segmentation, mobile robot navigation</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Sheng%20Quan%20Xie%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Mehmet R. Doğar</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="F73" t="n">
+        <v>10</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>2</v>
+      </c>
+      <c r="K73" t="n">
+        <v>25</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Real-time robot topological localization and mapping with limited visual sampling in simulated buried pipe networks</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>2023</v>
+      </c>
+      <c r="O73" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5025603635</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=948)</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X73" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>2628</v>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>robot localization, autonomous navigation</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Mehmet%20R.%20Do%C4%9Far%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Richard A. Romano</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="F74" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>2</v>
+      </c>
+      <c r="K74" t="n">
+        <v>25</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Multi-level and Multi-modal Feature Fusion for Accurate 3D Object Detection in Connected and Automated Vehicles</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>2022</v>
+      </c>
+      <c r="O74" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5022268696</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=948)</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X74" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>1634</v>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>lidar camera fusion, 3d object detection, object detection</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Richard%20A.%20Romano%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>5</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Sharib Ali</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F75" t="n">
+        <v>10</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>2</v>
+      </c>
+      <c r="K75" t="n">
+        <v>25</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Self-Supervised Monocular Depth and Pose Estimation for Endoscopy With Latent Priors</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O75" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5080765299</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=948)</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="X75" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3328</v>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>pose estimation, 3d reconstruction, depth estimation, deep learning</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Sharib%20Ali%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>6</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Mahdi Rezaei</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F76" t="n">
+        <v>10</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; State Estimation &amp; Factor Graphs; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>8</v>
+      </c>
+      <c r="K76" t="n">
+        <v>25</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Multi-level and multi-modal feature fusion for accurate 3D object detection in Connected and Automated Vehicles</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>2022</v>
+      </c>
+      <c r="O76" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5067789332</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=948)</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X76" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>1410</v>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>lidar camera fusion, 3d object detection, object detection, trajectory estimation, computer vision, autonomous vehicles</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Mahdi%20Rezaei%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>7</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Duygu Sarıkaya</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F77" t="n">
+        <v>10</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>2</v>
+      </c>
+      <c r="K77" t="n">
+        <v>25</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>PICO: Projection-Informed Consistency Optimisation for 6DoF surgical tool pose estimation</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O77" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5050695785</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=948)</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="X77" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>7246</v>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>pose estimation, depth estimation, deep learning</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Duygu%20Sar%C4%B1kaya%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>8</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Robert C. Richardson</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F78" t="n">
+        <v>10</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>2</v>
+      </c>
+      <c r="K78" t="n">
+        <v>22</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Autonomous control for miniaturized mobile robots in unknown pipe networks</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>2022</v>
+      </c>
+      <c r="O78" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5065382176</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=948)</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="X78" t="n">
+        <v>52</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>9110</v>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>autonomous navigation</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Robert%20C.%20Richardson%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>9</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Netta Cohen</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F79" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="n">
+        <v>11</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Autonomous control for miniaturized mobile robots in unknown pipe networks</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>2022</v>
+      </c>
+      <c r="O79" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5059480877</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=948)</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X79" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>1919</v>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>autonomous navigation</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Netta%20Cohen%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>10</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>George Jackson-Mills</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F80" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>2</v>
+      </c>
+      <c r="K80" t="n">
+        <v>9</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Autonomous control for miniaturized mobile robots in unknown pipe networks</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>2022</v>
+      </c>
+      <c r="O80" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5011558590</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=948)</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="X80" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>82</v>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>autonomous navigation</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22George%20Jackson-Mills%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>11</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Andrew R. Barber</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F81" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>2</v>
+      </c>
+      <c r="K81" t="n">
+        <v>6</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Autonomous control for miniaturized mobile robots in unknown pipe networks</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>2022</v>
+      </c>
+      <c r="O81" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5057885483</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=948)</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="X81" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>autonomous navigation</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Andrew%20R.%20Barber%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Newcastle University</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Xinrun Li</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F82" t="n">
+        <v>10</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>3</v>
+      </c>
+      <c r="K82" t="n">
+        <v>16</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>ALIVE: Asynchronous Lower Body Pose Estimation with Images, Visual-Inertial Odometry and Electromyography</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O82" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5028776321</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Newcastle upon Tyne</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=928)</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>@ncl.ac.uk</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="X82" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, sensor fusion, pose estimation, 3d reconstruction, computer vision</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ancl.ac.uk%20%22Xinrun%20Li%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Newcastle University</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Rosemary A. Norman</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F83" t="n">
+        <v>10</v>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; State Estimation &amp; Factor Graphs; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>3</v>
+      </c>
+      <c r="K83" t="n">
+        <v>25</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>A Low-Cost Visual Inertial Odometry System for Underwater Vehicles</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>2021</v>
+      </c>
+      <c r="O83" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5001239975</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Newcastle upon Tyne</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=928)</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>@ncl.ac.uk</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X83" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>1882</v>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, sensor fusion, visual odometry, pose estimation</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ancl.ac.uk%20%22Rosemary%20A.%20Norman%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Newcastle University</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>3</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Jeffrey A. Neasham</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F84" t="n">
+        <v>10</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; State Estimation &amp; Factor Graphs; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>3</v>
+      </c>
+      <c r="K84" t="n">
+        <v>25</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>A Low-Cost Visual Inertial Odometry System for Underwater Vehicles</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>2021</v>
+      </c>
+      <c r="O84" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5073279805</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Newcastle upon Tyne</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=928)</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>@ncl.ac.uk</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X84" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>1850</v>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, sensor fusion, visual odometry, pose estimation</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ancl.ac.uk%20%22Jeffrey%20A.%20Neasham%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Newcastle University</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>4</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Maryam Haroutunian</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F85" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; State Estimation &amp; Factor Graphs; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>3</v>
+      </c>
+      <c r="K85" t="n">
+        <v>10</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>A Low-Cost Visual Inertial Odometry System for Underwater Vehicles</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>2021</v>
+      </c>
+      <c r="O85" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5036549995</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>Newcastle upon Tyne</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=928)</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>@ncl.ac.uk</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="X85" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>246</v>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, sensor fusion, visual odometry, pose estimation</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ancl.ac.uk%20%22Maryam%20Haroutunian%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Newcastle University</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>5</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Hafiz Husnain Raza Sherazi</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="F86" t="n">
+        <v>10</v>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" t="n">
+        <v>25</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>PLC-Fusion: Perspective-Based Hierarchical and Deep LiDAR Camera Fusion for 3D Object Detection in Autonomous Vehicles</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O86" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5070150180</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Newcastle upon Tyne</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=928)</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>@ncl.ac.uk</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X86" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>1541</v>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>lidar camera fusion, autonomous vehicles, 3d object detection, object detection</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ancl.ac.uk%20%22Hafiz%20Husnain%20Raza%20Sherazi%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Newcastle University</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>6</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Zhizun Xu</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="F87" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; State Estimation &amp; Factor Graphs; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" t="n">
+        <v>9</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Advancements in Sensor Fusion for Underwater SLAM: A Review on Enhanced Navigation and Environmental Perception</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O87" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5005265198</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Newcastle upon Tyne</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=928)</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>@ncl.ac.uk</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="X87" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>206</v>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>sensor fusion, kalman filter</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ancl.ac.uk%20%22Zhizun%20Xu%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Newcastle University</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>7</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Christopher J. Holder</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="F88" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" t="n">
+        <v>6</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>On the Application of Efficient Neural Mapping to Real-Time Indoor Localisation for Unmanned Ground Vehicles</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>2023</v>
+      </c>
+      <c r="O88" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5055783706</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Newcastle upon Tyne</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=928)</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>@ncl.ac.uk</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="X88" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>168</v>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>visual localization, pose estimation</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ancl.ac.uk%20%22Christopher%20J.%20Holder%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Newcastle University</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>8</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Vladimir V. Terzija</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="F89" t="n">
+        <v>10</v>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" t="n">
+        <v>25</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Variational Bayesian Unscented Kalman Filter for Active Distribution System State Estimation</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O89" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5038764115</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Newcastle upon Tyne</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=928)</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>@ncl.ac.uk</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="X89" t="n">
+        <v>63</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>16587</v>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>state estimation, kalman filter</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ancl.ac.uk%20%22Vladimir%20V.%20Terzija%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Zhihao Lin</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="F90" t="n">
+        <v>10</v>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>2</v>
+      </c>
+      <c r="K90" t="n">
+        <v>25</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>SLAM 2 : Simultaneous Localization and Multimode Mapping for indoor dynamic environments</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O90" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5103276629</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X90" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>861</v>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>visual slam, pose estimation, deep learning, object detection</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Zhihao%20Lin%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>2</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Zhen Tian</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="F91" t="n">
+        <v>10</v>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>2</v>
+      </c>
+      <c r="K91" t="n">
+        <v>25</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>SLAM 2 : Simultaneous Localization and Multimode Mapping for indoor dynamic environments</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O91" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5101311536</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X91" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>399</v>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>visual slam, pose estimation, deep learning, object detection</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Zhen%20Tian%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>3</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Chongfeng Wei</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="F92" t="n">
+        <v>10</v>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="n">
+        <v>25</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Online Adaptive Keypoint Extraction for Visual Odometry Across Different Scenes</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O92" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5054213642</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="X92" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>4214</v>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>visual odometry, pose estimation, deep learning</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Chongfeng%20Wei%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>4</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Jianglin Lan</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F93" t="n">
+        <v>10</v>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>3</v>
+      </c>
+      <c r="K93" t="n">
+        <v>25</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>SLAM 2 : Simultaneous Localization and Multimode Mapping for indoor dynamic environments</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O93" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5050760087</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X93" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>1801</v>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>visual slam, pose estimation, deep learning, object detection, visual inertial odometry</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Jianglin%20Lan%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>5</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Mahmoud A. Shawky</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F94" t="n">
+        <v>10</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; Visual-Inertial Navigation &amp; SLAM; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>3</v>
+      </c>
+      <c r="K94" t="n">
+        <v>25</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Enhanced Navigation Precision Through Interaction Multiple Filtering: Integrating Invariant and Extended Kalman Filters</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O94" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5082156702</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X94" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>440</v>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>inertial navigation, extended kalman filter, kalman filter, sensor fusion</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Mahmoud%20A.%20Shawky%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>6</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Prajval Kumar Murali</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="F95" t="n">
+        <v>9</v>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>4</v>
+      </c>
+      <c r="K95" t="n">
+        <v>8</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>GMCR: Graph-based Maximum Consensus Estimation for Point Cloud Registration</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>2023</v>
+      </c>
+      <c r="O95" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5041052457</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="X95" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>379</v>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>point cloud registration, pose estimation, sensor calibration, semantic segmentation</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Prajval%20Kumar%20Murali%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>7</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Anahid Basiri</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="F96" t="n">
+        <v>10</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>2</v>
+      </c>
+      <c r="K96" t="n">
+        <v>25</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Scalable 3D mapping of cities using computer vision and signals of opportunity</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>2023</v>
+      </c>
+      <c r="O96" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5076329659</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X96" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>1301</v>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>gnss positioning, 3d reconstruction, autonomous vehicles, computer vision, deep learning, semantic segmentation</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Anahid%20Basiri%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>8</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Shuja Ansari</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="F97" t="n">
+        <v>10</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" t="n">
+        <v>25</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>An experimental analysis of outdoor UAV localisation through diverse estimators and crowd-sensed data fusion</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O97" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5001835000</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X97" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>1206</v>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>extended kalman filter, kalman filter</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Shuja%20Ansari%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>9</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Lei Zhang</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F98" t="n">
+        <v>10</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>1</v>
+      </c>
+      <c r="K98" t="n">
+        <v>25</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>A Fine-Grained Attention Model for High Accuracy Operational Robot Guidance</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>2022</v>
+      </c>
+      <c r="O98" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5075816408</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="X98" t="n">
+        <v>39</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>6742</v>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>visual localization, deep learning, computer vision</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Lei%20Zhang%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>10</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Mark David Butala</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F99" t="n">
+        <v>10</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>1</v>
+      </c>
+      <c r="K99" t="n">
+        <v>25</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>SCI-Gaussian: Optimizing 3D Gaussian Radiance Fields from a Snapshot Compressive Image</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O99" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5075035096</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X99" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>1404</v>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>pose estimation, gaussian splatting</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Mark%20David%20Butala%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>11</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Junyin Qiu</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="F100" t="n">
+        <v>10</v>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>1</v>
+      </c>
+      <c r="K100" t="n">
+        <v>10</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Direct Sparse Initialization for Stereo Visual-Inertial Odometry</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O100" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5067191498</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="X100" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>visual inertial odometry</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Junyin%20Qiu%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>12</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Roderick Murray‐Smith</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="F101" t="n">
+        <v>10</v>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>2</v>
+      </c>
+      <c r="K101" t="n">
+        <v>25</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>IGAF: Incremental Guided Attention Fusion for Depth Super-Resolution</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O101" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5070918132</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="X101" t="n">
+        <v>48</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>8639</v>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>sensor fusion, depth estimation</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Roderick%20Murray%E2%80%90Smith%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>13</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Hang Dai</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F102" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>1</v>
+      </c>
+      <c r="K102" t="n">
+        <v>25</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>IGAF: Incremental Guided Attention Fusion for Depth Super-Resolution</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O102" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5080852978</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X102" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>2151</v>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>sensor fusion, depth estimation</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Hang%20Dai%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>14</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Chaitanya Kaul</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="F103" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>2</v>
+      </c>
+      <c r="K103" t="n">
+        <v>16</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>IGAF: Incremental Guided Attention Fusion for Depth Super-Resolution</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O103" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5076295200</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="X103" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>604</v>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>sensor fusion, depth estimation</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Chaitanya%20Kaul%22%20email</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>15</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Henrik Hesse</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F104" t="n">
+        <v>10</v>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>1</v>
+      </c>
+      <c r="K104" t="n">
+        <v>17</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Bat-Grid SLAM: Bio-Inspired Active SLAM Approach Using Neural Grid Cells for Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O104" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5066082686</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="X104" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>778</v>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>autonomous navigation</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Henrik%20Hesse%22%20email</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q51"/>
+  <autoFilter ref="A1:AA104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AG$127</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Z$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Z$169</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,10 +475,10 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="35" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
     <col width="42" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
     <col width="25" customWidth="1" min="21" max="21"/>
     <col width="42" customWidth="1" min="22" max="22"/>
@@ -1424,23 +1424,133 @@
           <t>University of Edinburgh</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>QS #27 | Tier S+ (Global Elite | h=1366)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5057962470</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mike E. Davies</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Adaptive Kernel Kalman Filter Multi-Sensor Fusion (2021)</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>I98677209</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=42)</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, sensor fusion, kalman filter, state estimation</t>
+        </is>
+      </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="Z7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>7.36</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="4" t="inlineStr"/>
-      <c r="AE7" s="4" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Mike E. Davies; James R. Hopgood; Yunjie Yang; Mohsen Khadem; Vaishak Belle; Robert Bob Fisher; István Gyöngy; Robert Henderson; Barbara H. Webb; Oisin Mac Aodha; Hakan Bilen; Steven McDonagh</t>
+        </is>
+      </c>
+      <c r="AD7" s="4" t="inlineStr">
+        <is>
+          <t>1. Mike E. Davies (Full / Senior Prof (Large Lab), h=42) | Fit=9.4/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=multi-sensor fusion, sensor fusion, kalman filter, state estimation | Paper=Adaptive Kernel Kalman Filter Multi-Sensor Fusion (2021)
+2. James R. Hopgood (Associate / Established PI (High Fit), h=18) | Fit=9.4/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=multi-sensor fusion, sensor fusion, kalman filter, state estimation | Paper=Adaptive Kernel Kalman Filter Multi-Sensor Fusion (2021)
+3. Yunjie Yang (Full / Senior Prof (Large Lab), h=30) | Fit=8.8/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.6/10 | Keywords=point cloud registration, pose estimation, robot perception | Paper=Self-Supervised Cross-Source Point Cloud Registration Framework With Geometric Tree Transformer (2026)
+4. Mohsen Khadem (Associate / Established PI (High Fit), h=17) | Fit=8.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.5/10 | Keywords=visual odometry, sensor fusion | Paper=Geometry-Aware Visual Odometry for Bronchoscopic Navigation via High-Gain Observer Fusion (2026)
+5. Vaishak Belle (Full / Senior Prof (Large Lab), h=19) | Fit=7.0/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=6.2/10 | Keywords=robot localization | Paper=Localization (2023)
+6. Robert Bob Fisher (Full / Senior Prof (Large Lab), h=47) | Fit=6.4/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=6.0/10 | Keywords=pose estimation, point cloud registration, autonomous vehicles, deep learning | Paper=A general mobile manipulator automation framework for flexible tasks in controlled environments (2023)
+7. István Gyöngy (Associate / Established PI (High Fit), h=22) | Fit=5.8/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=5.6/10 | Keywords=sensor fusion, depth estimation, autonomous vehicles | Paper=Guided Direct Time-of-Flight Lidar Using Stereo Cameras for Enhanced Laser Power Efficiency (2023)
+8. Robert Henderson (Full / Senior Prof (Large Lab), h=53) | Fit=5.8/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=5.5/10 | Keywords=sensor fusion, depth estimation, autonomous vehicles, 3d reconstruction | Paper=Guided Direct Time-of-Flight Lidar Using Stereo Cameras for Enhanced Laser Power Efficiency (2023)
+9. Barbara H. Webb (Full / Senior Prof (Large Lab), h=44) | Fit=5.4/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.3/10 | Keywords=mobile robot navigation, trajectory estimation, computer vision | Paper=Embodied visual route following by an insect-inspired robot (2024)
+10. Oisin Mac Aodha (Associate / Established PI (High Fit), h=25) | Fit=4.0/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.4/10 | Keywords=3d reconstruction, computer vision | Paper=Heightfields for Efficient Scene Reconstruction for AR (2023)
+11. Hakan Bilen (Associate / Established PI (High Fit), h=28) | Fit=3.8/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.2/10 | Keywords=depth estimation, computer vision, semantic segmentation | Paper=Multi-task Learning with 3D-Aware Regularization (2023)
+12. Steven McDonagh (Associate / Established PI (High Fit), h=22) | Fit=3.8/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.2/10 | Keywords=depth estimation, computer vision, semantic segmentation | Paper=Multi-task Learning with 3D-Aware Regularization (2023)</t>
+        </is>
+      </c>
+      <c r="AE7" s="4" t="inlineStr">
+        <is>
+          <t>Mike E. Davies: No homepage/funding evidence available
+James R. Hopgood: No homepage/funding evidence available
+Yunjie Yang: No homepage/funding evidence available
+Mohsen Khadem: No homepage/funding evidence available
+Vaishak Belle: No homepage/funding evidence available
+Robert Bob Fisher: No homepage/funding evidence available
+István Gyöngy: No homepage/funding evidence available
+Robert Henderson: No homepage/funding evidence available
+Barbara H. Webb: No homepage/funding evidence available
+Oisin Mac Aodha: No homepage/funding evidence available
+Hakan Bilen: No homepage/funding evidence available
+Steven McDonagh: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aed.ac.uk%20%22Mike%20E.%20Davies%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -1448,23 +1558,123 @@
           <t>University of Southampton</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=937)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5103245109</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Shoaib Ehsan</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>TAT-VPR: Ternary Adaptive Transformer for Dynamic and Efficient Visual Place Recognition (2025)</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>@southampton.ac.uk</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>I43439940</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit) (h=21)</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>place recognition, visual slam, loop closure, robot localization, embedded systems, autonomous vehicles</t>
+        </is>
+      </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>9.93</v>
       </c>
       <c r="Z8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="4" t="inlineStr"/>
-      <c r="AE8" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Shoaib Ehsan; Sarvapali D. Ramchurn; David J. White; Blair Thornton; Nicolas Peter Avdelidis; Huanhuan Li; Xiaohao Cai</t>
+        </is>
+      </c>
+      <c r="AD8" s="4" t="inlineStr">
+        <is>
+          <t>1. Shoaib Ehsan (Associate / Established PI (High Fit), h=21) | Fit=9.7/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.3/10 | Keywords=place recognition, visual slam, loop closure, robot localization, embedded systems, autonomous vehicles | Paper=TAT-VPR: Ternary Adaptive Transformer for Dynamic and Efficient Visual Place Recognition (2025)
+2. Sarvapali D. Ramchurn (Full / Senior Prof (Large Lab), h=42) | Fit=9.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.2/10 | Keywords=place recognition, visual slam, loop closure, robot localization, embedded systems, autonomous vehicles | Paper=TAT-VPR: Ternary Adaptive Transformer for Dynamic and Efficient Visual Place Recognition (2025)
+3. David J. White (Full / Senior Prof (Large Lab), h=65) | Fit=6.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.4/10 | Keywords=robot localization, autonomous navigation | Paper=Development of a prototype autonomous inspection robot for offshore riser cables (2022)
+4. Blair Thornton (Full / Senior Prof (Large Lab), h=26) | Fit=6.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.4/10 | Keywords=robot localization, autonomous navigation | Paper=Development of a prototype autonomous inspection robot for offshore riser cables (2022)
+5. Nicolas Peter Avdelidis (Full / Senior Prof (Large Lab), h=30) | Fit=4.0/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=4.5/10 | Keywords=robot localization | Paper=Techno-economic analysis for smart hangar inspection operations through sensing and localisatio (2025)
+6. Huanhuan Li (Full / Senior Prof (Large Lab), h=33) | Fit=3.9/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.4/10 | Keywords=autonomous navigation, deep learning | Paper=Uncertainty-aware ship trajectory prediction via Spatio-Temporal Graph Transformer (2025)
+7. Xiaohao Cai (Associate / Established PI (High Fit), h=20) | Fit=3.7/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.2/10 | Keywords=3d object detection, object detection | Paper=Revisiting Cross-Domain Problem for LiDAR-Based 3D Object Detection (2025)</t>
+        </is>
+      </c>
+      <c r="AE8" s="4" t="inlineStr">
+        <is>
+          <t>Shoaib Ehsan: No homepage/funding evidence available
+Sarvapali D. Ramchurn: No homepage/funding evidence available
+David J. White: No homepage/funding evidence available
+Blair Thornton: No homepage/funding evidence available
+Nicolas Peter Avdelidis: No homepage/funding evidence available
+Huanhuan Li: No homepage/funding evidence available
+Xiaohao Cai: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asouthampton.ac.uk%20%22Shoaib%20Ehsan%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -1472,23 +1682,141 @@
           <t>Cranfield University</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=469)</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5015986514</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ivan V. Petrunin</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Error Correction Using Bayesian GRU Network in Hybrid Visual Inertial Navigation System (2026)</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Cranfield</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>@cranfield.ac.uk</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>I82284825</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit) (h=17)</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>visual inertial navigation, inertial navigation, visual inertial odometry, sensor fusion, visual odometry, kalman filter</t>
+        </is>
+      </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="Z9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>7.82</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="4" t="inlineStr"/>
-      <c r="AE9" s="4" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ivan V. Petrunin; Dmitry Ignatyev; Weisi Guo; Hyo‐Sang Shin; Argyrios C. Zolotas; Teng Li; Boyu Kuang; Antonios Tsourdos; Gökhan İnalhan; Phil Webb; S. A. Syed Asif; Leon Williams; Yang Xing; Adolfo Perrusquía; Saba Al–Rubaye; Mark A. Richardson</t>
+        </is>
+      </c>
+      <c r="AD9" s="4" t="inlineStr">
+        <is>
+          <t>1. Ivan V. Petrunin (Associate / Established PI (High Fit), h=17) | Fit=10.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.5/10 | Keywords=visual inertial navigation, inertial navigation, visual inertial odometry, sensor fusion, visual odometry, kalman filter | Paper=Error Correction Using Bayesian GRU Network in Hybrid Visual Inertial Navigation System (2026)
+2. Dmitry Ignatyev (Associate / Established PI (High Fit), h=14) | Fit=9.4/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=8.0/10 | Keywords=loop closure, visual slam, object detection | Paper=Advancing autonomous SLAM systems: Integrating YOLO object detection and enhanced loop closure  (2024)
+3. Weisi Guo (Full / Senior Prof (Large Lab), h=38) | Fit=9.1/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=visual odometry, sensor fusion, extended kalman filter, kalman filter, stereo vision, depth estimation | Paper=Resilient Multi-Sensor UAV Navigation with a Hybrid Federated Fusion Architecture (2024)
+4. Hyo‐Sang Shin (Full / Senior Prof (Large Lab), h=36) | Fit=8.9/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=visual inertial navigation, inertial navigation, sensor fusion, state estimation | Paper=Robust Multi-Sensor Navigation in GNSS Degraded Environments (2023)
+5. Argyrios C. Zolotas (Full / Senior Prof (Large Lab), h=24) | Fit=8.1/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.2/10 | Keywords=visual odometry, sensor fusion, robot localization | Paper=GNSS/INS/VO fusion using Gated Recurrent Unit in GNSS denied environments (2023)
+6. Teng Li (Associate / Established PI (High Fit), h=18) | Fit=7.4/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=6.8/10 | Keywords=factor graph optimization, gnss positioning | Paper=Comparative Analysis of Factor Graph Models for Carrier Phase-Based Precision Navigation (2026)
+7. Boyu Kuang (Assistant Prof / Rising Star (Responsive), h=17) | Fit=7.4/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=6.4/10 | Keywords=visual slam, trajectory estimation, computer vision, semantic segmentation | Paper=OG-SLAM: A real-time and high-accurate monocular visual SLAM framework (2022)
+8. Antonios Tsourdos (Full / Senior Prof (Large Lab), h=59) | Fit=6.8/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=6.4/10 | Keywords=gnss positioning, inertial navigation, lidar camera fusion, object detection, trajectory estimation, stereo vision | Paper=Experimental Evaluation of GNSS and IMU Fusion Using Gated Recurrent Unit (2022)
+9. Gökhan İnalhan (Full / Senior Prof (Large Lab), h=28) | Fit=7.0/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=6.2/10 | Keywords=visual odometry, pose estimation | Paper=Federated Meta Learning for Visual Navigation in GPS-denied Urban Airspace (2023)
+10. Phil Webb (Associate / Established PI (High Fit), h=24) | Fit=6.8/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.2/10 | Keywords=pose estimation, robot perception, object detection, ros, ros2 | Paper=Unlocking the potential of Robot Manipulators: Seamless Integration Framework (2024)
+11. S. A. Syed Asif (Associate / Established PI (High Fit), h=25) | Fit=6.8/10 | Activity=6.6/10 | Funding=0.0/10 | Overall=5.7/10 | Keywords=pose estimation, robot perception, object detection, ros, ros2 | Paper=Unlocking the potential of Robot Manipulators: Seamless Integration Framework (2024)
+12. Leon Williams (Associate / Established PI (High Fit), h=20) | Fit=5.8/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=5.4/10 | Keywords=visual slam, computer vision | Paper=Advanced Visual SLAM and Image Segmentation Techniques for Augmented Reality (2022)
+13. Yang Xing (Full / Senior Prof (Large Lab), h=42) | Fit=5.1/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=5.1/10 | Keywords=trajectory estimation, stereo vision, object detection | Paper=Eyes-Out Airborne Object Detector for Pilots Situational Awareness (2024)
+14. Adolfo Perrusquía (Associate / Established PI (High Fit), h=22) | Fit=4.8/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.9/10 | Keywords=stereo vision, depth estimation, deep learning, trajectory estimation | Paper=Enhancing Situational Awareness of Helicopter Pilots in Unmanned Aerial Vehicle-Congested Envir (2024)
+15. Saba Al–Rubaye (Associate / Established PI (High Fit), h=27) | Fit=4.2/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.6/10 | Keywords=gnss positioning, deep learning, hardware acceleration, autonomous vehicles, fpga, embedded systems | Paper=Intelligent 5G-Aided UAV Positioning in High-Density Environments Using Neural Networks for NLO (2025)
+16. Mark A. Richardson (Associate / Established PI (High Fit), h=22) | Fit=4.3/10 | Activity=6.8/10 | Funding=0.0/10 | Overall=4.2/10 | Keywords=pose estimation, deep learning | Paper=ChiNet: Deep Recurrent Convolutional Learning for Multimodal Spacecraft Pose Estimation (2022)</t>
+        </is>
+      </c>
+      <c r="AE9" s="4" t="inlineStr">
+        <is>
+          <t>Ivan V. Petrunin: No homepage/funding evidence available
+Dmitry Ignatyev: No homepage/funding evidence available
+Weisi Guo: No homepage/funding evidence available
+Hyo‐Sang Shin: No homepage/funding evidence available
+Argyrios C. Zolotas: No homepage/funding evidence available
+Teng Li: No homepage/funding evidence available
+Boyu Kuang: No homepage/funding evidence available
+Antonios Tsourdos: No homepage/funding evidence available
+Gökhan İnalhan: No homepage/funding evidence available
+Phil Webb: No homepage/funding evidence available
+S. A. Syed Asif: No homepage/funding evidence available
+Leon Williams: No homepage/funding evidence available
+Yang Xing: No homepage/funding evidence available
+Adolfo Perrusquía: No homepage/funding evidence available
+Saba Al–Rubaye: No homepage/funding evidence available
+Mark A. Richardson: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Acranfield.ac.uk%20%22Ivan%20V.%20Petrunin%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -1496,23 +1824,133 @@
           <t>University of Birmingham</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=1267)</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5058814232</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Yongjing Wang</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>The SVD-enhanced bees algorithm, a novel procedure for point cloud registration (2024)</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>@birmingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>I79619799</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=30)</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>point cloud registration</t>
+        </is>
+      </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>6.86</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>9.26</v>
       </c>
       <c r="Z10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="4" t="inlineStr"/>
-      <c r="AE10" s="4" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Yongjing Wang; Marco Castellani; Mubashir Ali; Hyung Jin Chang; Rustam Stolkin; Aleš Leonardis; Naresh Marturi; Mozafar Saadat; Alan George Wood; Christopher Gilliam; Beth Jelfs; David R. Themens</t>
+        </is>
+      </c>
+      <c r="AD10" s="4" t="inlineStr">
+        <is>
+          <t>1. Yongjing Wang (Full / Senior Prof (Large Lab), h=30) | Fit=7.2/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.5/10 | Keywords=point cloud registration | Paper=The SVD-enhanced bees algorithm, a novel procedure for point cloud registration (2024)
+2. Marco Castellani (Associate / Established PI (High Fit), h=21) | Fit=7.2/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.5/10 | Keywords=point cloud registration | Paper=The SVD-enhanced bees algorithm, a novel procedure for point cloud registration (2024)
+3. Mubashir Ali (Associate / Established PI (High Fit), h=15) | Fit=7.0/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=6.4/10 | Keywords=lidar camera fusion, autonomous vehicles, 3d object detection, object detection | Paper=PLC-Fusion: Perspective-Based Hierarchical and Deep LiDAR Camera Fusion for 3D Object Detection (2024)
+4. Hyung Jin Chang (Full / Senior Prof (Large Lab), h=34) | Fit=6.7/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=6.3/10 | Keywords=pose estimation, 3d computer vision, computer vision | Paper=Bidirectional regression for monocular 6DoF head pose estimation and reference system alignment (2026)
+5. Rustam Stolkin (Full / Senior Prof (Large Lab), h=43) | Fit=6.2/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.9/10 | Keywords=point cloud registration, pose estimation, mobile robot navigation, trajectory estimation | Paper=Local Region-to-Region Mapping-based Approach to Classify Articulated Objects (2023)
+6. Aleš Leonardis (Full / Senior Prof (Large Lab), h=57) | Fit=6.4/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=5.9/10 | Keywords=pose estimation, 3d computer vision, computer vision, depth estimation, semantic segmentation, deep learning | Paper=Trans6D: Transformer-Based 6D Object Pose Estimation and Refinement (2023)
+7. Naresh Marturi (Associate / Established PI (High Fit), h=19) | Fit=5.8/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=5.5/10 | Keywords=point cloud registration, pose estimation, computer vision, object detection | Paper=Local Region-to-Region Mapping-based Approach to Classify Articulated Objects (2023)
+8. Mozafar Saadat (Associate / Established PI (High Fit), h=21) | Fit=5.2/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.3/10 | Keywords=extended kalman filter, kalman filter, computer vision | Paper=Robust Real-Time Sperm Tracking with Identity Reassignment Using Extended Kalman Filtering (2025)
+9. Alan George Wood (Associate / Established PI (High Fit), h=11) | Fit=5.0/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.1/10 | Keywords=gnss positioning | Paper=HF Doppler ionospheric monitoring applications: Indications of GNSS positioning accuracy degrad (2025)
+10. Christopher Gilliam (Associate / Established PI (High Fit), h=16) | Fit=4.8/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=extended kalman filter, kalman filter, sensor fusion | Paper=Landmark Management in the Application of Radar SLAM (2022)
+11. Beth Jelfs (Associate / Established PI (High Fit), h=18) | Fit=4.8/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=extended kalman filter, kalman filter | Paper=Landmark Management in the Application of Radar SLAM (2022)
+12. David R. Themens (Full / Senior Prof (Large Lab), h=21) | Fit=3.5/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.1/10 | Keywords=gnss positioning | Paper=Statistical models of the variability of plasma in the topside ionosphere: 2. Performance asses (2024)</t>
+        </is>
+      </c>
+      <c r="AE10" s="4" t="inlineStr">
+        <is>
+          <t>Yongjing Wang: No homepage/funding evidence available
+Marco Castellani: No homepage/funding evidence available
+Mubashir Ali: No homepage/funding evidence available
+Hyung Jin Chang: No homepage/funding evidence available
+Rustam Stolkin: No homepage/funding evidence available
+Aleš Leonardis: No homepage/funding evidence available
+Naresh Marturi: No homepage/funding evidence available
+Mozafar Saadat: No homepage/funding evidence available
+Alan George Wood: No homepage/funding evidence available
+Christopher Gilliam: No homepage/funding evidence available
+Beth Jelfs: No homepage/funding evidence available
+David R. Themens: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abirmingham.ac.uk%20%22Yongjing%20Wang%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -1520,23 +1958,145 @@
           <t>University of Manchester</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>QS #34 | Tier S+ (Global Elite | h=1302)</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5056402291</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kieran T. Wood</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Dynamic Feature Filtering for Robust Monocular Visual SLAM (2025)</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>@manchester.ac.uk</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>I28407311</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive) (h=15)</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>visual slam, pose estimation, object detection</t>
+        </is>
+      </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>9.31</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="Z11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>7.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="4" t="inlineStr"/>
-      <c r="AE11" s="4" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Kieran T. Wood; Alexandru Stancu; Paulo Bártolo; Zekai Murat Kılıç; Hujun Yin; Mikel Luján; Simon Watson; Victor A. Levi; Adel G. Nasser; Mostafa R. A. Nabawy; Long Zhang; Jyoti Kumar Sinha; Graham D. Riley; Wei Li Pan; Angelo Cangelosi; Anthony  J. Peyton; Frank J. W. Podd; John L. Davidson</t>
+        </is>
+      </c>
+      <c r="AD11" s="4" t="inlineStr">
+        <is>
+          <t>1. Kieran T. Wood (Assistant Prof / Rising Star (Responsive), h=15) | Fit=9.7/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.2/10 | Keywords=visual slam, pose estimation, object detection | Paper=Dynamic Feature Filtering for Robust Monocular Visual SLAM (2025)
+2. Alexandru Stancu (Assistant Prof / Rising Star (Responsive), h=11) | Fit=9.5/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=8.0/10 | Keywords=visual slam, robot localization, extended kalman filter, kalman filter, multi-sensor fusion, sensor fusion | Paper=Improved Computation Efficiency 2D Visual SLAM Based on Particle Filter With Distance Sliding W (2024)
+3. Paulo Bártolo (Full / Senior Prof (Large Lab), h=68) | Fit=9.2/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=robot localization, kalman filter | Paper=Localization and Control of a Mobile Robot for Additive Manufacturing (2023)
+4. Zekai Murat Kılıç (Associate / Established PI (High Fit), h=19) | Fit=9.2/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=robot localization, kalman filter | Paper=Localization and Control of a Mobile Robot for Additive Manufacturing (2023)
+5. Hujun Yin (Full / Senior Prof (Large Lab), h=34) | Fit=8.8/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=visual slam, pose estimation, object detection, robot perception | Paper=Dynamic Feature Filtering for Robust Monocular Visual SLAM (2025)
+6. Mikel Luján (Full / Senior Prof (Large Lab), h=28) | Fit=8.3/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=7.2/10 | Keywords=visual slam, robot localization, deep learning, visual odometry, fpga, embedded systems | Paper=NGD-SLAM: Towards Real-Time Dynamic SLAM without GPU (2025)
+7. Simon Watson (Associate / Established PI (High Fit), h=23) | Fit=7.4/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=6.7/10 | Keywords=lidar slam, robust localization, ros2, mobile robot navigation | Paper=Low-Cost Rapid-Development Air-Ground Robotic Solution for Nuclear Power Plant Inspection (2025)
+8. Victor A. Levi (Associate / Established PI (High Fit), h=20) | Fit=7.3/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.5/10 | Keywords=state estimation, kalman filter | Paper=Variational Bayesian Unscented Kalman Filter for Active Distribution System State Estimation (2024)
+9. Adel G. Nasser (Associate / Established PI (High Fit), h=20) | Fit=7.1/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=6.5/10 | Keywords=lidar slam, sensor fusion | Paper=Remote Wind Turbine Inspections: Exploring the Potential of Multimodal Drones (2024)
+10. Mostafa R. A. Nabawy (Associate / Established PI (High Fit), h=19) | Fit=7.1/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=6.5/10 | Keywords=lidar slam, sensor fusion | Paper=Remote Wind Turbine Inspections: Exploring the Potential of Multimodal Drones (2024)
+11. Long Zhang (Full / Senior Prof (Large Lab), h=32) | Fit=7.1/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.4/10 | Keywords=state estimation, extended kalman filter, kalman filter | Paper=Early Prediction of Remaining Useful Life for Rolling Bearings Based on Envelope Spectral Indic (2024)
+12. Jyoti Kumar Sinha (Full / Senior Prof (Large Lab), h=27) | Fit=7.1/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.4/10 | Keywords=state estimation, extended kalman filter, kalman filter | Paper=Early Prediction of Remaining Useful Life for Rolling Bearings Based on Envelope Spectral Indic (2024)
+13. Graham D. Riley (Associate / Established PI (High Fit), h=15) | Fit=6.7/10 | Activity=6.3/10 | Funding=0.0/10 | Overall=5.6/10 | Keywords=visual odometry, fpga, embedded systems | Paper=Exploring Sparse Visual Odometry Acceleration With High-Level Synthesis (2023)
+14. Wei Li Pan (Full / Senior Prof (Large Lab), h=32) | Fit=5.2/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.4/10 | Keywords=autonomous navigation | Paper=DF$^3$: World Modeling via Decoder-Free Feature Forecasting in Autonomous Navigation (2026)
+15. Angelo Cangelosi (Full / Senior Prof (Large Lab), h=50) | Fit=4.1/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.7/10 | Keywords=robot perception | Paper=INPERAL: Interactive Perception Alignment in Human-Robot Interaction (2026)
+16. Anthony  J. Peyton (Full / Senior Prof (Large Lab), h=46) | Fit=4.2/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=4.6/10 | Keywords=visual localization, computer vision | Paper=Evaluation of a Low-Power Computer Vision-Based Positioning System for a Handheld Landmine Dete (2025)
+17. Frank J. W. Podd (Assistant Prof / Rising Star (Responsive), h=14) | Fit=4.2/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=4.6/10 | Keywords=visual localization, computer vision | Paper=Evaluation of a Low-Power Computer Vision-Based Positioning System for a Handheld Landmine Dete (2025)
+18. John L. Davidson (Assistant Prof / Rising Star (Responsive), h=15) | Fit=4.2/10 | Activity=9.0/10 | Funding=0.0/10 | Overall=4.5/10 | Keywords=visual localization, computer vision | Paper=Evaluation of a Low-Power Computer Vision-Based Positioning System for a Handheld Landmine Dete (2025)</t>
+        </is>
+      </c>
+      <c r="AE11" s="4" t="inlineStr">
+        <is>
+          <t>Kieran T. Wood: No homepage/funding evidence available
+Alexandru Stancu: No homepage/funding evidence available
+Paulo Bártolo: No homepage/funding evidence available
+Zekai Murat Kılıç: No homepage/funding evidence available
+Hujun Yin: No homepage/funding evidence available
+Mikel Luján: No homepage/funding evidence available
+Simon Watson: No homepage/funding evidence available
+Victor A. Levi: No homepage/funding evidence available
+Adel G. Nasser: No homepage/funding evidence available
+Mostafa R. A. Nabawy: No homepage/funding evidence available
+Long Zhang: No homepage/funding evidence available
+Jyoti Kumar Sinha: No homepage/funding evidence available
+Graham D. Riley: No homepage/funding evidence available
+Wei Li Pan: No homepage/funding evidence available
+Angelo Cangelosi: No homepage/funding evidence available
+Anthony  J. Peyton: No homepage/funding evidence available
+Frank J. W. Podd: No homepage/funding evidence available
+John L. Davidson: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Amanchester.ac.uk%20%22Kieran%20T.%20Wood%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -4269,7 +4829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z104"/>
+  <dimension ref="A1:Z169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -15453,8 +16013,6963 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>QS #27 | Tier S+ (Global Elite | h=1366)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Mike E. Davies</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>42</v>
+      </c>
+      <c r="K105" t="n">
+        <v>11616</v>
+      </c>
+      <c r="L105" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="M105" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, sensor fusion, kalman filter, state estimation</t>
+        </is>
+      </c>
+      <c r="R105" t="n">
+        <v>1</v>
+      </c>
+      <c r="S105" t="n">
+        <v>38</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Adaptive Kernel Kalman Filter Multi-Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="V105" t="n">
+        <v>2021</v>
+      </c>
+      <c r="W105" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aed.ac.uk%20%22Mike%20E.%20Davies%22%20email</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5057962470</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>QS #27 | Tier S+ (Global Elite | h=1366)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>2</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>James R. Hopgood</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>18</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1233</v>
+      </c>
+      <c r="L106" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="M106" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, sensor fusion, kalman filter, state estimation</t>
+        </is>
+      </c>
+      <c r="R106" t="n">
+        <v>1</v>
+      </c>
+      <c r="S106" t="n">
+        <v>47</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Adaptive Kernel Kalman Filter Multi-Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="V106" t="n">
+        <v>2021</v>
+      </c>
+      <c r="W106" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aed.ac.uk%20%22James%20R.%20Hopgood%22%20email</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5016434897</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>QS #27 | Tier S+ (Global Elite | h=1366)</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>3</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Yunjie Yang</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>30</v>
+      </c>
+      <c r="K107" t="n">
+        <v>2852</v>
+      </c>
+      <c r="L107" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="M107" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>point cloud registration, pose estimation, robot perception</t>
+        </is>
+      </c>
+      <c r="R107" t="n">
+        <v>2</v>
+      </c>
+      <c r="S107" t="n">
+        <v>121</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Self-Supervised Cross-Source Point Cloud Registration Framework With Geometric Tree Transformer for HMD Six-DoF Pose Estimation</t>
+        </is>
+      </c>
+      <c r="V107" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W107" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aed.ac.uk%20%22Yunjie%20Yang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5044092715</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>QS #27 | Tier S+ (Global Elite | h=1366)</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>4</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Mohsen Khadem</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>17</v>
+      </c>
+      <c r="K108" t="n">
+        <v>828</v>
+      </c>
+      <c r="L108" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M108" t="n">
+        <v>10</v>
+      </c>
+      <c r="N108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>visual odometry, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R108" t="n">
+        <v>1</v>
+      </c>
+      <c r="S108" t="n">
+        <v>47</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Geometry-Aware Visual Odometry for Bronchoscopic Navigation via High-Gain Observer Fusion</t>
+        </is>
+      </c>
+      <c r="V108" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W108" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aed.ac.uk%20%22Mohsen%20Khadem%22%20email</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5057363853</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>QS #27 | Tier S+ (Global Elite | h=1366)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>5</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Vaishak Belle</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>19</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1965</v>
+      </c>
+      <c r="L109" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="M109" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>robot localization</t>
+        </is>
+      </c>
+      <c r="R109" t="n">
+        <v>1</v>
+      </c>
+      <c r="S109" t="n">
+        <v>94</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="V109" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W109" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aed.ac.uk%20%22Vaishak%20Belle%22%20email</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5002932153</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>QS #27 | Tier S+ (Global Elite | h=1366)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>6</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Robert Bob Fisher</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>47</v>
+      </c>
+      <c r="K110" t="n">
+        <v>12407</v>
+      </c>
+      <c r="L110" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="M110" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>6</v>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>pose estimation, point cloud registration, autonomous vehicles, deep learning</t>
+        </is>
+      </c>
+      <c r="R110" t="n">
+        <v>2</v>
+      </c>
+      <c r="S110" t="n">
+        <v>44</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>A general mobile manipulator automation framework for flexible tasks in controlled environments</t>
+        </is>
+      </c>
+      <c r="V110" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W110" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aed.ac.uk%20%22Robert%20Bob%20Fisher%22%20email</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5020686179</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>QS #27 | Tier S+ (Global Elite | h=1366)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>7</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>István Gyöngy</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>22</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1725</v>
+      </c>
+      <c r="L111" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="M111" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>sensor fusion, depth estimation, autonomous vehicles</t>
+        </is>
+      </c>
+      <c r="R111" t="n">
+        <v>1</v>
+      </c>
+      <c r="S111" t="n">
+        <v>68</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>2023-11-03</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Guided Direct Time-of-Flight Lidar Using Stereo Cameras for Enhanced Laser Power Efficiency</t>
+        </is>
+      </c>
+      <c r="V111" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W111" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aed.ac.uk%20%22Istv%C3%A1n%20Gy%C3%B6ngy%22%20email</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5081151296</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>QS #27 | Tier S+ (Global Elite | h=1366)</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>8</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Robert Henderson</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>53</v>
+      </c>
+      <c r="K112" t="n">
+        <v>10827</v>
+      </c>
+      <c r="L112" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="M112" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N112" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>sensor fusion, depth estimation, autonomous vehicles, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R112" t="n">
+        <v>3</v>
+      </c>
+      <c r="S112" t="n">
+        <v>99</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>2024-01-19</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Guided Direct Time-of-Flight Lidar Using Stereo Cameras for Enhanced Laser Power Efficiency</t>
+        </is>
+      </c>
+      <c r="V112" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W112" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aed.ac.uk%20%22Robert%20Henderson%22%20email</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5103198569</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>QS #27 | Tier S+ (Global Elite | h=1366)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>9</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Barbara H. Webb</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>44</v>
+      </c>
+      <c r="K113" t="n">
+        <v>7356</v>
+      </c>
+      <c r="L113" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="M113" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N113" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; State Estimation &amp; Factor Graphs; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>mobile robot navigation, trajectory estimation, computer vision</t>
+        </is>
+      </c>
+      <c r="R113" t="n">
+        <v>3</v>
+      </c>
+      <c r="S113" t="n">
+        <v>40</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Embodied visual route following by an insect-inspired robot</t>
+        </is>
+      </c>
+      <c r="V113" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W113" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aed.ac.uk%20%22Barbara%20H.%20Webb%22%20email</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5066496499</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>QS #27 | Tier S+ (Global Elite | h=1366)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>10</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Oisin Mac Aodha</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>25</v>
+      </c>
+      <c r="K114" t="n">
+        <v>9585</v>
+      </c>
+      <c r="L114" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="M114" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N114" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>3d reconstruction, computer vision</t>
+        </is>
+      </c>
+      <c r="R114" t="n">
+        <v>2</v>
+      </c>
+      <c r="S114" t="n">
+        <v>102</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Heightfields for Efficient Scene Reconstruction for AR</t>
+        </is>
+      </c>
+      <c r="V114" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W114" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aed.ac.uk%20%22Oisin%20Mac%20Aodha%22%20email</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5063600180</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>QS #27 | Tier S+ (Global Elite | h=1366)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>11</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Hakan Bilen</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>28</v>
+      </c>
+      <c r="K115" t="n">
+        <v>4708</v>
+      </c>
+      <c r="L115" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="M115" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>depth estimation, computer vision, semantic segmentation</t>
+        </is>
+      </c>
+      <c r="R115" t="n">
+        <v>1</v>
+      </c>
+      <c r="S115" t="n">
+        <v>62</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Multi-task Learning with 3D-Aware Regularization</t>
+        </is>
+      </c>
+      <c r="V115" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W115" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aed.ac.uk%20%22Hakan%20Bilen%22%20email</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5056977175</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>QS #27 | Tier S+ (Global Elite | h=1366)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>12</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Steven McDonagh</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>22</v>
+      </c>
+      <c r="K116" t="n">
+        <v>7535</v>
+      </c>
+      <c r="L116" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="M116" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N116" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>depth estimation, computer vision, semantic segmentation</t>
+        </is>
+      </c>
+      <c r="R116" t="n">
+        <v>1</v>
+      </c>
+      <c r="S116" t="n">
+        <v>52</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Multi-task Learning with 3D-Aware Regularization</t>
+        </is>
+      </c>
+      <c r="V116" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W116" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aed.ac.uk%20%22Steven%20McDonagh%22%20email</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5052824649</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>University of Southampton</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=937)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>@southampton.ac.uk</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Shoaib Ehsan</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>21</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1700</v>
+      </c>
+      <c r="L117" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="M117" t="n">
+        <v>10</v>
+      </c>
+      <c r="N117" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>place recognition, visual slam, loop closure, robot localization, embedded systems, autonomous vehicles</t>
+        </is>
+      </c>
+      <c r="R117" t="n">
+        <v>9</v>
+      </c>
+      <c r="S117" t="n">
+        <v>51</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>TAT-VPR: Ternary Adaptive Transformer for Dynamic and Efficient Visual Place Recognition</t>
+        </is>
+      </c>
+      <c r="V117" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W117" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asouthampton.ac.uk%20%22Shoaib%20Ehsan%22%20email</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5103245109</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>University of Southampton</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=937)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>@southampton.ac.uk</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>2</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sarvapali D. Ramchurn</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>42</v>
+      </c>
+      <c r="K118" t="n">
+        <v>7361</v>
+      </c>
+      <c r="L118" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="M118" t="n">
+        <v>10</v>
+      </c>
+      <c r="N118" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>place recognition, visual slam, loop closure, robot localization, embedded systems, autonomous vehicles</t>
+        </is>
+      </c>
+      <c r="R118" t="n">
+        <v>9</v>
+      </c>
+      <c r="S118" t="n">
+        <v>103</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>TAT-VPR: Ternary Adaptive Transformer for Dynamic and Efficient Visual Place Recognition</t>
+        </is>
+      </c>
+      <c r="V118" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W118" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asouthampton.ac.uk%20%22Sarvapali%20D.%20Ramchurn%22%20email</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5065527041</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>University of Southampton</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=937)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>@southampton.ac.uk</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>3</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>David J. White</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>65</v>
+      </c>
+      <c r="K119" t="n">
+        <v>20568</v>
+      </c>
+      <c r="L119" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="M119" t="n">
+        <v>10</v>
+      </c>
+      <c r="N119" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>robot localization, autonomous navigation</t>
+        </is>
+      </c>
+      <c r="R119" t="n">
+        <v>2</v>
+      </c>
+      <c r="S119" t="n">
+        <v>88</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Development of a prototype autonomous inspection robot for offshore riser cables</t>
+        </is>
+      </c>
+      <c r="V119" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W119" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asouthampton.ac.uk%20%22David%20J.%20White%22%20email</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5065698184</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>University of Southampton</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=937)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>@southampton.ac.uk</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>4</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Blair Thornton</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>26</v>
+      </c>
+      <c r="K120" t="n">
+        <v>2588</v>
+      </c>
+      <c r="L120" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="M120" t="n">
+        <v>10</v>
+      </c>
+      <c r="N120" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>robot localization, autonomous navigation</t>
+        </is>
+      </c>
+      <c r="R120" t="n">
+        <v>2</v>
+      </c>
+      <c r="S120" t="n">
+        <v>67</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Development of a prototype autonomous inspection robot for offshore riser cables</t>
+        </is>
+      </c>
+      <c r="V120" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W120" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asouthampton.ac.uk%20%22Blair%20Thornton%22%20email</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5039161868</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>University of Southampton</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=937)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>@southampton.ac.uk</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>5</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Nicolas Peter Avdelidis</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>30</v>
+      </c>
+      <c r="K121" t="n">
+        <v>3984</v>
+      </c>
+      <c r="L121" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="M121" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N121" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>robot localization</t>
+        </is>
+      </c>
+      <c r="R121" t="n">
+        <v>2</v>
+      </c>
+      <c r="S121" t="n">
+        <v>69</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Techno-economic analysis for smart hangar inspection operations through sensing and localisation at scale</t>
+        </is>
+      </c>
+      <c r="V121" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W121" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asouthampton.ac.uk%20%22Nicolas%20Peter%20Avdelidis%22%20email</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5075071683</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>University of Southampton</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=937)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>@southampton.ac.uk</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>6</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Huanhuan Li</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>33</v>
+      </c>
+      <c r="K122" t="n">
+        <v>3625</v>
+      </c>
+      <c r="L122" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="M122" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>autonomous navigation, deep learning</t>
+        </is>
+      </c>
+      <c r="R122" t="n">
+        <v>1</v>
+      </c>
+      <c r="S122" t="n">
+        <v>104</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Uncertainty-aware ship trajectory prediction via Spatio-Temporal Graph Transformer</t>
+        </is>
+      </c>
+      <c r="V122" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W122" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asouthampton.ac.uk%20%22Huanhuan%20Li%22%20email</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100334077</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>University of Southampton</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=937)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>@southampton.ac.uk</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>7</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Xiaohao Cai</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>20</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1536</v>
+      </c>
+      <c r="L123" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="M123" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>3d object detection, object detection</t>
+        </is>
+      </c>
+      <c r="R123" t="n">
+        <v>3</v>
+      </c>
+      <c r="S123" t="n">
+        <v>97</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Revisiting Cross-Domain Problem for LiDAR-Based 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="V123" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W123" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asouthampton.ac.uk%20%22Xiaohao%20Cai%22%20email</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5078326698</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Cranfield</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=469)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>@cranfield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Ivan V. Petrunin</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>17</v>
+      </c>
+      <c r="K124" t="n">
+        <v>945</v>
+      </c>
+      <c r="L124" t="n">
+        <v>10</v>
+      </c>
+      <c r="M124" t="n">
+        <v>10</v>
+      </c>
+      <c r="N124" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; GNSS &amp; Robust Localization; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>visual inertial navigation, inertial navigation, visual inertial odometry, sensor fusion, visual odometry, kalman filter</t>
+        </is>
+      </c>
+      <c r="R124" t="n">
+        <v>19</v>
+      </c>
+      <c r="S124" t="n">
+        <v>86</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Error Correction Using Bayesian GRU Network in Hybrid Visual Inertial Navigation System</t>
+        </is>
+      </c>
+      <c r="V124" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W124" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Acranfield.ac.uk%20%22Ivan%20V.%20Petrunin%22%20email</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5015986514</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Cranfield</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=469)</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>@cranfield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>2</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Dmitry Ignatyev</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>14</v>
+      </c>
+      <c r="K125" t="n">
+        <v>653</v>
+      </c>
+      <c r="L125" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="M125" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N125" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>loop closure, visual slam, object detection</t>
+        </is>
+      </c>
+      <c r="R125" t="n">
+        <v>1</v>
+      </c>
+      <c r="S125" t="n">
+        <v>68</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Advancing autonomous SLAM systems: Integrating YOLO object detection and enhanced loop closure techniques for robust environment mapping</t>
+        </is>
+      </c>
+      <c r="V125" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W125" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Acranfield.ac.uk%20%22Dmitry%20Ignatyev%22%20email</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5038662808</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Cranfield</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=469)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>@cranfield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>3</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Weisi Guo</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>38</v>
+      </c>
+      <c r="K126" t="n">
+        <v>6310</v>
+      </c>
+      <c r="L126" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="M126" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N126" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; State Estimation &amp; Factor Graphs; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>visual odometry, sensor fusion, extended kalman filter, kalman filter, stereo vision, depth estimation</t>
+        </is>
+      </c>
+      <c r="R126" t="n">
+        <v>5</v>
+      </c>
+      <c r="S126" t="n">
+        <v>158</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Resilient Multi-Sensor UAV Navigation with a Hybrid Federated Fusion Architecture</t>
+        </is>
+      </c>
+      <c r="V126" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W126" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Acranfield.ac.uk%20%22Weisi%20Guo%22%20email</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5062362866</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Cranfield</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=469)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>@cranfield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>4</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Hyo‐Sang Shin</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>36</v>
+      </c>
+      <c r="K127" t="n">
+        <v>4692</v>
+      </c>
+      <c r="L127" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="M127" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N127" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>visual inertial navigation, inertial navigation, sensor fusion, state estimation</t>
+        </is>
+      </c>
+      <c r="R127" t="n">
+        <v>4</v>
+      </c>
+      <c r="S127" t="n">
+        <v>124</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Robust Multi-Sensor Navigation in GNSS Degraded Environments</t>
+        </is>
+      </c>
+      <c r="V127" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W127" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Acranfield.ac.uk%20%22Hyo%E2%80%90Sang%20Shin%22%20email</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5001666073</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Cranfield</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=469)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>@cranfield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>5</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Argyrios C. Zolotas</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>24</v>
+      </c>
+      <c r="K128" t="n">
+        <v>2424</v>
+      </c>
+      <c r="L128" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="M128" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>visual odometry, sensor fusion, robot localization</t>
+        </is>
+      </c>
+      <c r="R128" t="n">
+        <v>3</v>
+      </c>
+      <c r="S128" t="n">
+        <v>102</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>GNSS/INS/VO fusion using Gated Recurrent Unit in GNSS denied environments</t>
+        </is>
+      </c>
+      <c r="V128" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W128" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Acranfield.ac.uk%20%22Argyrios%20C.%20Zolotas%22%20email</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5089252134</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Cranfield</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=469)</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>@cranfield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>6</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Teng Li</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>18</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1056</v>
+      </c>
+      <c r="L129" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="M129" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>factor graph optimization, gnss positioning</t>
+        </is>
+      </c>
+      <c r="R129" t="n">
+        <v>1</v>
+      </c>
+      <c r="S129" t="n">
+        <v>53</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Comparative Analysis of Factor Graph Models for Carrier Phase-Based Precision Navigation</t>
+        </is>
+      </c>
+      <c r="V129" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W129" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Acranfield.ac.uk%20%22Teng%20Li%22%20email</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5020227658</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Cranfield</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=469)</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>@cranfield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>7</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Boyu Kuang</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>17</v>
+      </c>
+      <c r="K130" t="n">
+        <v>2188</v>
+      </c>
+      <c r="L130" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="M130" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N130" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>visual slam, trajectory estimation, computer vision, semantic segmentation</t>
+        </is>
+      </c>
+      <c r="R130" t="n">
+        <v>3</v>
+      </c>
+      <c r="S130" t="n">
+        <v>29</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>2022-07-26</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>OG-SLAM: A real-time and high-accurate monocular visual SLAM framework</t>
+        </is>
+      </c>
+      <c r="V130" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W130" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Acranfield.ac.uk%20%22Boyu%20Kuang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5026493446</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Cranfield</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=469)</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>@cranfield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>8</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Antonios Tsourdos</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>59</v>
+      </c>
+      <c r="K131" t="n">
+        <v>14278</v>
+      </c>
+      <c r="L131" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="M131" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N131" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; State Estimation &amp; Factor Graphs; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>gnss positioning, inertial navigation, lidar camera fusion, object detection, trajectory estimation, stereo vision</t>
+        </is>
+      </c>
+      <c r="R131" t="n">
+        <v>8</v>
+      </c>
+      <c r="S131" t="n">
+        <v>292</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Experimental Evaluation of GNSS and IMU Fusion Using Gated Recurrent Unit</t>
+        </is>
+      </c>
+      <c r="V131" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W131" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Acranfield.ac.uk%20%22Antonios%20Tsourdos%22%20email</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5085012064</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Cranfield</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=469)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>@cranfield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>9</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Gökhan İnalhan</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>28</v>
+      </c>
+      <c r="K132" t="n">
+        <v>3823</v>
+      </c>
+      <c r="L132" t="n">
+        <v>7</v>
+      </c>
+      <c r="M132" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N132" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>visual odometry, pose estimation</t>
+        </is>
+      </c>
+      <c r="R132" t="n">
+        <v>1</v>
+      </c>
+      <c r="S132" t="n">
+        <v>110</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Federated Meta Learning for Visual Navigation in GPS-denied Urban Airspace</t>
+        </is>
+      </c>
+      <c r="V132" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W132" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Acranfield.ac.uk%20%22G%C3%B6khan%20%C4%B0nalhan%22%20email</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5037931913</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Cranfield</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=469)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>@cranfield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>10</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Phil Webb</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>24</v>
+      </c>
+      <c r="K133" t="n">
+        <v>1792</v>
+      </c>
+      <c r="L133" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="M133" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N133" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>pose estimation, robot perception, object detection, ros, ros2</t>
+        </is>
+      </c>
+      <c r="R133" t="n">
+        <v>1</v>
+      </c>
+      <c r="S133" t="n">
+        <v>32</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Unlocking the potential of Robot Manipulators: Seamless Integration Framework</t>
+        </is>
+      </c>
+      <c r="V133" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W133" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Acranfield.ac.uk%20%22Phil%20Webb%22%20email</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5073792029</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Cranfield</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=469)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>@cranfield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>11</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>S. A. Syed Asif</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>25</v>
+      </c>
+      <c r="K134" t="n">
+        <v>4249</v>
+      </c>
+      <c r="L134" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="M134" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="N134" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>pose estimation, robot perception, object detection, ros, ros2</t>
+        </is>
+      </c>
+      <c r="R134" t="n">
+        <v>1</v>
+      </c>
+      <c r="S134" t="n">
+        <v>4</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Unlocking the potential of Robot Manipulators: Seamless Integration Framework</t>
+        </is>
+      </c>
+      <c r="V134" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W134" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Acranfield.ac.uk%20%22S.%20A.%20Syed%20Asif%22%20email</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5066278351</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Cranfield</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=469)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>@cranfield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>12</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Leon Williams</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>20</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1280</v>
+      </c>
+      <c r="L135" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="M135" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N135" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>visual slam, computer vision</t>
+        </is>
+      </c>
+      <c r="R135" t="n">
+        <v>1</v>
+      </c>
+      <c r="S135" t="n">
+        <v>19</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>2022-08-05</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Advanced Visual SLAM and Image Segmentation Techniques for Augmented Reality</t>
+        </is>
+      </c>
+      <c r="V135" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W135" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Acranfield.ac.uk%20%22Leon%20Williams%22%20email</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5010775999</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Cranfield</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=469)</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>@cranfield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>13</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Yang Xing</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>42</v>
+      </c>
+      <c r="K136" t="n">
+        <v>7090</v>
+      </c>
+      <c r="L136" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="M136" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N136" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>trajectory estimation, stereo vision, object detection</t>
+        </is>
+      </c>
+      <c r="R136" t="n">
+        <v>1</v>
+      </c>
+      <c r="S136" t="n">
+        <v>71</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Eyes-Out Airborne Object Detector for Pilots Situational Awareness</t>
+        </is>
+      </c>
+      <c r="V136" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W136" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Acranfield.ac.uk%20%22Yang%20Xing%22%20email</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5052678450</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Cranfield</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=469)</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>@cranfield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>14</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Adolfo Perrusquía</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>22</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1493</v>
+      </c>
+      <c r="L137" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="M137" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N137" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>stereo vision, depth estimation, deep learning, trajectory estimation</t>
+        </is>
+      </c>
+      <c r="R137" t="n">
+        <v>2</v>
+      </c>
+      <c r="S137" t="n">
+        <v>97</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Enhancing Situational Awareness of Helicopter Pilots in Unmanned Aerial Vehicle-Congested Environments Using an Airborne Visual Artificial Intelligence Approach</t>
+        </is>
+      </c>
+      <c r="V137" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W137" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Acranfield.ac.uk%20%22Adolfo%20Perrusqu%C3%ADa%22%20email</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5065156490</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Cranfield</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=469)</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>@cranfield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>15</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Saba Al–Rubaye</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>27</v>
+      </c>
+      <c r="K138" t="n">
+        <v>3459</v>
+      </c>
+      <c r="L138" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="M138" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N138" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>gnss positioning, deep learning, hardware acceleration, autonomous vehicles, fpga, embedded systems</t>
+        </is>
+      </c>
+      <c r="R138" t="n">
+        <v>3</v>
+      </c>
+      <c r="S138" t="n">
+        <v>79</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Intelligent 5G-Aided UAV Positioning in High-Density Environments Using Neural Networks for NLOS Mitigation</t>
+        </is>
+      </c>
+      <c r="V138" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W138" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Acranfield.ac.uk%20%22Saba%20Al%E2%80%93Rubaye%22%20email</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5023648639</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Cranfield University</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Cranfield</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=469)</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>@cranfield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>16</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Mark A. Richardson</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>22</v>
+      </c>
+      <c r="K139" t="n">
+        <v>1888</v>
+      </c>
+      <c r="L139" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="M139" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="N139" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>pose estimation, deep learning</t>
+        </is>
+      </c>
+      <c r="R139" t="n">
+        <v>1</v>
+      </c>
+      <c r="S139" t="n">
+        <v>6</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>ChiNet: Deep Recurrent Convolutional Learning for Multimodal Spacecraft Pose Estimation</t>
+        </is>
+      </c>
+      <c r="V139" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W139" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Acranfield.ac.uk%20%22Mark%20A.%20Richardson%22%20email</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5049973451</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=1267)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>@birmingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Yongjing Wang</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>30</v>
+      </c>
+      <c r="K140" t="n">
+        <v>3183</v>
+      </c>
+      <c r="L140" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="M140" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N140" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>point cloud registration</t>
+        </is>
+      </c>
+      <c r="R140" t="n">
+        <v>2</v>
+      </c>
+      <c r="S140" t="n">
+        <v>115</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>The SVD-enhanced bees algorithm, a novel procedure for point cloud registration</t>
+        </is>
+      </c>
+      <c r="V140" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W140" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abirmingham.ac.uk%20%22Yongjing%20Wang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5058814232</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=1267)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>@birmingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>2</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Marco Castellani</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>21</v>
+      </c>
+      <c r="K141" t="n">
+        <v>1633</v>
+      </c>
+      <c r="L141" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="M141" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N141" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>point cloud registration</t>
+        </is>
+      </c>
+      <c r="R141" t="n">
+        <v>2</v>
+      </c>
+      <c r="S141" t="n">
+        <v>41</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>The SVD-enhanced bees algorithm, a novel procedure for point cloud registration</t>
+        </is>
+      </c>
+      <c r="V141" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W141" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abirmingham.ac.uk%20%22Marco%20Castellani%22%20email</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5079759495</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=1267)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>@birmingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>3</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Mubashir Ali</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>15</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1382</v>
+      </c>
+      <c r="L142" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="M142" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N142" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>lidar camera fusion, autonomous vehicles, 3d object detection, object detection</t>
+        </is>
+      </c>
+      <c r="R142" t="n">
+        <v>2</v>
+      </c>
+      <c r="S142" t="n">
+        <v>34</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>PLC-Fusion: Perspective-Based Hierarchical and Deep LiDAR Camera Fusion for 3D Object Detection in Autonomous Vehicles</t>
+        </is>
+      </c>
+      <c r="V142" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W142" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abirmingham.ac.uk%20%22Mubashir%20Ali%22%20email</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5033406444</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=1267)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>@birmingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>4</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Hyung Jin Chang</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>34</v>
+      </c>
+      <c r="K143" t="n">
+        <v>5748</v>
+      </c>
+      <c r="L143" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="M143" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N143" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; 3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>pose estimation, 3d computer vision, computer vision</t>
+        </is>
+      </c>
+      <c r="R143" t="n">
+        <v>5</v>
+      </c>
+      <c r="S143" t="n">
+        <v>92</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Bidirectional regression for monocular 6DoF head pose estimation and reference system alignment</t>
+        </is>
+      </c>
+      <c r="V143" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W143" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abirmingham.ac.uk%20%22Hyung%20Jin%20Chang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5004895698</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=1267)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>@birmingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>5</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Rustam Stolkin</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>43</v>
+      </c>
+      <c r="K144" t="n">
+        <v>10521</v>
+      </c>
+      <c r="L144" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="M144" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N144" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; LiDAR &amp; Multimodal Sensor Fusion; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>point cloud registration, pose estimation, mobile robot navigation, trajectory estimation</t>
+        </is>
+      </c>
+      <c r="R144" t="n">
+        <v>13</v>
+      </c>
+      <c r="S144" t="n">
+        <v>122</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Local Region-to-Region Mapping-based Approach to Classify Articulated Objects</t>
+        </is>
+      </c>
+      <c r="V144" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W144" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abirmingham.ac.uk%20%22Rustam%20Stolkin%22%20email</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5005183926</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=1267)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>@birmingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>6</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Aleš Leonardis</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>57</v>
+      </c>
+      <c r="K145" t="n">
+        <v>19485</v>
+      </c>
+      <c r="L145" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="M145" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N145" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>pose estimation, 3d computer vision, computer vision, depth estimation, semantic segmentation, deep learning</t>
+        </is>
+      </c>
+      <c r="R145" t="n">
+        <v>5</v>
+      </c>
+      <c r="S145" t="n">
+        <v>192</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Trans6D: Transformer-Based 6D Object Pose Estimation and Refinement</t>
+        </is>
+      </c>
+      <c r="V145" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W145" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abirmingham.ac.uk%20%22Ale%C5%A1%20Leonardis%22%20email</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5085971943</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=1267)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>@birmingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>7</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Naresh Marturi</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>19</v>
+      </c>
+      <c r="K146" t="n">
+        <v>1240</v>
+      </c>
+      <c r="L146" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="M146" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N146" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>point cloud registration, pose estimation, computer vision, object detection</t>
+        </is>
+      </c>
+      <c r="R146" t="n">
+        <v>3</v>
+      </c>
+      <c r="S146" t="n">
+        <v>23</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Local Region-to-Region Mapping-based Approach to Classify Articulated Objects</t>
+        </is>
+      </c>
+      <c r="V146" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W146" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abirmingham.ac.uk%20%22Naresh%20Marturi%22%20email</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5011562571</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=1267)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>@birmingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>8</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Mozafar Saadat</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>21</v>
+      </c>
+      <c r="K147" t="n">
+        <v>1457</v>
+      </c>
+      <c r="L147" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="M147" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N147" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>extended kalman filter, kalman filter, computer vision</t>
+        </is>
+      </c>
+      <c r="R147" t="n">
+        <v>1</v>
+      </c>
+      <c r="S147" t="n">
+        <v>28</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Robust Real-Time Sperm Tracking with Identity Reassignment Using Extended Kalman Filtering</t>
+        </is>
+      </c>
+      <c r="V147" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W147" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abirmingham.ac.uk%20%22Mozafar%20Saadat%22%20email</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5065890212</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=1267)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>@birmingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>9</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Alan George Wood</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>11</v>
+      </c>
+      <c r="K148" t="n">
+        <v>673</v>
+      </c>
+      <c r="L148" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="M148" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N148" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>gnss positioning</t>
+        </is>
+      </c>
+      <c r="R148" t="n">
+        <v>4</v>
+      </c>
+      <c r="S148" t="n">
+        <v>38</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>HF Doppler ionospheric monitoring applications: Indications of GNSS positioning accuracy degradation and for LOFAR operations</t>
+        </is>
+      </c>
+      <c r="V148" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W148" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abirmingham.ac.uk%20%22Alan%20George%20Wood%22%20email</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5022231955</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=1267)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>@birmingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>10</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Christopher Gilliam</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>16</v>
+      </c>
+      <c r="K149" t="n">
+        <v>770</v>
+      </c>
+      <c r="L149" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M149" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N149" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>extended kalman filter, kalman filter, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R149" t="n">
+        <v>2</v>
+      </c>
+      <c r="S149" t="n">
+        <v>32</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Landmark Management in the Application of Radar SLAM</t>
+        </is>
+      </c>
+      <c r="V149" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W149" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abirmingham.ac.uk%20%22Christopher%20Gilliam%22%20email</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5019026432</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=1267)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>@birmingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>11</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Beth Jelfs</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>18</v>
+      </c>
+      <c r="K150" t="n">
+        <v>1277</v>
+      </c>
+      <c r="L150" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="M150" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N150" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>extended kalman filter, kalman filter</t>
+        </is>
+      </c>
+      <c r="R150" t="n">
+        <v>1</v>
+      </c>
+      <c r="S150" t="n">
+        <v>38</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>2022-11-07</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Landmark Management in the Application of Radar SLAM</t>
+        </is>
+      </c>
+      <c r="V150" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W150" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abirmingham.ac.uk%20%22Beth%20Jelfs%22%20email</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5025470623</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>QS #80 | Tier S+ (Global Elite | h=1267)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>@birmingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>12</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>David R. Themens</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>21</v>
+      </c>
+      <c r="K151" t="n">
+        <v>1841</v>
+      </c>
+      <c r="L151" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="M151" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N151" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>gnss positioning</t>
+        </is>
+      </c>
+      <c r="R151" t="n">
+        <v>2</v>
+      </c>
+      <c r="S151" t="n">
+        <v>128</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Statistical models of the variability of plasma in the topside ionosphere: 2. Performance assessment</t>
+        </is>
+      </c>
+      <c r="V151" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W151" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abirmingham.ac.uk%20%22David%20R.%20Themens%22%20email</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5041868527</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>QS #34 | Tier S+ (Global Elite | h=1302)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>@manchester.ac.uk</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Kieran T. Wood</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>15</v>
+      </c>
+      <c r="K152" t="n">
+        <v>701</v>
+      </c>
+      <c r="L152" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="M152" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N152" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>visual slam, pose estimation, object detection</t>
+        </is>
+      </c>
+      <c r="R152" t="n">
+        <v>1</v>
+      </c>
+      <c r="S152" t="n">
+        <v>23</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Dynamic Feature Filtering for Robust Monocular Visual SLAM</t>
+        </is>
+      </c>
+      <c r="V152" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W152" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Amanchester.ac.uk%20%22Kieran%20T.%20Wood%22%20email</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5056402291</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>QS #34 | Tier S+ (Global Elite | h=1302)</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>@manchester.ac.uk</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>2</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Alexandru Stancu</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>11</v>
+      </c>
+      <c r="K153" t="n">
+        <v>537</v>
+      </c>
+      <c r="L153" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="M153" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N153" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>visual slam, robot localization, extended kalman filter, kalman filter, multi-sensor fusion, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R153" t="n">
+        <v>4</v>
+      </c>
+      <c r="S153" t="n">
+        <v>19</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>2024-12-29</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Improved Computation Efficiency 2D Visual SLAM Based on Particle Filter With Distance Sliding Window</t>
+        </is>
+      </c>
+      <c r="V153" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W153" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Amanchester.ac.uk%20%22Alexandru%20Stancu%22%20email</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5013721697</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>QS #34 | Tier S+ (Global Elite | h=1302)</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>@manchester.ac.uk</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>3</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Paulo Bártolo</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>68</v>
+      </c>
+      <c r="K154" t="n">
+        <v>16889</v>
+      </c>
+      <c r="L154" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="M154" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N154" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>robot localization, kalman filter</t>
+        </is>
+      </c>
+      <c r="R154" t="n">
+        <v>1</v>
+      </c>
+      <c r="S154" t="n">
+        <v>125</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Localization and Control of a Mobile Robot for Additive Manufacturing</t>
+        </is>
+      </c>
+      <c r="V154" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W154" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Amanchester.ac.uk%20%22Paulo%20B%C3%A1rtolo%22%20email</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5011324823</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>QS #34 | Tier S+ (Global Elite | h=1302)</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>@manchester.ac.uk</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>4</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Zekai Murat Kılıç</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>19</v>
+      </c>
+      <c r="K155" t="n">
+        <v>1409</v>
+      </c>
+      <c r="L155" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="M155" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N155" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>robot localization, kalman filter</t>
+        </is>
+      </c>
+      <c r="R155" t="n">
+        <v>1</v>
+      </c>
+      <c r="S155" t="n">
+        <v>35</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Localization and Control of a Mobile Robot for Additive Manufacturing</t>
+        </is>
+      </c>
+      <c r="V155" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W155" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Amanchester.ac.uk%20%22Zekai%20Murat%20K%C4%B1l%C4%B1%C3%A7%22%20email</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5063577676</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>QS #34 | Tier S+ (Global Elite | h=1302)</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>@manchester.ac.uk</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>5</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Hujun Yin</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
+        <v>34</v>
+      </c>
+      <c r="K156" t="n">
+        <v>4505</v>
+      </c>
+      <c r="L156" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="M156" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N156" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>visual slam, pose estimation, object detection, robot perception</t>
+        </is>
+      </c>
+      <c r="R156" t="n">
+        <v>2</v>
+      </c>
+      <c r="S156" t="n">
+        <v>71</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Dynamic Feature Filtering for Robust Monocular Visual SLAM</t>
+        </is>
+      </c>
+      <c r="V156" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W156" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Amanchester.ac.uk%20%22Hujun%20Yin%22%20email</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5055149475</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>QS #34 | Tier S+ (Global Elite | h=1302)</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>@manchester.ac.uk</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>6</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Mikel Luján</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>28</v>
+      </c>
+      <c r="K157" t="n">
+        <v>3833</v>
+      </c>
+      <c r="L157" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="M157" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N157" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>visual slam, robot localization, deep learning, visual odometry, fpga, embedded systems</t>
+        </is>
+      </c>
+      <c r="R157" t="n">
+        <v>4</v>
+      </c>
+      <c r="S157" t="n">
+        <v>35</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>NGD-SLAM: Towards Real-Time Dynamic SLAM without GPU</t>
+        </is>
+      </c>
+      <c r="V157" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W157" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Amanchester.ac.uk%20%22Mikel%20Luj%C3%A1n%22%20email</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5026069638</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>QS #34 | Tier S+ (Global Elite | h=1302)</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>@manchester.ac.uk</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>7</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Simon Watson</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J158" t="n">
+        <v>23</v>
+      </c>
+      <c r="K158" t="n">
+        <v>1567</v>
+      </c>
+      <c r="L158" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="M158" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N158" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>lidar slam, robust localization, ros2, mobile robot navigation</t>
+        </is>
+      </c>
+      <c r="R158" t="n">
+        <v>5</v>
+      </c>
+      <c r="S158" t="n">
+        <v>42</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Low-Cost Rapid-Development Air-Ground Robotic Solution for Nuclear Power Plant Inspection</t>
+        </is>
+      </c>
+      <c r="V158" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W158" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Amanchester.ac.uk%20%22Simon%20Watson%22%20email</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5080310566</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>QS #34 | Tier S+ (Global Elite | h=1302)</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>@manchester.ac.uk</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>8</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Victor A. Levi</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>20</v>
+      </c>
+      <c r="K159" t="n">
+        <v>1350</v>
+      </c>
+      <c r="L159" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="M159" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N159" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>state estimation, kalman filter</t>
+        </is>
+      </c>
+      <c r="R159" t="n">
+        <v>2</v>
+      </c>
+      <c r="S159" t="n">
+        <v>26</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Variational Bayesian Unscented Kalman Filter for Active Distribution System State Estimation</t>
+        </is>
+      </c>
+      <c r="V159" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W159" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Amanchester.ac.uk%20%22Victor%20A.%20Levi%22%20email</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5036763499</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>QS #34 | Tier S+ (Global Elite | h=1302)</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>@manchester.ac.uk</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>9</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Adel G. Nasser</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>20</v>
+      </c>
+      <c r="K160" t="n">
+        <v>1172</v>
+      </c>
+      <c r="L160" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="M160" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N160" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>lidar slam, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R160" t="n">
+        <v>1</v>
+      </c>
+      <c r="S160" t="n">
+        <v>33</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>2024-12-24</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Remote Wind Turbine Inspections: Exploring the Potential of Multimodal Drones</t>
+        </is>
+      </c>
+      <c r="V160" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W160" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Amanchester.ac.uk%20%22Adel%20G.%20Nasser%22%20email</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5085659476</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>QS #34 | Tier S+ (Global Elite | h=1302)</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>@manchester.ac.uk</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>10</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Mostafa R. A. Nabawy</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>19</v>
+      </c>
+      <c r="K161" t="n">
+        <v>1092</v>
+      </c>
+      <c r="L161" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="M161" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N161" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>lidar slam, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R161" t="n">
+        <v>1</v>
+      </c>
+      <c r="S161" t="n">
+        <v>68</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>2024-12-24</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Remote Wind Turbine Inspections: Exploring the Potential of Multimodal Drones</t>
+        </is>
+      </c>
+      <c r="V161" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W161" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Amanchester.ac.uk%20%22Mostafa%20R.%20A.%20Nabawy%22%20email</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5018262156</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>QS #34 | Tier S+ (Global Elite | h=1302)</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>@manchester.ac.uk</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>11</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Long Zhang</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>32</v>
+      </c>
+      <c r="K162" t="n">
+        <v>3942</v>
+      </c>
+      <c r="L162" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="M162" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N162" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>state estimation, extended kalman filter, kalman filter</t>
+        </is>
+      </c>
+      <c r="R162" t="n">
+        <v>1</v>
+      </c>
+      <c r="S162" t="n">
+        <v>127</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Early Prediction of Remaining Useful Life for Rolling Bearings Based on Envelope Spectral Indicator and Bayesian Filter</t>
+        </is>
+      </c>
+      <c r="V162" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W162" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Amanchester.ac.uk%20%22Long%20Zhang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100363496</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>QS #34 | Tier S+ (Global Elite | h=1302)</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>@manchester.ac.uk</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>12</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Jyoti Kumar Sinha</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
+        <v>27</v>
+      </c>
+      <c r="K163" t="n">
+        <v>3175</v>
+      </c>
+      <c r="L163" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="M163" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N163" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>state estimation, extended kalman filter, kalman filter</t>
+        </is>
+      </c>
+      <c r="R163" t="n">
+        <v>1</v>
+      </c>
+      <c r="S163" t="n">
+        <v>57</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Early Prediction of Remaining Useful Life for Rolling Bearings Based on Envelope Spectral Indicator and Bayesian Filter</t>
+        </is>
+      </c>
+      <c r="V163" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W163" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Amanchester.ac.uk%20%22Jyoti%20Kumar%20Sinha%22%20email</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5057125584</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>QS #34 | Tier S+ (Global Elite | h=1302)</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>@manchester.ac.uk</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>13</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Graham D. Riley</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J164" t="n">
+        <v>15</v>
+      </c>
+      <c r="K164" t="n">
+        <v>1281</v>
+      </c>
+      <c r="L164" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="M164" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="N164" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>visual odometry, fpga, embedded systems</t>
+        </is>
+      </c>
+      <c r="R164" t="n">
+        <v>1</v>
+      </c>
+      <c r="S164" t="n">
+        <v>4</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Exploring Sparse Visual Odometry Acceleration With High-Level Synthesis</t>
+        </is>
+      </c>
+      <c r="V164" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W164" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Amanchester.ac.uk%20%22Graham%20D.%20Riley%22%20email</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5087600309</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>QS #34 | Tier S+ (Global Elite | h=1302)</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>@manchester.ac.uk</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>14</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Wei Li Pan</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>32</v>
+      </c>
+      <c r="K165" t="n">
+        <v>4779</v>
+      </c>
+      <c r="L165" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="M165" t="n">
+        <v>10</v>
+      </c>
+      <c r="N165" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Deep Learning for Navigation &amp; Perception; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>autonomous navigation</t>
+        </is>
+      </c>
+      <c r="R165" t="n">
+        <v>2</v>
+      </c>
+      <c r="S165" t="n">
+        <v>101</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>DF$^3$: World Modeling via Decoder-Free Feature Forecasting in Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="V165" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W165" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Amanchester.ac.uk%20%22Wei%20Li%20Pan%22%20email</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100721259</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>QS #34 | Tier S+ (Global Elite | h=1302)</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>@manchester.ac.uk</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>15</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Angelo Cangelosi</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>50</v>
+      </c>
+      <c r="K166" t="n">
+        <v>10714</v>
+      </c>
+      <c r="L166" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="M166" t="n">
+        <v>10</v>
+      </c>
+      <c r="N166" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>robot perception</t>
+        </is>
+      </c>
+      <c r="R166" t="n">
+        <v>2</v>
+      </c>
+      <c r="S166" t="n">
+        <v>163</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>INPERAL: Interactive Perception Alignment in Human-Robot Interaction</t>
+        </is>
+      </c>
+      <c r="V166" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W166" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Amanchester.ac.uk%20%22Angelo%20Cangelosi%22%20email</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5091768977</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>QS #34 | Tier S+ (Global Elite | h=1302)</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>@manchester.ac.uk</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>16</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Anthony  J. Peyton</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>46</v>
+      </c>
+      <c r="K167" t="n">
+        <v>7010</v>
+      </c>
+      <c r="L167" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="M167" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N167" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>visual localization, computer vision</t>
+        </is>
+      </c>
+      <c r="R167" t="n">
+        <v>1</v>
+      </c>
+      <c r="S167" t="n">
+        <v>78</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Evaluation of a Low-Power Computer Vision-Based Positioning System for a Handheld Landmine Detector Using AprilTag Markers</t>
+        </is>
+      </c>
+      <c r="V167" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W167" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Amanchester.ac.uk%20%22Anthony%20%20J.%20Peyton%22%20email</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5009569523</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>QS #34 | Tier S+ (Global Elite | h=1302)</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>@manchester.ac.uk</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>17</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Frank J. W. Podd</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
+        <v>14</v>
+      </c>
+      <c r="K168" t="n">
+        <v>673</v>
+      </c>
+      <c r="L168" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="M168" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N168" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>visual localization, computer vision</t>
+        </is>
+      </c>
+      <c r="R168" t="n">
+        <v>1</v>
+      </c>
+      <c r="S168" t="n">
+        <v>18</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Evaluation of a Low-Power Computer Vision-Based Positioning System for a Handheld Landmine Detector Using AprilTag Markers</t>
+        </is>
+      </c>
+      <c r="V168" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W168" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Amanchester.ac.uk%20%22Frank%20J.%20W.%20Podd%22%20email</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5066363867</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>QS #34 | Tier S+ (Global Elite | h=1302)</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>@manchester.ac.uk</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>18</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>John L. Davidson</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>15</v>
+      </c>
+      <c r="K169" t="n">
+        <v>630</v>
+      </c>
+      <c r="L169" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="M169" t="n">
+        <v>9</v>
+      </c>
+      <c r="N169" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>visual localization, computer vision</t>
+        </is>
+      </c>
+      <c r="R169" t="n">
+        <v>1</v>
+      </c>
+      <c r="S169" t="n">
+        <v>11</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Evaluation of a Low-Power Computer Vision-Based Positioning System for a Handheld Landmine Detector Using AprilTag Markers</t>
+        </is>
+      </c>
+      <c r="V169" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W169" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Amanchester.ac.uk%20%22John%20L.%20Davidson%22%20email</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5102770106</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z104"/>
+  <autoFilter ref="A1:Z169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AG$127</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Z$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Z$230</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,9 +475,9 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="35" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
     <col width="42" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
     <col width="25" customWidth="1" min="21" max="21"/>
@@ -2104,23 +2104,131 @@
           <t>University of Sheffield</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5071097412</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sean Anderson</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Assessing the feasibility of monocular visual simultaneous localization and mapping for live sewer pipes: a field robotics study (2021)</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>I91136226</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit) (h=22)</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>visual slam, visual odometry, loop closure, field robotics, pose estimation, robot localization</t>
+        </is>
+      </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>8.76</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>9.33</v>
       </c>
       <c r="Z12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="4" t="inlineStr"/>
-      <c r="AE12" s="4" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Sean Anderson; Jonathan M. Aitken; Lyudmila S. Mihaylova; Kirill V. Horoshenkov; Valentin Radu; John Anthony Rossiter; Ashutosh Tiwari; Windo Hutabarat; Sándor M. Veres; Tony J. Prescott; Zeyneb Kurt</t>
+        </is>
+      </c>
+      <c r="AD12" s="4" t="inlineStr">
+        <is>
+          <t>1. Sean Anderson (Associate / Established PI (High Fit), h=22) | Fit=9.6/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.2/10 | Keywords=visual slam, visual odometry, loop closure, field robotics, pose estimation, robot localization | Paper=Assessing the feasibility of monocular visual simultaneous localization and mapping for live se (2021)
+2. Jonathan M. Aitken (Assistant Prof / Rising Star (Responsive), h=17) | Fit=10.0/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=8.2/10 | Keywords=visual-inertial slam, sensor fusion, visual slam, visual odometry, loop closure, field robotics | Paper=Investigating Scene Visibility Estimation Within ORB-SLAM3 (2022)
+3. Lyudmila S. Mihaylova (Full / Senior Prof (Large Lab), h=41) | Fit=9.0/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=robot localization, visual odometry, visual inertial odometry, kalman filter, state estimation, extended kalman filter | Paper=A robust method for approximate visual robot localization in feature-sparse sewer pipes (2023)
+4. Kirill V. Horoshenkov (Full / Senior Prof (Large Lab), h=42) | Fit=7.7/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=6.9/10 | Keywords=robot localization, loop closure, kalman filter, autonomous navigation | Paper=Acoustic Echo Sensing for Robot Localization in Buried Pipe Networks (2023)
+5. Valentin Radu (Assistant Prof / Rising Star (Responsive), h=14) | Fit=7.5/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=6.8/10 | Keywords=multi-sensor fusion, sensor fusion, sensor calibration | Paper=Multi-Sensor Fusion for Indoor Smartphone Localization with Attention Mechanism (2025)
+6. John Anthony Rossiter (Full / Senior Prof (Large Lab), h=37) | Fit=7.3/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=6.3/10 | Keywords=pose estimation, robot perception, 3d reconstruction | Paper=Advanced Environment Modelling for Remote Teleoperation to Improve Operator Experience (2021)
+7. Ashutosh Tiwari (Full / Senior Prof (Large Lab), h=51) | Fit=7.0/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.3/10 | Keywords=pose estimation, stereo vision, computer vision, ros | Paper=A Lightweight Target Following Architecture for Indoor Mobile Robot (2024)
+8. Windo Hutabarat (Associate / Established PI (High Fit), h=17) | Fit=7.0/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.3/10 | Keywords=pose estimation, stereo vision, computer vision, ros | Paper=A Lightweight Target Following Architecture for Indoor Mobile Robot (2024)
+9. Sándor M. Veres (Full / Senior Prof (Large Lab), h=21) | Fit=7.3/10 | Activity=6.8/10 | Funding=0.0/10 | Overall=6.1/10 | Keywords=pose estimation, robot perception, 3d reconstruction | Paper=Advanced Environment Modelling for Remote Teleoperation to Improve Operator Experience (2021)
+10. Tony J. Prescott (Full / Senior Prof (Large Lab), h=48) | Fit=5.2/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.3/10 | Keywords=stereo vision, deep learning | Paper=Improving the Robustness of Visual Teach‐and‐Repeat Navigation Using Drift Error Correction and (2025)
+11. Zeyneb Kurt (Associate / Established PI (High Fit), h=17) | Fit=3.8/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.2/10 | Keywords=kalman filter, object detection | Paper=CosmosDSR -- a methodology for automated detection and tracking of orbital debris using the Uns (2023)</t>
+        </is>
+      </c>
+      <c r="AE12" s="4" t="inlineStr">
+        <is>
+          <t>Sean Anderson: No homepage/funding evidence available
+Jonathan M. Aitken: No homepage/funding evidence available
+Lyudmila S. Mihaylova: No homepage/funding evidence available
+Kirill V. Horoshenkov: No homepage/funding evidence available
+Valentin Radu: No homepage/funding evidence available
+John Anthony Rossiter: No homepage/funding evidence available
+Ashutosh Tiwari: No homepage/funding evidence available
+Windo Hutabarat: No homepage/funding evidence available
+Sándor M. Veres: No homepage/funding evidence available
+Tony J. Prescott: No homepage/funding evidence available
+Zeyneb Kurt: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Sean%20Anderson%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -2128,23 +2236,125 @@
           <t>University of Nottingham</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=877)</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5019813634</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nicholas Hamm</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>GCBi-ScintNet: Predicting GNSS Positioning Errors under Ionospheric Scintillation with a GA-CNN-BiLSTM Hybrid Model (2026)</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Nottingham</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>@nottingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>I142263535</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=27)</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>gnss positioning, kalman filter</t>
+        </is>
+      </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="Z13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>6.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="4" t="inlineStr"/>
-      <c r="AE13" s="4" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Nicholas Hamm; Xin Dong; Luis Figueredo; Paul Blunt; Panos A. Psimoulis; V. Sreeja; Richard Leach; Samanta Piano</t>
+        </is>
+      </c>
+      <c r="AD13" s="4" t="inlineStr">
+        <is>
+          <t>1. Nicholas Hamm (Full / Senior Prof (Large Lab), h=27) | Fit=7.4/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=6.8/10 | Keywords=gnss positioning, kalman filter | Paper=GCBi-ScintNet: Predicting GNSS Positioning Errors under Ionospheric Scintillation with a GA-CNN (2026)
+2. Xin Dong (Associate / Established PI (High Fit), h=28) | Fit=7.6/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.7/10 | Keywords=sensor fusion, pose estimation, point cloud registration | Paper=Sensors and Sensor Fusion Methodologies for Indoor Odometry: A Review (2022)
+3. Luis Figueredo (Associate / Established PI (High Fit), h=15) | Fit=7.0/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=6.5/10 | Keywords=lidar slam, robust localization, ros2 | Paper=Low-Cost Rapid-Development Air-Ground Robotic Solution for Nuclear Power Plant Inspection (2025)
+4. Paul Blunt (Assistant Prof / Rising Star (Responsive), h=13) | Fit=4.9/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.2/10 | Keywords=gnss positioning, fpga, embedded systems | Paper=Interference Mitigation for GNSS Receivers Using FFT Excision Filtering Implemented on an FPGA (2022)
+5. Panos A. Psimoulis (Associate / Established PI (High Fit), h=24) | Fit=4.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.9/10 | Keywords=gnss positioning | Paper=Nottingham smartphone GNSS Raw to RINEX (NSGRX) Converter: a new smartphone data converter: pri (2026)
+6. V. Sreeja (Associate / Established PI (High Fit), h=21) | Fit=5.5/10 | Activity=6.3/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=gnss positioning, kalman filter | Paper=Mitigating the Scintillation Effect on GNSS Signals Using MP and ROTI (2022)
+7. Richard Leach (Full / Senior Prof (Large Lab), h=54) | Fit=3.6/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.0/10 | Keywords=pose estimation, object detection, sensor fusion | Paper=Vision-based detection and coordinate metrology of a spatially encoded multi-sphere artefact (2023)
+8. Samanta Piano (Associate / Established PI (High Fit), h=20) | Fit=3.6/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.0/10 | Keywords=pose estimation, object detection, sensor fusion | Paper=Vision-based detection and coordinate metrology of a spatially encoded multi-sphere artefact (2023)</t>
+        </is>
+      </c>
+      <c r="AE13" s="4" t="inlineStr">
+        <is>
+          <t>Nicholas Hamm: No homepage/funding evidence available
+Xin Dong: No homepage/funding evidence available
+Luis Figueredo: No homepage/funding evidence available
+Paul Blunt: No homepage/funding evidence available
+Panos A. Psimoulis: No homepage/funding evidence available
+V. Sreeja: No homepage/funding evidence available
+Richard Leach: No homepage/funding evidence available
+Samanta Piano: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Anottingham.ac.uk%20%22Nicholas%20Hamm%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
@@ -2152,23 +2362,143 @@
           <t>University of Leeds</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=949)</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5057324156</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mounir Ghogho</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Deep Learning Techniques for Visual SLAM: A Survey (2023)</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>I130828816</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=44)</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>visual slam, robot localization, deep learning</t>
+        </is>
+      </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>7.57</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>9.34</v>
       </c>
       <c r="Z14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>6.79</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="4" t="inlineStr"/>
-      <c r="AE14" s="4" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Mounir Ghogho; Mahdi Rezaei; Richard A. Romano; Sheng Quan Xie; Pietro Valdastri; Mehmet R. Doğar; Netta Cohen; Robert C. Richardson; Zeike A. Taylor; Gustav M. Markkula; Anthony G. Cohn; Maryam Hafeez; Sharib Ali; Syed Ali Raza Zaidi; David Wong; Samuel David Relton; Zhiqiang Zhang</t>
+        </is>
+      </c>
+      <c r="AD14" s="4" t="inlineStr">
+        <is>
+          <t>1. Mounir Ghogho (Full / Senior Prof (Large Lab), h=44) | Fit=9.8/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=8.1/10 | Keywords=visual slam, robot localization, deep learning | Paper=Deep Learning Techniques for Visual SLAM: A Survey (2023)
+2. Mahdi Rezaei (Associate / Established PI (High Fit), h=19) | Fit=8.2/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.4/10 | Keywords=lidar camera fusion, 3d object detection, object detection, trajectory estimation, autonomous vehicles, pose estimation | Paper=Multi-level and Multi-modal Feature Fusion for Accurate 3D Object Detection in Connected and Au (2022)
+3. Richard A. Romano (Associate / Established PI (High Fit), h=21) | Fit=7.9/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=6.8/10 | Keywords=lidar camera fusion, 3d object detection, object detection | Paper=Multi-level and Multi-modal Feature Fusion for Accurate 3D Object Detection in Connected and Au (2022)
+4. Sheng Quan Xie (Full / Senior Prof (Large Lab), h=52) | Fit=6.3/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=6.0/10 | Keywords=lidar camera fusion, sensor calibration, semantic segmentation, mobile robot navigation | Paper=Object-Based Semantic Fusion Algorithm of Lidar and Camera via Inverse Projection (2025)
+5. Pietro Valdastri (Full / Senior Prof (Large Lab), h=49) | Fit=5.6/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.7/10 | Keywords=pose estimation, depth estimation, deep learning | Paper=PICO: Projection-Informed Consistency Optimisation for 6DoF surgical tool pose estimation (2026)
+6. Mehmet R. Doğar (Associate / Established PI (High Fit), h=25) | Fit=5.5/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=5.3/10 | Keywords=robot localization, autonomous navigation | Paper=Real-time robot topological localization and mapping with limited visual sampling in simulated  (2023)
+7. Netta Cohen (Associate / Established PI (High Fit), h=22) | Fit=5.5/10 | Activity=8.2/10 | Funding=0.0/10 | Overall=5.2/10 | Keywords=robot localization, autonomous navigation | Paper=Real-time robot topological localization and mapping with limited visual sampling in simulated  (2023)
+8. Robert C. Richardson (Full / Senior Prof (Large Lab), h=52) | Fit=5.0/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.1/10 | Keywords=autonomous navigation | Paper=Autonomous control for miniaturized mobile robots in unknown pipe networks (2022)
+9. Zeike A. Taylor (Associate / Established PI (High Fit), h=28) | Fit=5.0/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=5.0/10 | Keywords=point cloud registration | Paper=Density-adaptive registration of pointclouds based on Dirichlet Process Gaussian Mixture Models (2023)
+10. Gustav M. Markkula (Full / Senior Prof (Large Lab), h=33) | Fit=4.7/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.0/10 | Keywords=gaussian splatting, 3d reconstruction | Paper=Weathergs: 3D Scene Reconstruction in Adverse Weather Conditions Via Gaussian Splatting (2025)
+11. Anthony G. Cohn (Full / Senior Prof (Large Lab), h=50) | Fit=4.9/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=5.0/10 | Keywords=robot localization | Paper=Real-time robot topological localization and mapping with limited visual sampling in simulated  (2023)
+12. Maryam Hafeez (Associate / Established PI (High Fit), h=18) | Fit=4.4/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=robot perception | Paper=Vision Language Models on the Edge for Real-Time Robotic Perception (2026)
+13. Sharib Ali (Full / Senior Prof (Large Lab), h=24) | Fit=4.8/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=depth estimation, 3d reconstruction, deep learning | Paper=A comprehensive survey on recent deep learning-based methods applied to surgical data (2022)
+14. Syed Ali Raza Zaidi (Full / Senior Prof (Large Lab), h=33) | Fit=4.1/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.7/10 | Keywords=robot perception | Paper=Vision Language Models on the Edge for Real-Time Robotic Perception (2026)
+15. David Wong (Associate / Established PI (High Fit), h=26) | Fit=3.6/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=4.3/10 | Keywords=depth estimation, deep learning, computer vision | Paper=Comparison of monocular video-based methods for measuring the amplitude of hand tremor (2026)
+16. Samuel David Relton (Associate / Established PI (High Fit), h=23) | Fit=3.6/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=4.3/10 | Keywords=depth estimation, deep learning, computer vision | Paper=Comparison of monocular video-based methods for measuring the amplitude of hand tremor (2026)
+17. Zhiqiang Zhang (Full / Senior Prof (Large Lab), h=42) | Fit=3.7/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.2/10 | Keywords=trajectory estimation | Paper=An Offline‐Cascade‐Online Learning‐Based Algorithm for Distal Trajectory Estimation of Medical  (2024)</t>
+        </is>
+      </c>
+      <c r="AE14" s="4" t="inlineStr">
+        <is>
+          <t>Mounir Ghogho: No homepage/funding evidence available
+Mahdi Rezaei: No homepage/funding evidence available
+Richard A. Romano: No homepage/funding evidence available
+Sheng Quan Xie: No homepage/funding evidence available
+Pietro Valdastri: No homepage/funding evidence available
+Mehmet R. Doğar: No homepage/funding evidence available
+Netta Cohen: No homepage/funding evidence available
+Robert C. Richardson: No homepage/funding evidence available
+Zeike A. Taylor: No homepage/funding evidence available
+Gustav M. Markkula: No homepage/funding evidence available
+Anthony G. Cohn: No homepage/funding evidence available
+Maryam Hafeez: No homepage/funding evidence available
+Sharib Ali: No homepage/funding evidence available
+Syed Ali Raza Zaidi: No homepage/funding evidence available
+David Wong: No homepage/funding evidence available
+Samuel David Relton: No homepage/funding evidence available
+Zhiqiang Zhang: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Mounir%20Ghogho%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
@@ -2176,23 +2506,123 @@
           <t>Newcastle University</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=929)</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5001239975</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rosemary A. Norman</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>A Low-Cost Visual Inertial Odometry System for Underwater Vehicles (2021)</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Newcastle upon Tyne</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>@ncl.ac.uk</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>I84884186</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit) (h=23)</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, sensor fusion, visual odometry, pose estimation</t>
+        </is>
+      </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>7.54</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>8.56</v>
       </c>
       <c r="Z15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>6.61</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="4" t="inlineStr"/>
-      <c r="AE15" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rosemary A. Norman; Jeffrey A. Neasham; Hafiz Husnain Raza Sherazi; Vladimir V. Terzija; Jenny C. A. Read; Jon P Mills; Varun Ojha</t>
+        </is>
+      </c>
+      <c r="AD15" s="4" t="inlineStr">
+        <is>
+          <t>1. Rosemary A. Norman (Associate / Established PI (High Fit), h=23) | Fit=9.1/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=7.5/10 | Keywords=visual inertial odometry, sensor fusion, visual odometry, pose estimation | Paper=A Low-Cost Visual Inertial Odometry System for Underwater Vehicles (2021)
+2. Jeffrey A. Neasham (Associate / Established PI (High Fit), h=22) | Fit=9.1/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=7.5/10 | Keywords=visual inertial odometry, sensor fusion, visual odometry, pose estimation | Paper=A Low-Cost Visual Inertial Odometry System for Underwater Vehicles (2021)
+3. Hafiz Husnain Raza Sherazi (Associate / Established PI (High Fit), h=18) | Fit=7.3/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=6.6/10 | Keywords=lidar camera fusion, autonomous vehicles, 3d object detection, object detection | Paper=PLC-Fusion: Perspective-Based Hierarchical and Deep LiDAR Camera Fusion for 3D Object Detection (2024)
+4. Vladimir V. Terzija (Full / Senior Prof (Large Lab), h=63) | Fit=7.1/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.4/10 | Keywords=state estimation, kalman filter | Paper=Variational Bayesian Unscented Kalman Filter for Active Distribution System State Estimation (2024)
+5. Jenny C. A. Read (Full / Senior Prof (Large Lab), h=34) | Fit=5.2/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=5.1/10 | Keywords=stereo vision, autonomous vehicles, computer vision | Paper=Stereo Vision, Models of (2022)
+6. Jon P Mills (Full / Senior Prof (Large Lab), h=34) | Fit=4.4/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=point cloud registration, object detection, 3d reconstruction, deep learning, sensor calibration | Paper=Roadside lidar-based scene understanding toward intelligent traffic perception: A comprehensive (2026)
+7. Varun Ojha (Associate / Established PI (High Fit), h=17) | Fit=4.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.6/10 | Keywords=3d reconstruction, computer vision | Paper=3D modeling and automated measurement of concrete cracks via segment anything refinement and vi (2026)</t>
+        </is>
+      </c>
+      <c r="AE15" s="4" t="inlineStr">
+        <is>
+          <t>Rosemary A. Norman: No homepage/funding evidence available
+Jeffrey A. Neasham: No homepage/funding evidence available
+Hafiz Husnain Raza Sherazi: No homepage/funding evidence available
+Vladimir V. Terzija: No homepage/funding evidence available
+Jenny C. A. Read: No homepage/funding evidence available
+Jon P Mills: No homepage/funding evidence available
+Varun Ojha: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ancl.ac.uk%20%22Rosemary%20A.%20Norman%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
@@ -2200,23 +2630,145 @@
           <t>University of Glasgow</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5050760087</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Jianglin Lan</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Enhanced Visual SLAM for Collision-Free Driving with Lightweight Autonomous Cars (2024)</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>I7882870</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit) (h=21)</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>visual slam, pose estimation, deep learning, object detection, visual inertial odometry</t>
+        </is>
+      </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>9.33</v>
       </c>
       <c r="Z16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="4" t="inlineStr"/>
-      <c r="AE16" s="4" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Jianglin Lan; Chongfeng Wei; Shuja Ansari; Mahmoud A. Shawky; Dezong Zhao; Anahid Basiri; Henrik Hesse; Chee Kiat Seow; Daniele Faccio; Lei Zhang; Roderick Murray‐Smith; Hang Dai; Bernd Porr; Mark David Butala; Hui Ling Yu; Marc Sorel; Nicolas Pugeault; Edmond S. L. Ho</t>
+        </is>
+      </c>
+      <c r="AD16" s="4" t="inlineStr">
+        <is>
+          <t>1. Jianglin Lan (Associate / Established PI (High Fit), h=21) | Fit=8.5/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.4/10 | Keywords=visual slam, pose estimation, deep learning, object detection, visual inertial odometry | Paper=Enhanced Visual SLAM for Collision-Free Driving with Lightweight Autonomous Cars (2024)
+2. Chongfeng Wei (Full / Senior Prof (Large Lab), h=36) | Fit=8.5/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=7.4/10 | Keywords=visual odometry, pose estimation, deep learning | Paper=Online Adaptive Keypoint Extraction for Visual Odometry Across Different Scenes (2025)
+3. Shuja Ansari (Associate / Established PI (High Fit), h=19) | Fit=8.4/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=7.2/10 | Keywords=extended kalman filter, kalman filter | Paper=An experimental analysis of outdoor UAV localisation through diverse estimators and crowd-sense (2024)
+4. Mahmoud A. Shawky (Associate / Established PI (High Fit), h=12) | Fit=8.3/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=7.2/10 | Keywords=extended kalman filter, kalman filter, inertial navigation, sensor fusion | Paper=An experimental analysis of outdoor UAV localisation through diverse estimators and crowd-sense (2024)
+5. Dezong Zhao (Full / Senior Prof (Large Lab), h=29) | Fit=6.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.2/10 | Keywords=sensor fusion, depth estimation, semantic segmentation, autonomous driving perception, object detection | Paper=Dual-Mode SPL-SLAM: A Robust Semantic Point-Line SLAM System with Monocular Neural Depth and Se (2026)
+6. Anahid Basiri (Associate / Established PI (High Fit), h=19) | Fit=6.4/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.2/10 | Keywords=gnss positioning, 3d reconstruction, autonomous vehicles, computer vision, deep learning, semantic segmentation | Paper=Scalable 3D mapping of cities using computer vision and signals of opportunity (2023)
+7. Henrik Hesse (Associate / Established PI (High Fit), h=15) | Fit=5.4/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.4/10 | Keywords=autonomous navigation | Paper=Bat-Grid SLAM: Bio-Inspired Active SLAM Approach Using Neural Grid Cells for Autonomous Navigat (2025)
+8. Chee Kiat Seow (Associate / Established PI (High Fit), h=14) | Fit=5.3/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.4/10 | Keywords=autonomous navigation | Paper=Bat-Grid SLAM: Bio-Inspired Active SLAM Approach Using Neural Grid Cells for Autonomous Navigat (2025)
+9. Daniele Faccio (Full / Senior Prof (Large Lab), h=59) | Fit=5.1/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.2/10 | Keywords=sensor fusion, depth estimation, 3d reconstruction | Paper=IGAF: Incremental Guided Attention Fusion for Depth Super-Resolution (2024)
+10. Lei Zhang (Full / Senior Prof (Large Lab), h=39) | Fit=5.6/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=5.2/10 | Keywords=visual localization, deep learning, computer vision | Paper=A Fine-Grained Attention Model for High Accuracy Operational Robot Guidance (2022)
+11. Roderick Murray‐Smith (Full / Senior Prof (Large Lab), h=48) | Fit=5.1/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.1/10 | Keywords=sensor fusion, depth estimation | Paper=IGAF: Incremental Guided Attention Fusion for Depth Super-Resolution (2024)
+12. Hang Dai (Associate / Established PI (High Fit), h=18) | Fit=4.9/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.0/10 | Keywords=sensor fusion, depth estimation | Paper=IGAF: Incremental Guided Attention Fusion for Depth Super-Resolution (2024)
+13. Bernd Porr (Full / Senior Prof (Large Lab), h=19) | Fit=4.7/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.0/10 | Keywords=pose estimation, mobile robot navigation, autonomous vehicles | Paper=Shared visuo-tactile interactive perception for robust object pose estimation (2024)
+14. Mark David Butala (Associate / Established PI (High Fit), h=20) | Fit=4.7/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.9/10 | Keywords=pose estimation, gaussian splatting | Paper=SCI-Gaussian: Optimizing 3D Gaussian Radiance Fields from a Snapshot Compressive Image (2025)
+15. Hui Ling Yu (Full / Senior Prof (Large Lab), h=56) | Fit=4.4/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=point cloud registration, computer vision, 3d computer vision | Paper=Visual perception-inspired 3D point cloud sampling (2025)
+16. Marc Sorel (Full / Senior Prof (Large Lab), h=54) | Fit=4.1/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=4.3/10 | Keywords=3d computer vision, autonomous vehicles, computer vision | Paper=Metasurface-enhanced light detection and ranging technology (2022)
+17. Nicolas Pugeault (Full / Senior Prof (Large Lab), h=26) | Fit=3.7/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.2/10 | Keywords=autonomous navigation, robot perception, autonomous vehicles | Paper=Efficient Autonomous Exploration with Dueling DDQN Enhancing Active SLAM through Reinforcement  (2024)
+18. Edmond S. L. Ho (Associate / Established PI (High Fit), h=28) | Fit=3.8/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.2/10 | Keywords=point cloud registration, deep learning | Paper=AlignBodyNet: Deep Learning-Based Alignment of Non-Overlapping Partial Body Point Clouds From a (2022)</t>
+        </is>
+      </c>
+      <c r="AE16" s="4" t="inlineStr">
+        <is>
+          <t>Jianglin Lan: No homepage/funding evidence available
+Chongfeng Wei: No homepage/funding evidence available
+Shuja Ansari: No homepage/funding evidence available
+Mahmoud A. Shawky: No homepage/funding evidence available
+Dezong Zhao: No homepage/funding evidence available
+Anahid Basiri: No homepage/funding evidence available
+Henrik Hesse: No homepage/funding evidence available
+Chee Kiat Seow: No homepage/funding evidence available
+Daniele Faccio: No homepage/funding evidence available
+Lei Zhang: No homepage/funding evidence available
+Roderick Murray‐Smith: No homepage/funding evidence available
+Hang Dai: No homepage/funding evidence available
+Bernd Porr: No homepage/funding evidence available
+Mark David Butala: No homepage/funding evidence available
+Hui Ling Yu: No homepage/funding evidence available
+Marc Sorel: No homepage/funding evidence available
+Nicolas Pugeault: No homepage/funding evidence available
+Edmond S. L. Ho: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Jianglin%20Lan%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
@@ -4829,7 +5381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z169"/>
+  <dimension ref="A1:Z230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -22968,8 +23520,6535 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sean Anderson</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>22</v>
+      </c>
+      <c r="K170" t="n">
+        <v>1795</v>
+      </c>
+      <c r="L170" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="M170" t="n">
+        <v>10</v>
+      </c>
+      <c r="N170" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>visual slam, visual odometry, loop closure, field robotics, pose estimation, robot localization</t>
+        </is>
+      </c>
+      <c r="R170" t="n">
+        <v>8</v>
+      </c>
+      <c r="S170" t="n">
+        <v>35</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Assessing the feasibility of monocular visual simultaneous localization and mapping for live sewer pipes: a field robotics study</t>
+        </is>
+      </c>
+      <c r="V170" t="n">
+        <v>2021</v>
+      </c>
+      <c r="W170" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Sean%20Anderson%22%20email</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5071097412</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>2</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Jonathan M. Aitken</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J171" t="n">
+        <v>17</v>
+      </c>
+      <c r="K171" t="n">
+        <v>841</v>
+      </c>
+      <c r="L171" t="n">
+        <v>10</v>
+      </c>
+      <c r="M171" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N171" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>visual-inertial slam, sensor fusion, visual slam, visual odometry, loop closure, field robotics</t>
+        </is>
+      </c>
+      <c r="R171" t="n">
+        <v>4</v>
+      </c>
+      <c r="S171" t="n">
+        <v>19</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>2023-04-17</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Investigating Scene Visibility Estimation Within ORB-SLAM3</t>
+        </is>
+      </c>
+      <c r="V171" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W171" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Jonathan%20M.%20Aitken%22%20email</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5080450263</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>3</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Lyudmila S. Mihaylova</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J172" t="n">
+        <v>41</v>
+      </c>
+      <c r="K172" t="n">
+        <v>6475</v>
+      </c>
+      <c r="L172" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="M172" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N172" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O172" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>robot localization, visual odometry, visual inertial odometry, kalman filter, state estimation, extended kalman filter</t>
+        </is>
+      </c>
+      <c r="R172" t="n">
+        <v>8</v>
+      </c>
+      <c r="S172" t="n">
+        <v>111</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>A robust method for approximate visual robot localization in feature-sparse sewer pipes</t>
+        </is>
+      </c>
+      <c r="V172" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W172" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Lyudmila%20S.%20Mihaylova%22%20email</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5006505402</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>4</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Kirill V. Horoshenkov</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J173" t="n">
+        <v>42</v>
+      </c>
+      <c r="K173" t="n">
+        <v>5221</v>
+      </c>
+      <c r="L173" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="M173" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N173" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>robot localization, loop closure, kalman filter, autonomous navigation</t>
+        </is>
+      </c>
+      <c r="R173" t="n">
+        <v>6</v>
+      </c>
+      <c r="S173" t="n">
+        <v>86</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Acoustic Echo Sensing for Robot Localization in Buried Pipe Networks</t>
+        </is>
+      </c>
+      <c r="V173" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W173" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Kirill%20V.%20Horoshenkov%22%20email</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5035135063</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>5</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Valentin Radu</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
+        <v>14</v>
+      </c>
+      <c r="K174" t="n">
+        <v>1054</v>
+      </c>
+      <c r="L174" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="M174" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N174" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; GNSS &amp; Robust Localization; Deep Learning for Navigation &amp; Perception</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, sensor fusion, sensor calibration</t>
+        </is>
+      </c>
+      <c r="R174" t="n">
+        <v>2</v>
+      </c>
+      <c r="S174" t="n">
+        <v>21</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Multi-Sensor Fusion for Indoor Smartphone Localization with Attention Mechanism</t>
+        </is>
+      </c>
+      <c r="V174" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W174" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Valentin%20Radu%22%20email</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5007676144</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>6</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>John Anthony Rossiter</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
+        <v>37</v>
+      </c>
+      <c r="K175" t="n">
+        <v>6763</v>
+      </c>
+      <c r="L175" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="M175" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N175" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>pose estimation, robot perception, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R175" t="n">
+        <v>1</v>
+      </c>
+      <c r="S175" t="n">
+        <v>55</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>2021-10-28</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Advanced Environment Modelling for Remote Teleoperation to Improve Operator Experience</t>
+        </is>
+      </c>
+      <c r="V175" t="n">
+        <v>2021</v>
+      </c>
+      <c r="W175" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22John%20Anthony%20Rossiter%22%20email</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5039249886</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>7</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Ashutosh Tiwari</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J176" t="n">
+        <v>51</v>
+      </c>
+      <c r="K176" t="n">
+        <v>12302</v>
+      </c>
+      <c r="L176" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="M176" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N176" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>pose estimation, stereo vision, computer vision, ros</t>
+        </is>
+      </c>
+      <c r="R176" t="n">
+        <v>1</v>
+      </c>
+      <c r="S176" t="n">
+        <v>72</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>A Lightweight Target Following Architecture for Indoor Mobile Robot</t>
+        </is>
+      </c>
+      <c r="V176" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W176" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Ashutosh%20Tiwari%22%20email</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5066657755</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>8</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Windo Hutabarat</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>17</v>
+      </c>
+      <c r="K177" t="n">
+        <v>1643</v>
+      </c>
+      <c r="L177" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="M177" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N177" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>pose estimation, stereo vision, computer vision, ros</t>
+        </is>
+      </c>
+      <c r="R177" t="n">
+        <v>1</v>
+      </c>
+      <c r="S177" t="n">
+        <v>17</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>A Lightweight Target Following Architecture for Indoor Mobile Robot</t>
+        </is>
+      </c>
+      <c r="V177" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W177" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Windo%20Hutabarat%22%20email</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5022038523</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>9</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sándor M. Veres</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
+        <v>21</v>
+      </c>
+      <c r="K178" t="n">
+        <v>1923</v>
+      </c>
+      <c r="L178" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="M178" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="N178" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>pose estimation, robot perception, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R178" t="n">
+        <v>1</v>
+      </c>
+      <c r="S178" t="n">
+        <v>7</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>2021-10-28</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Advanced Environment Modelling for Remote Teleoperation to Improve Operator Experience</t>
+        </is>
+      </c>
+      <c r="V178" t="n">
+        <v>2021</v>
+      </c>
+      <c r="W178" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22S%C3%A1ndor%20M.%20Veres%22%20email</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5058754653</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>10</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Tony J. Prescott</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>48</v>
+      </c>
+      <c r="K179" t="n">
+        <v>11046</v>
+      </c>
+      <c r="L179" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="M179" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N179" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O179" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; LiDAR &amp; Multimodal Sensor Fusion; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>stereo vision, deep learning</t>
+        </is>
+      </c>
+      <c r="R179" t="n">
+        <v>1</v>
+      </c>
+      <c r="S179" t="n">
+        <v>54</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Improving the Robustness of Visual Teach‐and‐Repeat Navigation Using Drift Error Correction and Event‐Based Vision for Low‐Light Environments</t>
+        </is>
+      </c>
+      <c r="V179" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W179" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Tony%20J.%20Prescott%22%20email</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5013009407</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1017)</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>@sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>11</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Zeyneb Kurt</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>17</v>
+      </c>
+      <c r="K180" t="n">
+        <v>1508</v>
+      </c>
+      <c r="L180" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="M180" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N180" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>kalman filter, object detection</t>
+        </is>
+      </c>
+      <c r="R180" t="n">
+        <v>1</v>
+      </c>
+      <c r="S180" t="n">
+        <v>54</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>CosmosDSR -- a methodology for automated detection and tracking of orbital debris using the Unscented Kalman Filter</t>
+        </is>
+      </c>
+      <c r="V180" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W180" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asheffield.ac.uk%20%22Zeyneb%20Kurt%22%20email</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5089781839</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>University of Nottingham</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Nottingham</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=877)</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>@nottingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Nicholas Hamm</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>27</v>
+      </c>
+      <c r="K181" t="n">
+        <v>4525</v>
+      </c>
+      <c r="L181" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="M181" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N181" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>gnss positioning, kalman filter</t>
+        </is>
+      </c>
+      <c r="R181" t="n">
+        <v>3</v>
+      </c>
+      <c r="S181" t="n">
+        <v>32</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>GCBi-ScintNet: Predicting GNSS Positioning Errors under Ionospheric Scintillation with a GA-CNN-BiLSTM Hybrid Model</t>
+        </is>
+      </c>
+      <c r="V181" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W181" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Anottingham.ac.uk%20%22Nicholas%20Hamm%22%20email</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5019813634</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>University of Nottingham</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Nottingham</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=877)</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>@nottingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>2</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Xin Dong</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>28</v>
+      </c>
+      <c r="K182" t="n">
+        <v>2609</v>
+      </c>
+      <c r="L182" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="M182" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N182" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>sensor fusion, pose estimation, point cloud registration</t>
+        </is>
+      </c>
+      <c r="R182" t="n">
+        <v>2</v>
+      </c>
+      <c r="S182" t="n">
+        <v>52</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>2024-01-30</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Sensors and Sensor Fusion Methodologies for Indoor Odometry: A Review</t>
+        </is>
+      </c>
+      <c r="V182" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W182" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Anottingham.ac.uk%20%22Xin%20Dong%22%20email</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5087034933</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>University of Nottingham</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Nottingham</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=877)</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>@nottingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>3</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Luis Figueredo</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>15</v>
+      </c>
+      <c r="K183" t="n">
+        <v>822</v>
+      </c>
+      <c r="L183" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="M183" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N183" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O183" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>lidar slam, robust localization, ros2</t>
+        </is>
+      </c>
+      <c r="R183" t="n">
+        <v>2</v>
+      </c>
+      <c r="S183" t="n">
+        <v>59</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Low-Cost Rapid-Development Air-Ground Robotic Solution for Nuclear Power Plant Inspection</t>
+        </is>
+      </c>
+      <c r="V183" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W183" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Anottingham.ac.uk%20%22Luis%20Figueredo%22%20email</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5040790541</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>University of Nottingham</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Nottingham</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=877)</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>@nottingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>4</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Paul Blunt</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J184" t="n">
+        <v>13</v>
+      </c>
+      <c r="K184" t="n">
+        <v>604</v>
+      </c>
+      <c r="L184" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="M184" t="n">
+        <v>10</v>
+      </c>
+      <c r="N184" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>gnss positioning, fpga, embedded systems</t>
+        </is>
+      </c>
+      <c r="R184" t="n">
+        <v>4</v>
+      </c>
+      <c r="S184" t="n">
+        <v>20</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Interference Mitigation for GNSS Receivers Using FFT Excision Filtering Implemented on an FPGA</t>
+        </is>
+      </c>
+      <c r="V184" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W184" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Anottingham.ac.uk%20%22Paul%20Blunt%22%20email</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5067176836</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>University of Nottingham</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Nottingham</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=877)</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>@nottingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>5</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Panos A. Psimoulis</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J185" t="n">
+        <v>24</v>
+      </c>
+      <c r="K185" t="n">
+        <v>1781</v>
+      </c>
+      <c r="L185" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="M185" t="n">
+        <v>10</v>
+      </c>
+      <c r="N185" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O185" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>gnss positioning</t>
+        </is>
+      </c>
+      <c r="R185" t="n">
+        <v>6</v>
+      </c>
+      <c r="S185" t="n">
+        <v>22</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Nottingham smartphone GNSS Raw to RINEX (NSGRX) Converter: a new smartphone data converter: principles, methodology and experimental evaluation</t>
+        </is>
+      </c>
+      <c r="V185" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W185" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Anottingham.ac.uk%20%22Panos%20A.%20Psimoulis%22%20email</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5065462530</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>University of Nottingham</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Nottingham</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=877)</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>@nottingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>6</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>V. Sreeja</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J186" t="n">
+        <v>21</v>
+      </c>
+      <c r="K186" t="n">
+        <v>1003</v>
+      </c>
+      <c r="L186" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="M186" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="N186" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O186" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>gnss positioning, kalman filter</t>
+        </is>
+      </c>
+      <c r="R186" t="n">
+        <v>2</v>
+      </c>
+      <c r="S186" t="n">
+        <v>4</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Mitigating the Scintillation Effect on GNSS Signals Using MP and ROTI</t>
+        </is>
+      </c>
+      <c r="V186" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W186" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Anottingham.ac.uk%20%22V.%20Sreeja%22%20email</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5054153924</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>University of Nottingham</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Nottingham</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=877)</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>@nottingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>7</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Richard Leach</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J187" t="n">
+        <v>54</v>
+      </c>
+      <c r="K187" t="n">
+        <v>14796</v>
+      </c>
+      <c r="L187" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="M187" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N187" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O187" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>pose estimation, object detection, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R187" t="n">
+        <v>2</v>
+      </c>
+      <c r="S187" t="n">
+        <v>87</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Vision-based detection and coordinate metrology of a spatially encoded multi-sphere artefact</t>
+        </is>
+      </c>
+      <c r="V187" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W187" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Anottingham.ac.uk%20%22Richard%20Leach%22%20email</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5002204160</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>University of Nottingham</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Nottingham</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=877)</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>@nottingham.ac.uk</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>8</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Samanta Piano</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J188" t="n">
+        <v>20</v>
+      </c>
+      <c r="K188" t="n">
+        <v>1614</v>
+      </c>
+      <c r="L188" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="M188" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N188" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>pose estimation, object detection, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R188" t="n">
+        <v>2</v>
+      </c>
+      <c r="S188" t="n">
+        <v>93</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Vision-based detection and coordinate metrology of a spatially encoded multi-sphere artefact</t>
+        </is>
+      </c>
+      <c r="V188" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W188" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Anottingham.ac.uk%20%22Samanta%20Piano%22%20email</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5017633397</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=949)</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>1</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Mounir Ghogho</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J189" t="n">
+        <v>44</v>
+      </c>
+      <c r="K189" t="n">
+        <v>8106</v>
+      </c>
+      <c r="L189" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="M189" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N189" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O189" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>visual slam, robot localization, deep learning</t>
+        </is>
+      </c>
+      <c r="R189" t="n">
+        <v>1</v>
+      </c>
+      <c r="S189" t="n">
+        <v>159</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>Deep Learning Techniques for Visual SLAM: A Survey</t>
+        </is>
+      </c>
+      <c r="V189" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W189" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Mounir%20Ghogho%22%20email</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5057324156</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=949)</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>2</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Mahdi Rezaei</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J190" t="n">
+        <v>19</v>
+      </c>
+      <c r="K190" t="n">
+        <v>1410</v>
+      </c>
+      <c r="L190" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="M190" t="n">
+        <v>10</v>
+      </c>
+      <c r="N190" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; State Estimation &amp; Factor Graphs; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>lidar camera fusion, 3d object detection, object detection, trajectory estimation, autonomous vehicles, pose estimation</t>
+        </is>
+      </c>
+      <c r="R190" t="n">
+        <v>9</v>
+      </c>
+      <c r="S190" t="n">
+        <v>34</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Multi-level and Multi-modal Feature Fusion for Accurate 3D Object Detection in Connected and Automated Vehicles</t>
+        </is>
+      </c>
+      <c r="V190" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W190" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Mahdi%20Rezaei%22%20email</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5067789332</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=949)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>3</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Richard A. Romano</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J191" t="n">
+        <v>21</v>
+      </c>
+      <c r="K191" t="n">
+        <v>1634</v>
+      </c>
+      <c r="L191" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="M191" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N191" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>lidar camera fusion, 3d object detection, object detection</t>
+        </is>
+      </c>
+      <c r="R191" t="n">
+        <v>2</v>
+      </c>
+      <c r="S191" t="n">
+        <v>37</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>2022-12-20</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Multi-level and Multi-modal Feature Fusion for Accurate 3D Object Detection in Connected and Automated Vehicles</t>
+        </is>
+      </c>
+      <c r="V191" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W191" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Richard%20A.%20Romano%22%20email</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5022268696</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=949)</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>4</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Sheng Quan Xie</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J192" t="n">
+        <v>52</v>
+      </c>
+      <c r="K192" t="n">
+        <v>10528</v>
+      </c>
+      <c r="L192" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="M192" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N192" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>lidar camera fusion, sensor calibration, semantic segmentation, mobile robot navigation</t>
+        </is>
+      </c>
+      <c r="R192" t="n">
+        <v>2</v>
+      </c>
+      <c r="S192" t="n">
+        <v>154</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Object-Based Semantic Fusion Algorithm of Lidar and Camera via Inverse Projection</t>
+        </is>
+      </c>
+      <c r="V192" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W192" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Sheng%20Quan%20Xie%22%20email</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5035866142</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=949)</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>5</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Pietro Valdastri</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J193" t="n">
+        <v>49</v>
+      </c>
+      <c r="K193" t="n">
+        <v>9407</v>
+      </c>
+      <c r="L193" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="M193" t="n">
+        <v>10</v>
+      </c>
+      <c r="N193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>pose estimation, depth estimation, deep learning</t>
+        </is>
+      </c>
+      <c r="R193" t="n">
+        <v>3</v>
+      </c>
+      <c r="S193" t="n">
+        <v>115</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>PICO: Projection-Informed Consistency Optimisation for 6DoF surgical tool pose estimation</t>
+        </is>
+      </c>
+      <c r="V193" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W193" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Pietro%20Valdastri%22%20email</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5035357710</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=949)</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>6</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Mehmet R. Doğar</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J194" t="n">
+        <v>25</v>
+      </c>
+      <c r="K194" t="n">
+        <v>2628</v>
+      </c>
+      <c r="L194" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="M194" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N194" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O194" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>robot localization, autonomous navigation</t>
+        </is>
+      </c>
+      <c r="R194" t="n">
+        <v>2</v>
+      </c>
+      <c r="S194" t="n">
+        <v>41</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Real-time robot topological localization and mapping with limited visual sampling in simulated buried pipe networks</t>
+        </is>
+      </c>
+      <c r="V194" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W194" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Mehmet%20R.%20Do%C4%9Far%22%20email</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5025603635</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=949)</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>7</v>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Netta Cohen</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J195" t="n">
+        <v>22</v>
+      </c>
+      <c r="K195" t="n">
+        <v>1919</v>
+      </c>
+      <c r="L195" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="M195" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="N195" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>robot localization, autonomous navigation</t>
+        </is>
+      </c>
+      <c r="R195" t="n">
+        <v>2</v>
+      </c>
+      <c r="S195" t="n">
+        <v>14</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Real-time robot topological localization and mapping with limited visual sampling in simulated buried pipe networks</t>
+        </is>
+      </c>
+      <c r="V195" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W195" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Netta%20Cohen%22%20email</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5059480877</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=949)</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>8</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Robert C. Richardson</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J196" t="n">
+        <v>52</v>
+      </c>
+      <c r="K196" t="n">
+        <v>9110</v>
+      </c>
+      <c r="L196" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="M196" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N196" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>autonomous navigation</t>
+        </is>
+      </c>
+      <c r="R196" t="n">
+        <v>2</v>
+      </c>
+      <c r="S196" t="n">
+        <v>21</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Autonomous control for miniaturized mobile robots in unknown pipe networks</t>
+        </is>
+      </c>
+      <c r="V196" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W196" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Robert%20C.%20Richardson%22%20email</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5065382176</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=949)</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>9</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Zeike A. Taylor</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J197" t="n">
+        <v>28</v>
+      </c>
+      <c r="K197" t="n">
+        <v>3805</v>
+      </c>
+      <c r="L197" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="M197" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N197" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O197" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>point cloud registration</t>
+        </is>
+      </c>
+      <c r="R197" t="n">
+        <v>1</v>
+      </c>
+      <c r="S197" t="n">
+        <v>24</v>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>2023-04-04</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>Density-adaptive registration of pointclouds based on Dirichlet Process Gaussian Mixture Models</t>
+        </is>
+      </c>
+      <c r="V197" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W197" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Zeike%20A.%20Taylor%22%20email</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5055587668</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=949)</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>10</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Gustav M. Markkula</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J198" t="n">
+        <v>33</v>
+      </c>
+      <c r="K198" t="n">
+        <v>4101</v>
+      </c>
+      <c r="L198" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="M198" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N198" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>gaussian splatting, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R198" t="n">
+        <v>2</v>
+      </c>
+      <c r="S198" t="n">
+        <v>80</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Weathergs: 3D Scene Reconstruction in Adverse Weather Conditions Via Gaussian Splatting</t>
+        </is>
+      </c>
+      <c r="V198" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W198" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Gustav%20M.%20Markkula%22%20email</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5019237761</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=949)</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>11</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Anthony G. Cohn</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J199" t="n">
+        <v>50</v>
+      </c>
+      <c r="K199" t="n">
+        <v>11284</v>
+      </c>
+      <c r="L199" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="M199" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N199" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>robot localization</t>
+        </is>
+      </c>
+      <c r="R199" t="n">
+        <v>2</v>
+      </c>
+      <c r="S199" t="n">
+        <v>85</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Real-time robot topological localization and mapping with limited visual sampling in simulated buried pipe networks</t>
+        </is>
+      </c>
+      <c r="V199" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W199" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Anthony%20G.%20Cohn%22%20email</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5024409281</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=949)</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>12</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Maryam Hafeez</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J200" t="n">
+        <v>18</v>
+      </c>
+      <c r="K200" t="n">
+        <v>1470</v>
+      </c>
+      <c r="L200" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="M200" t="n">
+        <v>10</v>
+      </c>
+      <c r="N200" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O200" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>robot perception</t>
+        </is>
+      </c>
+      <c r="R200" t="n">
+        <v>3</v>
+      </c>
+      <c r="S200" t="n">
+        <v>60</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Vision Language Models on the Edge for Real-Time Robotic Perception</t>
+        </is>
+      </c>
+      <c r="V200" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W200" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Maryam%20Hafeez%22%20email</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5090771677</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=949)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>13</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Sharib Ali</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J201" t="n">
+        <v>24</v>
+      </c>
+      <c r="K201" t="n">
+        <v>3328</v>
+      </c>
+      <c r="L201" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="M201" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N201" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; GNSS &amp; Robust Localization; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>depth estimation, 3d reconstruction, deep learning</t>
+        </is>
+      </c>
+      <c r="R201" t="n">
+        <v>1</v>
+      </c>
+      <c r="S201" t="n">
+        <v>133</v>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>2022-09-03</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>A comprehensive survey on recent deep learning-based methods applied to surgical data</t>
+        </is>
+      </c>
+      <c r="V201" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W201" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Sharib%20Ali%22%20email</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5080765299</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=949)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G202" t="n">
+        <v>14</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Syed Ali Raza Zaidi</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J202" t="n">
+        <v>33</v>
+      </c>
+      <c r="K202" t="n">
+        <v>5341</v>
+      </c>
+      <c r="L202" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="M202" t="n">
+        <v>10</v>
+      </c>
+      <c r="N202" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>robot perception</t>
+        </is>
+      </c>
+      <c r="R202" t="n">
+        <v>1</v>
+      </c>
+      <c r="S202" t="n">
+        <v>66</v>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>Vision Language Models on the Edge for Real-Time Robotic Perception</t>
+        </is>
+      </c>
+      <c r="V202" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W202" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Syed%20Ali%20Raza%20Zaidi%22%20email</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5011903629</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=949)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>15</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>David Wong</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J203" t="n">
+        <v>26</v>
+      </c>
+      <c r="K203" t="n">
+        <v>3323</v>
+      </c>
+      <c r="L203" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M203" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N203" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>depth estimation, deep learning, computer vision</t>
+        </is>
+      </c>
+      <c r="R203" t="n">
+        <v>1</v>
+      </c>
+      <c r="S203" t="n">
+        <v>62</v>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>Comparison of monocular video-based methods for measuring the amplitude of hand tremor</t>
+        </is>
+      </c>
+      <c r="V203" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W203" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22David%20Wong%22%20email</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5035842420</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=949)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G204" t="n">
+        <v>16</v>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Samuel David Relton</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J204" t="n">
+        <v>23</v>
+      </c>
+      <c r="K204" t="n">
+        <v>1495</v>
+      </c>
+      <c r="L204" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M204" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N204" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>depth estimation, deep learning, computer vision</t>
+        </is>
+      </c>
+      <c r="R204" t="n">
+        <v>1</v>
+      </c>
+      <c r="S204" t="n">
+        <v>113</v>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Comparison of monocular video-based methods for measuring the amplitude of hand tremor</t>
+        </is>
+      </c>
+      <c r="V204" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W204" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Samuel%20David%20Relton%22%20email</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5066256734</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=949)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>@leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>17</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Zhiqiang Zhang</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J205" t="n">
+        <v>42</v>
+      </c>
+      <c r="K205" t="n">
+        <v>5852</v>
+      </c>
+      <c r="L205" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="M205" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N205" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O205" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>trajectory estimation</t>
+        </is>
+      </c>
+      <c r="R205" t="n">
+        <v>1</v>
+      </c>
+      <c r="S205" t="n">
+        <v>184</v>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>2024-12-25</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>An Offline‐Cascade‐Online Learning‐Based Algorithm for Distal Trajectory Estimation of Medical Continuum Manipulators</t>
+        </is>
+      </c>
+      <c r="V205" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W205" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aleeds.ac.uk%20%22Zhiqiang%20Zhang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5050079548</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Newcastle University</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Newcastle upon Tyne</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=929)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>@ncl.ac.uk</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>1</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Rosemary A. Norman</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J206" t="n">
+        <v>23</v>
+      </c>
+      <c r="K206" t="n">
+        <v>1882</v>
+      </c>
+      <c r="L206" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="M206" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N206" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O206" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, sensor fusion, visual odometry, pose estimation</t>
+        </is>
+      </c>
+      <c r="R206" t="n">
+        <v>3</v>
+      </c>
+      <c r="S206" t="n">
+        <v>40</v>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>A Low-Cost Visual Inertial Odometry System for Underwater Vehicles</t>
+        </is>
+      </c>
+      <c r="V206" t="n">
+        <v>2021</v>
+      </c>
+      <c r="W206" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ancl.ac.uk%20%22Rosemary%20A.%20Norman%22%20email</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5001239975</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Newcastle University</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Newcastle upon Tyne</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=929)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>@ncl.ac.uk</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G207" t="n">
+        <v>2</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Jeffrey A. Neasham</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J207" t="n">
+        <v>22</v>
+      </c>
+      <c r="K207" t="n">
+        <v>1850</v>
+      </c>
+      <c r="L207" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="M207" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N207" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O207" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, sensor fusion, visual odometry, pose estimation</t>
+        </is>
+      </c>
+      <c r="R207" t="n">
+        <v>3</v>
+      </c>
+      <c r="S207" t="n">
+        <v>42</v>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>A Low-Cost Visual Inertial Odometry System for Underwater Vehicles</t>
+        </is>
+      </c>
+      <c r="V207" t="n">
+        <v>2021</v>
+      </c>
+      <c r="W207" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ancl.ac.uk%20%22Jeffrey%20A.%20Neasham%22%20email</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5073279805</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Newcastle University</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Newcastle upon Tyne</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=929)</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>@ncl.ac.uk</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G208" t="n">
+        <v>3</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Hafiz Husnain Raza Sherazi</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J208" t="n">
+        <v>18</v>
+      </c>
+      <c r="K208" t="n">
+        <v>1541</v>
+      </c>
+      <c r="L208" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="M208" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N208" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O208" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>lidar camera fusion, autonomous vehicles, 3d object detection, object detection</t>
+        </is>
+      </c>
+      <c r="R208" t="n">
+        <v>1</v>
+      </c>
+      <c r="S208" t="n">
+        <v>32</v>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>PLC-Fusion: Perspective-Based Hierarchical and Deep LiDAR Camera Fusion for 3D Object Detection in Autonomous Vehicles</t>
+        </is>
+      </c>
+      <c r="V208" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W208" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ancl.ac.uk%20%22Hafiz%20Husnain%20Raza%20Sherazi%22%20email</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5070150180</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Newcastle University</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Newcastle upon Tyne</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=929)</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>@ncl.ac.uk</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>4</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Vladimir V. Terzija</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J209" t="n">
+        <v>63</v>
+      </c>
+      <c r="K209" t="n">
+        <v>16587</v>
+      </c>
+      <c r="L209" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="M209" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N209" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>state estimation, kalman filter</t>
+        </is>
+      </c>
+      <c r="R209" t="n">
+        <v>1</v>
+      </c>
+      <c r="S209" t="n">
+        <v>217</v>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>Variational Bayesian Unscented Kalman Filter for Active Distribution System State Estimation</t>
+        </is>
+      </c>
+      <c r="V209" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W209" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ancl.ac.uk%20%22Vladimir%20V.%20Terzija%22%20email</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5038764115</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Newcastle University</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Newcastle upon Tyne</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=929)</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>@ncl.ac.uk</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>5</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Jenny C. A. Read</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J210" t="n">
+        <v>34</v>
+      </c>
+      <c r="K210" t="n">
+        <v>3188</v>
+      </c>
+      <c r="L210" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="M210" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N210" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O210" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>stereo vision, autonomous vehicles, computer vision</t>
+        </is>
+      </c>
+      <c r="R210" t="n">
+        <v>2</v>
+      </c>
+      <c r="S210" t="n">
+        <v>34</v>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>2022-12-13</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>Stereo Vision, Models of</t>
+        </is>
+      </c>
+      <c r="V210" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W210" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ancl.ac.uk%20%22Jenny%20C.%20A.%20Read%22%20email</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5056194889</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Newcastle University</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Newcastle upon Tyne</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=929)</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>@ncl.ac.uk</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>6</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Jon P Mills</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J211" t="n">
+        <v>34</v>
+      </c>
+      <c r="K211" t="n">
+        <v>6354</v>
+      </c>
+      <c r="L211" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="M211" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N211" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O211" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>point cloud registration, object detection, 3d reconstruction, deep learning, sensor calibration</t>
+        </is>
+      </c>
+      <c r="R211" t="n">
+        <v>3</v>
+      </c>
+      <c r="S211" t="n">
+        <v>54</v>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>Roadside lidar-based scene understanding toward intelligent traffic perception: A comprehensive review</t>
+        </is>
+      </c>
+      <c r="V211" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W211" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ancl.ac.uk%20%22Jon%20P%20Mills%22%20email</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5072568459</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Newcastle University</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Newcastle upon Tyne</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=929)</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>@ncl.ac.uk</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>7</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Varun Ojha</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J212" t="n">
+        <v>17</v>
+      </c>
+      <c r="K212" t="n">
+        <v>1519</v>
+      </c>
+      <c r="L212" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="M212" t="n">
+        <v>10</v>
+      </c>
+      <c r="N212" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>3d reconstruction, computer vision</t>
+        </is>
+      </c>
+      <c r="R212" t="n">
+        <v>2</v>
+      </c>
+      <c r="S212" t="n">
+        <v>77</v>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>3D modeling and automated measurement of concrete cracks via segment anything refinement and visual inertial LiDAR fusion</t>
+        </is>
+      </c>
+      <c r="V212" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W212" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ancl.ac.uk%20%22Varun%20Ojha%22%20email</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5058318377</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>1</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Jianglin Lan</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J213" t="n">
+        <v>21</v>
+      </c>
+      <c r="K213" t="n">
+        <v>1801</v>
+      </c>
+      <c r="L213" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="M213" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N213" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>visual slam, pose estimation, deep learning, object detection, visual inertial odometry</t>
+        </is>
+      </c>
+      <c r="R213" t="n">
+        <v>3</v>
+      </c>
+      <c r="S213" t="n">
+        <v>79</v>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>Enhanced Visual SLAM for Collision-Free Driving with Lightweight Autonomous Cars</t>
+        </is>
+      </c>
+      <c r="V213" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W213" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Jianglin%20Lan%22%20email</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5050760087</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>2</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Chongfeng Wei</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J214" t="n">
+        <v>36</v>
+      </c>
+      <c r="K214" t="n">
+        <v>4214</v>
+      </c>
+      <c r="L214" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="M214" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N214" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>visual odometry, pose estimation, deep learning</t>
+        </is>
+      </c>
+      <c r="R214" t="n">
+        <v>1</v>
+      </c>
+      <c r="S214" t="n">
+        <v>85</v>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>Online Adaptive Keypoint Extraction for Visual Odometry Across Different Scenes</t>
+        </is>
+      </c>
+      <c r="V214" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W214" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Chongfeng%20Wei%22%20email</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5054213642</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>3</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Shuja Ansari</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J215" t="n">
+        <v>19</v>
+      </c>
+      <c r="K215" t="n">
+        <v>1206</v>
+      </c>
+      <c r="L215" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="M215" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N215" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>extended kalman filter, kalman filter</t>
+        </is>
+      </c>
+      <c r="R215" t="n">
+        <v>1</v>
+      </c>
+      <c r="S215" t="n">
+        <v>98</v>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>An experimental analysis of outdoor UAV localisation through diverse estimators and crowd-sensed data fusion</t>
+        </is>
+      </c>
+      <c r="V215" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W215" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Shuja%20Ansari%22%20email</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5001835000</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>4</v>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Mahmoud A. Shawky</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J216" t="n">
+        <v>12</v>
+      </c>
+      <c r="K216" t="n">
+        <v>440</v>
+      </c>
+      <c r="L216" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="M216" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N216" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O216" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; Visual-Inertial Navigation &amp; SLAM; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>extended kalman filter, kalman filter, inertial navigation, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R216" t="n">
+        <v>3</v>
+      </c>
+      <c r="S216" t="n">
+        <v>74</v>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>An experimental analysis of outdoor UAV localisation through diverse estimators and crowd-sensed data fusion</t>
+        </is>
+      </c>
+      <c r="V216" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W216" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Mahmoud%20A.%20Shawky%22%20email</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5082156702</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>5</v>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Dezong Zhao</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J217" t="n">
+        <v>29</v>
+      </c>
+      <c r="K217" t="n">
+        <v>2925</v>
+      </c>
+      <c r="L217" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="M217" t="n">
+        <v>10</v>
+      </c>
+      <c r="N217" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O217" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>sensor fusion, depth estimation, semantic segmentation, autonomous driving perception, object detection</t>
+        </is>
+      </c>
+      <c r="R217" t="n">
+        <v>2</v>
+      </c>
+      <c r="S217" t="n">
+        <v>109</v>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>Dual-Mode SPL-SLAM: A Robust Semantic Point-Line SLAM System with Monocular Neural Depth and Sensor Fusion for Intelligent Transportation</t>
+        </is>
+      </c>
+      <c r="V217" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W217" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Dezong%20Zhao%22%20email</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5027569449</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>6</v>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Anahid Basiri</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J218" t="n">
+        <v>19</v>
+      </c>
+      <c r="K218" t="n">
+        <v>1301</v>
+      </c>
+      <c r="L218" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="M218" t="n">
+        <v>10</v>
+      </c>
+      <c r="N218" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O218" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>gnss positioning, 3d reconstruction, autonomous vehicles, computer vision, deep learning, semantic segmentation</t>
+        </is>
+      </c>
+      <c r="R218" t="n">
+        <v>2</v>
+      </c>
+      <c r="S218" t="n">
+        <v>63</v>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>Scalable 3D mapping of cities using computer vision and signals of opportunity</t>
+        </is>
+      </c>
+      <c r="V218" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W218" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Anahid%20Basiri%22%20email</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5076329659</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>7</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Henrik Hesse</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J219" t="n">
+        <v>15</v>
+      </c>
+      <c r="K219" t="n">
+        <v>778</v>
+      </c>
+      <c r="L219" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="M219" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N219" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O219" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>autonomous navigation</t>
+        </is>
+      </c>
+      <c r="R219" t="n">
+        <v>1</v>
+      </c>
+      <c r="S219" t="n">
+        <v>27</v>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>Bat-Grid SLAM: Bio-Inspired Active SLAM Approach Using Neural Grid Cells for Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="V219" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W219" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Henrik%20Hesse%22%20email</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5066082686</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>8</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Chee Kiat Seow</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J220" t="n">
+        <v>14</v>
+      </c>
+      <c r="K220" t="n">
+        <v>835</v>
+      </c>
+      <c r="L220" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="M220" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N220" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O220" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>autonomous navigation</t>
+        </is>
+      </c>
+      <c r="R220" t="n">
+        <v>2</v>
+      </c>
+      <c r="S220" t="n">
+        <v>49</v>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>Bat-Grid SLAM: Bio-Inspired Active SLAM Approach Using Neural Grid Cells for Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="V220" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W220" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Chee%20Kiat%20Seow%22%20email</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5043390157</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>9</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Daniele Faccio</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J221" t="n">
+        <v>59</v>
+      </c>
+      <c r="K221" t="n">
+        <v>11925</v>
+      </c>
+      <c r="L221" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="M221" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N221" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>sensor fusion, depth estimation, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R221" t="n">
+        <v>3</v>
+      </c>
+      <c r="S221" t="n">
+        <v>193</v>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>IGAF: Incremental Guided Attention Fusion for Depth Super-Resolution</t>
+        </is>
+      </c>
+      <c r="V221" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W221" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Daniele%20Faccio%22%20email</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5082496896</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>10</v>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Lei Zhang</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J222" t="n">
+        <v>39</v>
+      </c>
+      <c r="K222" t="n">
+        <v>6742</v>
+      </c>
+      <c r="L222" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="M222" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N222" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O222" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>visual localization, deep learning, computer vision</t>
+        </is>
+      </c>
+      <c r="R222" t="n">
+        <v>1</v>
+      </c>
+      <c r="S222" t="n">
+        <v>174</v>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>A Fine-Grained Attention Model for High Accuracy Operational Robot Guidance</t>
+        </is>
+      </c>
+      <c r="V222" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W222" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Lei%20Zhang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5075816408</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>11</v>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Roderick Murray‐Smith</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J223" t="n">
+        <v>48</v>
+      </c>
+      <c r="K223" t="n">
+        <v>8639</v>
+      </c>
+      <c r="L223" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="M223" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N223" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O223" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>sensor fusion, depth estimation</t>
+        </is>
+      </c>
+      <c r="R223" t="n">
+        <v>2</v>
+      </c>
+      <c r="S223" t="n">
+        <v>75</v>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>2024-12-24</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>IGAF: Incremental Guided Attention Fusion for Depth Super-Resolution</t>
+        </is>
+      </c>
+      <c r="V223" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W223" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Roderick%20Murray%E2%80%90Smith%22%20email</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5070918132</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>12</v>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Hang Dai</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J224" t="n">
+        <v>18</v>
+      </c>
+      <c r="K224" t="n">
+        <v>2151</v>
+      </c>
+      <c r="L224" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="M224" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N224" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O224" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>sensor fusion, depth estimation</t>
+        </is>
+      </c>
+      <c r="R224" t="n">
+        <v>1</v>
+      </c>
+      <c r="S224" t="n">
+        <v>36</v>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>2024-12-24</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>IGAF: Incremental Guided Attention Fusion for Depth Super-Resolution</t>
+        </is>
+      </c>
+      <c r="V224" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W224" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Hang%20Dai%22%20email</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5080852978</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>13</v>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Bernd Porr</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J225" t="n">
+        <v>19</v>
+      </c>
+      <c r="K225" t="n">
+        <v>1613</v>
+      </c>
+      <c r="L225" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="M225" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N225" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O225" t="n">
+        <v>5</v>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>pose estimation, mobile robot navigation, autonomous vehicles</t>
+        </is>
+      </c>
+      <c r="R225" t="n">
+        <v>2</v>
+      </c>
+      <c r="S225" t="n">
+        <v>38</v>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>Shared visuo-tactile interactive perception for robust object pose estimation</t>
+        </is>
+      </c>
+      <c r="V225" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W225" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Bernd%20Porr%22%20email</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5091850362</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>14</v>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Mark David Butala</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J226" t="n">
+        <v>20</v>
+      </c>
+      <c r="K226" t="n">
+        <v>1404</v>
+      </c>
+      <c r="L226" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="M226" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N226" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O226" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>pose estimation, gaussian splatting</t>
+        </is>
+      </c>
+      <c r="R226" t="n">
+        <v>1</v>
+      </c>
+      <c r="S226" t="n">
+        <v>31</v>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SCI-Gaussian: Optimizing 3D Gaussian Radiance Fields from a Snapshot Compressive Image</t>
+        </is>
+      </c>
+      <c r="V226" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W226" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Mark%20David%20Butala%22%20email</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5075035096</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>15</v>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Hui Ling Yu</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J227" t="n">
+        <v>56</v>
+      </c>
+      <c r="K227" t="n">
+        <v>14684</v>
+      </c>
+      <c r="L227" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="M227" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N227" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O227" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>point cloud registration, computer vision, 3d computer vision</t>
+        </is>
+      </c>
+      <c r="R227" t="n">
+        <v>3</v>
+      </c>
+      <c r="S227" t="n">
+        <v>251</v>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>Visual perception-inspired 3D point cloud sampling</t>
+        </is>
+      </c>
+      <c r="V227" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W227" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Hui%20Ling%20Yu%22%20email</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5006580423</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>16</v>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Marc Sorel</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J228" t="n">
+        <v>54</v>
+      </c>
+      <c r="K228" t="n">
+        <v>12827</v>
+      </c>
+      <c r="L228" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="M228" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N228" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O228" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>3d computer vision, autonomous vehicles, computer vision</t>
+        </is>
+      </c>
+      <c r="R228" t="n">
+        <v>1</v>
+      </c>
+      <c r="S228" t="n">
+        <v>91</v>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>2022-09-29</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>Metasurface-enhanced light detection and ranging technology</t>
+        </is>
+      </c>
+      <c r="V228" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W228" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Marc%20Sorel%22%20email</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5084372344</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>17</v>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Nicolas Pugeault</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J229" t="n">
+        <v>26</v>
+      </c>
+      <c r="K229" t="n">
+        <v>2278</v>
+      </c>
+      <c r="L229" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="M229" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N229" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O229" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>autonomous navigation, robot perception, autonomous vehicles</t>
+        </is>
+      </c>
+      <c r="R229" t="n">
+        <v>2</v>
+      </c>
+      <c r="S229" t="n">
+        <v>39</v>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>Efficient Autonomous Exploration with Dueling DDQN Enhancing Active SLAM through Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="V229" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W229" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Nicolas%20Pugeault%22%20email</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5087140377</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>QS #78 | Tier S+ (Global Elite | h=1600)</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>@gla.ac.uk</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>18</v>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Edmond S. L. Ho</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J230" t="n">
+        <v>28</v>
+      </c>
+      <c r="K230" t="n">
+        <v>2861</v>
+      </c>
+      <c r="L230" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="M230" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N230" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O230" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>point cloud registration, deep learning</t>
+        </is>
+      </c>
+      <c r="R230" t="n">
+        <v>1</v>
+      </c>
+      <c r="S230" t="n">
+        <v>78</v>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>AlignBodyNet: Deep Learning-Based Alignment of Non-Overlapping Partial Body Point Clouds From a Single Depth Camera</t>
+        </is>
+      </c>
+      <c r="V230" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W230" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Agla.ac.uk%20%22Edmond%20S.%20L.%20Ho%22%20email</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5080180158</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z169"/>
+  <autoFilter ref="A1:Z230"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AG$127</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Z$230</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Z$276</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -2776,23 +2776,127 @@
           <t>University of Strathclyde</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=553)</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5059893133</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hong Yue</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Unmanned Aerial Vehicle Visual Simultaneous Localization and Mapping: A Survey (2022)</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>@strath.ac.uk</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>I181647926</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=23)</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>visual slam, visual odometry, autonomous navigation, computer vision, deep learning</t>
+        </is>
+      </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>9.67</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>9.08</v>
       </c>
       <c r="Z17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="4" t="inlineStr"/>
-      <c r="AE17" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hong Yue; Erfu Yang; Gaetano Di Caterina; Ehsan Mohseni; Ian K. Proudler; Gordon Dobie; Malcolm Macdonald; Zhiming Yuan; Jaime Zabalza</t>
+        </is>
+      </c>
+      <c r="AD17" s="4" t="inlineStr">
+        <is>
+          <t>1. Hong Yue (Full / Senior Prof (Large Lab), h=23) | Fit=10.0/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=8.3/10 | Keywords=visual slam, visual odometry, autonomous navigation, computer vision, deep learning | Paper=Unmanned Aerial Vehicle Visual Simultaneous Localization and Mapping: A Survey (2022)
+2. Erfu Yang (Full / Senior Prof (Large Lab), h=40) | Fit=9.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.2/10 | Keywords=visual odometry, pose estimation, autonomous navigation, deep learning, multi-sensor fusion, sensor fusion | Paper=A Robust Learned Feature-Based Visual Odometry System for UAV Pose Estimation in Challenging In (2023)
+3. Gaetano Di Caterina (Associate / Established PI (High Fit), h=19) | Fit=9.7/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=8.2/10 | Keywords=visual inertial navigation, inertial navigation, visual inertial odometry | Paper=An Embedded Visual-Inertial Navigation System for Mobile Platforms Using an Event-Based Camera (2025)
+4. Ehsan Mohseni (Associate / Established PI (High Fit), h=18) | Fit=9.7/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=8.2/10 | Keywords=visual inertial navigation, inertial navigation, visual inertial odometry | Paper=An Embedded Visual-Inertial Navigation System for Mobile Platforms Using an Event-Based Camera (2025)
+5. Ian K. Proudler (Full / Senior Prof (Large Lab), h=24) | Fit=9.4/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=multi-sensor fusion, sensor fusion, kalman filter, state estimation | Paper=Adaptive Kernel Kalman Filter Multi-Sensor Fusion (2021)
+6. Gordon Dobie (Full / Senior Prof (Large Lab), h=23) | Fit=5.2/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.3/10 | Keywords=state estimation | Paper=An adaptable framework for remotely controlling a telepresence robot in a dynamic environment (2025)
+7. Malcolm Macdonald (Full / Senior Prof (Large Lab), h=27) | Fit=4.7/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.0/10 | Keywords=extended kalman filter, kalman filter, autonomous navigation, fpga | Paper=Efficient Orbit Determination Using Measurement-Directional State Transition Tensor (2025)
+8. Zhiming Yuan (Full / Senior Prof (Large Lab), h=39) | Fit=4.5/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=4.5/10 | Keywords=extended kalman filter, kalman filter | Paper=Time-optimal obstacle avoidance of autonomous ship based on nonlinear model predictive control (2022)
+9. Jaime Zabalza (Associate / Established PI (High Fit), h=25) | Fit=3.6/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=4.3/10 | Keywords=autonomous navigation, fpga | Paper=A Review of Machine Learning in Embedded Space Systems: Challenges, Techniques, and Future Dire (2026)</t>
+        </is>
+      </c>
+      <c r="AE17" s="4" t="inlineStr">
+        <is>
+          <t>Hong Yue: No homepage/funding evidence available
+Erfu Yang: No homepage/funding evidence available
+Gaetano Di Caterina: No homepage/funding evidence available
+Ehsan Mohseni: No homepage/funding evidence available
+Ian K. Proudler: No homepage/funding evidence available
+Gordon Dobie: No homepage/funding evidence available
+Malcolm Macdonald: No homepage/funding evidence available
+Zhiming Yuan: No homepage/funding evidence available
+Jaime Zabalza: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Astrath.ac.uk%20%22Hong%20Yue%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
@@ -2800,23 +2904,127 @@
           <t>University of Warwick</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=803)</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5053684989</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hongkai Wen</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>DeepEVO: Towards Robust Visual Odometry via Attention-Based Events and Video Fusion (2026)</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>@warwick.ac.uk</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>I39555362</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit) (h=28)</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>visual odometry, pose estimation, mobile robot navigation</t>
+        </is>
+      </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Z18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>7.32</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="4" t="inlineStr"/>
-      <c r="AE18" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hongkai Wen; Ligang He; Paul Jennings; Matthew D. Higgins; Kurt Debattista; Shan E Ahmed Raza; Mona Faraji Niri; Valentina Donzella; Roger Woodman</t>
+        </is>
+      </c>
+      <c r="AD18" s="4" t="inlineStr">
+        <is>
+          <t>1. Hongkai Wen (Associate / Established PI (High Fit), h=28) | Fit=10.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.5/10 | Keywords=visual odometry, pose estimation, mobile robot navigation | Paper=DeepEVO: Towards Robust Visual Odometry via Attention-Based Events and Video Fusion (2026)
+2. Ligang He (Full / Senior Prof (Large Lab), h=28) | Fit=8.8/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.6/10 | Keywords=point cloud registration, 3d computer vision, 3d reconstruction, computer vision | Paper=ACT‐Agent: Affinity‐Cross Transformer for Point Cloud Registration via Reinforcement Learning (2026)
+3. Paul Jennings (Full / Senior Prof (Large Lab), h=32) | Fit=8.0/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.1/10 | Keywords=gnss positioning, sensor fusion | Paper=A Study of Standalone GNSS Positioning Precision in Covered Agricultural Environments: ETFE Pol (2026)
+4. Matthew D. Higgins (Associate / Established PI (High Fit), h=25) | Fit=8.0/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.1/10 | Keywords=gnss positioning, sensor fusion | Paper=A Study of Standalone GNSS Positioning Precision in Covered Agricultural Environments: ETFE Pol (2026)
+5. Kurt Debattista (Full / Senior Prof (Large Lab), h=32) | Fit=7.1/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=6.2/10 | Keywords=visual localization, place recognition | Paper=Recognising place under distinct weather variability, a comparison between end-to-end and metri (2022)
+6. Shan E Ahmed Raza (Full / Senior Prof (Large Lab), h=31) | Fit=4.9/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.2/10 | Keywords=point cloud registration | Paper=Nuclei-Location Based Point Set Registration of Multi-stained Whole Slide Images (2024)
+7. Mona Faraji Niri (Associate / Established PI (High Fit), h=22) | Fit=4.6/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=4.9/10 | Keywords=extended kalman filter, kalman filter | Paper=Accurate State of Charge Estimation in Lithium‐Ion Batteries by Second‐Order Sliding Mode Obser (2026)
+8. Valentina Donzella (Associate / Established PI (High Fit), h=12) | Fit=4.5/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=sensor fusion, deep learning, autonomous driving perception, object detection, semantic segmentation, autonomous vehicles | Paper=REHEARSE-3D: A Multi-Modal Emulated Rain Dataset for 3D Point Cloud De-Raining (2026)
+9. Roger Woodman (Assistant Prof / Rising Star (Responsive), h=16) | Fit=4.2/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.5/10 | Keywords=trajectory estimation, autonomous vehicles, object detection, 3d object detection | Paper=Optical Flow Based Detection and Tracking of Moving Objects for Autonomous Vehicles (2024)</t>
+        </is>
+      </c>
+      <c r="AE18" s="4" t="inlineStr">
+        <is>
+          <t>Hongkai Wen: No homepage/funding evidence available
+Ligang He: No homepage/funding evidence available
+Paul Jennings: No homepage/funding evidence available
+Matthew D. Higgins: No homepage/funding evidence available
+Kurt Debattista: No homepage/funding evidence available
+Shan E Ahmed Raza: No homepage/funding evidence available
+Mona Faraji Niri: No homepage/funding evidence available
+Valentina Donzella: No homepage/funding evidence available
+Roger Woodman: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Awarwick.ac.uk%20%22Hongkai%20Wen%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -2824,23 +3032,131 @@
           <t>University of Surrey</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=541)</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5044490167</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Richard Bowden</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>AFT-VO: Asynchronous Fusion Transformers for Multi-View Visual Odometry Estimation (2022)</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Guildford</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>@surrey.ac.uk</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>I28290843</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=52)</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>visual odometry, sensor fusion, pose estimation, kalman filter, deep learning, depth estimation</t>
+        </is>
+      </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="Z19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>7.35</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" s="4" t="inlineStr"/>
-      <c r="AE19" s="4" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Richard Bowden; Rahim Tafazolli; Yi Ma; Ferrante Neri; Simon Hadfield; Xiatian Zhu; Wenwu Wang; Chuan Heng Foh; Atta Ul Quddus; Philip J. B. Jackson; Mahmood Shafiee</t>
+        </is>
+      </c>
+      <c r="AD19" s="4" t="inlineStr">
+        <is>
+          <t>1. Richard Bowden (Full / Senior Prof (Large Lab), h=52) | Fit=8.8/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=7.5/10 | Keywords=visual odometry, sensor fusion, pose estimation, kalman filter, deep learning, depth estimation | Paper=AFT-VO: Asynchronous Fusion Transformers for Multi-View Visual Odometry Estimation (2022)
+2. Rahim Tafazolli (Full / Senior Prof (Large Lab), h=66) | Fit=9.0/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=7.5/10 | Keywords=visual odometry, pose estimation, depth estimation | Paper=Transformer-Based Self-Supervised Monocular Depth and Visual Odometry (2022)
+3. Yi Ma (Full / Senior Prof (Large Lab), h=22) | Fit=9.0/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=7.5/10 | Keywords=visual odometry, pose estimation, depth estimation | Paper=Transformer-Based Self-Supervised Monocular Depth and Visual Odometry (2022)
+4. Ferrante Neri (Full / Senior Prof (Large Lab), h=51) | Fit=8.1/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=7.1/10 | Keywords=lidar inertial odometry, autonomous navigation | Paper=Gravity-Constrained Simultaneous Localization and Mapping for suppressing map warping in comple (2025)
+5. Simon Hadfield (Associate / Established PI (High Fit), h=21) | Fit=7.7/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.0/10 | Keywords=sensor fusion, kalman filter, robot localization, gaussian splatting, depth estimation | Paper=TACO: Trajectory Aligning Cross-view Optimisation (2026)
+6. Xiatian Zhu (Full / Senior Prof (Large Lab), h=53) | Fit=4.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.9/10 | Keywords=3d perception, 3d reconstruction, gaussian splatting, 3d object detection, object detection | Paper=Foundational Models for 3D Point Clouds: A Survey and Outlook (2025)
+7. Wenwu Wang (Full / Senior Prof (Large Lab), h=44) | Fit=4.4/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.6/10 | Keywords=state estimation, deep learning, robot perception | Paper=Audio-Visual Speaker Tracking: Progress, Challenges, and Future Directions (2023)
+8. Chuan Heng Foh (Full / Senior Prof (Large Lab), h=37) | Fit=4.3/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=4.4/10 | Keywords=gnss positioning, autonomous vehicles | Paper=Using Real-Time Kinematics Algorithm in Mission Critical Communication for Accurate Positioning (2022)
+9. Atta Ul Quddus (Associate / Established PI (High Fit), h=18) | Fit=4.3/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=4.4/10 | Keywords=gnss positioning, autonomous vehicles | Paper=Using Real-Time Kinematics Algorithm in Mission Critical Communication for Accurate Positioning (2022)
+10. Philip J. B. Jackson (Full / Senior Prof (Large Lab), h=21) | Fit=4.0/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.4/10 | Keywords=state estimation, deep learning | Paper=Audio-Visual Speaker Tracking: Progress, Challenges, and Future Directions (2023)
+11. Mahmood Shafiee (Full / Senior Prof (Large Lab), h=40) | Fit=4.1/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.3/10 | Keywords=pose estimation, deep learning, computer vision | Paper=Augmented Reality (AR) for Surgical Robotic and Autonomous Systems: State of the Art, Challenge (2023)</t>
+        </is>
+      </c>
+      <c r="AE19" s="4" t="inlineStr">
+        <is>
+          <t>Richard Bowden: No homepage/funding evidence available
+Rahim Tafazolli: No homepage/funding evidence available
+Yi Ma: No homepage/funding evidence available
+Ferrante Neri: No homepage/funding evidence available
+Simon Hadfield: No homepage/funding evidence available
+Xiatian Zhu: No homepage/funding evidence available
+Wenwu Wang: No homepage/funding evidence available
+Chuan Heng Foh: No homepage/funding evidence available
+Atta Ul Quddus: No homepage/funding evidence available
+Philip J. B. Jackson: No homepage/funding evidence available
+Mahmood Shafiee: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asurrey.ac.uk%20%22Richard%20Bowden%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
@@ -2848,23 +3164,123 @@
           <t>University of Bath</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=650)</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5034122422</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Peter Wilson</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Underwater localization system for marine seismic airgun arrays validated through robotics (2025)</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>@bath.ac.uk</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>I51601045</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=26)</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>inertial navigation, sensor fusion, extended kalman filter, kalman filter, ros</t>
+        </is>
+      </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>7.66</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="Z20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="4" t="inlineStr"/>
-      <c r="AE20" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Peter Wilson; Philippe Blondel; Biagio Forte; Paul Kinsler; Michael Ying Yang; Wenbin Li; Yong‐Liang Yang</t>
+        </is>
+      </c>
+      <c r="AD20" s="4" t="inlineStr">
+        <is>
+          <t>1. Peter Wilson (Full / Senior Prof (Large Lab), h=26) | Fit=9.3/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=7.9/10 | Keywords=inertial navigation, sensor fusion, extended kalman filter, kalman filter, ros | Paper=Underwater localization system for marine seismic airgun arrays validated through robotics (2025)
+2. Philippe Blondel (Full / Senior Prof (Large Lab), h=26) | Fit=9.3/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=7.9/10 | Keywords=inertial navigation, sensor fusion, extended kalman filter, kalman filter, ros | Paper=Underwater localization system for marine seismic airgun arrays validated through robotics (2025)
+3. Biagio Forte (Associate / Established PI (High Fit), h=19) | Fit=7.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.6/10 | Keywords=gnss positioning | Paper=Ionospheric degradation of GNSS positioning quality: a discussion about causes, impact, and for (2026)
+4. Paul Kinsler (Full / Senior Prof (Large Lab), h=27) | Fit=7.0/10 | Activity=8.7/10 | Funding=0.0/10 | Overall=6.3/10 | Keywords=gnss positioning | Paper=Ionospheric degradation of GNSS positioning quality: a discussion about causes, impact, and for (2026)
+5. Michael Ying Yang (Full / Senior Prof (Large Lab), h=38) | Fit=5.7/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.7/10 | Keywords=sensor fusion, pose estimation, gaussian splatting | Paper=DVLO4D: Deep Visual-Lidar Odometry with Sparse Spatial-Temporal Fusion (2025)
+6. Wenbin Li (Associate / Established PI (High Fit), h=21) | Fit=5.3/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=5.2/10 | Keywords=visual localization, object detection, state estimation | Paper=Visual Perception System for Autonomous Driving (2024)
+7. Yong‐Liang Yang (Associate / Established PI (High Fit), h=25) | Fit=3.7/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.1/10 | Keywords=3d computer vision, deep learning, computer vision | Paper=A survey of deep learning-based 3D shape generation (2023)</t>
+        </is>
+      </c>
+      <c r="AE20" s="4" t="inlineStr">
+        <is>
+          <t>Peter Wilson: No homepage/funding evidence available
+Philippe Blondel: No homepage/funding evidence available
+Biagio Forte: No homepage/funding evidence available
+Paul Kinsler: No homepage/funding evidence available
+Michael Ying Yang: No homepage/funding evidence available
+Wenbin Li: No homepage/funding evidence available
+Yong‐Liang Yang: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abath.ac.uk%20%22Peter%20Wilson%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
@@ -2872,23 +3288,129 @@
           <t>Heriot-Watt University</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=383)</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5034972272</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Yvan Pétillot</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Tank dataset: An underwater multi-sensor dataset for SLAM evaluation (2025)</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>@hw.ac.uk</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>I32062511</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=44)</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>visual slam, multi-sensor fusion, sensor fusion, sensor calibration, 3d reconstruction, pose estimation</t>
+        </is>
+      </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>8.76</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Z21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="4" t="inlineStr"/>
-      <c r="AE21" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Yvan Pétillot; Xianwen Kong; Patricia Amancio Vargas; Wenda Li; Cheng Wang; Fernando Auat Cheein; Andrew Michael Wallace; Mustafa Suphi Erden; Carlos Mastalli; Stephen McLaughlin</t>
+        </is>
+      </c>
+      <c r="AD21" s="4" t="inlineStr">
+        <is>
+          <t>1. Yvan Pétillot (Full / Senior Prof (Large Lab), h=44) | Fit=10.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.5/10 | Keywords=visual slam, multi-sensor fusion, sensor fusion, sensor calibration, 3d reconstruction, pose estimation | Paper=Tank dataset: An underwater multi-sensor dataset for SLAM evaluation (2025)
+2. Xianwen Kong (Full / Senior Prof (Large Lab), h=39) | Fit=9.4/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=8.0/10 | Keywords=lidar slam, loop closure, pose estimation, computer vision | Paper=CURL-SLAM: Continuous and Compact LiDAR Mapping (2025)
+3. Patricia Amancio Vargas (Associate / Established PI (High Fit), h=20) | Fit=8.7/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=7.5/10 | Keywords=visual slam, robot localization, loop closure, pose estimation, computer vision | Paper=NeoSLAM: Long-Term SLAM Using Computational Models of the Brain (2024)
+4. Wenda Li (Associate / Established PI (High Fit), h=21) | Fit=8.1/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.2/10 | Keywords=multi-sensor fusion, sensor fusion | Paper=Multi-Sensor Fusion for Indoor Smartphone Localization with Attention Mechanism (2025)
+5. Cheng Wang (Associate / Established PI (High Fit), h=17) | Fit=7.5/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=6.8/10 | Keywords=multi-sensor fusion, sensor fusion | Paper=Multi-Sensor Fusion for Indoor Smartphone Localization with Attention Mechanism (2025)
+6. Fernando Auat Cheein (Full / Senior Prof (Large Lab), h=35) | Fit=5.3/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=5.2/10 | Keywords=autonomous navigation, ros, gnss positioning, deep learning, object detection, robot localization | Paper=Internet of robotic things with a local LoRa network for teleoperation of an agricultural mobil (2024)
+7. Andrew Michael Wallace (Full / Senior Prof (Large Lab), h=38) | Fit=5.2/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=5.2/10 | Keywords=visual localization, depth estimation | Paper=Estimating Fog Parameters from an Image Sequence using Non-linear Optimisation (2024)
+8. Mustafa Suphi Erden (Associate / Established PI (High Fit), h=24) | Fit=5.1/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.2/10 | Keywords=pose estimation, computer vision | Paper=Precision Robotic Assembly of Industrial Components with Robust Pose Estimation and Cooperative (2024)
+9. Carlos Mastalli (Associate / Established PI (High Fit), h=19) | Fit=4.5/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=robot localization, state estimation | Paper=Multi-Contact Inertial Parameters Estimation and Localization in Legged Robots (2025)
+10. Stephen McLaughlin (Full / Senior Prof (Large Lab), h=55) | Fit=3.9/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.2/10 | Keywords=depth estimation, 3d reconstruction | Paper=Efficient joint surface detection and depth estimation of single-photon Lidar data using assume (2022)</t>
+        </is>
+      </c>
+      <c r="AE21" s="4" t="inlineStr">
+        <is>
+          <t>Yvan Pétillot: No homepage/funding evidence available
+Xianwen Kong: No homepage/funding evidence available
+Patricia Amancio Vargas: No homepage/funding evidence available
+Wenda Li: No homepage/funding evidence available
+Cheng Wang: No homepage/funding evidence available
+Fernando Auat Cheein: No homepage/funding evidence available
+Andrew Michael Wallace: No homepage/funding evidence available
+Mustafa Suphi Erden: No homepage/funding evidence available
+Carlos Mastalli: No homepage/funding evidence available
+Stephen McLaughlin: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ahw.ac.uk%20%22Yvan%20P%C3%A9tillot%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="X22" t="n">
@@ -5381,7 +5903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z230"/>
+  <dimension ref="A1:Z276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -30047,8 +30569,4930 @@
         </is>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>University of Strathclyde</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=553)</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>@strath.ac.uk</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G231" t="n">
+        <v>1</v>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Hong Yue</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J231" t="n">
+        <v>23</v>
+      </c>
+      <c r="K231" t="n">
+        <v>2059</v>
+      </c>
+      <c r="L231" t="n">
+        <v>10</v>
+      </c>
+      <c r="M231" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N231" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O231" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>visual slam, visual odometry, autonomous navigation, computer vision, deep learning</t>
+        </is>
+      </c>
+      <c r="R231" t="n">
+        <v>2</v>
+      </c>
+      <c r="S231" t="n">
+        <v>29</v>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>Unmanned Aerial Vehicle Visual Simultaneous Localization and Mapping: A Survey</t>
+        </is>
+      </c>
+      <c r="V231" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W231" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Astrath.ac.uk%20%22Hong%20Yue%22%20email</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5059893133</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>University of Strathclyde</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=553)</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>@strath.ac.uk</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>2</v>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Erfu Yang</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J232" t="n">
+        <v>40</v>
+      </c>
+      <c r="K232" t="n">
+        <v>5584</v>
+      </c>
+      <c r="L232" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="M232" t="n">
+        <v>10</v>
+      </c>
+      <c r="N232" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O232" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>visual odometry, pose estimation, autonomous navigation, deep learning, multi-sensor fusion, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R232" t="n">
+        <v>6</v>
+      </c>
+      <c r="S232" t="n">
+        <v>65</v>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>A Robust Learned Feature-Based Visual Odometry System for UAV Pose Estimation in Challenging Indoor Environments</t>
+        </is>
+      </c>
+      <c r="V232" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W232" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Astrath.ac.uk%20%22Erfu%20Yang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5022264324</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>University of Strathclyde</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=553)</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>@strath.ac.uk</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G233" t="n">
+        <v>3</v>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Gaetano Di Caterina</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J233" t="n">
+        <v>19</v>
+      </c>
+      <c r="K233" t="n">
+        <v>1439</v>
+      </c>
+      <c r="L233" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="M233" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N233" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O233" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>visual inertial navigation, inertial navigation, visual inertial odometry</t>
+        </is>
+      </c>
+      <c r="R233" t="n">
+        <v>1</v>
+      </c>
+      <c r="S233" t="n">
+        <v>74</v>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>An Embedded Visual-Inertial Navigation System for Mobile Platforms Using an Event-Based Camera</t>
+        </is>
+      </c>
+      <c r="V233" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W233" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Astrath.ac.uk%20%22Gaetano%20Di%20Caterina%22%20email</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5009371598</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>University of Strathclyde</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=553)</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>@strath.ac.uk</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G234" t="n">
+        <v>4</v>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Ehsan Mohseni</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J234" t="n">
+        <v>18</v>
+      </c>
+      <c r="K234" t="n">
+        <v>908</v>
+      </c>
+      <c r="L234" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="M234" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N234" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O234" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>visual inertial navigation, inertial navigation, visual inertial odometry</t>
+        </is>
+      </c>
+      <c r="R234" t="n">
+        <v>1</v>
+      </c>
+      <c r="S234" t="n">
+        <v>56</v>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>An Embedded Visual-Inertial Navigation System for Mobile Platforms Using an Event-Based Camera</t>
+        </is>
+      </c>
+      <c r="V234" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W234" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Astrath.ac.uk%20%22Ehsan%20Mohseni%22%20email</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5071738695</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>University of Strathclyde</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=553)</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>@strath.ac.uk</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G235" t="n">
+        <v>5</v>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Ian K. Proudler</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J235" t="n">
+        <v>24</v>
+      </c>
+      <c r="K235" t="n">
+        <v>2199</v>
+      </c>
+      <c r="L235" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="M235" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N235" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O235" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, sensor fusion, kalman filter, state estimation</t>
+        </is>
+      </c>
+      <c r="R235" t="n">
+        <v>1</v>
+      </c>
+      <c r="S235" t="n">
+        <v>41</v>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>Adaptive Kernel Kalman Filter Multi-Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="V235" t="n">
+        <v>2021</v>
+      </c>
+      <c r="W235" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Astrath.ac.uk%20%22Ian%20K.%20Proudler%22%20email</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5000845191</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>University of Strathclyde</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=553)</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>@strath.ac.uk</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G236" t="n">
+        <v>6</v>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Gordon Dobie</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J236" t="n">
+        <v>23</v>
+      </c>
+      <c r="K236" t="n">
+        <v>1607</v>
+      </c>
+      <c r="L236" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="M236" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N236" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O236" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>state estimation</t>
+        </is>
+      </c>
+      <c r="R236" t="n">
+        <v>1</v>
+      </c>
+      <c r="S236" t="n">
+        <v>93</v>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>An adaptable framework for remotely controlling a telepresence robot in a dynamic environment</t>
+        </is>
+      </c>
+      <c r="V236" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W236" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Astrath.ac.uk%20%22Gordon%20Dobie%22%20email</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5084926427</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>University of Strathclyde</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=553)</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>@strath.ac.uk</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G237" t="n">
+        <v>7</v>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Malcolm Macdonald</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J237" t="n">
+        <v>27</v>
+      </c>
+      <c r="K237" t="n">
+        <v>2731</v>
+      </c>
+      <c r="L237" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="M237" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N237" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O237" t="n">
+        <v>5</v>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>extended kalman filter, kalman filter, autonomous navigation, fpga</t>
+        </is>
+      </c>
+      <c r="R237" t="n">
+        <v>3</v>
+      </c>
+      <c r="S237" t="n">
+        <v>43</v>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>Efficient Orbit Determination Using Measurement-Directional State Transition Tensor</t>
+        </is>
+      </c>
+      <c r="V237" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W237" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Astrath.ac.uk%20%22Malcolm%20Macdonald%22%20email</t>
+        </is>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5062321958</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>University of Strathclyde</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=553)</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>@strath.ac.uk</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G238" t="n">
+        <v>8</v>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Zhiming Yuan</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J238" t="n">
+        <v>39</v>
+      </c>
+      <c r="K238" t="n">
+        <v>4539</v>
+      </c>
+      <c r="L238" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="M238" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N238" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O238" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>extended kalman filter, kalman filter</t>
+        </is>
+      </c>
+      <c r="R238" t="n">
+        <v>1</v>
+      </c>
+      <c r="S238" t="n">
+        <v>121</v>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>2022-10-06</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>Time-optimal obstacle avoidance of autonomous ship based on nonlinear model predictive control</t>
+        </is>
+      </c>
+      <c r="V238" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W238" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Astrath.ac.uk%20%22Zhiming%20Yuan%22%20email</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5019879443</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>University of Strathclyde</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=553)</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>@strath.ac.uk</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>9</v>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Jaime Zabalza</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J239" t="n">
+        <v>25</v>
+      </c>
+      <c r="K239" t="n">
+        <v>2974</v>
+      </c>
+      <c r="L239" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="M239" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N239" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O239" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>autonomous navigation, fpga</t>
+        </is>
+      </c>
+      <c r="R239" t="n">
+        <v>1</v>
+      </c>
+      <c r="S239" t="n">
+        <v>43</v>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>A Review of Machine Learning in Embedded Space Systems: Challenges, Techniques, and Future Directions</t>
+        </is>
+      </c>
+      <c r="V239" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W239" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Astrath.ac.uk%20%22Jaime%20Zabalza%22%20email</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5043785449</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>University of Warwick</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=803)</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>@warwick.ac.uk</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G240" t="n">
+        <v>1</v>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Hongkai Wen</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J240" t="n">
+        <v>28</v>
+      </c>
+      <c r="K240" t="n">
+        <v>4195</v>
+      </c>
+      <c r="L240" t="n">
+        <v>10</v>
+      </c>
+      <c r="M240" t="n">
+        <v>10</v>
+      </c>
+      <c r="N240" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O240" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>visual odometry, pose estimation, mobile robot navigation</t>
+        </is>
+      </c>
+      <c r="R240" t="n">
+        <v>1</v>
+      </c>
+      <c r="S240" t="n">
+        <v>53</v>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>DeepEVO: Towards Robust Visual Odometry via Attention-Based Events and Video Fusion</t>
+        </is>
+      </c>
+      <c r="V240" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W240" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Awarwick.ac.uk%20%22Hongkai%20Wen%22%20email</t>
+        </is>
+      </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5053684989</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>University of Warwick</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=803)</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>@warwick.ac.uk</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G241" t="n">
+        <v>2</v>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Ligang He</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J241" t="n">
+        <v>28</v>
+      </c>
+      <c r="K241" t="n">
+        <v>2862</v>
+      </c>
+      <c r="L241" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="M241" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N241" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O241" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>point cloud registration, 3d computer vision, 3d reconstruction, computer vision</t>
+        </is>
+      </c>
+      <c r="R241" t="n">
+        <v>3</v>
+      </c>
+      <c r="S241" t="n">
+        <v>72</v>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>ACT‐Agent: Affinity‐Cross Transformer for Point Cloud Registration via Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="V241" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W241" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Awarwick.ac.uk%20%22Ligang%20He%22%20email</t>
+        </is>
+      </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5064596191</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>University of Warwick</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=803)</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>@warwick.ac.uk</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G242" t="n">
+        <v>3</v>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Paul Jennings</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J242" t="n">
+        <v>32</v>
+      </c>
+      <c r="K242" t="n">
+        <v>4021</v>
+      </c>
+      <c r="L242" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="M242" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N242" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O242" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>gnss positioning, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R242" t="n">
+        <v>1</v>
+      </c>
+      <c r="S242" t="n">
+        <v>52</v>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>A Study of Standalone GNSS Positioning Precision in Covered Agricultural Environments: ETFE Polytunnels Versus Glass Greenhouses</t>
+        </is>
+      </c>
+      <c r="V242" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W242" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Awarwick.ac.uk%20%22Paul%20Jennings%22%20email</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5076549005</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>University of Warwick</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=803)</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>@warwick.ac.uk</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G243" t="n">
+        <v>4</v>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Matthew D. Higgins</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J243" t="n">
+        <v>25</v>
+      </c>
+      <c r="K243" t="n">
+        <v>1831</v>
+      </c>
+      <c r="L243" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="M243" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N243" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O243" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>gnss positioning, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R243" t="n">
+        <v>1</v>
+      </c>
+      <c r="S243" t="n">
+        <v>43</v>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>A Study of Standalone GNSS Positioning Precision in Covered Agricultural Environments: ETFE Polytunnels Versus Glass Greenhouses</t>
+        </is>
+      </c>
+      <c r="V243" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W243" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Awarwick.ac.uk%20%22Matthew%20D.%20Higgins%22%20email</t>
+        </is>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5088016846</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>University of Warwick</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=803)</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>@warwick.ac.uk</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G244" t="n">
+        <v>5</v>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Kurt Debattista</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J244" t="n">
+        <v>32</v>
+      </c>
+      <c r="K244" t="n">
+        <v>4340</v>
+      </c>
+      <c r="L244" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="M244" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N244" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O244" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>visual localization, place recognition</t>
+        </is>
+      </c>
+      <c r="R244" t="n">
+        <v>1</v>
+      </c>
+      <c r="S244" t="n">
+        <v>82</v>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>2022-06-05</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>Recognising place under distinct weather variability, a comparison between end-to-end and metric learning approaches</t>
+        </is>
+      </c>
+      <c r="V244" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W244" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Awarwick.ac.uk%20%22Kurt%20Debattista%22%20email</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5087052285</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>University of Warwick</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=803)</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>@warwick.ac.uk</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G245" t="n">
+        <v>6</v>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Shan E Ahmed Raza</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J245" t="n">
+        <v>31</v>
+      </c>
+      <c r="K245" t="n">
+        <v>5891</v>
+      </c>
+      <c r="L245" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="M245" t="n">
+        <v>10</v>
+      </c>
+      <c r="N245" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O245" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>point cloud registration</t>
+        </is>
+      </c>
+      <c r="R245" t="n">
+        <v>2</v>
+      </c>
+      <c r="S245" t="n">
+        <v>132</v>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>Nuclei-Location Based Point Set Registration of Multi-stained Whole Slide Images</t>
+        </is>
+      </c>
+      <c r="V245" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W245" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Awarwick.ac.uk%20%22Shan%20E%20Ahmed%20Raza%22%20email</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5041645982</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>University of Warwick</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=803)</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>@warwick.ac.uk</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G246" t="n">
+        <v>7</v>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Mona Faraji Niri</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J246" t="n">
+        <v>22</v>
+      </c>
+      <c r="K246" t="n">
+        <v>1438</v>
+      </c>
+      <c r="L246" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="M246" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N246" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O246" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>extended kalman filter, kalman filter</t>
+        </is>
+      </c>
+      <c r="R246" t="n">
+        <v>1</v>
+      </c>
+      <c r="S246" t="n">
+        <v>73</v>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>Accurate State of Charge Estimation in Lithium‐Ion Batteries by Second‐Order Sliding Mode Observer</t>
+        </is>
+      </c>
+      <c r="V246" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W246" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Awarwick.ac.uk%20%22Mona%20Faraji%20Niri%22%20email</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5067942735</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>University of Warwick</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=803)</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>@warwick.ac.uk</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G247" t="n">
+        <v>8</v>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Valentina Donzella</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J247" t="n">
+        <v>12</v>
+      </c>
+      <c r="K247" t="n">
+        <v>805</v>
+      </c>
+      <c r="L247" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="M247" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N247" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O247" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>sensor fusion, deep learning, autonomous driving perception, object detection, semantic segmentation, autonomous vehicles</t>
+        </is>
+      </c>
+      <c r="R247" t="n">
+        <v>4</v>
+      </c>
+      <c r="S247" t="n">
+        <v>65</v>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>REHEARSE-3D: A Multi-Modal Emulated Rain Dataset for 3D Point Cloud De-Raining</t>
+        </is>
+      </c>
+      <c r="V247" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W247" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Awarwick.ac.uk%20%22Valentina%20Donzella%22%20email</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5032382943</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>University of Warwick</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=803)</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>@warwick.ac.uk</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G248" t="n">
+        <v>9</v>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Roger Woodman</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J248" t="n">
+        <v>16</v>
+      </c>
+      <c r="K248" t="n">
+        <v>913</v>
+      </c>
+      <c r="L248" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="M248" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N248" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O248" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>trajectory estimation, autonomous vehicles, object detection, 3d object detection</t>
+        </is>
+      </c>
+      <c r="R248" t="n">
+        <v>3</v>
+      </c>
+      <c r="S248" t="n">
+        <v>45</v>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>Optical Flow Based Detection and Tracking of Moving Objects for Autonomous Vehicles</t>
+        </is>
+      </c>
+      <c r="V248" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W248" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Awarwick.ac.uk%20%22Roger%20Woodman%22%20email</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5005161674</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>University of Surrey</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Guildford</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=541)</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>@surrey.ac.uk</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G249" t="n">
+        <v>1</v>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Richard Bowden</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J249" t="n">
+        <v>52</v>
+      </c>
+      <c r="K249" t="n">
+        <v>14446</v>
+      </c>
+      <c r="L249" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="M249" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N249" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O249" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>visual odometry, sensor fusion, pose estimation, kalman filter, deep learning, depth estimation</t>
+        </is>
+      </c>
+      <c r="R249" t="n">
+        <v>4</v>
+      </c>
+      <c r="S249" t="n">
+        <v>107</v>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>AFT-VO: Asynchronous Fusion Transformers for Multi-View Visual Odometry Estimation</t>
+        </is>
+      </c>
+      <c r="V249" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W249" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asurrey.ac.uk%20%22Richard%20Bowden%22%20email</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5044490167</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>University of Surrey</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Guildford</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=541)</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>@surrey.ac.uk</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G250" t="n">
+        <v>2</v>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Rahim Tafazolli</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J250" t="n">
+        <v>66</v>
+      </c>
+      <c r="K250" t="n">
+        <v>21711</v>
+      </c>
+      <c r="L250" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="M250" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N250" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O250" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>visual odometry, pose estimation, depth estimation</t>
+        </is>
+      </c>
+      <c r="R250" t="n">
+        <v>1</v>
+      </c>
+      <c r="S250" t="n">
+        <v>353</v>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>2022-12-09</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>Transformer-Based Self-Supervised Monocular Depth and Visual Odometry</t>
+        </is>
+      </c>
+      <c r="V250" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W250" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asurrey.ac.uk%20%22Rahim%20Tafazolli%22%20email</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5032549075</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>University of Surrey</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Guildford</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=541)</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>@surrey.ac.uk</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G251" t="n">
+        <v>3</v>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Yi Ma</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J251" t="n">
+        <v>22</v>
+      </c>
+      <c r="K251" t="n">
+        <v>1646</v>
+      </c>
+      <c r="L251" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="M251" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N251" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O251" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>visual odometry, pose estimation, depth estimation</t>
+        </is>
+      </c>
+      <c r="R251" t="n">
+        <v>1</v>
+      </c>
+      <c r="S251" t="n">
+        <v>70</v>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>2022-12-09</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>Transformer-Based Self-Supervised Monocular Depth and Visual Odometry</t>
+        </is>
+      </c>
+      <c r="V251" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W251" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asurrey.ac.uk%20%22Yi%20Ma%22%20email</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5063447722</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>University of Surrey</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Guildford</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=541)</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>@surrey.ac.uk</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G252" t="n">
+        <v>4</v>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Ferrante Neri</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J252" t="n">
+        <v>51</v>
+      </c>
+      <c r="K252" t="n">
+        <v>9749</v>
+      </c>
+      <c r="L252" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="M252" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N252" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O252" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>lidar inertial odometry, autonomous navigation</t>
+        </is>
+      </c>
+      <c r="R252" t="n">
+        <v>1</v>
+      </c>
+      <c r="S252" t="n">
+        <v>121</v>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>Gravity-Constrained Simultaneous Localization and Mapping for suppressing map warping in complex large-scale environments</t>
+        </is>
+      </c>
+      <c r="V252" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W252" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asurrey.ac.uk%20%22Ferrante%20Neri%22%20email</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5063214931</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>University of Surrey</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Guildford</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=541)</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>@surrey.ac.uk</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G253" t="n">
+        <v>5</v>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Simon Hadfield</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J253" t="n">
+        <v>21</v>
+      </c>
+      <c r="K253" t="n">
+        <v>5151</v>
+      </c>
+      <c r="L253" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="M253" t="n">
+        <v>10</v>
+      </c>
+      <c r="N253" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O253" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>sensor fusion, kalman filter, robot localization, gaussian splatting, depth estimation</t>
+        </is>
+      </c>
+      <c r="R253" t="n">
+        <v>6</v>
+      </c>
+      <c r="S253" t="n">
+        <v>60</v>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>TACO: Trajectory Aligning Cross-view Optimisation</t>
+        </is>
+      </c>
+      <c r="V253" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W253" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asurrey.ac.uk%20%22Simon%20Hadfield%22%20email</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5091184063</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>University of Surrey</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Guildford</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=541)</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>@surrey.ac.uk</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G254" t="n">
+        <v>6</v>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Xiatian Zhu</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J254" t="n">
+        <v>53</v>
+      </c>
+      <c r="K254" t="n">
+        <v>16911</v>
+      </c>
+      <c r="L254" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="M254" t="n">
+        <v>10</v>
+      </c>
+      <c r="N254" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O254" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>Deep Learning for Navigation &amp; Perception; 3D Computer Vision &amp; Geometric Perception; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>3d perception, 3d reconstruction, gaussian splatting, 3d object detection, object detection</t>
+        </is>
+      </c>
+      <c r="R254" t="n">
+        <v>4</v>
+      </c>
+      <c r="S254" t="n">
+        <v>153</v>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>Foundational Models for 3D Point Clouds: A Survey and Outlook</t>
+        </is>
+      </c>
+      <c r="V254" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W254" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asurrey.ac.uk%20%22Xiatian%20Zhu%22%20email</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5028643592</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>University of Surrey</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Guildford</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=541)</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>@surrey.ac.uk</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G255" t="n">
+        <v>7</v>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Wenwu Wang</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J255" t="n">
+        <v>44</v>
+      </c>
+      <c r="K255" t="n">
+        <v>9131</v>
+      </c>
+      <c r="L255" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="M255" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N255" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O255" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>state estimation, deep learning, robot perception</t>
+        </is>
+      </c>
+      <c r="R255" t="n">
+        <v>2</v>
+      </c>
+      <c r="S255" t="n">
+        <v>252</v>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>Audio-Visual Speaker Tracking: Progress, Challenges, and Future Directions</t>
+        </is>
+      </c>
+      <c r="V255" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W255" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asurrey.ac.uk%20%22Wenwu%20Wang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100676721</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>University of Surrey</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Guildford</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=541)</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>@surrey.ac.uk</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G256" t="n">
+        <v>8</v>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Chuan Heng Foh</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J256" t="n">
+        <v>37</v>
+      </c>
+      <c r="K256" t="n">
+        <v>6227</v>
+      </c>
+      <c r="L256" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="M256" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N256" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O256" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>gnss positioning, autonomous vehicles</t>
+        </is>
+      </c>
+      <c r="R256" t="n">
+        <v>1</v>
+      </c>
+      <c r="S256" t="n">
+        <v>88</v>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>2022-06-01</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>Using Real-Time Kinematics Algorithm in Mission Critical Communication for Accurate Positioning and Time Correction over 5G and Beyond Networks</t>
+        </is>
+      </c>
+      <c r="V256" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W256" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asurrey.ac.uk%20%22Chuan%20Heng%20Foh%22%20email</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5073704569</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>University of Surrey</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Guildford</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=541)</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>@surrey.ac.uk</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G257" t="n">
+        <v>9</v>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Atta Ul Quddus</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J257" t="n">
+        <v>18</v>
+      </c>
+      <c r="K257" t="n">
+        <v>1814</v>
+      </c>
+      <c r="L257" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="M257" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N257" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O257" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>gnss positioning, autonomous vehicles</t>
+        </is>
+      </c>
+      <c r="R257" t="n">
+        <v>1</v>
+      </c>
+      <c r="S257" t="n">
+        <v>20</v>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>2022-06-01</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>Using Real-Time Kinematics Algorithm in Mission Critical Communication for Accurate Positioning and Time Correction over 5G and Beyond Networks</t>
+        </is>
+      </c>
+      <c r="V257" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W257" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asurrey.ac.uk%20%22Atta%20Ul%20Quddus%22%20email</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5112180290</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>University of Surrey</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Guildford</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=541)</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>@surrey.ac.uk</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G258" t="n">
+        <v>10</v>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Philip J. B. Jackson</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J258" t="n">
+        <v>21</v>
+      </c>
+      <c r="K258" t="n">
+        <v>2097</v>
+      </c>
+      <c r="L258" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="M258" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N258" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O258" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>state estimation, deep learning</t>
+        </is>
+      </c>
+      <c r="R258" t="n">
+        <v>1</v>
+      </c>
+      <c r="S258" t="n">
+        <v>31</v>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>Audio-Visual Speaker Tracking: Progress, Challenges, and Future Directions</t>
+        </is>
+      </c>
+      <c r="V258" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W258" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asurrey.ac.uk%20%22Philip%20J.%20B.%20Jackson%22%20email</t>
+        </is>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5022165330</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>University of Surrey</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Guildford</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=541)</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>@surrey.ac.uk</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G259" t="n">
+        <v>11</v>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Mahmood Shafiee</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J259" t="n">
+        <v>40</v>
+      </c>
+      <c r="K259" t="n">
+        <v>4273</v>
+      </c>
+      <c r="L259" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="M259" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N259" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O259" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>pose estimation, deep learning, computer vision</t>
+        </is>
+      </c>
+      <c r="R259" t="n">
+        <v>1</v>
+      </c>
+      <c r="S259" t="n">
+        <v>45</v>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>Augmented Reality (AR) for Surgical Robotic and Autonomous Systems: State of the Art, Challenges, and Solutions</t>
+        </is>
+      </c>
+      <c r="V259" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W259" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Asurrey.ac.uk%20%22Mahmood%20Shafiee%22%20email</t>
+        </is>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5051005684</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>University of Bath</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=650)</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>@bath.ac.uk</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G260" t="n">
+        <v>1</v>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Peter Wilson</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J260" t="n">
+        <v>26</v>
+      </c>
+      <c r="K260" t="n">
+        <v>2617</v>
+      </c>
+      <c r="L260" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="M260" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N260" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O260" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; State Estimation &amp; Factor Graphs; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>inertial navigation, sensor fusion, extended kalman filter, kalman filter, ros</t>
+        </is>
+      </c>
+      <c r="R260" t="n">
+        <v>1</v>
+      </c>
+      <c r="S260" t="n">
+        <v>23</v>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>Underwater localization system for marine seismic airgun arrays validated through robotics</t>
+        </is>
+      </c>
+      <c r="V260" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W260" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abath.ac.uk%20%22Peter%20Wilson%22%20email</t>
+        </is>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5034122422</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>University of Bath</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=650)</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>@bath.ac.uk</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G261" t="n">
+        <v>2</v>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Philippe Blondel</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J261" t="n">
+        <v>26</v>
+      </c>
+      <c r="K261" t="n">
+        <v>3080</v>
+      </c>
+      <c r="L261" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="M261" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N261" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O261" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; State Estimation &amp; Factor Graphs; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>inertial navigation, sensor fusion, extended kalman filter, kalman filter, ros</t>
+        </is>
+      </c>
+      <c r="R261" t="n">
+        <v>1</v>
+      </c>
+      <c r="S261" t="n">
+        <v>32</v>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>Underwater localization system for marine seismic airgun arrays validated through robotics</t>
+        </is>
+      </c>
+      <c r="V261" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W261" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abath.ac.uk%20%22Philippe%20Blondel%22%20email</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5086086006</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>University of Bath</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=650)</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>@bath.ac.uk</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>3</v>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Biagio Forte</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J262" t="n">
+        <v>19</v>
+      </c>
+      <c r="K262" t="n">
+        <v>1170</v>
+      </c>
+      <c r="L262" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="M262" t="n">
+        <v>10</v>
+      </c>
+      <c r="N262" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O262" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>gnss positioning</t>
+        </is>
+      </c>
+      <c r="R262" t="n">
+        <v>3</v>
+      </c>
+      <c r="S262" t="n">
+        <v>59</v>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>Ionospheric degradation of GNSS positioning quality: a discussion about causes, impact, and forecast</t>
+        </is>
+      </c>
+      <c r="V262" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W262" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abath.ac.uk%20%22Biagio%20Forte%22%20email</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5005402943</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>University of Bath</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=650)</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>@bath.ac.uk</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>4</v>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Paul Kinsler</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J263" t="n">
+        <v>27</v>
+      </c>
+      <c r="K263" t="n">
+        <v>2289</v>
+      </c>
+      <c r="L263" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="M263" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="N263" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O263" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>gnss positioning</t>
+        </is>
+      </c>
+      <c r="R263" t="n">
+        <v>2</v>
+      </c>
+      <c r="S263" t="n">
+        <v>9</v>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>Ionospheric degradation of GNSS positioning quality: a discussion about causes, impact, and forecast</t>
+        </is>
+      </c>
+      <c r="V263" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W263" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abath.ac.uk%20%22Paul%20Kinsler%22%20email</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5001631494</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>University of Bath</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=650)</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>@bath.ac.uk</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>5</v>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Michael Ying Yang</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J264" t="n">
+        <v>38</v>
+      </c>
+      <c r="K264" t="n">
+        <v>6573</v>
+      </c>
+      <c r="L264" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="M264" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N264" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O264" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>sensor fusion, pose estimation, gaussian splatting</t>
+        </is>
+      </c>
+      <c r="R264" t="n">
+        <v>3</v>
+      </c>
+      <c r="S264" t="n">
+        <v>108</v>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>DVLO4D: Deep Visual-Lidar Odometry with Sparse Spatial-Temporal Fusion</t>
+        </is>
+      </c>
+      <c r="V264" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W264" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abath.ac.uk%20%22Michael%20Ying%20Yang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5014321482</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>University of Bath</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=650)</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>@bath.ac.uk</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>6</v>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Wenbin Li</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J265" t="n">
+        <v>21</v>
+      </c>
+      <c r="K265" t="n">
+        <v>2094</v>
+      </c>
+      <c r="L265" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="M265" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N265" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O265" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Robotics &amp; Autonomous Navigation; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>visual localization, object detection, state estimation</t>
+        </is>
+      </c>
+      <c r="R265" t="n">
+        <v>3</v>
+      </c>
+      <c r="S265" t="n">
+        <v>47</v>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>Visual Perception System for Autonomous Driving</t>
+        </is>
+      </c>
+      <c r="V265" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W265" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abath.ac.uk%20%22Wenbin%20Li%22%20email</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100463006</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>University of Bath</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=650)</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>@bath.ac.uk</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>7</v>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Yong‐Liang Yang</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J266" t="n">
+        <v>25</v>
+      </c>
+      <c r="K266" t="n">
+        <v>2243</v>
+      </c>
+      <c r="L266" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="M266" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N266" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O266" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>3d computer vision, deep learning, computer vision</t>
+        </is>
+      </c>
+      <c r="R266" t="n">
+        <v>1</v>
+      </c>
+      <c r="S266" t="n">
+        <v>43</v>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>2023-05-17</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>A survey of deep learning-based 3D shape generation</t>
+        </is>
+      </c>
+      <c r="V266" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W266" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abath.ac.uk%20%22Yong%E2%80%90Liang%20Yang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5101763421</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Heriot-Watt University</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=383)</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>@hw.ac.uk</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>1</v>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Yvan Pétillot</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J267" t="n">
+        <v>44</v>
+      </c>
+      <c r="K267" t="n">
+        <v>7324</v>
+      </c>
+      <c r="L267" t="n">
+        <v>10</v>
+      </c>
+      <c r="M267" t="n">
+        <v>10</v>
+      </c>
+      <c r="N267" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O267" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>visual slam, multi-sensor fusion, sensor fusion, sensor calibration, 3d reconstruction, pose estimation</t>
+        </is>
+      </c>
+      <c r="R267" t="n">
+        <v>5</v>
+      </c>
+      <c r="S267" t="n">
+        <v>77</v>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>Tank dataset: An underwater multi-sensor dataset for SLAM evaluation</t>
+        </is>
+      </c>
+      <c r="V267" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W267" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ahw.ac.uk%20%22Yvan%20P%C3%A9tillot%22%20email</t>
+        </is>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5034972272</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Heriot-Watt University</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=383)</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>@hw.ac.uk</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>2</v>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Xianwen Kong</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J268" t="n">
+        <v>39</v>
+      </c>
+      <c r="K268" t="n">
+        <v>5382</v>
+      </c>
+      <c r="L268" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="M268" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N268" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O268" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; State Estimation &amp; Factor Graphs; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>lidar slam, loop closure, pose estimation, computer vision</t>
+        </is>
+      </c>
+      <c r="R268" t="n">
+        <v>4</v>
+      </c>
+      <c r="S268" t="n">
+        <v>42</v>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>CURL-SLAM: Continuous and Compact LiDAR Mapping</t>
+        </is>
+      </c>
+      <c r="V268" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W268" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X268" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ahw.ac.uk%20%22Xianwen%20Kong%22%20email</t>
+        </is>
+      </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5022962081</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Heriot-Watt University</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=383)</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>@hw.ac.uk</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>3</v>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Patricia Amancio Vargas</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J269" t="n">
+        <v>20</v>
+      </c>
+      <c r="K269" t="n">
+        <v>1752</v>
+      </c>
+      <c r="L269" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="M269" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N269" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O269" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; State Estimation &amp; Factor Graphs; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>visual slam, robot localization, loop closure, pose estimation, computer vision</t>
+        </is>
+      </c>
+      <c r="R269" t="n">
+        <v>3</v>
+      </c>
+      <c r="S269" t="n">
+        <v>21</v>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>NeoSLAM: Long-Term SLAM Using Computational Models of the Brain</t>
+        </is>
+      </c>
+      <c r="V269" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W269" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ahw.ac.uk%20%22Patricia%20Amancio%20Vargas%22%20email</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5090575787</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Heriot-Watt University</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=383)</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>@hw.ac.uk</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>4</v>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Wenda Li</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J270" t="n">
+        <v>21</v>
+      </c>
+      <c r="K270" t="n">
+        <v>1666</v>
+      </c>
+      <c r="L270" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="M270" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N270" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O270" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R270" t="n">
+        <v>1</v>
+      </c>
+      <c r="S270" t="n">
+        <v>108</v>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>Multi-Sensor Fusion for Indoor Smartphone Localization with Attention Mechanism</t>
+        </is>
+      </c>
+      <c r="V270" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W270" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ahw.ac.uk%20%22Wenda%20Li%22%20email</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100761698</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Heriot-Watt University</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=383)</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>@hw.ac.uk</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>5</v>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Cheng Wang</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J271" t="n">
+        <v>17</v>
+      </c>
+      <c r="K271" t="n">
+        <v>2106</v>
+      </c>
+      <c r="L271" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="M271" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N271" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O271" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Deep Learning for Navigation &amp; Perception</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R271" t="n">
+        <v>2</v>
+      </c>
+      <c r="S271" t="n">
+        <v>59</v>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>Multi-Sensor Fusion for Indoor Smartphone Localization with Attention Mechanism</t>
+        </is>
+      </c>
+      <c r="V271" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W271" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ahw.ac.uk%20%22Cheng%20Wang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100417008</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Heriot-Watt University</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=383)</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>@hw.ac.uk</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>6</v>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Fernando Auat Cheein</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J272" t="n">
+        <v>35</v>
+      </c>
+      <c r="K272" t="n">
+        <v>5141</v>
+      </c>
+      <c r="L272" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="M272" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N272" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O272" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>autonomous navigation, ros, gnss positioning, deep learning, object detection, robot localization</t>
+        </is>
+      </c>
+      <c r="R272" t="n">
+        <v>3</v>
+      </c>
+      <c r="S272" t="n">
+        <v>126</v>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>Internet of robotic things with a local LoRa network for teleoperation of an agricultural mobile robot using a digital shadow</t>
+        </is>
+      </c>
+      <c r="V272" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W272" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ahw.ac.uk%20%22Fernando%20Auat%20Cheein%22%20email</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5061931953</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Heriot-Watt University</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=383)</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>@hw.ac.uk</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>7</v>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Andrew Michael Wallace</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J273" t="n">
+        <v>38</v>
+      </c>
+      <c r="K273" t="n">
+        <v>6328</v>
+      </c>
+      <c r="L273" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="M273" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N273" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O273" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>visual localization, depth estimation</t>
+        </is>
+      </c>
+      <c r="R273" t="n">
+        <v>1</v>
+      </c>
+      <c r="S273" t="n">
+        <v>21</v>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>Estimating Fog Parameters from an Image Sequence using Non-linear Optimisation</t>
+        </is>
+      </c>
+      <c r="V273" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W273" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ahw.ac.uk%20%22Andrew%20Michael%20Wallace%22%20email</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5012904339</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Heriot-Watt University</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=383)</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>@hw.ac.uk</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G274" t="n">
+        <v>8</v>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Mustafa Suphi Erden</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J274" t="n">
+        <v>24</v>
+      </c>
+      <c r="K274" t="n">
+        <v>2291</v>
+      </c>
+      <c r="L274" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="M274" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N274" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O274" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>pose estimation, computer vision</t>
+        </is>
+      </c>
+      <c r="R274" t="n">
+        <v>2</v>
+      </c>
+      <c r="S274" t="n">
+        <v>68</v>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>Precision Robotic Assembly of Industrial Components with Robust Pose Estimation and Cooperative Manipulation</t>
+        </is>
+      </c>
+      <c r="V274" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W274" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ahw.ac.uk%20%22Mustafa%20Suphi%20Erden%22%20email</t>
+        </is>
+      </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5090243306</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Heriot-Watt University</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=383)</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>@hw.ac.uk</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G275" t="n">
+        <v>9</v>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Carlos Mastalli</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J275" t="n">
+        <v>19</v>
+      </c>
+      <c r="K275" t="n">
+        <v>1279</v>
+      </c>
+      <c r="L275" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="M275" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N275" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O275" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>robot localization, state estimation</t>
+        </is>
+      </c>
+      <c r="R275" t="n">
+        <v>2</v>
+      </c>
+      <c r="S275" t="n">
+        <v>22</v>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>Multi-Contact Inertial Parameters Estimation and Localization in Legged Robots</t>
+        </is>
+      </c>
+      <c r="V275" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W275" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ahw.ac.uk%20%22Carlos%20Mastalli%22%20email</t>
+        </is>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5032652050</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Heriot-Watt University</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=383)</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>@hw.ac.uk</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G276" t="n">
+        <v>10</v>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Stephen McLaughlin</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J276" t="n">
+        <v>55</v>
+      </c>
+      <c r="K276" t="n">
+        <v>16444</v>
+      </c>
+      <c r="L276" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="M276" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N276" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O276" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>depth estimation, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R276" t="n">
+        <v>4</v>
+      </c>
+      <c r="S276" t="n">
+        <v>80</v>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>Efficient joint surface detection and depth estimation of single-photon Lidar data using assumed density filtering</t>
+        </is>
+      </c>
+      <c r="V276" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W276" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ahw.ac.uk%20%22Stephen%20McLaughlin%22%20email</t>
+        </is>
+      </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5010538525</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z230"/>
+  <autoFilter ref="A1:Z276"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AG$127</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Z$276</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Z$352</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,9 +475,9 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="35" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
     <col width="42" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
     <col width="25" customWidth="1" min="21" max="21"/>
@@ -3437,23 +3437,155 @@
           <t>Technical University of Munich</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5087710605</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Daniel Cremers</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>VOCA: Visual Odometry with Codec Awareness (2026)</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>I62916508</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=102)</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>visual odometry, pose estimation, depth estimation, autonomous navigation, object detection, visual slam</t>
+        </is>
+      </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="Z23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>8.43</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="4" t="inlineStr"/>
-      <c r="AE23" s="4" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Daniel Cremers; Eckehard G. Steinbach; Stefan Leutenegger; Johannes Betz; Alois Knoll; Federico Tombari; Angela P. Schoellig; Gerhard Rigoll; Gan‐Lin Zhang; Xi Wang; Markus Lienkamp; Matthias Althoff; Achim J. Lilienthal; Nassir Navab; Laura Leal-Taixé; Daniel Roth; Rüdiger Daub; Benjamin Busam; B. Jutzi; Christoph Holst; Timo Oksanen; Michael F. Schmidt; Slobodan Ilić</t>
+        </is>
+      </c>
+      <c r="AD23" s="4" t="inlineStr">
+        <is>
+          <t>1. Daniel Cremers (Full / Senior Prof (Large Lab), h=102) | Fit=10.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.5/10 | Keywords=visual odometry, pose estimation, depth estimation, autonomous navigation, object detection, visual slam | Paper=VOCA: Visual Odometry with Codec Awareness (2026)
+2. Eckehard G. Steinbach (Full / Senior Prof (Large Lab), h=48) | Fit=10.0/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.4/10 | Keywords=visual-inertial slam, deep learning, visual slam, visual odometry, pose estimation, loop closure | Paper=AFDI-SLAM: Visual-Inertial SLAM With Adaptive Frame Control and Deep-Learning-Based IMU Signal  (2026)
+3. Stefan Leutenegger (Full / Senior Prof (Large Lab), h=40) | Fit=10.0/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.4/10 | Keywords=visual-inertial slam, autonomous navigation, loop closure, factor graph optimization, state estimation, sensor fusion | Paper=Scalable Outdoors Autonomous Drone Flight with Visual-Inertial SLAM and Dense Submaps Built wit (2025)
+4. Johannes Betz (Associate / Established PI (High Fit), h=26) | Fit=10.0/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.4/10 | Keywords=visual slam, gaussian splatting, 3d reconstruction, visual inertial navigation, inertial navigation, pose estimation | Paper=RoGER-SLAM: A Robust Gaussian Splatting SLAM System for Noisy and Low-Light Environment Resilie (2026)
+5. Alois Knoll (Full / Senior Prof (Large Lab), h=68) | Fit=9.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.4/10 | Keywords=gaussian splatting, pose estimation, 3d reconstruction, visual odometry, kalman filter, robot perception | Paper=MGS-Track: Monocular 6DoF Pose Tracking via Masked 3D Prior and Online Gaussian Splatting (2026)
+6. Federico Tombari (Full / Senior Prof (Large Lab), h=66) | Fit=9.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.3/10 | Keywords=visual odometry, pose estimation, factor graph optimization, computer vision, visual localization, 3d computer vision | Paper=E-Graph: Minimal Solution for Rigid Rotation with Extensibility Graphs (2022)
+7. Angela P. Schoellig (Full / Senior Prof (Large Lab), h=44) | Fit=9.7/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.3/10 | Keywords=pose estimation, multi-sensor fusion, sensor fusion, trajectory estimation, lidar inertial odometry, state estimation | Paper=Continuous-Time Range-Only Pose Estimation (2023)
+8. Gerhard Rigoll (Full / Senior Prof (Large Lab), h=59) | Fit=9.8/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.3/10 | Keywords=visual slam, gaussian splatting, 3d reconstruction | Paper=RoGER-SLAM: A Robust Gaussian Splatting SLAM System for Noisy and Low-Light Environment Resilie (2026)
+9. Gan‐Lin Zhang (Full / Senior Prof (Large Lab), h=56) | Fit=9.7/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.2/10 | Keywords=visual slam, loop closure, pose estimation, 3d reconstruction | Paper=ViSTA-SLAM: Visual SLAM with Symmetric Two-View Association (2026)
+10. Xi Wang (Full / Senior Prof (Large Lab), h=18) | Fit=9.7/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.2/10 | Keywords=visual slam, loop closure, pose estimation, 3d reconstruction | Paper=ViSTA-SLAM: Visual SLAM with Symmetric Two-View Association (2026)
+11. Markus Lienkamp (Full / Senior Prof (Large Lab), h=44) | Fit=8.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=lidar inertial odometry, extended kalman filter, kalman filter, cuda, pose estimation, object detection | Paper=FAR-LIO: Enabling High-Speed Autonomy through Fast, Accurate, and Robust LiDAR-Inertial Odometr (2026)
+12. Matthias Althoff (Full / Senior Prof (Large Lab), h=54) | Fit=8.6/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.5/10 | Keywords=point cloud registration, pose estimation, autonomous driving perception, visual localization | Paper=Offline Object Tracking With Joint Point Cloud Registration (2024)
+13. Achim J. Lilienthal (Full / Senior Prof (Large Lab), h=51) | Fit=8.6/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.5/10 | Keywords=loop closure, trajectory estimation, mobile robot navigation, point cloud registration, autonomous navigation, robot localization | Paper=Introspective Loop Closure for SLAM with 4D Imaging Radar (2025)
+14. Nassir Navab (Full / Senior Prof (Large Lab), h=108) | Fit=7.2/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.7/10 | Keywords=pose estimation, 3d computer vision, 3d reconstruction, computer vision, trajectory estimation, semantic segmentation | Paper=ESCAPE: Equivariant Shape Completion via Anchor Point Encoding (2025)
+15. Laura Leal-Taixé (Full / Senior Prof (Large Lab), h=43) | Fit=7.4/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=6.5/10 | Keywords=visual localization, visual odometry, 3d object detection, object detection | Paper=Is Geometry Enough for Matching in Visual Localization? (2022)
+16. Daniel Roth (Associate / Established PI (High Fit), h=26) | Fit=6.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.4/10 | Keywords=gaussian splatting, robot perception, pose estimation, trajectory estimation, semantic segmentation, 3d computer vision | Paper=SplatXtRact: Tractable Gaussian Splatting via Open World Region-of-Interest Extraction and Refi (2026)
+17. Rüdiger Daub (Full / Senior Prof (Large Lab), h=22) | Fit=7.1/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.4/10 | Keywords=learning-based localization, deep learning, robot perception | Paper=Deep learning-based localization of electrical connector sockets for automated mating (2024)
+18. Benjamin Busam (Associate / Established PI (High Fit), h=27) | Fit=6.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.4/10 | Keywords=pose estimation, 3d computer vision, computer vision, trajectory estimation, semantic segmentation, point cloud registration | Paper=Zero123-6D: Zero-shot Novel View Synthesis for RGB Category-level 6D Pose Estimation (2024)
+19. B. Jutzi (Full / Senior Prof (Large Lab), h=24) | Fit=6.7/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=6.3/10 | Keywords=visual localization, pose estimation, deep learning, computer vision, gaussian splatting, semantic segmentation | Paper=To Glue or Not to Glue? Classical vs Learned Image Matching for Mobile Mapping Cameras to Textu (2025)
+20. Christoph Holst (Associate / Established PI (High Fit), h=18) | Fit=6.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.9/10 | Keywords=point cloud registration, loop closure, visual slam, deep learning | Paper=Keypoint-based registration of TLS point clouds using a statistical matching approach (2023)
+21. Timo Oksanen (Associate / Established PI (High Fit), h=22) | Fit=6.1/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.8/10 | Keywords=visual odometry, 3d reconstruction, gnss positioning, object detection | Paper=Novel Dataset of RGB-D Images for Robotic Harvesting of Green Asparagus (2025)
+22. Michael F. Schmidt (Full / Senior Prof (Large Lab), h=45) | Fit=6.0/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=5.6/10 | Keywords=gnss positioning | Paper=Ongoing strategies for assessing VTEC maps performance over a low latitude region (2023)
+23. Slobodan Ilić (Full / Senior Prof (Large Lab), h=44) | Fit=5.3/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=5.2/10 | Keywords=point cloud registration, pose estimation, object detection | Paper=RIGA: Rotation-Invariant and Globally-Aware Descriptors for Point Cloud Registration (2024)</t>
+        </is>
+      </c>
+      <c r="AE23" s="4" t="inlineStr">
+        <is>
+          <t>Daniel Cremers: No homepage/funding evidence available
+Eckehard G. Steinbach: No homepage/funding evidence available
+Stefan Leutenegger: No homepage/funding evidence available
+Johannes Betz: No homepage/funding evidence available
+Alois Knoll: No homepage/funding evidence available
+Federico Tombari: No homepage/funding evidence available
+Angela P. Schoellig: No homepage/funding evidence available
+Gerhard Rigoll: No homepage/funding evidence available
+Gan‐Lin Zhang: No homepage/funding evidence available
+Xi Wang: No homepage/funding evidence available
+Markus Lienkamp: No homepage/funding evidence available
+Matthias Althoff: No homepage/funding evidence available
+Achim J. Lilienthal: No homepage/funding evidence available
+Nassir Navab: No homepage/funding evidence available
+Laura Leal-Taixé: No homepage/funding evidence available
+Daniel Roth: No homepage/funding evidence available
+Rüdiger Daub: No homepage/funding evidence available
+Benjamin Busam: No homepage/funding evidence available
+B. Jutzi: No homepage/funding evidence available
+Christoph Holst: No homepage/funding evidence available
+Timo Oksanen: No homepage/funding evidence available
+Michael F. Schmidt: No homepage/funding evidence available
+Slobodan Ilić: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Daniel%20Cremers%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -3461,23 +3593,131 @@
           <t>RWTH Aachen University</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>QS #99 (Top 25 Eng) | Tier S+ (Global Elite | h=956)</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5007760731</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Heike Vallery</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>GNSS/Multisensor Fusion Using Continuous-Time Factor Graph Optimization for Robust Localization (2024)</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Aachen</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>@rwth-aachen.de</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>I887968799</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=33)</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>factor graph optimization, robust localization, gnss sensor fusion, sensor fusion, trajectory estimation, state estimation</t>
+        </is>
+      </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="Z24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="4" t="inlineStr"/>
-      <c r="AE24" s="4" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Heike Vallery; Dirk Abel; Gerhard Lakemeyer; Jörg Blankenbach; Bassam Alrifaee; Burkhard J. Corves; Michael Meurer; Sigrid Brell‐Çokcan; Lutz Eckstein; Robert Heinrich Schmitt; Bastian Leibe</t>
+        </is>
+      </c>
+      <c r="AD24" s="4" t="inlineStr">
+        <is>
+          <t>1. Heike Vallery (Full / Senior Prof (Large Lab), h=33) | Fit=10.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.5/10 | Keywords=factor graph optimization, robust localization, gnss sensor fusion, sensor fusion, trajectory estimation, state estimation | Paper=GNSS/Multisensor Fusion Using Continuous-Time Factor Graph Optimization for Robust Localization (2024)
+2. Dirk Abel (Full / Senior Prof (Large Lab), h=27) | Fit=10.0/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=8.3/10 | Keywords=gnss positioning, state estimation, inertial navigation, extended kalman filter, kalman filter, factor graph optimization | Paper=Robust state and protection-level estimation within tightly coupled GNSS/INS navigation system (2023)
+3. Gerhard Lakemeyer (Full / Senior Prof (Large Lab), h=33) | Fit=9.0/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=robot localization, mobile robot navigation, ros, ros2, robot perception | Paper=A ROS 2-Based Navigation and Simulation Stack for the Robotino (2025)
+4. Jörg Blankenbach (Associate / Established PI (High Fit), h=19) | Fit=8.8/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=7.6/10 | Keywords=lidar slam, autonomous navigation, visual localization, pose estimation, point cloud registration | Paper=Autonomous As-Built Documentation with a Quadruped Robot and LiDAR-SLAM (2025)
+5. Bassam Alrifaee (Associate / Established PI (High Fit), h=16) | Fit=7.9/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.1/10 | Keywords=state estimation, sensor fusion, autonomous vehicles, ros, ros2 | Paper=Ufil: A Unified Framework for Infrastructure-based Localization (2026)
+6. Burkhard J. Corves (Full / Senior Prof (Large Lab), h=22) | Fit=7.6/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.7/10 | Keywords=point cloud registration, trajectory estimation | Paper=RaNDT SLAM: Radar SLAM Based on Intensity-Augmented Normal Distributions Transform (2024)
+7. Michael Meurer (Full / Senior Prof (Large Lab), h=23) | Fit=7.4/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=6.5/10 | Keywords=gnss positioning, visual localization | Paper=Integrity of Visual Navigation—Developments, Challenges, and Prospects (2022)
+8. Sigrid Brell‐Çokcan (Full / Senior Prof (Large Lab), h=17) | Fit=6.9/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.5/10 | Keywords=point cloud registration, deep learning, object detection, semantic segmentation | Paper=Grundlagen zur automatisierten Baufortschrittsüberwachung mittels Deep Learning basierend auf P (2024)
+9. Lutz Eckstein (Full / Senior Prof (Large Lab), h=26) | Fit=7.0/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.3/10 | Keywords=lidar camera fusion, 3d object detection, computer vision, object detection | Paper=MultiCorrupt: A Multi-Modal Robustness Dataset and Benchmark of LiDAR-Camera Fusion for 3D Obje (2024)
+10. Robert Heinrich Schmitt (Full / Senior Prof (Large Lab), h=41) | Fit=6.8/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=6.3/10 | Keywords=point cloud registration, mobile robot navigation, sensor fusion, computer vision, object detection | Paper=Robotergestütztes Schrauben – Endeffektor-basierte Sensorsysteme für mobile Roboter (2024)
+11. Bastian Leibe (Full / Senior Prof (Large Lab), h=80) | Fit=6.1/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=5.8/10 | Keywords=gaussian splatting, pose estimation, cuda | Paper=Look Gauss, No Pose: Novel View Synthesis using Gaussian Splatting without Accurate Pose Initia (2024)</t>
+        </is>
+      </c>
+      <c r="AE24" s="4" t="inlineStr">
+        <is>
+          <t>Heike Vallery: No homepage/funding evidence available
+Dirk Abel: No homepage/funding evidence available
+Gerhard Lakemeyer: No homepage/funding evidence available
+Jörg Blankenbach: No homepage/funding evidence available
+Bassam Alrifaee: No homepage/funding evidence available
+Burkhard J. Corves: No homepage/funding evidence available
+Michael Meurer: No homepage/funding evidence available
+Sigrid Brell‐Çokcan: No homepage/funding evidence available
+Lutz Eckstein: No homepage/funding evidence available
+Robert Heinrich Schmitt: No homepage/funding evidence available
+Bastian Leibe: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arwth-aachen.de%20%22Heike%20Vallery%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
@@ -3485,23 +3725,123 @@
           <t>University of Freiburg</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>QS #212 (Top Robotics/AIS) | Tier S+ (Global Elite | h=1062)</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5039639553</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Abhinav Valada</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Visual‐Inertial SLAM for Unstructured Outdoor Environments: Benchmarking the Benefits and Computational Costs of Loop Closing (2025)</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Freiburg im Breisgau</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>@uni-freiburg.de</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>I161046081</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=32)</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>visual-inertial slam, robot localization, autonomous navigation, robust localization, loop closure, embedded systems</t>
+        </is>
+      </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>7.47</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Z25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" s="4" t="inlineStr"/>
-      <c r="AE25" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Abhinav Valada; Thomas Brox; Christian Schindelhauer; Wenxin Xiong; Alexander Reiterer; Joschka Boedecker; Oliver Amft</t>
+        </is>
+      </c>
+      <c r="AD25" s="4" t="inlineStr">
+        <is>
+          <t>1. Abhinav Valada (Full / Senior Prof (Large Lab), h=32) | Fit=10.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.5/10 | Keywords=visual-inertial slam, robot localization, autonomous navigation, robust localization, loop closure, embedded systems | Paper=Visual‐Inertial SLAM for Unstructured Outdoor Environments: Benchmarking the Benefits and Compu (2025)
+2. Thomas Brox (Full / Senior Prof (Large Lab), h=92) | Fit=8.7/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.6/10 | Keywords=visual odometry, stereo vision, 3d reconstruction | Paper=SF2SE3: Clustering Scene Flow into SE(3)-Motions via Proposal and Selection (2022)
+3. Christian Schindelhauer (Full / Senior Prof (Large Lab), h=30) | Fit=7.2/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.5/10 | Keywords=visual localization, depth estimation, computer vision, robust localization | Paper=Depth Estimation Using Homographic Transformation (2023)
+4. Wenxin Xiong (Assistant Prof / Rising Star (Responsive), h=15) | Fit=5.9/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.8/10 | Keywords=robust localization | Paper=Sparsity-Driven Robust Passive Elliptic Positioning (2026)
+5. Alexander Reiterer (Full / Senior Prof (Large Lab), h=24) | Fit=5.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.6/10 | Keywords=point cloud registration, 3d reconstruction, semantic segmentation | Paper=Automated Method for SLAM Evaluation in GNSS-Denied Areas (2023)
+6. Joschka Boedecker (Associate / Established PI (High Fit), h=25) | Fit=4.5/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.6/10 | Keywords=sensor fusion, autonomous vehicles, autonomous navigation | Paper=Survey on LiDAR Perception in Adverse Weather Conditions (2023)
+7. Oliver Amft (Full / Senior Prof (Large Lab), h=45) | Fit=3.7/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.1/10 | Keywords=point cloud registration, deep learning | Paper=Image-based Live Tracking and Registration for AR-Guided Liver Surgery Using Hololens2: A Phant (2023)</t>
+        </is>
+      </c>
+      <c r="AE25" s="4" t="inlineStr">
+        <is>
+          <t>Abhinav Valada: No homepage/funding evidence available
+Thomas Brox: No homepage/funding evidence available
+Christian Schindelhauer: No homepage/funding evidence available
+Wenxin Xiong: No homepage/funding evidence available
+Alexander Reiterer: No homepage/funding evidence available
+Joschka Boedecker: No homepage/funding evidence available
+Oliver Amft: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-freiburg.de%20%22Abhinav%20Valada%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
@@ -3509,23 +3849,149 @@
           <t>University of Stuttgart</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=621)</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5007703467</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Uwe Soergel</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>3D Gaussian Splatting aided Localization for Large and Complex Indoor-Environments (2025)</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>@uni-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>I100066346</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=31)</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>visual slam, visual localization, gaussian splatting, pose estimation, trajectory estimation, stereo vision</t>
+        </is>
+      </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>9.43</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" s="4" t="inlineStr"/>
-      <c r="AE26" s="4" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Uwe Soergel; Norbert Haala A; Thomas Hobiger; Aamir Ahmad; Michael Hanss; Michael Cramer; Andreas Wortmann; Bin Yang; Oliver Sawodny; Alexander W. Verl; Armin Lechler; Peter Eberhard; Nico Sneeuw; Erik W. Grafarend; Nasser Jazdi; Kai O. Arras; Marco F. Huber; Volker Schwieger; Achim Menges; Erich Kasper</t>
+        </is>
+      </c>
+      <c r="AD26" s="4" t="inlineStr">
+        <is>
+          <t>1. Uwe Soergel (Full / Senior Prof (Large Lab), h=31) | Fit=10.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.5/10 | Keywords=visual slam, visual localization, gaussian splatting, pose estimation, trajectory estimation, stereo vision | Paper=3D Gaussian Splatting aided Localization for Large and Complex Indoor-Environments (2025)
+2. Norbert Haala A (Full / Senior Prof (Large Lab), h=30) | Fit=10.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.5/10 | Keywords=visual-inertial slam, gaussian splatting, loop closure, pose estimation, 3d reconstruction, lidar inertial odometry | Paper=VIGS-SLAM: Visual Inertial Gaussian Splatting SLAM (2026)
+3. Thomas Hobiger (Full / Senior Prof (Large Lab), h=28) | Fit=9.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.2/10 | Keywords=sensor fusion, gnss ins integration, gnss sensor fusion, factor graph optimization, gnss positioning, inertial navigation | Paper=INSTINCT: a flow-based open-source PNT framework for satellite navigation and sensor fusion (2025)
+4. Aamir Ahmad (Associate / Established PI (High Fit), h=15) | Fit=9.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.8/10 | Keywords=visual slam, object detection, deep learning, computer vision, robot perception, pose estimation | Paper=DynaPix SLAM: A Pixel-Based Dynamic Visual SLAM Approach (2025)
+5. Michael Hanss (Associate / Established PI (High Fit), h=19) | Fit=8.7/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=robot localization, state estimation, mobile robot navigation | Paper=Possibilistic filtering for reliable robot localization (2026)
+6. Michael Cramer (Associate / Established PI (High Fit), h=19) | Fit=8.8/10 | Activity=6.8/10 | Funding=0.0/10 | Overall=7.1/10 | Keywords=sensor fusion, trajectory estimation | Paper=Data Acquisition in Geographic Information Systems (2022)
+7. Andreas Wortmann (Full / Senior Prof (Large Lab), h=32) | Fit=7.2/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.7/10 | Keywords=autonomous navigation, mobile robot navigation, ros, ros2 | Paper=Tuning ROS 2 for Energy-Efficient Navigation: Empirical Insights from Costmap 2D Configurations (2026)
+8. Bin Yang (Full / Senior Prof (Large Lab), h=35) | Fit=7.1/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=6.5/10 | Keywords=sensor fusion, 3d perception, 3d object detection, deep learning, object detection, visual slam | Paper=Exploring Domain Shift on Radar-Based 3D Object Detection Amidst Diverse Environmental Conditio (2024)
+9. Oliver Sawodny (Full / Senior Prof (Large Lab), h=43) | Fit=5.9/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.8/10 | Keywords=visual slam | Paper=Active visual SLAM using potential fields and model predictive control (2026)
+10. Alexander W. Verl (Full / Senior Prof (Large Lab), h=40) | Fit=5.4/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.4/10 | Keywords=robot localization, pose estimation, deep learning | Paper=Autonomous Mobile Robot Localization for Material Transport in Construction Prefabrication (2025)
+11. Armin Lechler (Full / Senior Prof (Large Lab), h=20) | Fit=5.4/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.4/10 | Keywords=robot localization, pose estimation, deep learning | Paper=Autonomous Mobile Robot Localization for Material Transport in Construction Prefabrication (2025)
+12. Peter Eberhard (Full / Senior Prof (Large Lab), h=39) | Fit=5.2/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.4/10 | Keywords=state estimation, robot localization | Paper=Formulating Multibody Models for Moving Horizon Estimation (2026)
+13. Nico Sneeuw (Full / Senior Prof (Large Lab), h=38) | Fit=5.3/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.3/10 | Keywords=gnss positioning | Paper=Least squares Fourier filter for processing incomplete and heterogeneous GNSS position time ser (2025)
+14. Erik W. Grafarend (Full / Senior Prof (Large Lab), h=37) | Fit=5.5/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=5.2/10 | Keywords=gnss positioning | Paper=Integer Least Squares (2022)
+15. Nasser Jazdi (Full / Senior Prof (Large Lab), h=28) | Fit=5.0/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=4.9/10 | Keywords=stereo vision, kalman filter | Paper=Audio Guide for Visually Impaired People Based on Combination of Stereo Vision and Musical Tone (2022)
+16. Kai O. Arras (Full / Senior Prof (Large Lab), h=38) | Fit=4.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.6/10 | Keywords=robot perception, 3d object detection, object detection | Paper=FunGraph: Functionality Aware 3D Scene Graphs for Language-Prompted Scene Interaction (2025)
+17. Marco F. Huber (Full / Senior Prof (Large Lab), h=26) | Fit=4.0/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.5/10 | Keywords=pose estimation, deep learning, robot perception, point cloud registration | Paper=Robotic Wiring Harness Bin Picking Solution Using a Deep-Learning-Based Spline Prediction and a (2025)
+18. Volker Schwieger (Associate / Established PI (High Fit), h=15) | Fit=3.6/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.4/10 | Keywords=gnss positioning, point cloud registration | Paper=Multi-sensor system for efficient in-service vehicle-based track monitoring and fault localizat (2026)
+19. Achim Menges (Full / Senior Prof (Large Lab), h=43) | Fit=3.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.3/10 | Keywords=pose estimation | Paper=Toward autonomous timber construction using distributed robotic perception system in coordinati (2026)
+20. Erich Kasper (Full / Senior Prof (Large Lab), h=51) | Fit=3.5/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.1/10 | Keywords=robot perception | Paper=Design and Verification of a Two-Chip-Cascaded 4D mm-Wave Imaging Radar for Indoor SLAM (2024)</t>
+        </is>
+      </c>
+      <c r="AE26" s="4" t="inlineStr">
+        <is>
+          <t>Uwe Soergel: No homepage/funding evidence available
+Norbert Haala A: No homepage/funding evidence available
+Thomas Hobiger: No homepage/funding evidence available
+Aamir Ahmad: No homepage/funding evidence available
+Michael Hanss: No homepage/funding evidence available
+Michael Cramer: No homepage/funding evidence available
+Andreas Wortmann: No homepage/funding evidence available
+Bin Yang: No homepage/funding evidence available
+Oliver Sawodny: No homepage/funding evidence available
+Alexander W. Verl: No homepage/funding evidence available
+Armin Lechler: No homepage/funding evidence available
+Peter Eberhard: No homepage/funding evidence available
+Nico Sneeuw: No homepage/funding evidence available
+Erik W. Grafarend: No homepage/funding evidence available
+Nasser Jazdi: No homepage/funding evidence available
+Kai O. Arras: No homepage/funding evidence available
+Marco F. Huber: No homepage/funding evidence available
+Volker Schwieger: No homepage/funding evidence available
+Achim Menges: No homepage/funding evidence available
+Erich Kasper: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-stuttgart.de%20%22Uwe%20Soergel%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -3533,23 +3999,139 @@
           <t>Karlsruhe Institute of Technology</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>QS #102 (Strong Robotics) | Tier S+ (Global Elite | h=863)</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5087051920</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Rainer Stiefelhagen</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Tightly-Coupled LiDAR-Visual SLAM Based on Geometric Features for Mobile Agents (2023)</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Karlsruhe</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>@kit.edu</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>I102335020</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=65)</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>visual slam, visual odometry, autonomous navigation, sensor fusion, pose estimation, visual localization</t>
+        </is>
+      </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>9.16</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="Z27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>7.93</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="4" t="inlineStr"/>
-      <c r="AE27" s="4" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rainer Stiefelhagen; Ruiping Liu; Yufan Chen; Uwe D. Hanebeck; Markus Ulrich; Gert F. Trommer; Christoph Stiller; B. Jutzi; Rudolph Triebel; Martin Weinmann; Hansjörg Kutterer; Tamim Asfour; Gerhard M. Neumann; Jürgen Beyerer; Michael Heizmann</t>
+        </is>
+      </c>
+      <c r="AD27" s="4" t="inlineStr">
+        <is>
+          <t>1. Rainer Stiefelhagen (Full / Senior Prof (Large Lab), h=65) | Fit=9.9/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.4/10 | Keywords=visual slam, visual odometry, autonomous navigation, sensor fusion, pose estimation, visual localization | Paper=Tightly-Coupled LiDAR-Visual SLAM Based on Geometric Features for Mobile Agents (2023)
+2. Ruiping Liu (Assistant Prof / Rising Star (Responsive), h=14) | Fit=10.0/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.4/10 | Keywords=visual slam, visual odometry, autonomous navigation, sensor fusion, pose estimation, visual localization | Paper=Tightly-Coupled LiDAR-Visual SLAM Based on Geometric Features for Mobile Agents (2023)
+3. Yufan Chen (Associate / Established PI (High Fit), h=21) | Fit=9.4/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.0/10 | Keywords=visual localization, visual odometry, 3d reconstruction, robust localization, pose estimation | Paper=Scene-agnostic Pose Regression for Visual Localization (2025)
+4. Uwe D. Hanebeck (Full / Senior Prof (Large Lab), h=40) | Fit=8.4/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.5/10 | Keywords=multi-sensor fusion, state estimation, sensor fusion, kalman filter | Paper=Continuous-Time Ultra-Wideband-Inertial Fusion (2023)
+5. Markus Ulrich (Associate / Established PI (High Fit), h=15) | Fit=8.1/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.2/10 | Keywords=3d reconstruction, pose estimation, 3d computer vision, computer vision, robot localization, place recognition | Paper=An evaluation of DUSt3R/MASt3R/VGGT 3D reconstruction on photogrammetric aerial blocks (2025)
+6. Gert F. Trommer (Full / Senior Prof (Large Lab), h=22) | Fit=8.8/10 | Activity=6.8/10 | Funding=0.0/10 | Overall=7.1/10 | Keywords=visual inertial odometry, sensor fusion | Paper=x-RIO: Radar Inertial Odometry with Multiple Radar Sensors and Yaw Aiding (2021)
+7. Christoph Stiller (Full / Senior Prof (Large Lab), h=60) | Fit=7.4/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=6.5/10 | Keywords=visual slam, 3d perception, deep learning, point cloud registration, sensor fusion, 3d reconstruction | Paper=Deep geometry-aware camera self-calibration from video (2023)
+8. B. Jutzi (Full / Senior Prof (Large Lab), h=24) | Fit=6.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.4/10 | Keywords=gaussian splatting, pose estimation, computer vision, 3d reconstruction, depth estimation, deep learning | Paper=HoloGS: Instant Depth-based 3D Gaussian Splatting with Microsoft HoloLens 2 (2024)
+9. Rudolph Triebel (Full / Senior Prof (Large Lab), h=37) | Fit=6.8/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=6.3/10 | Keywords=visual slam, pose estimation, point cloud registration | Paper=Improving SLAM‐Based Navigation in Flexible Ureteroscopy by Kidney Stone and Surgical Tool Segm (2025)
+10. Martin Weinmann (Associate / Established PI (High Fit), h=28) | Fit=6.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.2/10 | Keywords=point cloud registration, sensor calibration, object detection, depth estimation, 3d reconstruction, deep learning | Paper=Preface: Workshop “Laser Scanning 2023” (2023)
+11. Hansjörg Kutterer (Full / Senior Prof (Large Lab), h=17) | Fit=4.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.1/10 | Keywords=gnss positioning, deep learning, point cloud registration | Paper=Real-Time GNSS Integrated Water Vapor Sensing Based on Time Series Correction Deep Learning Mod (2024)
+12. Tamim Asfour (Full / Senior Prof (Large Lab), h=59) | Fit=5.0/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.1/10 | Keywords=pose estimation, object detection, robot perception | Paper=Virtual Reality via Object Pose Estimation and Active Learning: Realizing Telepresence Robots w (2022)
+13. Gerhard M. Neumann (Full / Senior Prof (Large Lab), h=43) | Fit=5.2/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=5.1/10 | Keywords=pose estimation, computer vision, semantic segmentation | Paper=MV6D: Multi-View 6D Pose Estimation on RGB-D Frames Using a Deep Point-wise Voting Network (2022)
+14. Jürgen Beyerer (Full / Senior Prof (Large Lab), h=36) | Fit=4.4/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.7/10 | Keywords=pose estimation, point cloud registration, 3d computer vision, computer vision, kalman filter | Paper=6D Pose Estimation on Point Cloud Data through Prior Knowledge Integration: A Case Study in Aut (2024)
+15. Michael Heizmann (Full / Senior Prof (Large Lab), h=17) | Fit=4.3/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.6/10 | Keywords=pose estimation, deep learning, object detection, semantic segmentation | Paper=6D Pose Estimation on Point Cloud Data through Prior Knowledge Integration: A Case Study in Aut (2024)</t>
+        </is>
+      </c>
+      <c r="AE27" s="4" t="inlineStr">
+        <is>
+          <t>Rainer Stiefelhagen: No homepage/funding evidence available
+Ruiping Liu: No homepage/funding evidence available
+Yufan Chen: No homepage/funding evidence available
+Uwe D. Hanebeck: No homepage/funding evidence available
+Markus Ulrich: No homepage/funding evidence available
+Gert F. Trommer: No homepage/funding evidence available
+Christoph Stiller: No homepage/funding evidence available
+B. Jutzi: No homepage/funding evidence available
+Rudolph Triebel: No homepage/funding evidence available
+Martin Weinmann: No homepage/funding evidence available
+Hansjörg Kutterer: No homepage/funding evidence available
+Tamim Asfour: No homepage/funding evidence available
+Gerhard M. Neumann: No homepage/funding evidence available
+Jürgen Beyerer: No homepage/funding evidence available
+Michael Heizmann: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Akit.edu%20%22Rainer%20Stiefelhagen%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -5903,7 +6485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z276"/>
+  <dimension ref="A1:Z352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -35491,8 +36073,8140 @@
         </is>
       </c>
     </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G277" t="n">
+        <v>1</v>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Daniel Cremers</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J277" t="n">
+        <v>102</v>
+      </c>
+      <c r="K277" t="n">
+        <v>54071</v>
+      </c>
+      <c r="L277" t="n">
+        <v>10</v>
+      </c>
+      <c r="M277" t="n">
+        <v>10</v>
+      </c>
+      <c r="N277" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O277" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; State Estimation &amp; Factor Graphs; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>visual odometry, pose estimation, depth estimation, autonomous navigation, object detection, visual slam</t>
+        </is>
+      </c>
+      <c r="R277" t="n">
+        <v>18</v>
+      </c>
+      <c r="S277" t="n">
+        <v>275</v>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>VOCA: Visual Odometry with Codec Awareness</t>
+        </is>
+      </c>
+      <c r="V277" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W277" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Daniel%20Cremers%22%20email</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5087710605</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G278" t="n">
+        <v>2</v>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Eckehard G. Steinbach</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J278" t="n">
+        <v>48</v>
+      </c>
+      <c r="K278" t="n">
+        <v>10188</v>
+      </c>
+      <c r="L278" t="n">
+        <v>10</v>
+      </c>
+      <c r="M278" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N278" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>visual-inertial slam, deep learning, visual slam, visual odometry, pose estimation, loop closure</t>
+        </is>
+      </c>
+      <c r="R278" t="n">
+        <v>9</v>
+      </c>
+      <c r="S278" t="n">
+        <v>154</v>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>AFDI-SLAM: Visual-Inertial SLAM With Adaptive Frame Control and Deep-Learning-Based IMU Signal Denoising</t>
+        </is>
+      </c>
+      <c r="V278" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W278" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X278" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Eckehard%20G.%20Steinbach%22%20email</t>
+        </is>
+      </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5077346002</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G279" t="n">
+        <v>3</v>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Stefan Leutenegger</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J279" t="n">
+        <v>40</v>
+      </c>
+      <c r="K279" t="n">
+        <v>15023</v>
+      </c>
+      <c r="L279" t="n">
+        <v>10</v>
+      </c>
+      <c r="M279" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N279" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>visual-inertial slam, autonomous navigation, loop closure, factor graph optimization, state estimation, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R279" t="n">
+        <v>11</v>
+      </c>
+      <c r="S279" t="n">
+        <v>83</v>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>Scalable Outdoors Autonomous Drone Flight with Visual-Inertial SLAM and Dense Submaps Built without LiDAR</t>
+        </is>
+      </c>
+      <c r="V279" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W279" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Stefan%20Leutenegger%22%20email</t>
+        </is>
+      </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5006726091</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G280" t="n">
+        <v>4</v>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Johannes Betz</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J280" t="n">
+        <v>26</v>
+      </c>
+      <c r="K280" t="n">
+        <v>2669</v>
+      </c>
+      <c r="L280" t="n">
+        <v>10</v>
+      </c>
+      <c r="M280" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N280" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O280" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; GNSS &amp; Robust Localization; Deep Learning for Navigation &amp; Perception</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>visual slam, gaussian splatting, 3d reconstruction, visual inertial navigation, inertial navigation, pose estimation</t>
+        </is>
+      </c>
+      <c r="R280" t="n">
+        <v>8</v>
+      </c>
+      <c r="S280" t="n">
+        <v>116</v>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>RoGER-SLAM: A Robust Gaussian Splatting SLAM System for Noisy and Low-Light Environment Resilience</t>
+        </is>
+      </c>
+      <c r="V280" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W280" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Johannes%20Betz%22%20email</t>
+        </is>
+      </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5063677428</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G281" t="n">
+        <v>5</v>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Alois Knoll</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J281" t="n">
+        <v>68</v>
+      </c>
+      <c r="K281" t="n">
+        <v>28220</v>
+      </c>
+      <c r="L281" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="M281" t="n">
+        <v>10</v>
+      </c>
+      <c r="N281" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O281" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>gaussian splatting, pose estimation, 3d reconstruction, visual odometry, kalman filter, robot perception</t>
+        </is>
+      </c>
+      <c r="R281" t="n">
+        <v>16</v>
+      </c>
+      <c r="S281" t="n">
+        <v>584</v>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>MGS-Track: Monocular 6DoF Pose Tracking via Masked 3D Prior and Online Gaussian Splatting</t>
+        </is>
+      </c>
+      <c r="V281" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W281" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Alois%20Knoll%22%20email</t>
+        </is>
+      </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5063781430</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G282" t="n">
+        <v>6</v>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Federico Tombari</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J282" t="n">
+        <v>66</v>
+      </c>
+      <c r="K282" t="n">
+        <v>21541</v>
+      </c>
+      <c r="L282" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="M282" t="n">
+        <v>10</v>
+      </c>
+      <c r="N282" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O282" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; State Estimation &amp; Factor Graphs; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>visual odometry, pose estimation, factor graph optimization, computer vision, visual localization, 3d computer vision</t>
+        </is>
+      </c>
+      <c r="R282" t="n">
+        <v>18</v>
+      </c>
+      <c r="S282" t="n">
+        <v>276</v>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>E-Graph: Minimal Solution for Rigid Rotation with Extensibility Graphs</t>
+        </is>
+      </c>
+      <c r="V282" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W282" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Federico%20Tombari%22%20email</t>
+        </is>
+      </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5041092666</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G283" t="n">
+        <v>7</v>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Angela P. Schoellig</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J283" t="n">
+        <v>44</v>
+      </c>
+      <c r="K283" t="n">
+        <v>7733</v>
+      </c>
+      <c r="L283" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="M283" t="n">
+        <v>10</v>
+      </c>
+      <c r="N283" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O283" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>pose estimation, multi-sensor fusion, sensor fusion, trajectory estimation, lidar inertial odometry, state estimation</t>
+        </is>
+      </c>
+      <c r="R283" t="n">
+        <v>7</v>
+      </c>
+      <c r="S283" t="n">
+        <v>122</v>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>Continuous-Time Range-Only Pose Estimation</t>
+        </is>
+      </c>
+      <c r="V283" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W283" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Angela%20P.%20Schoellig%22%20email</t>
+        </is>
+      </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5052147335</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G284" t="n">
+        <v>8</v>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Gerhard Rigoll</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J284" t="n">
+        <v>59</v>
+      </c>
+      <c r="K284" t="n">
+        <v>15832</v>
+      </c>
+      <c r="L284" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="M284" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N284" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O284" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>visual slam, gaussian splatting, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R284" t="n">
+        <v>1</v>
+      </c>
+      <c r="S284" t="n">
+        <v>88</v>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>RoGER-SLAM: A Robust Gaussian Splatting SLAM System for Noisy and Low-Light Environment Resilience</t>
+        </is>
+      </c>
+      <c r="V284" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W284" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X284" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Gerhard%20Rigoll%22%20email</t>
+        </is>
+      </c>
+      <c r="Z284" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5039092855</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G285" t="n">
+        <v>9</v>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Gan‐Lin Zhang</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J285" t="n">
+        <v>56</v>
+      </c>
+      <c r="K285" t="n">
+        <v>13684</v>
+      </c>
+      <c r="L285" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="M285" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N285" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O285" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>visual slam, loop closure, pose estimation, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R285" t="n">
+        <v>1</v>
+      </c>
+      <c r="S285" t="n">
+        <v>117</v>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>ViSTA-SLAM: Visual SLAM with Symmetric Two-View Association</t>
+        </is>
+      </c>
+      <c r="V285" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W285" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X285" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Gan%E2%80%90Lin%20Zhang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100320387</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G286" t="n">
+        <v>10</v>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Xi Wang</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J286" t="n">
+        <v>18</v>
+      </c>
+      <c r="K286" t="n">
+        <v>1184</v>
+      </c>
+      <c r="L286" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="M286" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N286" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O286" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>visual slam, loop closure, pose estimation, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R286" t="n">
+        <v>1</v>
+      </c>
+      <c r="S286" t="n">
+        <v>86</v>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>ViSTA-SLAM: Visual SLAM with Symmetric Two-View Association</t>
+        </is>
+      </c>
+      <c r="V286" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W286" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X286" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Xi%20Wang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z286" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100442218</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G287" t="n">
+        <v>11</v>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Markus Lienkamp</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J287" t="n">
+        <v>44</v>
+      </c>
+      <c r="K287" t="n">
+        <v>8629</v>
+      </c>
+      <c r="L287" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="M287" t="n">
+        <v>10</v>
+      </c>
+      <c r="N287" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O287" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; State Estimation &amp; Factor Graphs; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>lidar inertial odometry, extended kalman filter, kalman filter, cuda, pose estimation, object detection</t>
+        </is>
+      </c>
+      <c r="R287" t="n">
+        <v>4</v>
+      </c>
+      <c r="S287" t="n">
+        <v>232</v>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>FAR-LIO: Enabling High-Speed Autonomy through Fast, Accurate, and Robust LiDAR-Inertial Odometry</t>
+        </is>
+      </c>
+      <c r="V287" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W287" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X287" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Markus%20Lienkamp%22%20email</t>
+        </is>
+      </c>
+      <c r="Z287" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5079718896</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G288" t="n">
+        <v>12</v>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Matthias Althoff</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J288" t="n">
+        <v>54</v>
+      </c>
+      <c r="K288" t="n">
+        <v>11748</v>
+      </c>
+      <c r="L288" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="M288" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N288" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O288" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>point cloud registration, pose estimation, autonomous driving perception, visual localization</t>
+        </is>
+      </c>
+      <c r="R288" t="n">
+        <v>4</v>
+      </c>
+      <c r="S288" t="n">
+        <v>194</v>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>Offline Object Tracking With Joint Point Cloud Registration</t>
+        </is>
+      </c>
+      <c r="V288" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W288" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Matthias%20Althoff%22%20email</t>
+        </is>
+      </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5005383495</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G289" t="n">
+        <v>13</v>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Achim J. Lilienthal</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J289" t="n">
+        <v>51</v>
+      </c>
+      <c r="K289" t="n">
+        <v>9588</v>
+      </c>
+      <c r="L289" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="M289" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N289" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O289" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; LiDAR &amp; Multimodal Sensor Fusion; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>loop closure, trajectory estimation, mobile robot navigation, point cloud registration, autonomous navigation, robot localization</t>
+        </is>
+      </c>
+      <c r="R289" t="n">
+        <v>7</v>
+      </c>
+      <c r="S289" t="n">
+        <v>127</v>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>Introspective Loop Closure for SLAM with 4D Imaging Radar</t>
+        </is>
+      </c>
+      <c r="V289" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W289" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X289" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Achim%20J.%20Lilienthal%22%20email</t>
+        </is>
+      </c>
+      <c r="Z289" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5088586617</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G290" t="n">
+        <v>14</v>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Nassir Navab</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J290" t="n">
+        <v>108</v>
+      </c>
+      <c r="K290" t="n">
+        <v>71532</v>
+      </c>
+      <c r="L290" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="M290" t="n">
+        <v>10</v>
+      </c>
+      <c r="N290" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O290" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; 3D Computer Vision &amp; Geometric Perception; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>pose estimation, 3d computer vision, 3d reconstruction, computer vision, trajectory estimation, semantic segmentation</t>
+        </is>
+      </c>
+      <c r="R290" t="n">
+        <v>17</v>
+      </c>
+      <c r="S290" t="n">
+        <v>632</v>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>ESCAPE: Equivariant Shape Completion via Anchor Point Encoding</t>
+        </is>
+      </c>
+      <c r="V290" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W290" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X290" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Nassir%20Navab%22%20email</t>
+        </is>
+      </c>
+      <c r="Z290" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5046896448</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G291" t="n">
+        <v>15</v>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Laura Leal-Taixé</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J291" t="n">
+        <v>43</v>
+      </c>
+      <c r="K291" t="n">
+        <v>11790</v>
+      </c>
+      <c r="L291" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="M291" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N291" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O291" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>visual localization, visual odometry, 3d object detection, object detection</t>
+        </is>
+      </c>
+      <c r="R291" t="n">
+        <v>2</v>
+      </c>
+      <c r="S291" t="n">
+        <v>86</v>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>2022-10-23</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>Is Geometry Enough for Matching in Visual Localization?</t>
+        </is>
+      </c>
+      <c r="V291" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W291" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X291" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Laura%20Leal-Taix%C3%A9%22%20email</t>
+        </is>
+      </c>
+      <c r="Z291" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5090283032</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G292" t="n">
+        <v>16</v>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Daniel Roth</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J292" t="n">
+        <v>26</v>
+      </c>
+      <c r="K292" t="n">
+        <v>3424</v>
+      </c>
+      <c r="L292" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="M292" t="n">
+        <v>10</v>
+      </c>
+      <c r="N292" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O292" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; Robotics &amp; Autonomous Navigation; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>gaussian splatting, robot perception, pose estimation, trajectory estimation, semantic segmentation, 3d computer vision</t>
+        </is>
+      </c>
+      <c r="R292" t="n">
+        <v>6</v>
+      </c>
+      <c r="S292" t="n">
+        <v>65</v>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>SplatXtRact: Tractable Gaussian Splatting via Open World Region-of-Interest Extraction and Refinement</t>
+        </is>
+      </c>
+      <c r="V292" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W292" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X292" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Daniel%20Roth%22%20email</t>
+        </is>
+      </c>
+      <c r="Z292" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5028687545</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G293" t="n">
+        <v>17</v>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Rüdiger Daub</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J293" t="n">
+        <v>22</v>
+      </c>
+      <c r="K293" t="n">
+        <v>1570</v>
+      </c>
+      <c r="L293" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="M293" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N293" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O293" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>Deep Learning for Navigation &amp; Perception; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>learning-based localization, deep learning, robot perception</t>
+        </is>
+      </c>
+      <c r="R293" t="n">
+        <v>2</v>
+      </c>
+      <c r="S293" t="n">
+        <v>163</v>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>Deep learning-based localization of electrical connector sockets for automated mating</t>
+        </is>
+      </c>
+      <c r="V293" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W293" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X293" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22R%C3%BCdiger%20Daub%22%20email</t>
+        </is>
+      </c>
+      <c r="Z293" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5024110966</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G294" t="n">
+        <v>18</v>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Benjamin Busam</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J294" t="n">
+        <v>27</v>
+      </c>
+      <c r="K294" t="n">
+        <v>2173</v>
+      </c>
+      <c r="L294" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="M294" t="n">
+        <v>10</v>
+      </c>
+      <c r="N294" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O294" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; 3D Computer Vision &amp; Geometric Perception; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>pose estimation, 3d computer vision, computer vision, trajectory estimation, semantic segmentation, point cloud registration</t>
+        </is>
+      </c>
+      <c r="R294" t="n">
+        <v>14</v>
+      </c>
+      <c r="S294" t="n">
+        <v>116</v>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>Zero123-6D: Zero-shot Novel View Synthesis for RGB Category-level 6D Pose Estimation</t>
+        </is>
+      </c>
+      <c r="V294" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W294" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X294" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Benjamin%20Busam%22%20email</t>
+        </is>
+      </c>
+      <c r="Z294" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5067135033</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G295" t="n">
+        <v>19</v>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>B. Jutzi</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J295" t="n">
+        <v>24</v>
+      </c>
+      <c r="K295" t="n">
+        <v>3362</v>
+      </c>
+      <c r="L295" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M295" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N295" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O295" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>visual localization, pose estimation, deep learning, computer vision, gaussian splatting, semantic segmentation</t>
+        </is>
+      </c>
+      <c r="R295" t="n">
+        <v>3</v>
+      </c>
+      <c r="S295" t="n">
+        <v>69</v>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>To Glue or Not to Glue? Classical vs Learned Image Matching for Mobile Mapping Cameras to Textured Semantic 3D Building Models</t>
+        </is>
+      </c>
+      <c r="V295" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W295" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X295" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22B.%20Jutzi%22%20email</t>
+        </is>
+      </c>
+      <c r="Z295" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5065772342</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G296" t="n">
+        <v>20</v>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Christoph Holst</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J296" t="n">
+        <v>18</v>
+      </c>
+      <c r="K296" t="n">
+        <v>931</v>
+      </c>
+      <c r="L296" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="M296" t="n">
+        <v>10</v>
+      </c>
+      <c r="N296" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O296" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; State Estimation &amp; Factor Graphs; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>point cloud registration, loop closure, visual slam, deep learning</t>
+        </is>
+      </c>
+      <c r="R296" t="n">
+        <v>10</v>
+      </c>
+      <c r="S296" t="n">
+        <v>68</v>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>Keypoint-based registration of TLS point clouds using a statistical matching approach</t>
+        </is>
+      </c>
+      <c r="V296" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W296" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X296" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Christoph%20Holst%22%20email</t>
+        </is>
+      </c>
+      <c r="Z296" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5006132386</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G297" t="n">
+        <v>21</v>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Timo Oksanen</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J297" t="n">
+        <v>22</v>
+      </c>
+      <c r="K297" t="n">
+        <v>2217</v>
+      </c>
+      <c r="L297" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="M297" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N297" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O297" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>visual odometry, 3d reconstruction, gnss positioning, object detection</t>
+        </is>
+      </c>
+      <c r="R297" t="n">
+        <v>3</v>
+      </c>
+      <c r="S297" t="n">
+        <v>56</v>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>Novel Dataset of RGB-D Images for Robotic Harvesting of Green Asparagus</t>
+        </is>
+      </c>
+      <c r="V297" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W297" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X297" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Timo%20Oksanen%22%20email</t>
+        </is>
+      </c>
+      <c r="Z297" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5021744500</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G298" t="n">
+        <v>22</v>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Michael F. Schmidt</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J298" t="n">
+        <v>45</v>
+      </c>
+      <c r="K298" t="n">
+        <v>7277</v>
+      </c>
+      <c r="L298" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="M298" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N298" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O298" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>gnss positioning</t>
+        </is>
+      </c>
+      <c r="R298" t="n">
+        <v>6</v>
+      </c>
+      <c r="S298" t="n">
+        <v>64</v>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>2023-02-25</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>Ongoing strategies for assessing VTEC maps performance over a low latitude region</t>
+        </is>
+      </c>
+      <c r="V298" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W298" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X298" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Michael%20F.%20Schmidt%22%20email</t>
+        </is>
+      </c>
+      <c r="Z298" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5073173295</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>QS #28 | Tier S+ (Global Elite | h=1084)</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>@tum.de</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G299" t="n">
+        <v>23</v>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Slobodan Ilić</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J299" t="n">
+        <v>44</v>
+      </c>
+      <c r="K299" t="n">
+        <v>11323</v>
+      </c>
+      <c r="L299" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="M299" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N299" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O299" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>point cloud registration, pose estimation, object detection</t>
+        </is>
+      </c>
+      <c r="R299" t="n">
+        <v>6</v>
+      </c>
+      <c r="S299" t="n">
+        <v>33</v>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>RIGA: Rotation-Invariant and Globally-Aware Descriptors for Point Cloud Registration</t>
+        </is>
+      </c>
+      <c r="V299" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W299" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X299" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atum.de%20%22Slobodan%20Ili%C4%87%22%20email</t>
+        </is>
+      </c>
+      <c r="Z299" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5045382199</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>RWTH Aachen University</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Aachen</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>QS #99 (Top 25 Eng) | Tier S+ (Global Elite | h=956)</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>@rwth-aachen.de</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G300" t="n">
+        <v>1</v>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Heike Vallery</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J300" t="n">
+        <v>33</v>
+      </c>
+      <c r="K300" t="n">
+        <v>5078</v>
+      </c>
+      <c r="L300" t="n">
+        <v>10</v>
+      </c>
+      <c r="M300" t="n">
+        <v>10</v>
+      </c>
+      <c r="N300" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O300" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; State Estimation &amp; Factor Graphs; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>factor graph optimization, robust localization, gnss sensor fusion, sensor fusion, trajectory estimation, state estimation</t>
+        </is>
+      </c>
+      <c r="R300" t="n">
+        <v>5</v>
+      </c>
+      <c r="S300" t="n">
+        <v>124</v>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>GNSS/Multisensor Fusion Using Continuous-Time Factor Graph Optimization for Robust Localization</t>
+        </is>
+      </c>
+      <c r="V300" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W300" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X300" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arwth-aachen.de%20%22Heike%20Vallery%22%20email</t>
+        </is>
+      </c>
+      <c r="Z300" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5007760731</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>RWTH Aachen University</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Aachen</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>QS #99 (Top 25 Eng) | Tier S+ (Global Elite | h=956)</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>@rwth-aachen.de</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G301" t="n">
+        <v>2</v>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Dirk Abel</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J301" t="n">
+        <v>27</v>
+      </c>
+      <c r="K301" t="n">
+        <v>6206</v>
+      </c>
+      <c r="L301" t="n">
+        <v>10</v>
+      </c>
+      <c r="M301" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N301" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O301" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>gnss positioning, state estimation, inertial navigation, extended kalman filter, kalman filter, factor graph optimization</t>
+        </is>
+      </c>
+      <c r="R301" t="n">
+        <v>6</v>
+      </c>
+      <c r="S301" t="n">
+        <v>130</v>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>Robust state and protection-level estimation within tightly coupled GNSS/INS navigation system</t>
+        </is>
+      </c>
+      <c r="V301" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W301" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X301" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arwth-aachen.de%20%22Dirk%20Abel%22%20email</t>
+        </is>
+      </c>
+      <c r="Z301" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5029739081</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>RWTH Aachen University</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Aachen</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>QS #99 (Top 25 Eng) | Tier S+ (Global Elite | h=956)</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>@rwth-aachen.de</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G302" t="n">
+        <v>3</v>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Gerhard Lakemeyer</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J302" t="n">
+        <v>33</v>
+      </c>
+      <c r="K302" t="n">
+        <v>5397</v>
+      </c>
+      <c r="L302" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="M302" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N302" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O302" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>robot localization, mobile robot navigation, ros, ros2, robot perception</t>
+        </is>
+      </c>
+      <c r="R302" t="n">
+        <v>2</v>
+      </c>
+      <c r="S302" t="n">
+        <v>72</v>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>A ROS 2-Based Navigation and Simulation Stack for the Robotino</t>
+        </is>
+      </c>
+      <c r="V302" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W302" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X302" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arwth-aachen.de%20%22Gerhard%20Lakemeyer%22%20email</t>
+        </is>
+      </c>
+      <c r="Z302" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5005730180</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>RWTH Aachen University</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Aachen</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>QS #99 (Top 25 Eng) | Tier S+ (Global Elite | h=956)</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>@rwth-aachen.de</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G303" t="n">
+        <v>4</v>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Jörg Blankenbach</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J303" t="n">
+        <v>19</v>
+      </c>
+      <c r="K303" t="n">
+        <v>1234</v>
+      </c>
+      <c r="L303" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="M303" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N303" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O303" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; 3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>lidar slam, autonomous navigation, visual localization, pose estimation, point cloud registration</t>
+        </is>
+      </c>
+      <c r="R303" t="n">
+        <v>4</v>
+      </c>
+      <c r="S303" t="n">
+        <v>62</v>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>Autonomous As-Built Documentation with a Quadruped Robot and LiDAR-SLAM</t>
+        </is>
+      </c>
+      <c r="V303" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W303" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X303" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arwth-aachen.de%20%22J%C3%B6rg%20Blankenbach%22%20email</t>
+        </is>
+      </c>
+      <c r="Z303" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5000085993</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>RWTH Aachen University</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Aachen</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>QS #99 (Top 25 Eng) | Tier S+ (Global Elite | h=956)</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>@rwth-aachen.de</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G304" t="n">
+        <v>5</v>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Bassam Alrifaee</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J304" t="n">
+        <v>16</v>
+      </c>
+      <c r="K304" t="n">
+        <v>855</v>
+      </c>
+      <c r="L304" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="M304" t="n">
+        <v>10</v>
+      </c>
+      <c r="N304" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O304" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>state estimation, sensor fusion, autonomous vehicles, ros, ros2</t>
+        </is>
+      </c>
+      <c r="R304" t="n">
+        <v>1</v>
+      </c>
+      <c r="S304" t="n">
+        <v>99</v>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>Ufil: A Unified Framework for Infrastructure-based Localization</t>
+        </is>
+      </c>
+      <c r="V304" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W304" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X304" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arwth-aachen.de%20%22Bassam%20Alrifaee%22%20email</t>
+        </is>
+      </c>
+      <c r="Z304" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5087905706</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>RWTH Aachen University</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Aachen</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>QS #99 (Top 25 Eng) | Tier S+ (Global Elite | h=956)</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>@rwth-aachen.de</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G305" t="n">
+        <v>6</v>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Burkhard J. Corves</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J305" t="n">
+        <v>22</v>
+      </c>
+      <c r="K305" t="n">
+        <v>2181</v>
+      </c>
+      <c r="L305" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="M305" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N305" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O305" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>point cloud registration, trajectory estimation</t>
+        </is>
+      </c>
+      <c r="R305" t="n">
+        <v>1</v>
+      </c>
+      <c r="S305" t="n">
+        <v>173</v>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>RaNDT SLAM: Radar SLAM Based on Intensity-Augmented Normal Distributions Transform</t>
+        </is>
+      </c>
+      <c r="V305" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W305" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X305" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arwth-aachen.de%20%22Burkhard%20J.%20Corves%22%20email</t>
+        </is>
+      </c>
+      <c r="Z305" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5054447183</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>RWTH Aachen University</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Aachen</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>QS #99 (Top 25 Eng) | Tier S+ (Global Elite | h=956)</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>@rwth-aachen.de</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G306" t="n">
+        <v>7</v>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Michael Meurer</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J306" t="n">
+        <v>23</v>
+      </c>
+      <c r="K306" t="n">
+        <v>2185</v>
+      </c>
+      <c r="L306" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="M306" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N306" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O306" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>gnss positioning, visual localization</t>
+        </is>
+      </c>
+      <c r="R306" t="n">
+        <v>3</v>
+      </c>
+      <c r="S306" t="n">
+        <v>70</v>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>Integrity of Visual Navigation—Developments, Challenges, and Prospects</t>
+        </is>
+      </c>
+      <c r="V306" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W306" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X306" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arwth-aachen.de%20%22Michael%20Meurer%22%20email</t>
+        </is>
+      </c>
+      <c r="Z306" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5064770488</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>RWTH Aachen University</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Aachen</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>QS #99 (Top 25 Eng) | Tier S+ (Global Elite | h=956)</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>@rwth-aachen.de</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G307" t="n">
+        <v>8</v>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Sigrid Brell‐Çokcan</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J307" t="n">
+        <v>17</v>
+      </c>
+      <c r="K307" t="n">
+        <v>978</v>
+      </c>
+      <c r="L307" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="M307" t="n">
+        <v>10</v>
+      </c>
+      <c r="N307" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O307" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>point cloud registration, deep learning, object detection, semantic segmentation</t>
+        </is>
+      </c>
+      <c r="R307" t="n">
+        <v>4</v>
+      </c>
+      <c r="S307" t="n">
+        <v>122</v>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>Grundlagen zur automatisierten Baufortschrittsüberwachung mittels Deep Learning basierend auf Punktwolken und Bauinformationsmodellen</t>
+        </is>
+      </c>
+      <c r="V307" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W307" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X307" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arwth-aachen.de%20%22Sigrid%20Brell%E2%80%90%C3%87okcan%22%20email</t>
+        </is>
+      </c>
+      <c r="Z307" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5049520188</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>RWTH Aachen University</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Aachen</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>QS #99 (Top 25 Eng) | Tier S+ (Global Elite | h=956)</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>@rwth-aachen.de</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G308" t="n">
+        <v>9</v>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Lutz Eckstein</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J308" t="n">
+        <v>26</v>
+      </c>
+      <c r="K308" t="n">
+        <v>4916</v>
+      </c>
+      <c r="L308" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="M308" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N308" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O308" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>lidar camera fusion, 3d object detection, computer vision, object detection</t>
+        </is>
+      </c>
+      <c r="R308" t="n">
+        <v>1</v>
+      </c>
+      <c r="S308" t="n">
+        <v>147</v>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>MultiCorrupt: A Multi-Modal Robustness Dataset and Benchmark of LiDAR-Camera Fusion for 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="V308" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W308" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X308" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arwth-aachen.de%20%22Lutz%20Eckstein%22%20email</t>
+        </is>
+      </c>
+      <c r="Z308" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5113050304</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>RWTH Aachen University</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Aachen</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>QS #99 (Top 25 Eng) | Tier S+ (Global Elite | h=956)</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>@rwth-aachen.de</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G309" t="n">
+        <v>10</v>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Robert Heinrich Schmitt</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J309" t="n">
+        <v>41</v>
+      </c>
+      <c r="K309" t="n">
+        <v>12181</v>
+      </c>
+      <c r="L309" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="M309" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N309" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O309" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>point cloud registration, mobile robot navigation, sensor fusion, computer vision, object detection</t>
+        </is>
+      </c>
+      <c r="R309" t="n">
+        <v>5</v>
+      </c>
+      <c r="S309" t="n">
+        <v>459</v>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>Robotergestütztes Schrauben – Endeffektor-basierte Sensorsysteme für mobile Roboter</t>
+        </is>
+      </c>
+      <c r="V309" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W309" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X309" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arwth-aachen.de%20%22Robert%20Heinrich%20Schmitt%22%20email</t>
+        </is>
+      </c>
+      <c r="Z309" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5045094368</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>RWTH Aachen University</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Aachen</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>QS #99 (Top 25 Eng) | Tier S+ (Global Elite | h=956)</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>@rwth-aachen.de</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G310" t="n">
+        <v>11</v>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Bastian Leibe</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J310" t="n">
+        <v>80</v>
+      </c>
+      <c r="K310" t="n">
+        <v>28988</v>
+      </c>
+      <c r="L310" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="M310" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N310" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O310" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>gaussian splatting, pose estimation, cuda</t>
+        </is>
+      </c>
+      <c r="R310" t="n">
+        <v>1</v>
+      </c>
+      <c r="S310" t="n">
+        <v>88</v>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>Look Gauss, No Pose: Novel View Synthesis using Gaussian Splatting without Accurate Pose Initialization</t>
+        </is>
+      </c>
+      <c r="V310" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W310" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X310" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arwth-aachen.de%20%22Bastian%20Leibe%22%20email</t>
+        </is>
+      </c>
+      <c r="Z310" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5071006649</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>University of Freiburg</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Freiburg im Breisgau</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>QS #212 (Top Robotics/AIS) | Tier S+ (Global Elite | h=1062)</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>@uni-freiburg.de</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G311" t="n">
+        <v>1</v>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Abhinav Valada</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J311" t="n">
+        <v>32</v>
+      </c>
+      <c r="K311" t="n">
+        <v>3801</v>
+      </c>
+      <c r="L311" t="n">
+        <v>10</v>
+      </c>
+      <c r="M311" t="n">
+        <v>10</v>
+      </c>
+      <c r="N311" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O311" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>visual-inertial slam, robot localization, autonomous navigation, robust localization, loop closure, embedded systems</t>
+        </is>
+      </c>
+      <c r="R311" t="n">
+        <v>50</v>
+      </c>
+      <c r="S311" t="n">
+        <v>161</v>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>Visual‐Inertial SLAM for Unstructured Outdoor Environments: Benchmarking the Benefits and Computational Costs of Loop Closing</t>
+        </is>
+      </c>
+      <c r="V311" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W311" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X311" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-freiburg.de%20%22Abhinav%20Valada%22%20email</t>
+        </is>
+      </c>
+      <c r="Z311" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5039639553</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>University of Freiburg</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Freiburg im Breisgau</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>QS #212 (Top Robotics/AIS) | Tier S+ (Global Elite | h=1062)</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>@uni-freiburg.de</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G312" t="n">
+        <v>2</v>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Thomas Brox</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J312" t="n">
+        <v>92</v>
+      </c>
+      <c r="K312" t="n">
+        <v>143731</v>
+      </c>
+      <c r="L312" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="M312" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N312" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O312" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>visual odometry, stereo vision, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R312" t="n">
+        <v>2</v>
+      </c>
+      <c r="S312" t="n">
+        <v>115</v>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>SF2SE3: Clustering Scene Flow into SE(3)-Motions via Proposal and Selection</t>
+        </is>
+      </c>
+      <c r="V312" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W312" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X312" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-freiburg.de%20%22Thomas%20Brox%22%20email</t>
+        </is>
+      </c>
+      <c r="Z312" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5070290355</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>University of Freiburg</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Freiburg im Breisgau</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>QS #212 (Top Robotics/AIS) | Tier S+ (Global Elite | h=1062)</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>@uni-freiburg.de</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G313" t="n">
+        <v>3</v>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Christian Schindelhauer</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J313" t="n">
+        <v>30</v>
+      </c>
+      <c r="K313" t="n">
+        <v>3350</v>
+      </c>
+      <c r="L313" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="M313" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N313" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O313" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>visual localization, depth estimation, computer vision, robust localization</t>
+        </is>
+      </c>
+      <c r="R313" t="n">
+        <v>2</v>
+      </c>
+      <c r="S313" t="n">
+        <v>41</v>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>2023-10-22</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>Depth Estimation Using Homographic Transformation</t>
+        </is>
+      </c>
+      <c r="V313" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W313" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X313" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-freiburg.de%20%22Christian%20Schindelhauer%22%20email</t>
+        </is>
+      </c>
+      <c r="Z313" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5068757827</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>University of Freiburg</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Freiburg im Breisgau</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>QS #212 (Top Robotics/AIS) | Tier S+ (Global Elite | h=1062)</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>@uni-freiburg.de</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G314" t="n">
+        <v>4</v>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Wenxin Xiong</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J314" t="n">
+        <v>15</v>
+      </c>
+      <c r="K314" t="n">
+        <v>660</v>
+      </c>
+      <c r="L314" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="M314" t="n">
+        <v>10</v>
+      </c>
+      <c r="N314" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O314" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>robust localization</t>
+        </is>
+      </c>
+      <c r="R314" t="n">
+        <v>5</v>
+      </c>
+      <c r="S314" t="n">
+        <v>44</v>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>Sparsity-Driven Robust Passive Elliptic Positioning</t>
+        </is>
+      </c>
+      <c r="V314" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W314" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X314" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-freiburg.de%20%22Wenxin%20Xiong%22%20email</t>
+        </is>
+      </c>
+      <c r="Z314" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5070717522</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>University of Freiburg</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Freiburg im Breisgau</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>QS #212 (Top Robotics/AIS) | Tier S+ (Global Elite | h=1062)</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>@uni-freiburg.de</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G315" t="n">
+        <v>5</v>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Alexander Reiterer</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J315" t="n">
+        <v>24</v>
+      </c>
+      <c r="K315" t="n">
+        <v>2729</v>
+      </c>
+      <c r="L315" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="M315" t="n">
+        <v>10</v>
+      </c>
+      <c r="N315" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O315" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>point cloud registration, 3d reconstruction, semantic segmentation</t>
+        </is>
+      </c>
+      <c r="R315" t="n">
+        <v>4</v>
+      </c>
+      <c r="S315" t="n">
+        <v>94</v>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>Automated Method for SLAM Evaluation in GNSS-Denied Areas</t>
+        </is>
+      </c>
+      <c r="V315" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W315" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X315" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-freiburg.de%20%22Alexander%20Reiterer%22%20email</t>
+        </is>
+      </c>
+      <c r="Z315" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5015835709</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>University of Freiburg</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Freiburg im Breisgau</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>QS #212 (Top Robotics/AIS) | Tier S+ (Global Elite | h=1062)</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>@uni-freiburg.de</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G316" t="n">
+        <v>6</v>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Joschka Boedecker</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J316" t="n">
+        <v>25</v>
+      </c>
+      <c r="K316" t="n">
+        <v>2946</v>
+      </c>
+      <c r="L316" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="M316" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N316" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O316" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>sensor fusion, autonomous vehicles, autonomous navigation</t>
+        </is>
+      </c>
+      <c r="R316" t="n">
+        <v>2</v>
+      </c>
+      <c r="S316" t="n">
+        <v>85</v>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>Survey on LiDAR Perception in Adverse Weather Conditions</t>
+        </is>
+      </c>
+      <c r="V316" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W316" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X316" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-freiburg.de%20%22Joschka%20Boedecker%22%20email</t>
+        </is>
+      </c>
+      <c r="Z316" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5038908529</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>University of Freiburg</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Freiburg im Breisgau</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>QS #212 (Top Robotics/AIS) | Tier S+ (Global Elite | h=1062)</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>@uni-freiburg.de</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G317" t="n">
+        <v>7</v>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Oliver Amft</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J317" t="n">
+        <v>45</v>
+      </c>
+      <c r="K317" t="n">
+        <v>7505</v>
+      </c>
+      <c r="L317" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="M317" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N317" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O317" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>point cloud registration, deep learning</t>
+        </is>
+      </c>
+      <c r="R317" t="n">
+        <v>1</v>
+      </c>
+      <c r="S317" t="n">
+        <v>76</v>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>Image-based Live Tracking and Registration for AR-Guided Liver Surgery Using Hololens2: A Phantom Study</t>
+        </is>
+      </c>
+      <c r="V317" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W317" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-freiburg.de%20%22Oliver%20Amft%22%20email</t>
+        </is>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5064135418</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=621)</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>@uni-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G318" t="n">
+        <v>1</v>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Uwe Soergel</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J318" t="n">
+        <v>31</v>
+      </c>
+      <c r="K318" t="n">
+        <v>3625</v>
+      </c>
+      <c r="L318" t="n">
+        <v>10</v>
+      </c>
+      <c r="M318" t="n">
+        <v>10</v>
+      </c>
+      <c r="N318" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O318" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>visual slam, visual localization, gaussian splatting, pose estimation, trajectory estimation, stereo vision</t>
+        </is>
+      </c>
+      <c r="R318" t="n">
+        <v>6</v>
+      </c>
+      <c r="S318" t="n">
+        <v>41</v>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>3D Gaussian Splatting aided Localization for Large and Complex Indoor-Environments</t>
+        </is>
+      </c>
+      <c r="V318" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W318" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-stuttgart.de%20%22Uwe%20Soergel%22%20email</t>
+        </is>
+      </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5007703467</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=621)</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>@uni-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G319" t="n">
+        <v>2</v>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Norbert Haala A</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J319" t="n">
+        <v>30</v>
+      </c>
+      <c r="K319" t="n">
+        <v>3795</v>
+      </c>
+      <c r="L319" t="n">
+        <v>10</v>
+      </c>
+      <c r="M319" t="n">
+        <v>10</v>
+      </c>
+      <c r="N319" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O319" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; LiDAR &amp; Multimodal Sensor Fusion; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>visual-inertial slam, gaussian splatting, loop closure, pose estimation, 3d reconstruction, lidar inertial odometry</t>
+        </is>
+      </c>
+      <c r="R319" t="n">
+        <v>18</v>
+      </c>
+      <c r="S319" t="n">
+        <v>48</v>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>VIGS-SLAM: Visual Inertial Gaussian Splatting SLAM</t>
+        </is>
+      </c>
+      <c r="V319" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W319" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-stuttgart.de%20%22Norbert%20Haala%20A%22%20email</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5049647675</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=621)</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>@uni-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G320" t="n">
+        <v>3</v>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Thomas Hobiger</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J320" t="n">
+        <v>28</v>
+      </c>
+      <c r="K320" t="n">
+        <v>2077</v>
+      </c>
+      <c r="L320" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="M320" t="n">
+        <v>10</v>
+      </c>
+      <c r="N320" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O320" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>sensor fusion, gnss ins integration, gnss sensor fusion, factor graph optimization, gnss positioning, inertial navigation</t>
+        </is>
+      </c>
+      <c r="R320" t="n">
+        <v>5</v>
+      </c>
+      <c r="S320" t="n">
+        <v>27</v>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>INSTINCT: a flow-based open-source PNT framework for satellite navigation and sensor fusion</t>
+        </is>
+      </c>
+      <c r="V320" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W320" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-stuttgart.de%20%22Thomas%20Hobiger%22%20email</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5013503605</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=621)</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>@uni-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G321" t="n">
+        <v>4</v>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Aamir Ahmad</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J321" t="n">
+        <v>15</v>
+      </c>
+      <c r="K321" t="n">
+        <v>731</v>
+      </c>
+      <c r="L321" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="M321" t="n">
+        <v>10</v>
+      </c>
+      <c r="N321" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O321" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>visual slam, object detection, deep learning, computer vision, robot perception, pose estimation</t>
+        </is>
+      </c>
+      <c r="R321" t="n">
+        <v>16</v>
+      </c>
+      <c r="S321" t="n">
+        <v>42</v>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>DynaPix SLAM: A Pixel-Based Dynamic Visual SLAM Approach</t>
+        </is>
+      </c>
+      <c r="V321" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W321" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-stuttgart.de%20%22Aamir%20Ahmad%22%20email</t>
+        </is>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5087038946</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=621)</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>@uni-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G322" t="n">
+        <v>5</v>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Michael Hanss</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J322" t="n">
+        <v>19</v>
+      </c>
+      <c r="K322" t="n">
+        <v>1826</v>
+      </c>
+      <c r="L322" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M322" t="n">
+        <v>10</v>
+      </c>
+      <c r="N322" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O322" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>robot localization, state estimation, mobile robot navigation</t>
+        </is>
+      </c>
+      <c r="R322" t="n">
+        <v>6</v>
+      </c>
+      <c r="S322" t="n">
+        <v>22</v>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>Possibilistic filtering for reliable robot localization</t>
+        </is>
+      </c>
+      <c r="V322" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W322" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X322" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-stuttgart.de%20%22Michael%20Hanss%22%20email</t>
+        </is>
+      </c>
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5057641104</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=621)</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>@uni-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G323" t="n">
+        <v>6</v>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Michael Cramer</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J323" t="n">
+        <v>19</v>
+      </c>
+      <c r="K323" t="n">
+        <v>1828</v>
+      </c>
+      <c r="L323" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="M323" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="N323" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O323" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>sensor fusion, trajectory estimation</t>
+        </is>
+      </c>
+      <c r="R323" t="n">
+        <v>1</v>
+      </c>
+      <c r="S323" t="n">
+        <v>9</v>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>Data Acquisition in Geographic Information Systems</t>
+        </is>
+      </c>
+      <c r="V323" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W323" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X323" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-stuttgart.de%20%22Michael%20Cramer%22%20email</t>
+        </is>
+      </c>
+      <c r="Z323" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5088063230</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=621)</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>@uni-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G324" t="n">
+        <v>7</v>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Andreas Wortmann</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J324" t="n">
+        <v>32</v>
+      </c>
+      <c r="K324" t="n">
+        <v>3215</v>
+      </c>
+      <c r="L324" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="M324" t="n">
+        <v>10</v>
+      </c>
+      <c r="N324" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O324" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>autonomous navigation, mobile robot navigation, ros, ros2</t>
+        </is>
+      </c>
+      <c r="R324" t="n">
+        <v>1</v>
+      </c>
+      <c r="S324" t="n">
+        <v>101</v>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>Tuning ROS 2 for Energy-Efficient Navigation: Empirical Insights from Costmap 2D Configurations</t>
+        </is>
+      </c>
+      <c r="V324" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W324" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X324" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-stuttgart.de%20%22Andreas%20Wortmann%22%20email</t>
+        </is>
+      </c>
+      <c r="Z324" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5052537841</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=621)</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>@uni-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G325" t="n">
+        <v>8</v>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Bin Yang</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J325" t="n">
+        <v>35</v>
+      </c>
+      <c r="K325" t="n">
+        <v>4976</v>
+      </c>
+      <c r="L325" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="M325" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N325" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O325" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>sensor fusion, 3d perception, 3d object detection, deep learning, object detection, visual slam</t>
+        </is>
+      </c>
+      <c r="R325" t="n">
+        <v>2</v>
+      </c>
+      <c r="S325" t="n">
+        <v>94</v>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>Exploring Domain Shift on Radar-Based 3D Object Detection Amidst Diverse Environmental Conditions</t>
+        </is>
+      </c>
+      <c r="V325" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W325" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X325" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-stuttgart.de%20%22Bin%20Yang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z325" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5101717968</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=621)</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>@uni-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G326" t="n">
+        <v>9</v>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Oliver Sawodny</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J326" t="n">
+        <v>43</v>
+      </c>
+      <c r="K326" t="n">
+        <v>8906</v>
+      </c>
+      <c r="L326" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M326" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N326" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O326" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>visual slam</t>
+        </is>
+      </c>
+      <c r="R326" t="n">
+        <v>1</v>
+      </c>
+      <c r="S326" t="n">
+        <v>241</v>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>Active visual SLAM using potential fields and model predictive control</t>
+        </is>
+      </c>
+      <c r="V326" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W326" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X326" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-stuttgart.de%20%22Oliver%20Sawodny%22%20email</t>
+        </is>
+      </c>
+      <c r="Z326" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5054507125</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=621)</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>@uni-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G327" t="n">
+        <v>10</v>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Alexander W. Verl</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J327" t="n">
+        <v>40</v>
+      </c>
+      <c r="K327" t="n">
+        <v>9054</v>
+      </c>
+      <c r="L327" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="M327" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N327" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O327" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>robot localization, pose estimation, deep learning</t>
+        </is>
+      </c>
+      <c r="R327" t="n">
+        <v>2</v>
+      </c>
+      <c r="S327" t="n">
+        <v>280</v>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>Autonomous Mobile Robot Localization for Material Transport in Construction Prefabrication</t>
+        </is>
+      </c>
+      <c r="V327" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W327" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X327" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-stuttgart.de%20%22Alexander%20W.%20Verl%22%20email</t>
+        </is>
+      </c>
+      <c r="Z327" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5048205111</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=621)</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>@uni-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G328" t="n">
+        <v>11</v>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Armin Lechler</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J328" t="n">
+        <v>20</v>
+      </c>
+      <c r="K328" t="n">
+        <v>1963</v>
+      </c>
+      <c r="L328" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="M328" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N328" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O328" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>robot localization, pose estimation, deep learning</t>
+        </is>
+      </c>
+      <c r="R328" t="n">
+        <v>2</v>
+      </c>
+      <c r="S328" t="n">
+        <v>167</v>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>Autonomous Mobile Robot Localization for Material Transport in Construction Prefabrication</t>
+        </is>
+      </c>
+      <c r="V328" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W328" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X328" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-stuttgart.de%20%22Armin%20Lechler%22%20email</t>
+        </is>
+      </c>
+      <c r="Z328" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5019055244</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=621)</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>@uni-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G329" t="n">
+        <v>12</v>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Peter Eberhard</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J329" t="n">
+        <v>39</v>
+      </c>
+      <c r="K329" t="n">
+        <v>7167</v>
+      </c>
+      <c r="L329" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="M329" t="n">
+        <v>10</v>
+      </c>
+      <c r="N329" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O329" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>state estimation, robot localization</t>
+        </is>
+      </c>
+      <c r="R329" t="n">
+        <v>2</v>
+      </c>
+      <c r="S329" t="n">
+        <v>323</v>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>Formulating Multibody Models for Moving Horizon Estimation</t>
+        </is>
+      </c>
+      <c r="V329" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W329" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X329" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-stuttgart.de%20%22Peter%20Eberhard%22%20email</t>
+        </is>
+      </c>
+      <c r="Z329" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5044233744</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=621)</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>@uni-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G330" t="n">
+        <v>13</v>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>Nico Sneeuw</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J330" t="n">
+        <v>38</v>
+      </c>
+      <c r="K330" t="n">
+        <v>5226</v>
+      </c>
+      <c r="L330" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="M330" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N330" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O330" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>gnss positioning</t>
+        </is>
+      </c>
+      <c r="R330" t="n">
+        <v>1</v>
+      </c>
+      <c r="S330" t="n">
+        <v>104</v>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>Least squares Fourier filter for processing incomplete and heterogeneous GNSS position time series</t>
+        </is>
+      </c>
+      <c r="V330" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W330" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X330" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-stuttgart.de%20%22Nico%20Sneeuw%22%20email</t>
+        </is>
+      </c>
+      <c r="Z330" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5063179093</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=621)</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>@uni-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G331" t="n">
+        <v>14</v>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Erik W. Grafarend</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J331" t="n">
+        <v>37</v>
+      </c>
+      <c r="K331" t="n">
+        <v>4771</v>
+      </c>
+      <c r="L331" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="M331" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N331" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O331" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>gnss positioning</t>
+        </is>
+      </c>
+      <c r="R331" t="n">
+        <v>1</v>
+      </c>
+      <c r="S331" t="n">
+        <v>18</v>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>Integer Least Squares</t>
+        </is>
+      </c>
+      <c r="V331" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W331" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X331" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-stuttgart.de%20%22Erik%20W.%20Grafarend%22%20email</t>
+        </is>
+      </c>
+      <c r="Z331" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5109594370</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=621)</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>@uni-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G332" t="n">
+        <v>15</v>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Nasser Jazdi</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J332" t="n">
+        <v>28</v>
+      </c>
+      <c r="K332" t="n">
+        <v>4465</v>
+      </c>
+      <c r="L332" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="M332" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N332" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O332" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>stereo vision, kalman filter</t>
+        </is>
+      </c>
+      <c r="R332" t="n">
+        <v>1</v>
+      </c>
+      <c r="S332" t="n">
+        <v>165</v>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>Audio Guide for Visually Impaired People Based on Combination of Stereo Vision and Musical Tones</t>
+        </is>
+      </c>
+      <c r="V332" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W332" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X332" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-stuttgart.de%20%22Nasser%20Jazdi%22%20email</t>
+        </is>
+      </c>
+      <c r="Z332" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5042926074</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=621)</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>@uni-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G333" t="n">
+        <v>16</v>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Kai O. Arras</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J333" t="n">
+        <v>38</v>
+      </c>
+      <c r="K333" t="n">
+        <v>5765</v>
+      </c>
+      <c r="L333" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="M333" t="n">
+        <v>10</v>
+      </c>
+      <c r="N333" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O333" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>robot perception, 3d object detection, object detection</t>
+        </is>
+      </c>
+      <c r="R333" t="n">
+        <v>3</v>
+      </c>
+      <c r="S333" t="n">
+        <v>28</v>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>FunGraph: Functionality Aware 3D Scene Graphs for Language-Prompted Scene Interaction</t>
+        </is>
+      </c>
+      <c r="V333" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W333" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X333" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-stuttgart.de%20%22Kai%20O.%20Arras%22%20email</t>
+        </is>
+      </c>
+      <c r="Z333" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5111969299</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=621)</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>@uni-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G334" t="n">
+        <v>17</v>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Marco F. Huber</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J334" t="n">
+        <v>26</v>
+      </c>
+      <c r="K334" t="n">
+        <v>4440</v>
+      </c>
+      <c r="L334" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="M334" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N334" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O334" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Robotics &amp; Autonomous Navigation; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>pose estimation, deep learning, robot perception, point cloud registration</t>
+        </is>
+      </c>
+      <c r="R334" t="n">
+        <v>3</v>
+      </c>
+      <c r="S334" t="n">
+        <v>179</v>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>Robotic Wiring Harness Bin Picking Solution Using a Deep-Learning-Based Spline Prediction and a Multi-stereo Camera Setup</t>
+        </is>
+      </c>
+      <c r="V334" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W334" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X334" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-stuttgart.de%20%22Marco%20F.%20Huber%22%20email</t>
+        </is>
+      </c>
+      <c r="Z334" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5031354877</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=621)</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>@uni-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G335" t="n">
+        <v>18</v>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Volker Schwieger</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J335" t="n">
+        <v>15</v>
+      </c>
+      <c r="K335" t="n">
+        <v>819</v>
+      </c>
+      <c r="L335" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="M335" t="n">
+        <v>10</v>
+      </c>
+      <c r="N335" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O335" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>gnss positioning, point cloud registration</t>
+        </is>
+      </c>
+      <c r="R335" t="n">
+        <v>2</v>
+      </c>
+      <c r="S335" t="n">
+        <v>46</v>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>Multi-sensor system for efficient in-service vehicle-based track monitoring and fault localization: a case study</t>
+        </is>
+      </c>
+      <c r="V335" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W335" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X335" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-stuttgart.de%20%22Volker%20Schwieger%22%20email</t>
+        </is>
+      </c>
+      <c r="Z335" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5076080173</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=621)</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>@uni-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G336" t="n">
+        <v>19</v>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>Achim Menges</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J336" t="n">
+        <v>43</v>
+      </c>
+      <c r="K336" t="n">
+        <v>7019</v>
+      </c>
+      <c r="L336" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="M336" t="n">
+        <v>10</v>
+      </c>
+      <c r="N336" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O336" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>pose estimation</t>
+        </is>
+      </c>
+      <c r="R336" t="n">
+        <v>1</v>
+      </c>
+      <c r="S336" t="n">
+        <v>200</v>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>Toward autonomous timber construction using distributed robotic perception system in coordination with a tower crane</t>
+        </is>
+      </c>
+      <c r="V336" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W336" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X336" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-stuttgart.de%20%22Achim%20Menges%22%20email</t>
+        </is>
+      </c>
+      <c r="Z336" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5008295233</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=621)</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>@uni-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G337" t="n">
+        <v>20</v>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Erich Kasper</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J337" t="n">
+        <v>51</v>
+      </c>
+      <c r="K337" t="n">
+        <v>9451</v>
+      </c>
+      <c r="L337" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="M337" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N337" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O337" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>robot perception</t>
+        </is>
+      </c>
+      <c r="R337" t="n">
+        <v>1</v>
+      </c>
+      <c r="S337" t="n">
+        <v>20</v>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>Design and Verification of a Two-Chip-Cascaded 4D mm-Wave Imaging Radar for Indoor SLAM</t>
+        </is>
+      </c>
+      <c r="V337" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W337" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X337" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-stuttgart.de%20%22Erich%20Kasper%22%20email</t>
+        </is>
+      </c>
+      <c r="Z337" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5081222836</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Karlsruhe Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Karlsruhe</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>QS #102 (Strong Robotics) | Tier S+ (Global Elite | h=863)</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>@kit.edu</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G338" t="n">
+        <v>1</v>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Rainer Stiefelhagen</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J338" t="n">
+        <v>65</v>
+      </c>
+      <c r="K338" t="n">
+        <v>18785</v>
+      </c>
+      <c r="L338" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="M338" t="n">
+        <v>10</v>
+      </c>
+      <c r="N338" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O338" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>visual slam, visual odometry, autonomous navigation, sensor fusion, pose estimation, visual localization</t>
+        </is>
+      </c>
+      <c r="R338" t="n">
+        <v>12</v>
+      </c>
+      <c r="S338" t="n">
+        <v>290</v>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>Tightly-Coupled LiDAR-Visual SLAM Based on Geometric Features for Mobile Agents</t>
+        </is>
+      </c>
+      <c r="V338" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W338" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X338" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Akit.edu%20%22Rainer%20Stiefelhagen%22%20email</t>
+        </is>
+      </c>
+      <c r="Z338" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5087051920</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Karlsruhe Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Karlsruhe</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>QS #102 (Strong Robotics) | Tier S+ (Global Elite | h=863)</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>@kit.edu</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G339" t="n">
+        <v>2</v>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>Ruiping Liu</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J339" t="n">
+        <v>14</v>
+      </c>
+      <c r="K339" t="n">
+        <v>929</v>
+      </c>
+      <c r="L339" t="n">
+        <v>10</v>
+      </c>
+      <c r="M339" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N339" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O339" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; GNSS &amp; Robust Localization; Deep Learning for Navigation &amp; Perception</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>visual slam, visual odometry, autonomous navigation, sensor fusion, pose estimation, visual localization</t>
+        </is>
+      </c>
+      <c r="R339" t="n">
+        <v>4</v>
+      </c>
+      <c r="S339" t="n">
+        <v>23</v>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>Tightly-Coupled LiDAR-Visual SLAM Based on Geometric Features for Mobile Agents</t>
+        </is>
+      </c>
+      <c r="V339" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W339" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X339" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Akit.edu%20%22Ruiping%20Liu%22%20email</t>
+        </is>
+      </c>
+      <c r="Z339" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100767259</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Karlsruhe Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Karlsruhe</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>QS #102 (Strong Robotics) | Tier S+ (Global Elite | h=863)</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>@kit.edu</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G340" t="n">
+        <v>3</v>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Yufan Chen</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J340" t="n">
+        <v>21</v>
+      </c>
+      <c r="K340" t="n">
+        <v>1423</v>
+      </c>
+      <c r="L340" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="M340" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N340" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O340" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>visual localization, visual odometry, 3d reconstruction, robust localization, pose estimation</t>
+        </is>
+      </c>
+      <c r="R340" t="n">
+        <v>2</v>
+      </c>
+      <c r="S340" t="n">
+        <v>87</v>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>Scene-agnostic Pose Regression for Visual Localization</t>
+        </is>
+      </c>
+      <c r="V340" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W340" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X340" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Akit.edu%20%22Yufan%20Chen%22%20email</t>
+        </is>
+      </c>
+      <c r="Z340" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100628847</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Karlsruhe Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Karlsruhe</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>QS #102 (Strong Robotics) | Tier S+ (Global Elite | h=863)</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>@kit.edu</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G341" t="n">
+        <v>4</v>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Uwe D. Hanebeck</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J341" t="n">
+        <v>40</v>
+      </c>
+      <c r="K341" t="n">
+        <v>8423</v>
+      </c>
+      <c r="L341" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="M341" t="n">
+        <v>10</v>
+      </c>
+      <c r="N341" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O341" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; Visual-Inertial Navigation &amp; SLAM; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, state estimation, sensor fusion, kalman filter</t>
+        </is>
+      </c>
+      <c r="R341" t="n">
+        <v>12</v>
+      </c>
+      <c r="S341" t="n">
+        <v>227</v>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>Continuous-Time Ultra-Wideband-Inertial Fusion</t>
+        </is>
+      </c>
+      <c r="V341" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W341" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X341" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Akit.edu%20%22Uwe%20D.%20Hanebeck%22%20email</t>
+        </is>
+      </c>
+      <c r="Z341" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5055331421</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Karlsruhe Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Karlsruhe</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>QS #102 (Strong Robotics) | Tier S+ (Global Elite | h=863)</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>@kit.edu</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G342" t="n">
+        <v>5</v>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Markus Ulrich</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J342" t="n">
+        <v>15</v>
+      </c>
+      <c r="K342" t="n">
+        <v>2168</v>
+      </c>
+      <c r="L342" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="M342" t="n">
+        <v>10</v>
+      </c>
+      <c r="N342" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O342" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>3d reconstruction, pose estimation, 3d computer vision, computer vision, robot localization, place recognition</t>
+        </is>
+      </c>
+      <c r="R342" t="n">
+        <v>13</v>
+      </c>
+      <c r="S342" t="n">
+        <v>66</v>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>An evaluation of DUSt3R/MASt3R/VGGT 3D reconstruction on photogrammetric aerial blocks</t>
+        </is>
+      </c>
+      <c r="V342" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W342" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X342" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Akit.edu%20%22Markus%20Ulrich%22%20email</t>
+        </is>
+      </c>
+      <c r="Z342" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5031522635</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Karlsruhe Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Karlsruhe</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>QS #102 (Strong Robotics) | Tier S+ (Global Elite | h=863)</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>@kit.edu</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G343" t="n">
+        <v>6</v>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Gert F. Trommer</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J343" t="n">
+        <v>22</v>
+      </c>
+      <c r="K343" t="n">
+        <v>1860</v>
+      </c>
+      <c r="L343" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="M343" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="N343" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O343" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R343" t="n">
+        <v>1</v>
+      </c>
+      <c r="S343" t="n">
+        <v>7</v>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>2021-12-01</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>x-RIO: Radar Inertial Odometry with Multiple Radar Sensors and Yaw Aiding</t>
+        </is>
+      </c>
+      <c r="V343" t="n">
+        <v>2021</v>
+      </c>
+      <c r="W343" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X343" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Akit.edu%20%22Gert%20F.%20Trommer%22%20email</t>
+        </is>
+      </c>
+      <c r="Z343" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5075440290</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Karlsruhe Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Karlsruhe</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>QS #102 (Strong Robotics) | Tier S+ (Global Elite | h=863)</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>@kit.edu</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G344" t="n">
+        <v>7</v>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>Christoph Stiller</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J344" t="n">
+        <v>60</v>
+      </c>
+      <c r="K344" t="n">
+        <v>24481</v>
+      </c>
+      <c r="L344" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="M344" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N344" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O344" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>visual slam, 3d perception, deep learning, point cloud registration, sensor fusion, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R344" t="n">
+        <v>5</v>
+      </c>
+      <c r="S344" t="n">
+        <v>120</v>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>Deep geometry-aware camera self-calibration from video</t>
+        </is>
+      </c>
+      <c r="V344" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W344" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X344" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Akit.edu%20%22Christoph%20Stiller%22%20email</t>
+        </is>
+      </c>
+      <c r="Z344" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5091574711</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Karlsruhe Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Karlsruhe</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>QS #102 (Strong Robotics) | Tier S+ (Global Elite | h=863)</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>@kit.edu</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G345" t="n">
+        <v>8</v>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>B. Jutzi</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J345" t="n">
+        <v>24</v>
+      </c>
+      <c r="K345" t="n">
+        <v>3362</v>
+      </c>
+      <c r="L345" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="M345" t="n">
+        <v>10</v>
+      </c>
+      <c r="N345" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O345" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>gaussian splatting, pose estimation, computer vision, 3d reconstruction, depth estimation, deep learning</t>
+        </is>
+      </c>
+      <c r="R345" t="n">
+        <v>12</v>
+      </c>
+      <c r="S345" t="n">
+        <v>69</v>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>HoloGS: Instant Depth-based 3D Gaussian Splatting with Microsoft HoloLens 2</t>
+        </is>
+      </c>
+      <c r="V345" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W345" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X345" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Akit.edu%20%22B.%20Jutzi%22%20email</t>
+        </is>
+      </c>
+      <c r="Z345" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5065772342</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Karlsruhe Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Karlsruhe</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>QS #102 (Strong Robotics) | Tier S+ (Global Elite | h=863)</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>@kit.edu</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G346" t="n">
+        <v>9</v>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Rudolph Triebel</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J346" t="n">
+        <v>37</v>
+      </c>
+      <c r="K346" t="n">
+        <v>7434</v>
+      </c>
+      <c r="L346" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M346" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N346" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O346" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>visual slam, pose estimation, point cloud registration</t>
+        </is>
+      </c>
+      <c r="R346" t="n">
+        <v>2</v>
+      </c>
+      <c r="S346" t="n">
+        <v>153</v>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>Improving SLAM‐Based Navigation in Flexible Ureteroscopy by Kidney Stone and Surgical Tool Segmentation</t>
+        </is>
+      </c>
+      <c r="V346" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W346" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X346" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Akit.edu%20%22Rudolph%20Triebel%22%20email</t>
+        </is>
+      </c>
+      <c r="Z346" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5050478468</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Karlsruhe Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Karlsruhe</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>QS #102 (Strong Robotics) | Tier S+ (Global Elite | h=863)</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>@kit.edu</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G347" t="n">
+        <v>10</v>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Martin Weinmann</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J347" t="n">
+        <v>28</v>
+      </c>
+      <c r="K347" t="n">
+        <v>3893</v>
+      </c>
+      <c r="L347" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="M347" t="n">
+        <v>10</v>
+      </c>
+      <c r="N347" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O347" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; LiDAR &amp; Multimodal Sensor Fusion; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>point cloud registration, sensor calibration, object detection, depth estimation, 3d reconstruction, deep learning</t>
+        </is>
+      </c>
+      <c r="R347" t="n">
+        <v>7</v>
+      </c>
+      <c r="S347" t="n">
+        <v>54</v>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>Preface: Workshop “Laser Scanning 2023”</t>
+        </is>
+      </c>
+      <c r="V347" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W347" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X347" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Akit.edu%20%22Martin%20Weinmann%22%20email</t>
+        </is>
+      </c>
+      <c r="Z347" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5083406305</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Karlsruhe Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Karlsruhe</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>QS #102 (Strong Robotics) | Tier S+ (Global Elite | h=863)</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>@kit.edu</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G348" t="n">
+        <v>11</v>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Hansjörg Kutterer</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J348" t="n">
+        <v>17</v>
+      </c>
+      <c r="K348" t="n">
+        <v>1399</v>
+      </c>
+      <c r="L348" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="M348" t="n">
+        <v>10</v>
+      </c>
+      <c r="N348" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O348" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>gnss positioning, deep learning, point cloud registration</t>
+        </is>
+      </c>
+      <c r="R348" t="n">
+        <v>4</v>
+      </c>
+      <c r="S348" t="n">
+        <v>77</v>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>Real-Time GNSS Integrated Water Vapor Sensing Based on Time Series Correction Deep Learning Models</t>
+        </is>
+      </c>
+      <c r="V348" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W348" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X348" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Akit.edu%20%22Hansj%C3%B6rg%20Kutterer%22%20email</t>
+        </is>
+      </c>
+      <c r="Z348" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5022425194</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Karlsruhe Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Karlsruhe</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>QS #102 (Strong Robotics) | Tier S+ (Global Elite | h=863)</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>@kit.edu</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G349" t="n">
+        <v>12</v>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Tamim Asfour</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J349" t="n">
+        <v>59</v>
+      </c>
+      <c r="K349" t="n">
+        <v>12955</v>
+      </c>
+      <c r="L349" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="M349" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N349" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O349" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; LiDAR &amp; Multimodal Sensor Fusion; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>pose estimation, object detection, robot perception</t>
+        </is>
+      </c>
+      <c r="R349" t="n">
+        <v>6</v>
+      </c>
+      <c r="S349" t="n">
+        <v>115</v>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>Virtual Reality via Object Pose Estimation and Active Learning: Realizing Telepresence Robots with Aerial Manipulation Capabilities</t>
+        </is>
+      </c>
+      <c r="V349" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W349" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X349" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Akit.edu%20%22Tamim%20Asfour%22%20email</t>
+        </is>
+      </c>
+      <c r="Z349" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5012730104</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Karlsruhe Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Karlsruhe</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>QS #102 (Strong Robotics) | Tier S+ (Global Elite | h=863)</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>@kit.edu</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G350" t="n">
+        <v>13</v>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Gerhard M. Neumann</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J350" t="n">
+        <v>43</v>
+      </c>
+      <c r="K350" t="n">
+        <v>8876</v>
+      </c>
+      <c r="L350" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="M350" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N350" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O350" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>pose estimation, computer vision, semantic segmentation</t>
+        </is>
+      </c>
+      <c r="R350" t="n">
+        <v>2</v>
+      </c>
+      <c r="S350" t="n">
+        <v>114</v>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>2023-07-07</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>MV6D: Multi-View 6D Pose Estimation on RGB-D Frames Using a Deep Point-wise Voting Network</t>
+        </is>
+      </c>
+      <c r="V350" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W350" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X350" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Akit.edu%20%22Gerhard%20M.%20Neumann%22%20email</t>
+        </is>
+      </c>
+      <c r="Z350" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5110467801</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Karlsruhe Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Karlsruhe</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>QS #102 (Strong Robotics) | Tier S+ (Global Elite | h=863)</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>@kit.edu</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G351" t="n">
+        <v>14</v>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Jürgen Beyerer</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J351" t="n">
+        <v>36</v>
+      </c>
+      <c r="K351" t="n">
+        <v>6038</v>
+      </c>
+      <c r="L351" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="M351" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N351" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O351" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; State Estimation &amp; Factor Graphs; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>pose estimation, point cloud registration, 3d computer vision, computer vision, kalman filter</t>
+        </is>
+      </c>
+      <c r="R351" t="n">
+        <v>4</v>
+      </c>
+      <c r="S351" t="n">
+        <v>379</v>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>6D Pose Estimation on Point Cloud Data through Prior Knowledge Integration: A Case Study in Autonomous Disassembly</t>
+        </is>
+      </c>
+      <c r="V351" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W351" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X351" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Akit.edu%20%22J%C3%BCrgen%20Beyerer%22%20email</t>
+        </is>
+      </c>
+      <c r="Z351" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5073930300</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Karlsruhe Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Karlsruhe</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>QS #102 (Strong Robotics) | Tier S+ (Global Elite | h=863)</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>@kit.edu</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G352" t="n">
+        <v>15</v>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Michael Heizmann</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J352" t="n">
+        <v>17</v>
+      </c>
+      <c r="K352" t="n">
+        <v>1112</v>
+      </c>
+      <c r="L352" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="M352" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N352" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O352" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; 3D Computer Vision &amp; Geometric Perception; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>pose estimation, deep learning, object detection, semantic segmentation</t>
+        </is>
+      </c>
+      <c r="R352" t="n">
+        <v>4</v>
+      </c>
+      <c r="S352" t="n">
+        <v>136</v>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>6D Pose Estimation on Point Cloud Data through Prior Knowledge Integration: A Case Study in Autonomous Disassembly</t>
+        </is>
+      </c>
+      <c r="V352" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W352" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X352" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Akit.edu%20%22Michael%20Heizmann%22%20email</t>
+        </is>
+      </c>
+      <c r="Z352" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5065874009</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z276"/>
+  <autoFilter ref="A1:Z352"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AG$127</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Z$352</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Z$379</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +474,7 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
     <col width="21" customWidth="1" min="16" max="16"/>
     <col width="42" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
@@ -4139,23 +4139,147 @@
           <t>Technische Universität Berlin</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=658)</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5036853118</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Suman Ghosh</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>ES-PTAM: Event-Based Stereo Parallel Tracking and Mapping (2025)</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>@tu.berlin</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>I4577782</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=22)</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>visual odometry, pose estimation, depth estimation, 3d reconstruction, computer vision, deep learning</t>
+        </is>
+      </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>9.69</v>
       </c>
       <c r="Z28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>7.54</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" s="4" t="inlineStr"/>
-      <c r="AE28" s="4" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Suman Ghosh; Guillermo Gallego; Harald Schuh; Maarten Uijt de Haag; Jörg Krüger; Jens Lambrecht; Şahin Albayrak; Peter B. Neubauer; Rudibert King; Mariano Nicolás Cruz Bournazou; Giuseppe Caire; Olaf Hellwich; Oliver Brock; Maorong Ge; Jens Wickert; Cornelia Weltzien; Jungang Wang; David Bermbach; T. Hartmann</t>
+        </is>
+      </c>
+      <c r="AD28" s="4" t="inlineStr">
+        <is>
+          <t>1. Suman Ghosh (Full / Senior Prof (Large Lab), h=22) | Fit=9.6/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=8.1/10 | Keywords=visual odometry, pose estimation, depth estimation, 3d reconstruction, computer vision, deep learning | Paper=ES-PTAM: Event-Based Stereo Parallel Tracking and Mapping (2025)
+2. Guillermo Gallego (Full / Senior Prof (Large Lab), h=39) | Fit=9.4/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=8.0/10 | Keywords=visual inertial odometry, visual odometry, field robotics, pose estimation, depth estimation, 3d reconstruction | Paper=ESVO2: Direct Visual-Inertial Odometry With Stereo Event Cameras (2025)
+3. Harald Schuh (Full / Senior Prof (Large Lab), h=55) | Fit=8.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=gnss positioning, kalman filter, extended kalman filter | Paper=A novel robust sub-meter smartphone positioning using Graph Neural Networks and Kalman filter f (2026)
+4. Maarten Uijt de Haag (Full / Senior Prof (Large Lab), h=16) | Fit=7.9/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.1/10 | Keywords=factor graph optimization, sensor fusion, gnss positioning | Paper=Accuracy and Integrity Assessment of a sUAS UWB-Indoor Positioning System Using Factor Graph Op (2025)
+5. Jörg Krüger (Full / Senior Prof (Large Lab), h=32) | Fit=7.4/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.8/10 | Keywords=pose estimation, depth estimation, deep learning, robot localization | Paper=Vanishing Depth: Training Generalized Depth Adapters with Sinusoidal Depth Preprocessing for Pr (2026)
+6. Jens Lambrecht (Associate / Established PI (High Fit), h=19) | Fit=6.9/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.3/10 | Keywords=learning-based localization, ros, autonomous navigation, mobile robot navigation, object detection, semantic segmentation | Paper=Design of a Mobile Data Collection Robot for Learning-based Localization and Autonomous Driving (2023)
+7. Şahin Albayrak (Full / Senior Prof (Large Lab), h=34) | Fit=6.2/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.9/10 | Keywords=pose estimation, autonomous vehicles, computer vision | Paper=APR-Transformer: Initial Pose Estimation for Localization in Complex Environments through Absol (2025)
+8. Peter B. Neubauer (Full / Senior Prof (Large Lab), h=60) | Fit=6.2/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=5.7/10 | Keywords=state estimation, kalman filter | Paper=Nonlinear state estimation as tool for online monitoring and adaptive feed in high throughput c (2023)
+9. Rudibert King (Full / Senior Prof (Large Lab), h=40) | Fit=6.2/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=5.7/10 | Keywords=state estimation, kalman filter | Paper=Nonlinear state estimation as tool for online monitoring and adaptive feed in high throughput c (2023)
+10. Mariano Nicolás Cruz Bournazou (Associate / Established PI (High Fit), h=24) | Fit=6.2/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=5.7/10 | Keywords=state estimation, kalman filter | Paper=Nonlinear state estimation as tool for online monitoring and adaptive feed in high throughput c (2023)
+11. Giuseppe Caire (Full / Senior Prof (Large Lab), h=88) | Fit=5.4/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.5/10 | Keywords=gaussian splatting, gnss positioning, deep learning | Paper=Planar Gaussian Splatting with Bilinear Spatial Transformer for Wireless Radiance Field Reconst (2026)
+12. Olaf Hellwich (Full / Senior Prof (Large Lab), h=33) | Fit=5.4/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.4/10 | Keywords=depth estimation, pose estimation | Paper=MonoPP: Metric-Scaled Self-Supervised Monocular Depth Estimation by Planar-Parallax Geometry in (2025)
+13. Oliver Brock (Full / Senior Prof (Large Lab), h=48) | Fit=5.2/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.4/10 | Keywords=sensor fusion, robot perception | Paper=Coupled Particle Filters for Robust Affordance Estimation (2026)
+14. Maorong Ge (Full / Senior Prof (Large Lab), h=55) | Fit=5.2/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.2/10 | Keywords=gnss positioning | Paper=An integrated hierarchical wide-area augmentation for real-time GNSS positioning (2023)
+15. Jens Wickert (Full / Senior Prof (Large Lab), h=65) | Fit=4.9/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.0/10 | Keywords=gnss positioning, deep learning | Paper=Advancing Accuracy in Sea Level Estimation with GNSS-R: A Fusion of LSTM-DNN-Based Deep Learnin (2024)
+16. Cornelia Weltzien (Associate / Established PI (High Fit), h=23) | Fit=4.8/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.9/10 | Keywords=autonomous navigation, ros | Paper=Internet of robotic things with a local LoRa network for teleoperation of an agricultural mobil (2024)
+17. Jungang Wang (Associate / Established PI (High Fit), h=17) | Fit=4.5/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=4.9/10 | Keywords=gnss positioning | Paper=Accelerating multi-GNSS and multi-frequency PPP-AR convergence using global operational NWM for (2026)
+18. David Bermbach (Full / Senior Prof (Large Lab), h=27) | Fit=4.1/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.4/10 | Keywords=autonomous navigation | Paper=Supporting UAVs with Edge Computing: A Review of Opportunities and Challenges (2023)
+19. T. Hartmann (Full / Senior Prof (Large Lab), h=29) | Fit=3.6/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.3/10 | Keywords=point cloud registration, ros, ros2 | Paper=Automated integration of as-is point cloud information with as-planned BIM for interior constru (2023)</t>
+        </is>
+      </c>
+      <c r="AE28" s="4" t="inlineStr">
+        <is>
+          <t>Suman Ghosh: No homepage/funding evidence available
+Guillermo Gallego: No homepage/funding evidence available
+Harald Schuh: No homepage/funding evidence available
+Maarten Uijt de Haag: No homepage/funding evidence available
+Jörg Krüger: No homepage/funding evidence available
+Jens Lambrecht: No homepage/funding evidence available
+Şahin Albayrak: No homepage/funding evidence available
+Peter B. Neubauer: No homepage/funding evidence available
+Rudibert King: No homepage/funding evidence available
+Mariano Nicolás Cruz Bournazou: No homepage/funding evidence available
+Giuseppe Caire: No homepage/funding evidence available
+Olaf Hellwich: No homepage/funding evidence available
+Oliver Brock: No homepage/funding evidence available
+Maorong Ge: No homepage/funding evidence available
+Jens Wickert: No homepage/funding evidence available
+Cornelia Weltzien: No homepage/funding evidence available
+Jungang Wang: No homepage/funding evidence available
+David Bermbach: No homepage/funding evidence available
+T. Hartmann: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu.berlin%20%22Suman%20Ghosh%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
@@ -4163,23 +4287,111 @@
           <t>Freie Universität Berlin</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=742)</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5007762628</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Daniel Goehring</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>MaskVal: Simple but Effective Uncertainty Quantification for 6D Pose Estimation (2024)</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>@fu-berlin.de</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>I75951250</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive) (h=15)</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>pose estimation</t>
+        </is>
+      </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="Z29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="4" t="inlineStr"/>
-      <c r="AE29" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Daniel Goehring</t>
+        </is>
+      </c>
+      <c r="AD29" s="4" t="inlineStr">
+        <is>
+          <t>1. Daniel Goehring (Assistant Prof / Rising Star (Responsive), h=15) | Fit=4.5/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.7/10 | Keywords=pose estimation | Paper=MaskVal: Simple but Effective Uncertainty Quantification for 6D Pose Estimation (2024)</t>
+        </is>
+      </c>
+      <c r="AE29" s="4" t="inlineStr">
+        <is>
+          <t>Daniel Goehring: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Afu-berlin.de%20%22Daniel%20Goehring%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
@@ -4187,23 +4399,117 @@
           <t>Humboldt University of Berlin</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=816)</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5085207296</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Jürgen Kurths</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Perception and Navigation in Autonomous Systems in the Era of Learning: A Survey (2022)</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>@hu-berlin.de</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>I39343248</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=135)</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>visual slam, state estimation, autonomous navigation, depth estimation, deep learning, object detection</t>
+        </is>
+      </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="Z30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" s="4" t="inlineStr"/>
-      <c r="AE30" s="4" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Jürgen Kurths; Peter Eisert; Jens Krause; Anna Hilsmann</t>
+        </is>
+      </c>
+      <c r="AD30" s="4" t="inlineStr">
+        <is>
+          <t>1. Jürgen Kurths (Full / Senior Prof (Large Lab), h=135) | Fit=10.0/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=8.1/10 | Keywords=visual slam, state estimation, autonomous navigation, depth estimation, deep learning, object detection | Paper=Perception and Navigation in Autonomous Systems in the Era of Learning: A Survey (2022)
+2. Peter Eisert (Full / Senior Prof (Large Lab), h=34) | Fit=8.9/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=point cloud registration, sensor fusion, pose estimation, autonomous driving perception, computer vision, gaussian splatting | Paper=EdgeRegNet: Edge Feature-Based Multimodal Registration Network Between Images and LiDAR Point C (2025)
+3. Jens Krause (Full / Senior Prof (Large Lab), h=84) | Fit=8.6/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.5/10 | Keywords=multi-sensor fusion, state estimation, sensor fusion, computer vision, semantic segmentation | Paper=Watching Swarm Dynamics from Above: A Framework for Advanced Object Tracking in Drone Videos (2024)
+4. Anna Hilsmann (Full / Senior Prof (Large Lab), h=21) | Fit=5.0/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.2/10 | Keywords=gaussian splatting | Paper=KISS-GS: 3D Gaussian Splatting Compression Kept Simple (2026)</t>
+        </is>
+      </c>
+      <c r="AE30" s="4" t="inlineStr">
+        <is>
+          <t>Jürgen Kurths: No homepage/funding evidence available
+Peter Eisert: No homepage/funding evidence available
+Jens Krause: No homepage/funding evidence available
+Anna Hilsmann: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ahu-berlin.de%20%22J%C3%BCrgen%20Kurths%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
@@ -4211,28 +4517,153 @@
           <t>Saarland University</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=559)</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5026514026</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Philipp Slusallek</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Edge-Aware Consistent Stereo Video Depth Estimation (2025)</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Saarbrücken</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>@uni-saarland.de</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>I91712215</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=41)</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>depth estimation</t>
+        </is>
+      </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Z31" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="4" t="inlineStr"/>
-      <c r="AE31" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Philipp Slusallek; M. Schneider</t>
+        </is>
+      </c>
+      <c r="AD31" s="4" t="inlineStr">
+        <is>
+          <t>1. Philipp Slusallek (Full / Senior Prof (Large Lab), h=41) | Fit=5.1/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.1/10 | Keywords=depth estimation | Paper=Edge-Aware Consistent Stereo Video Depth Estimation (2025)
+2. M. Schneider (Associate / Established PI (High Fit), h=15) | Fit=4.2/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.5/10 | Keywords=point cloud registration | Paper=An Approach for Precise Robotic Sanding Applications of Uneven Surfaces Based on Improved Point (2024)</t>
+        </is>
+      </c>
+      <c r="AE31" s="4" t="inlineStr">
+        <is>
+          <t>Philipp Slusallek: No homepage/funding evidence available
+M. Schneider: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-saarland.de%20%22Philipp%20Slusallek%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
           <t>TU Dresden</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Tier B (Specialized/Regional | h=11)</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Dresden</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>@vufo.de</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>I4405269591</t>
         </is>
       </c>
       <c r="X32" t="n">
@@ -6485,7 +6916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z352"/>
+  <dimension ref="A1:Z379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -44205,8 +44636,2847 @@
         </is>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Technische Universität Berlin</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=658)</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>@tu.berlin</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G353" t="n">
+        <v>1</v>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Suman Ghosh</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J353" t="n">
+        <v>22</v>
+      </c>
+      <c r="K353" t="n">
+        <v>2097</v>
+      </c>
+      <c r="L353" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="M353" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N353" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O353" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>visual odometry, pose estimation, depth estimation, 3d reconstruction, computer vision, deep learning</t>
+        </is>
+      </c>
+      <c r="R353" t="n">
+        <v>5</v>
+      </c>
+      <c r="S353" t="n">
+        <v>45</v>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>ES-PTAM: Event-Based Stereo Parallel Tracking and Mapping</t>
+        </is>
+      </c>
+      <c r="V353" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W353" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X353" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu.berlin%20%22Suman%20Ghosh%22%20email</t>
+        </is>
+      </c>
+      <c r="Z353" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5036853118</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Technische Universität Berlin</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=658)</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>@tu.berlin</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G354" t="n">
+        <v>2</v>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Guillermo Gallego</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J354" t="n">
+        <v>39</v>
+      </c>
+      <c r="K354" t="n">
+        <v>9884</v>
+      </c>
+      <c r="L354" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="M354" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N354" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O354" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, visual odometry, field robotics, pose estimation, depth estimation, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R354" t="n">
+        <v>10</v>
+      </c>
+      <c r="S354" t="n">
+        <v>85</v>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>ESVO2: Direct Visual-Inertial Odometry With Stereo Event Cameras</t>
+        </is>
+      </c>
+      <c r="V354" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W354" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X354" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu.berlin%20%22Guillermo%20Gallego%22%20email</t>
+        </is>
+      </c>
+      <c r="Z354" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5068567652</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Technische Universität Berlin</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=658)</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>@tu.berlin</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G355" t="n">
+        <v>3</v>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Harald Schuh</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J355" t="n">
+        <v>55</v>
+      </c>
+      <c r="K355" t="n">
+        <v>14542</v>
+      </c>
+      <c r="L355" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="M355" t="n">
+        <v>10</v>
+      </c>
+      <c r="N355" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O355" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>gnss positioning, kalman filter, extended kalman filter</t>
+        </is>
+      </c>
+      <c r="R355" t="n">
+        <v>17</v>
+      </c>
+      <c r="S355" t="n">
+        <v>381</v>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>A novel robust sub-meter smartphone positioning using Graph Neural Networks and Kalman filter fusion in complex urban environments</t>
+        </is>
+      </c>
+      <c r="V355" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W355" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X355" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu.berlin%20%22Harald%20Schuh%22%20email</t>
+        </is>
+      </c>
+      <c r="Z355" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5014145696</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Technische Universität Berlin</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=658)</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>@tu.berlin</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G356" t="n">
+        <v>4</v>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Maarten Uijt de Haag</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J356" t="n">
+        <v>16</v>
+      </c>
+      <c r="K356" t="n">
+        <v>1125</v>
+      </c>
+      <c r="L356" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="M356" t="n">
+        <v>10</v>
+      </c>
+      <c r="N356" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O356" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>factor graph optimization, sensor fusion, gnss positioning</t>
+        </is>
+      </c>
+      <c r="R356" t="n">
+        <v>3</v>
+      </c>
+      <c r="S356" t="n">
+        <v>44</v>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>Accuracy and Integrity Assessment of a sUAS UWB-Indoor Positioning System Using Factor Graph Optimization</t>
+        </is>
+      </c>
+      <c r="V356" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W356" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X356" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu.berlin%20%22Maarten%20Uijt%20de%20Haag%22%20email</t>
+        </is>
+      </c>
+      <c r="Z356" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5018613285</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Technische Universität Berlin</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=658)</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>@tu.berlin</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G357" t="n">
+        <v>5</v>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Jörg Krüger</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J357" t="n">
+        <v>32</v>
+      </c>
+      <c r="K357" t="n">
+        <v>4895</v>
+      </c>
+      <c r="L357" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="M357" t="n">
+        <v>10</v>
+      </c>
+      <c r="N357" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O357" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>pose estimation, depth estimation, deep learning, robot localization</t>
+        </is>
+      </c>
+      <c r="R357" t="n">
+        <v>3</v>
+      </c>
+      <c r="S357" t="n">
+        <v>110</v>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>Vanishing Depth: Training Generalized Depth Adapters with Sinusoidal Depth Preprocessing for Pretrained RGB Encoders</t>
+        </is>
+      </c>
+      <c r="V357" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W357" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X357" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu.berlin%20%22J%C3%B6rg%20Kr%C3%BCger%22%20email</t>
+        </is>
+      </c>
+      <c r="Z357" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5065074078</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Technische Universität Berlin</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=658)</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>@tu.berlin</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G358" t="n">
+        <v>6</v>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Jens Lambrecht</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J358" t="n">
+        <v>19</v>
+      </c>
+      <c r="K358" t="n">
+        <v>935</v>
+      </c>
+      <c r="L358" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="M358" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N358" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O358" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Deep Learning for Navigation &amp; Perception; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>learning-based localization, ros, autonomous navigation, mobile robot navigation, object detection, semantic segmentation</t>
+        </is>
+      </c>
+      <c r="R358" t="n">
+        <v>10</v>
+      </c>
+      <c r="S358" t="n">
+        <v>65</v>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>Design of a Mobile Data Collection Robot for Learning-based Localization and Autonomous Driving</t>
+        </is>
+      </c>
+      <c r="V358" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W358" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X358" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu.berlin%20%22Jens%20Lambrecht%22%20email</t>
+        </is>
+      </c>
+      <c r="Z358" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5002499102</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Technische Universität Berlin</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=658)</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>@tu.berlin</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G359" t="n">
+        <v>7</v>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Şahin Albayrak</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J359" t="n">
+        <v>34</v>
+      </c>
+      <c r="K359" t="n">
+        <v>5946</v>
+      </c>
+      <c r="L359" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="M359" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N359" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O359" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>pose estimation, autonomous vehicles, computer vision</t>
+        </is>
+      </c>
+      <c r="R359" t="n">
+        <v>1</v>
+      </c>
+      <c r="S359" t="n">
+        <v>53</v>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>APR-Transformer: Initial Pose Estimation for Localization in Complex Environments through Absolute Pose Regression</t>
+        </is>
+      </c>
+      <c r="V359" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W359" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X359" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu.berlin%20%22%C5%9Eahin%20Albayrak%22%20email</t>
+        </is>
+      </c>
+      <c r="Z359" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5089847337</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Technische Universität Berlin</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=658)</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>@tu.berlin</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G360" t="n">
+        <v>8</v>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Peter B. Neubauer</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J360" t="n">
+        <v>60</v>
+      </c>
+      <c r="K360" t="n">
+        <v>13688</v>
+      </c>
+      <c r="L360" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="M360" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N360" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O360" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>state estimation, kalman filter</t>
+        </is>
+      </c>
+      <c r="R360" t="n">
+        <v>1</v>
+      </c>
+      <c r="S360" t="n">
+        <v>167</v>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>Nonlinear state estimation as tool for online monitoring and adaptive feed in high throughput cultivations</t>
+        </is>
+      </c>
+      <c r="V360" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W360" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X360" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu.berlin%20%22Peter%20B.%20Neubauer%22%20email</t>
+        </is>
+      </c>
+      <c r="Z360" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5001739345</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Technische Universität Berlin</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=658)</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>@tu.berlin</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G361" t="n">
+        <v>9</v>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Rudibert King</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J361" t="n">
+        <v>40</v>
+      </c>
+      <c r="K361" t="n">
+        <v>6138</v>
+      </c>
+      <c r="L361" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="M361" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N361" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O361" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>state estimation, kalman filter</t>
+        </is>
+      </c>
+      <c r="R361" t="n">
+        <v>1</v>
+      </c>
+      <c r="S361" t="n">
+        <v>17</v>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>Nonlinear state estimation as tool for online monitoring and adaptive feed in high throughput cultivations</t>
+        </is>
+      </c>
+      <c r="V361" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W361" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X361" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu.berlin%20%22Rudibert%20King%22%20email</t>
+        </is>
+      </c>
+      <c r="Z361" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5020867309</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Technische Universität Berlin</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=658)</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>@tu.berlin</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G362" t="n">
+        <v>10</v>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Mariano Nicolás Cruz Bournazou</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J362" t="n">
+        <v>24</v>
+      </c>
+      <c r="K362" t="n">
+        <v>1947</v>
+      </c>
+      <c r="L362" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="M362" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N362" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O362" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>state estimation, kalman filter</t>
+        </is>
+      </c>
+      <c r="R362" t="n">
+        <v>1</v>
+      </c>
+      <c r="S362" t="n">
+        <v>88</v>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>Nonlinear state estimation as tool for online monitoring and adaptive feed in high throughput cultivations</t>
+        </is>
+      </c>
+      <c r="V362" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W362" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X362" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu.berlin%20%22Mariano%20Nicol%C3%A1s%20Cruz%20Bournazou%22%20email</t>
+        </is>
+      </c>
+      <c r="Z362" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5022278329</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Technische Universität Berlin</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=658)</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>@tu.berlin</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G363" t="n">
+        <v>11</v>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Giuseppe Caire</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J363" t="n">
+        <v>88</v>
+      </c>
+      <c r="K363" t="n">
+        <v>42165</v>
+      </c>
+      <c r="L363" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="M363" t="n">
+        <v>10</v>
+      </c>
+      <c r="N363" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O363" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>gaussian splatting, gnss positioning, deep learning</t>
+        </is>
+      </c>
+      <c r="R363" t="n">
+        <v>2</v>
+      </c>
+      <c r="S363" t="n">
+        <v>409</v>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>Planar Gaussian Splatting with Bilinear Spatial Transformer for Wireless Radiance Field Reconstruction</t>
+        </is>
+      </c>
+      <c r="V363" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W363" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X363" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu.berlin%20%22Giuseppe%20Caire%22%20email</t>
+        </is>
+      </c>
+      <c r="Z363" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5058252389</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Technische Universität Berlin</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=658)</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>@tu.berlin</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G364" t="n">
+        <v>12</v>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Olaf Hellwich</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J364" t="n">
+        <v>33</v>
+      </c>
+      <c r="K364" t="n">
+        <v>3806</v>
+      </c>
+      <c r="L364" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="M364" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N364" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O364" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>depth estimation, pose estimation</t>
+        </is>
+      </c>
+      <c r="R364" t="n">
+        <v>1</v>
+      </c>
+      <c r="S364" t="n">
+        <v>119</v>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>MonoPP: Metric-Scaled Self-Supervised Monocular Depth Estimation by Planar-Parallax Geometry in Automotive Applications</t>
+        </is>
+      </c>
+      <c r="V364" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W364" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X364" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu.berlin%20%22Olaf%20Hellwich%22%20email</t>
+        </is>
+      </c>
+      <c r="Z364" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5081055268</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Technische Universität Berlin</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=658)</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>@tu.berlin</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G365" t="n">
+        <v>13</v>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Oliver Brock</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J365" t="n">
+        <v>48</v>
+      </c>
+      <c r="K365" t="n">
+        <v>9903</v>
+      </c>
+      <c r="L365" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="M365" t="n">
+        <v>10</v>
+      </c>
+      <c r="N365" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O365" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>sensor fusion, robot perception</t>
+        </is>
+      </c>
+      <c r="R365" t="n">
+        <v>2</v>
+      </c>
+      <c r="S365" t="n">
+        <v>96</v>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>Coupled Particle Filters for Robust Affordance Estimation</t>
+        </is>
+      </c>
+      <c r="V365" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W365" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X365" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu.berlin%20%22Oliver%20Brock%22%20email</t>
+        </is>
+      </c>
+      <c r="Z365" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5039143538</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Technische Universität Berlin</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=658)</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>@tu.berlin</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G366" t="n">
+        <v>14</v>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Maorong Ge</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J366" t="n">
+        <v>55</v>
+      </c>
+      <c r="K366" t="n">
+        <v>11021</v>
+      </c>
+      <c r="L366" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="M366" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N366" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O366" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>gnss positioning</t>
+        </is>
+      </c>
+      <c r="R366" t="n">
+        <v>6</v>
+      </c>
+      <c r="S366" t="n">
+        <v>67</v>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>An integrated hierarchical wide-area augmentation for real-time GNSS positioning</t>
+        </is>
+      </c>
+      <c r="V366" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W366" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X366" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu.berlin%20%22Maorong%20Ge%22%20email</t>
+        </is>
+      </c>
+      <c r="Z366" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5061833277</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Technische Universität Berlin</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=658)</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>@tu.berlin</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G367" t="n">
+        <v>15</v>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Jens Wickert</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J367" t="n">
+        <v>65</v>
+      </c>
+      <c r="K367" t="n">
+        <v>13722</v>
+      </c>
+      <c r="L367" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="M367" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N367" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O367" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>gnss positioning, deep learning</t>
+        </is>
+      </c>
+      <c r="R367" t="n">
+        <v>9</v>
+      </c>
+      <c r="S367" t="n">
+        <v>194</v>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>Advancing Accuracy in Sea Level Estimation with GNSS-R: A Fusion of LSTM-DNN-Based Deep Learning and SNR Residual Sequences</t>
+        </is>
+      </c>
+      <c r="V367" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W367" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X367" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu.berlin%20%22Jens%20Wickert%22%20email</t>
+        </is>
+      </c>
+      <c r="Z367" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5035533740</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Technische Universität Berlin</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=658)</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>@tu.berlin</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G368" t="n">
+        <v>16</v>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Cornelia Weltzien</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J368" t="n">
+        <v>23</v>
+      </c>
+      <c r="K368" t="n">
+        <v>2534</v>
+      </c>
+      <c r="L368" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="M368" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N368" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O368" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>autonomous navigation, ros</t>
+        </is>
+      </c>
+      <c r="R368" t="n">
+        <v>2</v>
+      </c>
+      <c r="S368" t="n">
+        <v>85</v>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>Internet of robotic things with a local LoRa network for teleoperation of an agricultural mobile robot using a digital shadow</t>
+        </is>
+      </c>
+      <c r="V368" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W368" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X368" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu.berlin%20%22Cornelia%20Weltzien%22%20email</t>
+        </is>
+      </c>
+      <c r="Z368" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5059009808</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Technische Universität Berlin</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=658)</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>@tu.berlin</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G369" t="n">
+        <v>17</v>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Jungang Wang</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J369" t="n">
+        <v>17</v>
+      </c>
+      <c r="K369" t="n">
+        <v>1033</v>
+      </c>
+      <c r="L369" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="M369" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N369" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O369" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>gnss positioning</t>
+        </is>
+      </c>
+      <c r="R369" t="n">
+        <v>7</v>
+      </c>
+      <c r="S369" t="n">
+        <v>71</v>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>Accelerating multi-GNSS and multi-frequency PPP-AR convergence using global operational NWM forecasts</t>
+        </is>
+      </c>
+      <c r="V369" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W369" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X369" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu.berlin%20%22Jungang%20Wang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z369" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5056037777</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Technische Universität Berlin</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=658)</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>@tu.berlin</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G370" t="n">
+        <v>18</v>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>David Bermbach</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J370" t="n">
+        <v>27</v>
+      </c>
+      <c r="K370" t="n">
+        <v>2156</v>
+      </c>
+      <c r="L370" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="M370" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N370" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O370" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>autonomous navigation</t>
+        </is>
+      </c>
+      <c r="R370" t="n">
+        <v>1</v>
+      </c>
+      <c r="S370" t="n">
+        <v>88</v>
+      </c>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="U370" t="inlineStr">
+        <is>
+          <t>Supporting UAVs with Edge Computing: A Review of Opportunities and Challenges</t>
+        </is>
+      </c>
+      <c r="V370" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W370" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X370" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu.berlin%20%22David%20Bermbach%22%20email</t>
+        </is>
+      </c>
+      <c r="Z370" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5032206962</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Technische Universität Berlin</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=658)</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>@tu.berlin</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G371" t="n">
+        <v>19</v>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>T. Hartmann</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J371" t="n">
+        <v>29</v>
+      </c>
+      <c r="K371" t="n">
+        <v>3151</v>
+      </c>
+      <c r="L371" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="M371" t="n">
+        <v>10</v>
+      </c>
+      <c r="N371" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O371" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>point cloud registration, ros, ros2</t>
+        </is>
+      </c>
+      <c r="R371" t="n">
+        <v>3</v>
+      </c>
+      <c r="S371" t="n">
+        <v>130</v>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>Automated integration of as-is point cloud information with as-planned BIM for interior construction</t>
+        </is>
+      </c>
+      <c r="V371" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W371" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X371" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu.berlin%20%22T.%20Hartmann%22%20email</t>
+        </is>
+      </c>
+      <c r="Z371" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5109370769</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Freie Universität Berlin</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=742)</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>@fu-berlin.de</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G372" t="n">
+        <v>1</v>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Daniel Goehring</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J372" t="n">
+        <v>15</v>
+      </c>
+      <c r="K372" t="n">
+        <v>891</v>
+      </c>
+      <c r="L372" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="M372" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N372" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O372" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>pose estimation</t>
+        </is>
+      </c>
+      <c r="R372" t="n">
+        <v>2</v>
+      </c>
+      <c r="S372" t="n">
+        <v>29</v>
+      </c>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>MaskVal: Simple but Effective Uncertainty Quantification for 6D Pose Estimation</t>
+        </is>
+      </c>
+      <c r="V372" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W372" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X372" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Afu-berlin.de%20%22Daniel%20Goehring%22%20email</t>
+        </is>
+      </c>
+      <c r="Z372" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5007762628</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Humboldt University of Berlin</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=816)</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>@hu-berlin.de</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G373" t="n">
+        <v>1</v>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Jürgen Kurths</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J373" t="n">
+        <v>135</v>
+      </c>
+      <c r="K373" t="n">
+        <v>104432</v>
+      </c>
+      <c r="L373" t="n">
+        <v>10</v>
+      </c>
+      <c r="M373" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N373" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O373" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>visual slam, state estimation, autonomous navigation, depth estimation, deep learning, object detection</t>
+        </is>
+      </c>
+      <c r="R373" t="n">
+        <v>1</v>
+      </c>
+      <c r="S373" t="n">
+        <v>526</v>
+      </c>
+      <c r="T373" t="inlineStr">
+        <is>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>Perception and Navigation in Autonomous Systems in the Era of Learning: A Survey</t>
+        </is>
+      </c>
+      <c r="V373" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W373" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X373" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ahu-berlin.de%20%22J%C3%BCrgen%20Kurths%22%20email</t>
+        </is>
+      </c>
+      <c r="Z373" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5085207296</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Humboldt University of Berlin</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=816)</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>@hu-berlin.de</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G374" t="n">
+        <v>2</v>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Peter Eisert</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J374" t="n">
+        <v>34</v>
+      </c>
+      <c r="K374" t="n">
+        <v>5055</v>
+      </c>
+      <c r="L374" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="M374" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N374" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O374" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; LiDAR &amp; Multimodal Sensor Fusion; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>point cloud registration, sensor fusion, pose estimation, autonomous driving perception, computer vision, gaussian splatting</t>
+        </is>
+      </c>
+      <c r="R374" t="n">
+        <v>8</v>
+      </c>
+      <c r="S374" t="n">
+        <v>149</v>
+      </c>
+      <c r="T374" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>EdgeRegNet: Edge Feature-Based Multimodal Registration Network Between Images and LiDAR Point Clouds</t>
+        </is>
+      </c>
+      <c r="V374" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W374" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X374" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ahu-berlin.de%20%22Peter%20Eisert%22%20email</t>
+        </is>
+      </c>
+      <c r="Z374" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5009614926</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Humboldt University of Berlin</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=816)</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>@hu-berlin.de</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G375" t="n">
+        <v>3</v>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Jens Krause</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J375" t="n">
+        <v>84</v>
+      </c>
+      <c r="K375" t="n">
+        <v>30737</v>
+      </c>
+      <c r="L375" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="M375" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N375" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O375" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, state estimation, sensor fusion, computer vision, semantic segmentation</t>
+        </is>
+      </c>
+      <c r="R375" t="n">
+        <v>2</v>
+      </c>
+      <c r="S375" t="n">
+        <v>62</v>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>Watching Swarm Dynamics from Above: A Framework for Advanced Object Tracking in Drone Videos</t>
+        </is>
+      </c>
+      <c r="V375" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W375" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X375" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ahu-berlin.de%20%22Jens%20Krause%22%20email</t>
+        </is>
+      </c>
+      <c r="Z375" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5025717153</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Humboldt University of Berlin</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=816)</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>@hu-berlin.de</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G376" t="n">
+        <v>4</v>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Anna Hilsmann</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J376" t="n">
+        <v>21</v>
+      </c>
+      <c r="K376" t="n">
+        <v>1527</v>
+      </c>
+      <c r="L376" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="M376" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N376" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O376" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>gaussian splatting</t>
+        </is>
+      </c>
+      <c r="R376" t="n">
+        <v>1</v>
+      </c>
+      <c r="S376" t="n">
+        <v>100</v>
+      </c>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>KISS-GS: 3D Gaussian Splatting Compression Kept Simple</t>
+        </is>
+      </c>
+      <c r="V376" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W376" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X376" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ahu-berlin.de%20%22Anna%20Hilsmann%22%20email</t>
+        </is>
+      </c>
+      <c r="Z376" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5074580099</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Saarland University</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Saarbrücken</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=559)</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>@uni-saarland.de</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G377" t="n">
+        <v>1</v>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Philipp Slusallek</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J377" t="n">
+        <v>41</v>
+      </c>
+      <c r="K377" t="n">
+        <v>9112</v>
+      </c>
+      <c r="L377" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="M377" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N377" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O377" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>depth estimation</t>
+        </is>
+      </c>
+      <c r="R377" t="n">
+        <v>1</v>
+      </c>
+      <c r="S377" t="n">
+        <v>68</v>
+      </c>
+      <c r="T377" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>Edge-Aware Consistent Stereo Video Depth Estimation</t>
+        </is>
+      </c>
+      <c r="V377" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W377" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X377" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-saarland.de%20%22Philipp%20Slusallek%22%20email</t>
+        </is>
+      </c>
+      <c r="Z377" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5026514026</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Saarland University</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Saarbrücken</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=559)</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>@uni-saarland.de</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G378" t="n">
+        <v>2</v>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>M. Schneider</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J378" t="n">
+        <v>15</v>
+      </c>
+      <c r="K378" t="n">
+        <v>1083</v>
+      </c>
+      <c r="L378" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="M378" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N378" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O378" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>point cloud registration</t>
+        </is>
+      </c>
+      <c r="R378" t="n">
+        <v>1</v>
+      </c>
+      <c r="S378" t="n">
+        <v>34</v>
+      </c>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>An Approach for Precise Robotic Sanding Applications of Uneven Surfaces Based on Improved Point Cloud Registration Methods*</t>
+        </is>
+      </c>
+      <c r="V378" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W378" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X378" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-saarland.de%20%22M.%20Schneider%22%20email</t>
+        </is>
+      </c>
+      <c r="Z378" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5015377349</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>TU Dresden</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Dresden</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Tier B (Specialized/Regional | h=11)</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>@vufo.de</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="J379" t="n">
+        <v>0</v>
+      </c>
+      <c r="K379" t="n">
+        <v>0</v>
+      </c>
+      <c r="L379" t="n">
+        <v>0</v>
+      </c>
+      <c r="M379" t="n">
+        <v>0</v>
+      </c>
+      <c r="N379" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O379" t="n">
+        <v>0</v>
+      </c>
+      <c r="R379" t="n">
+        <v>0</v>
+      </c>
+      <c r="S379" t="n">
+        <v>0</v>
+      </c>
+      <c r="W379" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z352"/>
+  <autoFilter ref="A1:Z379"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AG$127</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Z$379</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Z$414</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <col width="21" customWidth="1" min="16" max="16"/>
     <col width="42" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
     <col width="25" customWidth="1" min="21" max="21"/>
     <col width="42" customWidth="1" min="22" max="22"/>
@@ -4690,23 +4690,135 @@
           <t>Leibniz University Hannover</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=927)</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5101541221</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bernardo Wagner</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Interval-based Robot Localization with Uncertainty Evaluation (2022)</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Hanover</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>@uni-hannover.de</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>I114112103</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit) (h=22)</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>robot localization, lidar slam, point cloud registration, sensor fusion, state estimation</t>
+        </is>
+      </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>8.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z33" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" s="4" t="inlineStr"/>
-      <c r="AE33" s="4" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Bernardo Wagner; Claus Brenner A; Steffen Schön; Monika Sester; Hamza Alkhatib; Franz Rottensteiner; Annika Raatz; Holger Blume; Gaël Kermarrec; Ingo Neumann; Eduard Reithmeier; Christian Heipke; Tobias Johannes Ortmaier</t>
+        </is>
+      </c>
+      <c r="AD33" s="4" t="inlineStr">
+        <is>
+          <t>1. Bernardo Wagner (Associate / Established PI (High Fit), h=22) | Fit=9.2/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.0/10 | Keywords=robot localization, lidar slam, point cloud registration, sensor fusion, state estimation | Paper=Interval-based Robot Localization with Uncertainty Evaluation (2022)
+2. Claus Brenner A (Full / Senior Prof (Large Lab), h=30) | Fit=8.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=robust localization, pose estimation, kalman filter, autonomous vehicles, lidar slam, robot localization | Paper=Maximum Consensus Localization Using an Objective Function Based on Helmert's Point Error (2023)
+3. Steffen Schön (Full / Senior Prof (Large Lab), h=22) | Fit=8.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.5/10 | Keywords=gnss positioning, extended kalman filter, kalman filter, autonomous navigation, autonomous vehicles | Paper=Feature Map Aided Robust High Precision GNSS Positioning in Harsh Urban Environments (2025)
+4. Monika Sester (Full / Senior Prof (Large Lab), h=40) | Fit=6.9/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.5/10 | Keywords=lidar slam, robot localization, pose estimation, state estimation, point cloud registration | Paper=Range-View-Based Normal Estimation for Sparse LiDAR SLAM (2025)
+5. Hamza Alkhatib (Associate / Established PI (High Fit), h=15) | Fit=6.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.5/10 | Keywords=sensor fusion, kalman filter, robust localization, pose estimation, trajectory estimation, state estimation | Paper=Geometry-aware Subsampling and pole-enhanced Map Constraints for urban Localization of LiDAR-ba (2026)
+6. Franz Rottensteiner (Full / Senior Prof (Large Lab), h=42) | Fit=6.6/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.3/10 | Keywords=3d reconstruction, computer vision, semantic segmentation, state estimation | Paper=Preface: Workshop “Semantics3D - Semantic Scene Analysis and 3D Reconstruction from Images and  (2023)
+7. Annika Raatz (Full / Senior Prof (Large Lab), h=29) | Fit=6.8/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=6.3/10 | Keywords=robot localization, robust localization, pose estimation, trajectory estimation | Paper=Challenges of Mobile Robots in Motion: A Comparative Trajectory Accuracy Evaluation of AMCL Usi (2026)
+8. Holger Blume (Full / Senior Prof (Large Lab), h=24) | Fit=6.9/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.2/10 | Keywords=point cloud registration, sensor fusion | Paper=Learning of Multimodal Point Descriptors in Radar and LIDAR Point Clouds (2024)
+9. Gaël Kermarrec (Associate / Established PI (High Fit), h=15) | Fit=5.8/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.6/10 | Keywords=gnss positioning, kalman filter | Paper=Modeling trends and periodic components in geodetic time series: a unified approach (2024)
+10. Ingo Neumann (Associate / Established PI (High Fit), h=22) | Fit=5.4/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.5/10 | Keywords=robust localization, pose estimation, state estimation, point cloud registration | Paper=Semantic-Guided Geometric Feature Extraction from Dense LiDAR for Vehicle Localization with Abs (2026)
+11. Eduard Reithmeier (Full / Senior Prof (Large Lab), h=21) | Fit=5.4/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=5.2/10 | Keywords=visual odometry, robot localization | Paper=Robust RGBD Visual Odometry Using Windowed Direct Bundle Adjustment and Slanted Support Plane (2021)
+12. Christian Heipke (Full / Senior Prof (Large Lab), h=39) | Fit=4.2/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=state estimation, gnss positioning, pose estimation | Paper=Contributions to Integrity and Collaboration in Dynamic Sensor Networks (2026)
+13. Tobias Johannes Ortmaier (Full / Senior Prof (Large Lab), h=34) | Fit=3.8/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=4.1/10 | Keywords=pose estimation | Paper=LiDAR-Based Localization for Formation Control of Multi-Robot Systems (2022)</t>
+        </is>
+      </c>
+      <c r="AE33" s="4" t="inlineStr">
+        <is>
+          <t>Bernardo Wagner: No homepage/funding evidence available
+Claus Brenner A: No homepage/funding evidence available
+Steffen Schön: No homepage/funding evidence available
+Monika Sester: No homepage/funding evidence available
+Hamza Alkhatib: No homepage/funding evidence available
+Franz Rottensteiner: No homepage/funding evidence available
+Annika Raatz: No homepage/funding evidence available
+Holger Blume: No homepage/funding evidence available
+Gaël Kermarrec: No homepage/funding evidence available
+Ingo Neumann: No homepage/funding evidence available
+Eduard Reithmeier: No homepage/funding evidence available
+Christian Heipke: No homepage/funding evidence available
+Tobias Johannes Ortmaier: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-hannover.de%20%22Bernardo%20Wagner%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
@@ -4714,23 +4826,135 @@
           <t>University of Bonn</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>QS #227 (Top Geodesy/Robotics) | Tier S+ (Global Elite | h=1063)</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5011166267</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Cyrill Stachniss</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Robust Approach for LiDAR-Inertial Odometry Without Sensor-Specific Modeling (2026)</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Bonn</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>@uni-bonn.de</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>I135140700</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=77)</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>lidar inertial odometry, sensor fusion, kalman filter, lidar slam, autonomous navigation, loop closure</t>
+        </is>
+      </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="Z34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="4" t="inlineStr"/>
-      <c r="AE34" s="4" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Cyrill Stachniss; Heiner Kuhlmann; Lasse Klingbeil; Jens Behley; Sven Behnke; Yue Pan; Hermann Blum; Maren Bennewitz; Arul Selvam Periyasamy; Florian Bernard; Chris McCool; Jan‐Henrik Haunert; Jüergen Gall</t>
+        </is>
+      </c>
+      <c r="AD34" s="4" t="inlineStr">
+        <is>
+          <t>1. Cyrill Stachniss (Full / Senior Prof (Large Lab), h=77) | Fit=10.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.5/10 | Keywords=lidar inertial odometry, sensor fusion, kalman filter, lidar slam, autonomous navigation, loop closure | Paper=Robust Approach for LiDAR-Inertial Odometry Without Sensor-Specific Modeling (2026)
+2. Heiner Kuhlmann (Full / Senior Prof (Large Lab), h=32) | Fit=10.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.5/10 | Keywords=lidar inertial odometry, sensor fusion, pose estimation, extended kalman filter, kalman filter, gnss positioning | Paper=LIO-EKF: High Frequency LiDAR-Inertial Odometry using Extended Kalman Filters (2024)
+3. Lasse Klingbeil (Full / Senior Prof (Large Lab), h=29) | Fit=10.0/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.4/10 | Keywords=lidar inertial odometry, sensor fusion, pose estimation, extended kalman filter, kalman filter, gnss positioning | Paper=LIO-EKF: High Frequency LiDAR-Inertial Odometry using Extended Kalman Filters (2024)
+4. Jens Behley (Full / Senior Prof (Large Lab), h=40) | Fit=9.8/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.3/10 | Keywords=point cloud registration, robot localization, 3d reconstruction, lidar slam, robust localization, pose estimation | Paper=Register Any Point: Scaling 3D Point Cloud Registration by Flow Matching (2026)
+5. Sven Behnke (Full / Senior Prof (Large Lab), h=54) | Fit=9.5/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.1/10 | Keywords=pose estimation, robot localization, 3d reconstruction, sensor fusion, robot perception, mobile robot navigation | Paper=Hierarchical Pose Estimation and Mapping with Multi-Scale Neural Feature Fields (2024)
+6. Yue Pan (Assistant Prof / Rising Star (Responsive), h=16) | Fit=9.4/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.1/10 | Keywords=visual slam, lidar slam, point cloud registration, loop closure, gaussian splatting, robust localization | Paper=Neural Representations for Simultaneous Localization and Mapping (2026)
+7. Hermann Blum (Full / Senior Prof (Large Lab), h=17) | Fit=9.2/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.0/10 | Keywords=loop closure, visual slam, trajectory estimation, pose estimation, semantic segmentation, autonomous navigation | Paper=Loop Closure From Two Views: Revisiting PGO for Scalable Trajectory Estimation Through Monocula (2026)
+8. Maren Bennewitz (Full / Senior Prof (Large Lab), h=37) | Fit=8.9/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=7.5/10 | Keywords=multi-sensor fusion, state estimation, sensor fusion, robot perception, visual odometry, deep learning | Paper=Perception for Humanoid Robots (2023)
+9. Arul Selvam Periyasamy (Assistant Prof / Rising Star (Responsive), h=13) | Fit=6.5/10 | Activity=8.2/10 | Funding=0.0/10 | Overall=5.9/10 | Keywords=pose estimation, point cloud registration, deep learning, object detection, computer vision, robot perception | Paper=YOLOPose V2: Understanding and improving transformer-based 6D pose estimation (2023)
+10. Florian Bernard (Associate / Established PI (High Fit), h=30) | Fit=4.1/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=4.6/10 | Keywords=pose estimation, computer vision, point cloud registration, 3d reconstruction | Paper=The Probabilistic Normal Epipolar Constraint for Frame- To-Frame Rotation Optimization under Un (2022)
+11. Chris McCool (Full / Senior Prof (Large Lab), h=37) | Fit=4.0/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.3/10 | Keywords=robot localization | Paper=BonnBot-I: A Precise Weed Management and Crop Monitoring Platform (2022)
+12. Jan‐Henrik Haunert (Associate / Established PI (High Fit), h=22) | Fit=3.8/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.3/10 | Keywords=point cloud registration, gnss positioning | Paper=Simultaneous planning of standpoints and routing for laser scanning of buildings with network r (2025)
+13. Jüergen Gall (Full / Senior Prof (Large Lab), h=73) | Fit=4.0/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.3/10 | Keywords=kalman filter, autonomous vehicles, object detection | Paper=3DMOTFormer: Graph Transformer for Online 3D Multi-Object Tracking (2023)</t>
+        </is>
+      </c>
+      <c r="AE34" s="4" t="inlineStr">
+        <is>
+          <t>Cyrill Stachniss: No homepage/funding evidence available
+Heiner Kuhlmann: No homepage/funding evidence available
+Lasse Klingbeil: No homepage/funding evidence available
+Jens Behley: No homepage/funding evidence available
+Sven Behnke: No homepage/funding evidence available
+Yue Pan: No homepage/funding evidence available
+Hermann Blum: No homepage/funding evidence available
+Maren Bennewitz: No homepage/funding evidence available
+Arul Selvam Periyasamy: No homepage/funding evidence available
+Florian Bernard: No homepage/funding evidence available
+Chris McCool: No homepage/funding evidence available
+Jan‐Henrik Haunert: No homepage/funding evidence available
+Jüergen Gall: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bonn.de%20%22Cyrill%20Stachniss%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
@@ -4738,23 +4962,115 @@
           <t>University of Duisburg-Essen</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=679)</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5047117780</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Pedro José Marrón</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Visual Foreign Object Detection for Wireless Charging of Electric Vehicles (2023)</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Essen</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>@uni-due.de</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>I62318514</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=28)</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>visual localization, object detection, pose estimation, autonomous vehicles, computer vision, autonomous navigation</t>
+        </is>
+      </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>9.74</v>
       </c>
       <c r="Z35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="4" t="inlineStr"/>
-      <c r="AE35" s="4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Pedro José Marrón; Thomas Kaiser; Mohammed El‐Absi</t>
+        </is>
+      </c>
+      <c r="AD35" s="4" t="inlineStr">
+        <is>
+          <t>1. Pedro José Marrón (Full / Senior Prof (Large Lab), h=28) | Fit=6.8/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=6.2/10 | Keywords=visual localization, object detection, pose estimation, autonomous vehicles, computer vision, autonomous navigation | Paper=Visual Foreign Object Detection for Wireless Charging of Electric Vehicles (2023)
+2. Thomas Kaiser (Full / Senior Prof (Large Lab), h=34) | Fit=4.6/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.0/10 | Keywords=extended kalman filter, kalman filter | Paper=3D Self-Localization and Tracking with Minimum Anchor Dependency: A Hybrid Measurement and EKF- (2026)
+3. Mohammed El‐Absi (Associate / Established PI (High Fit), h=17) | Fit=4.6/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.0/10 | Keywords=extended kalman filter, kalman filter | Paper=3D Self-Localization and Tracking with Minimum Anchor Dependency: A Hybrid Measurement and EKF- (2026)</t>
+        </is>
+      </c>
+      <c r="AE35" s="4" t="inlineStr">
+        <is>
+          <t>Pedro José Marrón: No homepage/funding evidence available
+Thomas Kaiser: No homepage/funding evidence available
+Mohammed El‐Absi: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-due.de%20%22Pedro%20Jos%C3%A9%20Marr%C3%B3n%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
@@ -4762,28 +5078,159 @@
           <t>TU Dortmund University</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=555)</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5071909921</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Moritz Roidl</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Object Pose Estimation Annotation Pipeline for Multi-view Monocular Camera Systems in Industrial Settings (2023)</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>@tu-dortmund.de</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>I200332995</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit) (h=10)</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>pose estimation, visual localization, deep learning, event camera, object detection, autonomous navigation</t>
+        </is>
+      </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>6.33</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" s="4" t="inlineStr"/>
-      <c r="AE36" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Moritz Roidl; Torsten Bertram; Matthias G.R. Faes; Frank Hoffmann B; Mirco Hünnefeld</t>
+        </is>
+      </c>
+      <c r="AD36" s="4" t="inlineStr">
+        <is>
+          <t>1. Moritz Roidl (Associate / Established PI (High Fit), h=10) | Fit=8.2/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=7.2/10 | Keywords=pose estimation, visual localization, deep learning, event camera, object detection, autonomous navigation | Paper=Object Pose Estimation Annotation Pipeline for Multi-view Monocular Camera Systems in Industria (2023)
+2. Torsten Bertram (Full / Senior Prof (Large Lab), h=31) | Fit=7.5/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=6.7/10 | Keywords=sensor fusion, kalman filter, autonomous driving perception, object detection, lidar camera fusion, depth estimation | Paper=HiLO: High-Level Object Fusion for Autonomous Driving Using Transformers (2025)
+3. Matthias G.R. Faes (Full / Senior Prof (Large Lab), h=30) | Fit=6.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.5/10 | Keywords=pose estimation, gaussian splatting, 3d reconstruction, computer vision | Paper=Complex 3D structure and crack reconstruction by an online hybrid stereo photogrammetry approac (2026)
+4. Frank Hoffmann B (Full / Senior Prof (Large Lab), h=35) | Fit=6.6/10 | Activity=9.0/10 | Funding=0.0/10 | Overall=6.1/10 | Keywords=pose estimation, event camera, object detection, mobile robot navigation | Paper=Mtevent: a Multi-Task Event Camera Dataset for 6D Pose Estimation and Moving Object Detection (2025)
+5. Mirco Hünnefeld (Full / Senior Prof (Large Lab), h=42) | Fit=5.4/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=5.2/10 | Keywords=robot localization | Paper=A Grid-based Sensor Floor Platform for Robot Localization using Machine Learning (2023)</t>
+        </is>
+      </c>
+      <c r="AE36" s="4" t="inlineStr">
+        <is>
+          <t>Moritz Roidl: No homepage/funding evidence available
+Torsten Bertram: No homepage/funding evidence available
+Matthias G.R. Faes: No homepage/funding evidence available
+Frank Hoffmann B: No homepage/funding evidence available
+Mirco Hünnefeld: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu-dortmund.de%20%22Moritz%20Roidl%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
           <t>University of Hamburg</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Tier B (Specialized/Regional | h=5)</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>@brand-university.de</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Direct to PI + University Portal</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>I4387154191</t>
         </is>
       </c>
       <c r="X37" t="n">
@@ -6916,7 +7363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z379"/>
+  <dimension ref="A1:Z414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -47475,8 +47922,3703 @@
       </c>
       <c r="W379" s="4" t="inlineStr"/>
     </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Leibniz University Hannover</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Hanover</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=927)</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>@uni-hannover.de</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G380" t="n">
+        <v>1</v>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Bernardo Wagner</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J380" t="n">
+        <v>22</v>
+      </c>
+      <c r="K380" t="n">
+        <v>1656</v>
+      </c>
+      <c r="L380" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="M380" t="n">
+        <v>10</v>
+      </c>
+      <c r="N380" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O380" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>robot localization, lidar slam, point cloud registration, sensor fusion, state estimation</t>
+        </is>
+      </c>
+      <c r="R380" t="n">
+        <v>4</v>
+      </c>
+      <c r="S380" t="n">
+        <v>15</v>
+      </c>
+      <c r="T380" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>Interval-based Robot Localization with Uncertainty Evaluation</t>
+        </is>
+      </c>
+      <c r="V380" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W380" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X380" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-hannover.de%20%22Bernardo%20Wagner%22%20email</t>
+        </is>
+      </c>
+      <c r="Z380" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5101541221</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Leibniz University Hannover</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Hanover</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=927)</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>@uni-hannover.de</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G381" t="n">
+        <v>2</v>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Claus Brenner A</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J381" t="n">
+        <v>30</v>
+      </c>
+      <c r="K381" t="n">
+        <v>3403</v>
+      </c>
+      <c r="L381" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="M381" t="n">
+        <v>10</v>
+      </c>
+      <c r="N381" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O381" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>robust localization, pose estimation, kalman filter, autonomous vehicles, lidar slam, robot localization</t>
+        </is>
+      </c>
+      <c r="R381" t="n">
+        <v>6</v>
+      </c>
+      <c r="S381" t="n">
+        <v>33</v>
+      </c>
+      <c r="T381" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>Maximum Consensus Localization Using an Objective Function Based on Helmert's Point Error</t>
+        </is>
+      </c>
+      <c r="V381" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W381" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X381" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-hannover.de%20%22Claus%20Brenner%20A%22%20email</t>
+        </is>
+      </c>
+      <c r="Z381" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5016827109</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Leibniz University Hannover</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Hanover</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=927)</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>@uni-hannover.de</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G382" t="n">
+        <v>3</v>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Steffen Schön</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J382" t="n">
+        <v>22</v>
+      </c>
+      <c r="K382" t="n">
+        <v>1845</v>
+      </c>
+      <c r="L382" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="M382" t="n">
+        <v>10</v>
+      </c>
+      <c r="N382" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O382" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>gnss positioning, extended kalman filter, kalman filter, autonomous navigation, autonomous vehicles</t>
+        </is>
+      </c>
+      <c r="R382" t="n">
+        <v>21</v>
+      </c>
+      <c r="S382" t="n">
+        <v>163</v>
+      </c>
+      <c r="T382" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>Feature Map Aided Robust High Precision GNSS Positioning in Harsh Urban Environments</t>
+        </is>
+      </c>
+      <c r="V382" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W382" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X382" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-hannover.de%20%22Steffen%20Sch%C3%B6n%22%20email</t>
+        </is>
+      </c>
+      <c r="Z382" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5091144096</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Leibniz University Hannover</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Hanover</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=927)</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>@uni-hannover.de</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G383" t="n">
+        <v>4</v>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Monika Sester</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J383" t="n">
+        <v>40</v>
+      </c>
+      <c r="K383" t="n">
+        <v>5711</v>
+      </c>
+      <c r="L383" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="M383" t="n">
+        <v>10</v>
+      </c>
+      <c r="N383" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O383" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>lidar slam, robot localization, pose estimation, state estimation, point cloud registration</t>
+        </is>
+      </c>
+      <c r="R383" t="n">
+        <v>5</v>
+      </c>
+      <c r="S383" t="n">
+        <v>147</v>
+      </c>
+      <c r="T383" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>Range-View-Based Normal Estimation for Sparse LiDAR SLAM</t>
+        </is>
+      </c>
+      <c r="V383" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W383" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X383" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-hannover.de%20%22Monika%20Sester%22%20email</t>
+        </is>
+      </c>
+      <c r="Z383" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5020817045</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Leibniz University Hannover</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Hanover</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=927)</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>@uni-hannover.de</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G384" t="n">
+        <v>5</v>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>Hamza Alkhatib</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J384" t="n">
+        <v>15</v>
+      </c>
+      <c r="K384" t="n">
+        <v>728</v>
+      </c>
+      <c r="L384" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="M384" t="n">
+        <v>10</v>
+      </c>
+      <c r="N384" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O384" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; State Estimation &amp; Factor Graphs; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>sensor fusion, kalman filter, robust localization, pose estimation, trajectory estimation, state estimation</t>
+        </is>
+      </c>
+      <c r="R384" t="n">
+        <v>5</v>
+      </c>
+      <c r="S384" t="n">
+        <v>48</v>
+      </c>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>Geometry-aware Subsampling and pole-enhanced Map Constraints for urban Localization of LiDAR-based Systems</t>
+        </is>
+      </c>
+      <c r="V384" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W384" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X384" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-hannover.de%20%22Hamza%20Alkhatib%22%20email</t>
+        </is>
+      </c>
+      <c r="Z384" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5063876414</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Leibniz University Hannover</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Hanover</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=927)</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>@uni-hannover.de</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G385" t="n">
+        <v>6</v>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Franz Rottensteiner</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J385" t="n">
+        <v>42</v>
+      </c>
+      <c r="K385" t="n">
+        <v>6765</v>
+      </c>
+      <c r="L385" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="M385" t="n">
+        <v>10</v>
+      </c>
+      <c r="N385" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O385" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; GNSS &amp; Robust Localization; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>3d reconstruction, computer vision, semantic segmentation, state estimation</t>
+        </is>
+      </c>
+      <c r="R385" t="n">
+        <v>3</v>
+      </c>
+      <c r="S385" t="n">
+        <v>90</v>
+      </c>
+      <c r="T385" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>Preface: Workshop “Semantics3D - Semantic Scene Analysis and 3D Reconstruction from Images and Image Sequences”</t>
+        </is>
+      </c>
+      <c r="V385" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W385" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X385" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-hannover.de%20%22Franz%20Rottensteiner%22%20email</t>
+        </is>
+      </c>
+      <c r="Z385" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5033807047</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Leibniz University Hannover</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Hanover</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=927)</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>@uni-hannover.de</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G386" t="n">
+        <v>7</v>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Annika Raatz</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J386" t="n">
+        <v>29</v>
+      </c>
+      <c r="K386" t="n">
+        <v>3338</v>
+      </c>
+      <c r="L386" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="M386" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N386" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O386" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; State Estimation &amp; Factor Graphs; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>robot localization, robust localization, pose estimation, trajectory estimation</t>
+        </is>
+      </c>
+      <c r="R386" t="n">
+        <v>3</v>
+      </c>
+      <c r="S386" t="n">
+        <v>180</v>
+      </c>
+      <c r="T386" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>Challenges of Mobile Robots in Motion: A Comparative Trajectory Accuracy Evaluation of AMCL Using Motion Capture Systems</t>
+        </is>
+      </c>
+      <c r="V386" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W386" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X386" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-hannover.de%20%22Annika%20Raatz%22%20email</t>
+        </is>
+      </c>
+      <c r="Z386" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5032319988</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Leibniz University Hannover</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Hanover</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=927)</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>@uni-hannover.de</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G387" t="n">
+        <v>8</v>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Holger Blume</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J387" t="n">
+        <v>24</v>
+      </c>
+      <c r="K387" t="n">
+        <v>2444</v>
+      </c>
+      <c r="L387" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="M387" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N387" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O387" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>point cloud registration, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R387" t="n">
+        <v>1</v>
+      </c>
+      <c r="S387" t="n">
+        <v>106</v>
+      </c>
+      <c r="T387" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>Learning of Multimodal Point Descriptors in Radar and LIDAR Point Clouds</t>
+        </is>
+      </c>
+      <c r="V387" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W387" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X387" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-hannover.de%20%22Holger%20Blume%22%20email</t>
+        </is>
+      </c>
+      <c r="Z387" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5016532646</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Leibniz University Hannover</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Hanover</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=927)</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>@uni-hannover.de</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G388" t="n">
+        <v>9</v>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Gaël Kermarrec</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J388" t="n">
+        <v>15</v>
+      </c>
+      <c r="K388" t="n">
+        <v>536</v>
+      </c>
+      <c r="L388" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="M388" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N388" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O388" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>gnss positioning, kalman filter</t>
+        </is>
+      </c>
+      <c r="R388" t="n">
+        <v>8</v>
+      </c>
+      <c r="S388" t="n">
+        <v>80</v>
+      </c>
+      <c r="T388" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="U388" t="inlineStr">
+        <is>
+          <t>Modeling trends and periodic components in geodetic time series: a unified approach</t>
+        </is>
+      </c>
+      <c r="V388" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W388" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X388" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-hannover.de%20%22Ga%C3%ABl%20Kermarrec%22%20email</t>
+        </is>
+      </c>
+      <c r="Z388" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5046313245</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Leibniz University Hannover</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Hanover</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=927)</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>@uni-hannover.de</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G389" t="n">
+        <v>10</v>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Ingo Neumann</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J389" t="n">
+        <v>22</v>
+      </c>
+      <c r="K389" t="n">
+        <v>1568</v>
+      </c>
+      <c r="L389" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="M389" t="n">
+        <v>10</v>
+      </c>
+      <c r="N389" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O389" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; State Estimation &amp; Factor Graphs; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>robust localization, pose estimation, state estimation, point cloud registration</t>
+        </is>
+      </c>
+      <c r="R389" t="n">
+        <v>3</v>
+      </c>
+      <c r="S389" t="n">
+        <v>27</v>
+      </c>
+      <c r="T389" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>Semantic-Guided Geometric Feature Extraction from Dense LiDAR for Vehicle Localization with Abstract Maps</t>
+        </is>
+      </c>
+      <c r="V389" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W389" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X389" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-hannover.de%20%22Ingo%20Neumann%22%20email</t>
+        </is>
+      </c>
+      <c r="Z389" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5079857116</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Leibniz University Hannover</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Hanover</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=927)</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>@uni-hannover.de</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G390" t="n">
+        <v>11</v>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Eduard Reithmeier</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J390" t="n">
+        <v>21</v>
+      </c>
+      <c r="K390" t="n">
+        <v>1775</v>
+      </c>
+      <c r="L390" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="M390" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N390" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O390" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>visual odometry, robot localization</t>
+        </is>
+      </c>
+      <c r="R390" t="n">
+        <v>2</v>
+      </c>
+      <c r="S390" t="n">
+        <v>56</v>
+      </c>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>2023-05-08</t>
+        </is>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>Robust RGBD Visual Odometry Using Windowed Direct Bundle Adjustment and Slanted Support Plane</t>
+        </is>
+      </c>
+      <c r="V390" t="n">
+        <v>2021</v>
+      </c>
+      <c r="W390" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X390" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-hannover.de%20%22Eduard%20Reithmeier%22%20email</t>
+        </is>
+      </c>
+      <c r="Z390" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5052224154</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Leibniz University Hannover</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Hanover</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=927)</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>@uni-hannover.de</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G391" t="n">
+        <v>12</v>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Christian Heipke</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J391" t="n">
+        <v>39</v>
+      </c>
+      <c r="K391" t="n">
+        <v>6959</v>
+      </c>
+      <c r="L391" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="M391" t="n">
+        <v>10</v>
+      </c>
+      <c r="N391" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O391" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; 3D Computer Vision &amp; Geometric Perception; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>state estimation, gnss positioning, pose estimation</t>
+        </is>
+      </c>
+      <c r="R391" t="n">
+        <v>4</v>
+      </c>
+      <c r="S391" t="n">
+        <v>107</v>
+      </c>
+      <c r="T391" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>Contributions to Integrity and Collaboration in Dynamic Sensor Networks</t>
+        </is>
+      </c>
+      <c r="V391" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W391" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X391" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-hannover.de%20%22Christian%20Heipke%22%20email</t>
+        </is>
+      </c>
+      <c r="Z391" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5069418475</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Leibniz University Hannover</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Hanover</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=927)</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>@uni-hannover.de</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G392" t="n">
+        <v>13</v>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Tobias Johannes Ortmaier</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J392" t="n">
+        <v>34</v>
+      </c>
+      <c r="K392" t="n">
+        <v>4219</v>
+      </c>
+      <c r="L392" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="M392" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N392" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O392" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>pose estimation</t>
+        </is>
+      </c>
+      <c r="R392" t="n">
+        <v>1</v>
+      </c>
+      <c r="S392" t="n">
+        <v>32</v>
+      </c>
+      <c r="T392" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>LiDAR-Based Localization for Formation Control of Multi-Robot Systems</t>
+        </is>
+      </c>
+      <c r="V392" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W392" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X392" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-hannover.de%20%22Tobias%20Johannes%20Ortmaier%22%20email</t>
+        </is>
+      </c>
+      <c r="Z392" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5028164919</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>University of Bonn</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Bonn</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>QS #227 (Top Geodesy/Robotics) | Tier S+ (Global Elite | h=1063)</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>@uni-bonn.de</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G393" t="n">
+        <v>1</v>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>Cyrill Stachniss</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J393" t="n">
+        <v>77</v>
+      </c>
+      <c r="K393" t="n">
+        <v>31777</v>
+      </c>
+      <c r="L393" t="n">
+        <v>10</v>
+      </c>
+      <c r="M393" t="n">
+        <v>10</v>
+      </c>
+      <c r="N393" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O393" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>lidar inertial odometry, sensor fusion, kalman filter, lidar slam, autonomous navigation, loop closure</t>
+        </is>
+      </c>
+      <c r="R393" t="n">
+        <v>34</v>
+      </c>
+      <c r="S393" t="n">
+        <v>213</v>
+      </c>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>Robust Approach for LiDAR-Inertial Odometry Without Sensor-Specific Modeling</t>
+        </is>
+      </c>
+      <c r="V393" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W393" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X393" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bonn.de%20%22Cyrill%20Stachniss%22%20email</t>
+        </is>
+      </c>
+      <c r="Z393" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5011166267</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>University of Bonn</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Bonn</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>QS #227 (Top Geodesy/Robotics) | Tier S+ (Global Elite | h=1063)</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>@uni-bonn.de</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G394" t="n">
+        <v>2</v>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>Heiner Kuhlmann</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J394" t="n">
+        <v>32</v>
+      </c>
+      <c r="K394" t="n">
+        <v>3569</v>
+      </c>
+      <c r="L394" t="n">
+        <v>10</v>
+      </c>
+      <c r="M394" t="n">
+        <v>10</v>
+      </c>
+      <c r="N394" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O394" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; LiDAR &amp; Multimodal Sensor Fusion; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>lidar inertial odometry, sensor fusion, pose estimation, extended kalman filter, kalman filter, gnss positioning</t>
+        </is>
+      </c>
+      <c r="R394" t="n">
+        <v>13</v>
+      </c>
+      <c r="S394" t="n">
+        <v>57</v>
+      </c>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>LIO-EKF: High Frequency LiDAR-Inertial Odometry using Extended Kalman Filters</t>
+        </is>
+      </c>
+      <c r="V394" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W394" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X394" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bonn.de%20%22Heiner%20Kuhlmann%22%20email</t>
+        </is>
+      </c>
+      <c r="Z394" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5071453769</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>University of Bonn</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Bonn</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>QS #227 (Top Geodesy/Robotics) | Tier S+ (Global Elite | h=1063)</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>@uni-bonn.de</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G395" t="n">
+        <v>3</v>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Lasse Klingbeil</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J395" t="n">
+        <v>29</v>
+      </c>
+      <c r="K395" t="n">
+        <v>3481</v>
+      </c>
+      <c r="L395" t="n">
+        <v>10</v>
+      </c>
+      <c r="M395" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N395" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O395" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; LiDAR &amp; Multimodal Sensor Fusion; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>lidar inertial odometry, sensor fusion, pose estimation, extended kalman filter, kalman filter, gnss positioning</t>
+        </is>
+      </c>
+      <c r="R395" t="n">
+        <v>13</v>
+      </c>
+      <c r="S395" t="n">
+        <v>67</v>
+      </c>
+      <c r="T395" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>LIO-EKF: High Frequency LiDAR-Inertial Odometry using Extended Kalman Filters</t>
+        </is>
+      </c>
+      <c r="V395" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W395" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X395" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bonn.de%20%22Lasse%20Klingbeil%22%20email</t>
+        </is>
+      </c>
+      <c r="Z395" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5048316690</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>University of Bonn</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Bonn</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>QS #227 (Top Geodesy/Robotics) | Tier S+ (Global Elite | h=1063)</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>@uni-bonn.de</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G396" t="n">
+        <v>4</v>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>Jens Behley</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J396" t="n">
+        <v>40</v>
+      </c>
+      <c r="K396" t="n">
+        <v>9982</v>
+      </c>
+      <c r="L396" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="M396" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N396" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O396" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>point cloud registration, robot localization, 3d reconstruction, lidar slam, robust localization, pose estimation</t>
+        </is>
+      </c>
+      <c r="R396" t="n">
+        <v>18</v>
+      </c>
+      <c r="S396" t="n">
+        <v>122</v>
+      </c>
+      <c r="T396" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>Register Any Point: Scaling 3D Point Cloud Registration by Flow Matching</t>
+        </is>
+      </c>
+      <c r="V396" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W396" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X396" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bonn.de%20%22Jens%20Behley%22%20email</t>
+        </is>
+      </c>
+      <c r="Z396" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5068364473</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>University of Bonn</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Bonn</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>QS #227 (Top Geodesy/Robotics) | Tier S+ (Global Elite | h=1063)</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>@uni-bonn.de</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G397" t="n">
+        <v>5</v>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>Sven Behnke</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J397" t="n">
+        <v>54</v>
+      </c>
+      <c r="K397" t="n">
+        <v>15864</v>
+      </c>
+      <c r="L397" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="M397" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N397" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O397" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; LiDAR &amp; Multimodal Sensor Fusion; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>pose estimation, robot localization, 3d reconstruction, sensor fusion, robot perception, mobile robot navigation</t>
+        </is>
+      </c>
+      <c r="R397" t="n">
+        <v>18</v>
+      </c>
+      <c r="S397" t="n">
+        <v>210</v>
+      </c>
+      <c r="T397" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>Hierarchical Pose Estimation and Mapping with Multi-Scale Neural Feature Fields</t>
+        </is>
+      </c>
+      <c r="V397" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W397" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X397" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bonn.de%20%22Sven%20Behnke%22%20email</t>
+        </is>
+      </c>
+      <c r="Z397" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5027761977</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>University of Bonn</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Bonn</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>QS #227 (Top Geodesy/Robotics) | Tier S+ (Global Elite | h=1063)</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>@uni-bonn.de</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G398" t="n">
+        <v>6</v>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>Yue Pan</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J398" t="n">
+        <v>16</v>
+      </c>
+      <c r="K398" t="n">
+        <v>1021</v>
+      </c>
+      <c r="L398" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="M398" t="n">
+        <v>10</v>
+      </c>
+      <c r="N398" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O398" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; 3D Computer Vision &amp; Geometric Perception; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>visual slam, lidar slam, point cloud registration, loop closure, gaussian splatting, robust localization</t>
+        </is>
+      </c>
+      <c r="R398" t="n">
+        <v>6</v>
+      </c>
+      <c r="S398" t="n">
+        <v>19</v>
+      </c>
+      <c r="T398" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>Neural Representations for Simultaneous Localization and Mapping</t>
+        </is>
+      </c>
+      <c r="V398" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W398" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X398" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bonn.de%20%22Yue%20Pan%22%20email</t>
+        </is>
+      </c>
+      <c r="Z398" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5074413345</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>University of Bonn</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Bonn</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>QS #227 (Top Geodesy/Robotics) | Tier S+ (Global Elite | h=1063)</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>@uni-bonn.de</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G399" t="n">
+        <v>7</v>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>Hermann Blum</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J399" t="n">
+        <v>17</v>
+      </c>
+      <c r="K399" t="n">
+        <v>1247</v>
+      </c>
+      <c r="L399" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="M399" t="n">
+        <v>10</v>
+      </c>
+      <c r="N399" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O399" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>loop closure, visual slam, trajectory estimation, pose estimation, semantic segmentation, autonomous navigation</t>
+        </is>
+      </c>
+      <c r="R399" t="n">
+        <v>24</v>
+      </c>
+      <c r="S399" t="n">
+        <v>4826</v>
+      </c>
+      <c r="T399" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U399" t="inlineStr">
+        <is>
+          <t>Loop Closure From Two Views: Revisiting PGO for Scalable Trajectory Estimation Through Monocular Priors</t>
+        </is>
+      </c>
+      <c r="V399" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W399" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X399" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bonn.de%20%22Hermann%20Blum%22%20email</t>
+        </is>
+      </c>
+      <c r="Z399" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5012921430</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>University of Bonn</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Bonn</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>QS #227 (Top Geodesy/Robotics) | Tier S+ (Global Elite | h=1063)</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>@uni-bonn.de</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G400" t="n">
+        <v>8</v>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>Maren Bennewitz</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J400" t="n">
+        <v>37</v>
+      </c>
+      <c r="K400" t="n">
+        <v>8903</v>
+      </c>
+      <c r="L400" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="M400" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N400" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O400" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, state estimation, sensor fusion, robot perception, visual odometry, deep learning</t>
+        </is>
+      </c>
+      <c r="R400" t="n">
+        <v>7</v>
+      </c>
+      <c r="S400" t="n">
+        <v>135</v>
+      </c>
+      <c r="T400" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="U400" t="inlineStr">
+        <is>
+          <t>Perception for Humanoid Robots</t>
+        </is>
+      </c>
+      <c r="V400" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W400" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X400" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bonn.de%20%22Maren%20Bennewitz%22%20email</t>
+        </is>
+      </c>
+      <c r="Z400" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5103231515</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>University of Bonn</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Bonn</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>QS #227 (Top Geodesy/Robotics) | Tier S+ (Global Elite | h=1063)</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>@uni-bonn.de</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G401" t="n">
+        <v>9</v>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>Arul Selvam Periyasamy</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J401" t="n">
+        <v>13</v>
+      </c>
+      <c r="K401" t="n">
+        <v>598</v>
+      </c>
+      <c r="L401" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="M401" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="N401" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O401" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; LiDAR &amp; Multimodal Sensor Fusion; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>pose estimation, point cloud registration, deep learning, object detection, computer vision, robot perception</t>
+        </is>
+      </c>
+      <c r="R401" t="n">
+        <v>6</v>
+      </c>
+      <c r="S401" t="n">
+        <v>14</v>
+      </c>
+      <c r="T401" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="U401" t="inlineStr">
+        <is>
+          <t>YOLOPose V2: Understanding and improving transformer-based 6D pose estimation</t>
+        </is>
+      </c>
+      <c r="V401" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W401" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X401" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bonn.de%20%22Arul%20Selvam%20Periyasamy%22%20email</t>
+        </is>
+      </c>
+      <c r="Z401" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5007129803</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>University of Bonn</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Bonn</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>QS #227 (Top Geodesy/Robotics) | Tier S+ (Global Elite | h=1063)</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>@uni-bonn.de</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G402" t="n">
+        <v>10</v>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Florian Bernard</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J402" t="n">
+        <v>30</v>
+      </c>
+      <c r="K402" t="n">
+        <v>4692</v>
+      </c>
+      <c r="L402" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="M402" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N402" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O402" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>pose estimation, computer vision, point cloud registration, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R402" t="n">
+        <v>4</v>
+      </c>
+      <c r="S402" t="n">
+        <v>40</v>
+      </c>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>The Probabilistic Normal Epipolar Constraint for Frame- To-Frame Rotation Optimization under Uncertain Feature Positions</t>
+        </is>
+      </c>
+      <c r="V402" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W402" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X402" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bonn.de%20%22Florian%20Bernard%22%20email</t>
+        </is>
+      </c>
+      <c r="Z402" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5102989985</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>University of Bonn</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Bonn</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>QS #227 (Top Geodesy/Robotics) | Tier S+ (Global Elite | h=1063)</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>@uni-bonn.de</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G403" t="n">
+        <v>11</v>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>Chris McCool</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J403" t="n">
+        <v>37</v>
+      </c>
+      <c r="K403" t="n">
+        <v>4951</v>
+      </c>
+      <c r="L403" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="M403" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N403" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O403" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>robot localization</t>
+        </is>
+      </c>
+      <c r="R403" t="n">
+        <v>1</v>
+      </c>
+      <c r="S403" t="n">
+        <v>54</v>
+      </c>
+      <c r="T403" t="inlineStr">
+        <is>
+          <t>2022-10-23</t>
+        </is>
+      </c>
+      <c r="U403" t="inlineStr">
+        <is>
+          <t>BonnBot-I: A Precise Weed Management and Crop Monitoring Platform</t>
+        </is>
+      </c>
+      <c r="V403" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W403" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X403" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bonn.de%20%22Chris%20McCool%22%20email</t>
+        </is>
+      </c>
+      <c r="Z403" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5007627004</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>University of Bonn</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Bonn</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>QS #227 (Top Geodesy/Robotics) | Tier S+ (Global Elite | h=1063)</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>@uni-bonn.de</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G404" t="n">
+        <v>12</v>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Jan‐Henrik Haunert</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J404" t="n">
+        <v>22</v>
+      </c>
+      <c r="K404" t="n">
+        <v>1381</v>
+      </c>
+      <c r="L404" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="M404" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N404" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O404" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>point cloud registration, gnss positioning</t>
+        </is>
+      </c>
+      <c r="R404" t="n">
+        <v>3</v>
+      </c>
+      <c r="S404" t="n">
+        <v>84</v>
+      </c>
+      <c r="T404" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="U404" t="inlineStr">
+        <is>
+          <t>Simultaneous planning of standpoints and routing for laser scanning of buildings with network redundancy</t>
+        </is>
+      </c>
+      <c r="V404" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W404" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X404" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bonn.de%20%22Jan%E2%80%90Henrik%20Haunert%22%20email</t>
+        </is>
+      </c>
+      <c r="Z404" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5049298894</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>University of Bonn</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Bonn</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>QS #227 (Top Geodesy/Robotics) | Tier S+ (Global Elite | h=1063)</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>@uni-bonn.de</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G405" t="n">
+        <v>13</v>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Jüergen Gall</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J405" t="n">
+        <v>73</v>
+      </c>
+      <c r="K405" t="n">
+        <v>21032</v>
+      </c>
+      <c r="L405" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="M405" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N405" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O405" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>kalman filter, autonomous vehicles, object detection</t>
+        </is>
+      </c>
+      <c r="R405" t="n">
+        <v>1</v>
+      </c>
+      <c r="S405" t="n">
+        <v>544</v>
+      </c>
+      <c r="T405" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="U405" t="inlineStr">
+        <is>
+          <t>3DMOTFormer: Graph Transformer for Online 3D Multi-Object Tracking</t>
+        </is>
+      </c>
+      <c r="V405" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W405" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X405" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bonn.de%20%22J%C3%BCergen%20Gall%22%20email</t>
+        </is>
+      </c>
+      <c r="Z405" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5012240246</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>University of Duisburg-Essen</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Essen</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=679)</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>@uni-due.de</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G406" t="n">
+        <v>1</v>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Pedro José Marrón</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J406" t="n">
+        <v>28</v>
+      </c>
+      <c r="K406" t="n">
+        <v>2702</v>
+      </c>
+      <c r="L406" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="M406" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N406" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O406" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; 3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>visual localization, object detection, pose estimation, autonomous vehicles, computer vision, autonomous navigation</t>
+        </is>
+      </c>
+      <c r="R406" t="n">
+        <v>4</v>
+      </c>
+      <c r="S406" t="n">
+        <v>47</v>
+      </c>
+      <c r="T406" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="U406" t="inlineStr">
+        <is>
+          <t>Visual Foreign Object Detection for Wireless Charging of Electric Vehicles</t>
+        </is>
+      </c>
+      <c r="V406" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W406" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X406" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-due.de%20%22Pedro%20Jos%C3%A9%20Marr%C3%B3n%22%20email</t>
+        </is>
+      </c>
+      <c r="Z406" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5047117780</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>University of Duisburg-Essen</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Essen</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=679)</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>@uni-due.de</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G407" t="n">
+        <v>2</v>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>Thomas Kaiser</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J407" t="n">
+        <v>34</v>
+      </c>
+      <c r="K407" t="n">
+        <v>5146</v>
+      </c>
+      <c r="L407" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M407" t="n">
+        <v>10</v>
+      </c>
+      <c r="N407" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O407" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>Deep Learning for Navigation &amp; Perception</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>extended kalman filter, kalman filter</t>
+        </is>
+      </c>
+      <c r="R407" t="n">
+        <v>1</v>
+      </c>
+      <c r="S407" t="n">
+        <v>129</v>
+      </c>
+      <c r="T407" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>3D Self-Localization and Tracking with Minimum Anchor Dependency: A Hybrid Measurement and EKF-Based Approach</t>
+        </is>
+      </c>
+      <c r="V407" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W407" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X407" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-due.de%20%22Thomas%20Kaiser%22%20email</t>
+        </is>
+      </c>
+      <c r="Z407" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5071644998</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>University of Duisburg-Essen</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Essen</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=679)</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>@uni-due.de</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G408" t="n">
+        <v>3</v>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>Mohammed El‐Absi</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J408" t="n">
+        <v>17</v>
+      </c>
+      <c r="K408" t="n">
+        <v>849</v>
+      </c>
+      <c r="L408" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M408" t="n">
+        <v>10</v>
+      </c>
+      <c r="N408" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O408" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>Deep Learning for Navigation &amp; Perception</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>extended kalman filter, kalman filter</t>
+        </is>
+      </c>
+      <c r="R408" t="n">
+        <v>1</v>
+      </c>
+      <c r="S408" t="n">
+        <v>26</v>
+      </c>
+      <c r="T408" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>3D Self-Localization and Tracking with Minimum Anchor Dependency: A Hybrid Measurement and EKF-Based Approach</t>
+        </is>
+      </c>
+      <c r="V408" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W408" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X408" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-due.de%20%22Mohammed%20El%E2%80%90Absi%22%20email</t>
+        </is>
+      </c>
+      <c r="Z408" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5073646134</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>TU Dortmund University</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=555)</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>@tu-dortmund.de</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G409" t="n">
+        <v>1</v>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>Moritz Roidl</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J409" t="n">
+        <v>10</v>
+      </c>
+      <c r="K409" t="n">
+        <v>353</v>
+      </c>
+      <c r="L409" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="M409" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N409" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O409" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>pose estimation, visual localization, deep learning, event camera, object detection, autonomous navigation</t>
+        </is>
+      </c>
+      <c r="R409" t="n">
+        <v>6</v>
+      </c>
+      <c r="S409" t="n">
+        <v>63</v>
+      </c>
+      <c r="T409" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>Object Pose Estimation Annotation Pipeline for Multi-view Monocular Camera Systems in Industrial Settings</t>
+        </is>
+      </c>
+      <c r="V409" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W409" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X409" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu-dortmund.de%20%22Moritz%20Roidl%22%20email</t>
+        </is>
+      </c>
+      <c r="Z409" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5071909921</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>TU Dortmund University</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=555)</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>@tu-dortmund.de</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G410" t="n">
+        <v>2</v>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>Torsten Bertram</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J410" t="n">
+        <v>31</v>
+      </c>
+      <c r="K410" t="n">
+        <v>4175</v>
+      </c>
+      <c r="L410" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="M410" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N410" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O410" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>sensor fusion, kalman filter, autonomous driving perception, object detection, lidar camera fusion, depth estimation</t>
+        </is>
+      </c>
+      <c r="R410" t="n">
+        <v>4</v>
+      </c>
+      <c r="S410" t="n">
+        <v>89</v>
+      </c>
+      <c r="T410" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
+          <t>HiLO: High-Level Object Fusion for Autonomous Driving Using Transformers</t>
+        </is>
+      </c>
+      <c r="V410" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W410" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X410" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu-dortmund.de%20%22Torsten%20Bertram%22%20email</t>
+        </is>
+      </c>
+      <c r="Z410" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5051394730</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>TU Dortmund University</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=555)</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>@tu-dortmund.de</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G411" t="n">
+        <v>3</v>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>Matthias G.R. Faes</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J411" t="n">
+        <v>30</v>
+      </c>
+      <c r="K411" t="n">
+        <v>3003</v>
+      </c>
+      <c r="L411" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="M411" t="n">
+        <v>10</v>
+      </c>
+      <c r="N411" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O411" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>pose estimation, gaussian splatting, 3d reconstruction, computer vision</t>
+        </is>
+      </c>
+      <c r="R411" t="n">
+        <v>1</v>
+      </c>
+      <c r="S411" t="n">
+        <v>166</v>
+      </c>
+      <c r="T411" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>Complex 3D structure and crack reconstruction by an online hybrid stereo photogrammetry approach</t>
+        </is>
+      </c>
+      <c r="V411" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W411" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X411" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu-dortmund.de%20%22Matthias%20G.R.%20Faes%22%20email</t>
+        </is>
+      </c>
+      <c r="Z411" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5013454797</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>TU Dortmund University</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=555)</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>@tu-dortmund.de</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G412" t="n">
+        <v>4</v>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>Frank Hoffmann B</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J412" t="n">
+        <v>35</v>
+      </c>
+      <c r="K412" t="n">
+        <v>6335</v>
+      </c>
+      <c r="L412" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="M412" t="n">
+        <v>9</v>
+      </c>
+      <c r="N412" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O412" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>pose estimation, event camera, object detection, mobile robot navigation</t>
+        </is>
+      </c>
+      <c r="R412" t="n">
+        <v>3</v>
+      </c>
+      <c r="S412" t="n">
+        <v>13</v>
+      </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>Mtevent: a Multi-Task Event Camera Dataset for 6D Pose Estimation and Moving Object Detection</t>
+        </is>
+      </c>
+      <c r="V412" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W412" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X412" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu-dortmund.de%20%22Frank%20Hoffmann%20B%22%20email</t>
+        </is>
+      </c>
+      <c r="Z412" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5103267358</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>TU Dortmund University</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=555)</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>@tu-dortmund.de</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G413" t="n">
+        <v>5</v>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>Mirco Hünnefeld</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J413" t="n">
+        <v>42</v>
+      </c>
+      <c r="K413" t="n">
+        <v>13793</v>
+      </c>
+      <c r="L413" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="M413" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N413" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O413" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>robot localization</t>
+        </is>
+      </c>
+      <c r="R413" t="n">
+        <v>1</v>
+      </c>
+      <c r="S413" t="n">
+        <v>339</v>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>A Grid-based Sensor Floor Platform for Robot Localization using Machine Learning</t>
+        </is>
+      </c>
+      <c r="V413" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W413" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X413" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atu-dortmund.de%20%22Mirco%20H%C3%BCnnefeld%22%20email</t>
+        </is>
+      </c>
+      <c r="Z413" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5112948759</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>University of Hamburg</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Tier B (Specialized/Regional | h=5)</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>@brand-university.de</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Direct to PI + University Portal</t>
+        </is>
+      </c>
+      <c r="J414" t="n">
+        <v>0</v>
+      </c>
+      <c r="K414" t="n">
+        <v>0</v>
+      </c>
+      <c r="L414" t="n">
+        <v>0</v>
+      </c>
+      <c r="M414" t="n">
+        <v>0</v>
+      </c>
+      <c r="N414" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O414" t="n">
+        <v>0</v>
+      </c>
+      <c r="R414" t="n">
+        <v>0</v>
+      </c>
+      <c r="S414" t="n">
+        <v>0</v>
+      </c>
+      <c r="W414" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z379"/>
+  <autoFilter ref="A1:Z414"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AG$127</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Z$414</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Z$490</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +462,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -5257,23 +5257,121 @@
           <t>University of Tübingen</t>
         </is>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=937)</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5016606943</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Andreas Geiger</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>MVSplat: Efficient 3D Gaussian Splatting from Sparse Multi-view Images (2024)</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Tübingen</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>@uni-tuebingen.de</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>I8087733</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=90)</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>gaussian splatting, depth estimation, 3d reconstruction, visual slam, pose estimation, 3d perception</t>
+        </is>
+      </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Z38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>5.89</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="4" t="inlineStr"/>
-      <c r="AE38" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Andreas Geiger; Andreas Zell; Gerard Pons‐Moll; Anpei Chen; Ziad M. Hafed; Oliver Bringmann</t>
+        </is>
+      </c>
+      <c r="AD38" s="4" t="inlineStr">
+        <is>
+          <t>1. Andreas Geiger (Full / Senior Prof (Large Lab), h=90) | Fit=8.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=gaussian splatting, depth estimation, 3d reconstruction, visual slam, pose estimation, 3d perception | Paper=MVSplat: Efficient 3D Gaussian Splatting from Sparse Multi-view Images (2024)
+2. Andreas Zell (Full / Senior Prof (Large Lab), h=58) | Fit=8.3/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.3/10 | Keywords=autonomous navigation, robot perception, depth estimation, deep learning, 3d reconstruction, pose estimation | Paper=Learning-Based Distance Estimation for 360° Single-Sensor Setups (2025)
+3. Gerard Pons‐Moll (Full / Senior Prof (Large Lab), h=57) | Fit=5.8/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.7/10 | Keywords=point cloud registration, visual localization, visual slam | Paper=NICP: Neural ICP for 3D Human Registration at Scale (2024)
+4. Anpei Chen (Associate / Established PI (High Fit), h=19) | Fit=4.0/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=4.5/10 | Keywords=gaussian splatting, 3d reconstruction | Paper=ConeGS: Error-Guided Densification Using Pixel Cones for Improved Reconstruction with Fewer Pri (2026)
+5. Ziad M. Hafed (Full / Senior Prof (Large Lab), h=36) | Fit=3.7/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.3/10 | Keywords=visual localization | Paper=Two-Dimensional Perisaccadic Visual Mislocalization in Rhesus Macaque Monkeys (2025)
+6. Oliver Bringmann (Full / Senior Prof (Large Lab), h=28) | Fit=3.5/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.1/10 | Keywords=autonomous vehicles, 3d object detection, object detection, semantic segmentation | Paper=Collective Perception Datasets for Autonomous Driving: A Comprehensive Review (2024)</t>
+        </is>
+      </c>
+      <c r="AE38" s="4" t="inlineStr">
+        <is>
+          <t>Andreas Geiger: No homepage/funding evidence available
+Andreas Zell: No homepage/funding evidence available
+Gerard Pons‐Moll: No homepage/funding evidence available
+Anpei Chen: No homepage/funding evidence available
+Ziad M. Hafed: No homepage/funding evidence available
+Oliver Bringmann: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-tuebingen.de%20%22Andreas%20Geiger%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
@@ -5281,23 +5379,131 @@
           <t>University of Erlangen-Nuremberg</t>
         </is>
       </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=898)</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5059197069</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Jörg E. Franke</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>GeoHash3D: Robust and Efficient 6-DoF Pose Estimation from 3D Marker Sets (2026)</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Erlangen</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>@fau.de</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>I181369854</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=38)</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>pose estimation, point cloud registration, 3d reconstruction, robot perception, object detection</t>
+        </is>
+      </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="Z39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" s="4" t="inlineStr"/>
-      <c r="AE39" s="4" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Jörg E. Franke; Andreas Bück; Bernhard Egger; Andreas Maier; Knut Graichen; Philipp Beckerle; Martin Vossiek; Bernhard Kainz; Franziska Mathis-Ullrich; Tobias Feigl; Jörn Thielecke</t>
+        </is>
+      </c>
+      <c r="AD39" s="4" t="inlineStr">
+        <is>
+          <t>1. Jörg E. Franke (Full / Senior Prof (Large Lab), h=38) | Fit=7.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.8/10 | Keywords=pose estimation, point cloud registration, 3d reconstruction, robot perception, object detection | Paper=GeoHash3D: Robust and Efficient 6-DoF Pose Estimation from 3D Marker Sets (2026)
+2. Andreas Bück (Full / Senior Prof (Large Lab), h=31) | Fit=5.7/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=5.3/10 | Keywords=state estimation, sensor fusion | Paper=Multi-Rate Data Fusion for State and Parameter Estimation in (Bio-)Chemical Process Engineering (2021)
+3. Bernhard Egger (Associate / Established PI (High Fit), h=18) | Fit=5.1/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.3/10 | Keywords=depth estimation, 3d reconstruction, semantic segmentation, autonomous vehicles, 3d object detection, object detection | Paper=Gen3DSR: Generalizable 3D Scene Reconstruction Via Divide and Conquer From a Single View (2025)
+4. Andreas Maier (Full / Senior Prof (Large Lab), h=65) | Fit=5.1/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=5.1/10 | Keywords=point cloud registration | Paper=Abstract: Generation of Synthetic 3D Data using Simulated MR Examinations in Augmented Reality (2024)
+5. Knut Graichen (Full / Senior Prof (Large Lab), h=29) | Fit=5.1/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=5.0/10 | Keywords=state estimation, kalman filter | Paper=Online Learning and Adaptation of Nonlinear Thermal Networks for Power Inverters (2023)
+6. Philipp Beckerle (Full / Senior Prof (Large Lab), h=25) | Fit=4.9/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.0/10 | Keywords=pose estimation, deep learning, object detection | Paper=ASDF: Assembly State Detection Utilizing Late Fusion by Integrating 6D Pose Estimation (2024)
+7. Martin Vossiek (Full / Senior Prof (Large Lab), h=35) | Fit=4.5/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=trajectory estimation, autonomous vehicles, kalman filter | Paper=Integrated Self-Contained Trajectory Estimation and Multistatic SAR Imaging in a Non-Static Unc (2025)
+8. Bernhard Kainz (Full / Senior Prof (Large Lab), h=49) | Fit=4.2/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.7/10 | Keywords=pose estimation | Paper=Multi-camera AR Guidance System for Surgical Instrument Handling and Assembly: Investigating Wo (2026)
+9. Franziska Mathis-Ullrich (Full / Senior Prof (Large Lab), h=22) | Fit=3.6/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.4/10 | Keywords=sensor fusion, semantic segmentation, 3d reconstruction | Paper=Intraoperative fusion of models and data for robust distance sensing (2026)
+10. Tobias Feigl (Associate / Established PI (High Fit), h=17) | Fit=3.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.3/10 | Keywords=gnss positioning | Paper=Active Sensing with Meta-Reinforcement Learning for Emitter Localization from RF Observations (2026)
+11. Jörn Thielecke (Associate / Established PI (High Fit), h=18) | Fit=4.0/10 | Activity=7.4/10 | Funding=0.0/10 | Overall=4.1/10 | Keywords=visual slam | Paper=Error Evaluation of Semantic VSLAM Algorithms for Smart Farming (2022)</t>
+        </is>
+      </c>
+      <c r="AE39" s="4" t="inlineStr">
+        <is>
+          <t>Jörg E. Franke: No homepage/funding evidence available
+Andreas Bück: No homepage/funding evidence available
+Bernhard Egger: No homepage/funding evidence available
+Andreas Maier: No homepage/funding evidence available
+Knut Graichen: No homepage/funding evidence available
+Philipp Beckerle: No homepage/funding evidence available
+Martin Vossiek: No homepage/funding evidence available
+Bernhard Kainz: No homepage/funding evidence available
+Franziska Mathis-Ullrich: No homepage/funding evidence available
+Tobias Feigl: No homepage/funding evidence available
+Jörn Thielecke: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Afau.de%20%22J%C3%B6rg%20E.%20Franke%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
@@ -5305,23 +5511,129 @@
           <t>University of Bremen</t>
         </is>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=488)</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5069823460</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kerstin Schill</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Odometry aided by Speed and Steering Angle Measurements (2022)</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Bremen</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>@uni-bremen.de</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>I180437899</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit) (h=18)</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, state estimation, kalman filter</t>
+        </is>
+      </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>8.58</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>8.57</v>
       </c>
       <c r="Z40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>7.29</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" s="4" t="inlineStr"/>
-      <c r="AE40" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Kerstin Schill; S. Patel; Christof Büskens; Michael Beetz; Ralf Bachmayer; Steffen Paul A; Hui Liu; Nico Hochgeschwender; Gabriel Zachmann; René Weller</t>
+        </is>
+      </c>
+      <c r="AD40" s="4" t="inlineStr">
+        <is>
+          <t>1. Kerstin Schill (Associate / Established PI (High Fit), h=18) | Fit=10.0/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=8.1/10 | Keywords=visual inertial odometry, state estimation, kalman filter | Paper=Visual-Inertial Odometry aided by Speed and Steering Angle Measurements (2022)
+2. S. Patel (Associate / Established PI (High Fit), h=25) | Fit=9.8/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=8.1/10 | Keywords=multi-sensor fusion, sensor fusion, robust localization, extended kalman filter, kalman filter | Paper=Indoor Localization for an Autonomous Model Car: A Marker-Based Multi-Sensor Fusion Framework (2023)
+3. Christof Büskens (Full / Senior Prof (Large Lab), h=18) | Fit=9.8/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=8.1/10 | Keywords=multi-sensor fusion, sensor fusion, robust localization, extended kalman filter, kalman filter | Paper=Indoor Localization for an Autonomous Model Car: A Marker-Based Multi-Sensor Fusion Framework (2023)
+4. Michael Beetz (Full / Senior Prof (Large Lab), h=59) | Fit=7.5/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=6.8/10 | Keywords=robot perception, pose estimation, computer vision, object detection, state estimation | Paper=An Open and Flexible Robot Perception Framework for Mobile Manipulation Tasks (2024)
+5. Ralf Bachmayer (Associate / Established PI (High Fit), h=22) | Fit=5.8/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=5.4/10 | Keywords=depth estimation, hardware acceleration, computer vision, fpga, embedded systems | Paper=Towards Energy-Optimized On-Board Computer Vision for Autonomous Underwater Vehicles (2022)
+6. Steffen Paul A (Full / Senior Prof (Large Lab), h=17) | Fit=5.8/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=5.4/10 | Keywords=depth estimation, hardware acceleration, computer vision, fpga, embedded systems | Paper=Towards Energy-Optimized On-Board Computer Vision for Autonomous Underwater Vehicles (2022)
+7. Hui Liu (Full / Senior Prof (Large Lab), h=32) | Fit=5.1/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.2/10 | Keywords=autonomous navigation, deep learning, object detection, semantic segmentation | Paper=Integrated neural network framework for multi-object detection and recognition using UAV imager (2025)
+8. Nico Hochgeschwender (Associate / Established PI (High Fit), h=15) | Fit=4.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.2/10 | Keywords=robot localization, robot perception, mobile robot navigation | Paper=From Developer Needs to Domain-Specific Languages: Specifying Sceneries for Simulation-Based Va (2025)
+9. Gabriel Zachmann (Full / Senior Prof (Large Lab), h=26) | Fit=4.8/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.0/10 | Keywords=pose estimation, deep learning, robot perception, point cloud registration | Paper=Recurrent multi-view 6DoF pose estimation for marker-less surgical tool tracking (2025)
+10. René Weller (Associate / Established PI (High Fit), h=15) | Fit=4.3/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.5/10 | Keywords=robot perception, point cloud registration | Paper=NaivPhys4RP - Towards Human-like Robot Perception “Physical Reasoning based on Embodied Probabi (2022)</t>
+        </is>
+      </c>
+      <c r="AE40" s="4" t="inlineStr">
+        <is>
+          <t>Kerstin Schill: No homepage/funding evidence available
+S. Patel: No homepage/funding evidence available
+Christof Büskens: No homepage/funding evidence available
+Michael Beetz: No homepage/funding evidence available
+Ralf Bachmayer: No homepage/funding evidence available
+Steffen Paul A: No homepage/funding evidence available
+Hui Liu: No homepage/funding evidence available
+Nico Hochgeschwender: No homepage/funding evidence available
+Gabriel Zachmann: No homepage/funding evidence available
+René Weller: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bremen.de%20%22Kerstin%20Schill%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="X41" t="n">
@@ -5348,23 +5660,165 @@
           <t>Delft University of Technology</t>
         </is>
       </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5058902676</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Guido de Croon</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Self-Supervised Monocular Visual Drone Model Identification through Improved Occlusion Handling (2025)</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>I98358874</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=44)</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>visual odometry, state estimation, pose estimation, visual inertial odometry, autonomous navigation, extended kalman filter</t>
+        </is>
+      </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>9.65</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>9.57</v>
       </c>
       <c r="Z42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>8.19</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" s="4" t="inlineStr"/>
-      <c r="AE42" s="4" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Guido de Croon; Heike Vallery; Christophe De Wagter; Liangliang Nan; Xucong Zhang; Holger Caesar; Julian F. P. Kooij; Emmanuel Vander Poorten; Raj Thilak Rajan; Marija Popović; Jan C. van Gemert; Coen C. de Visser; Michael Weinmann; Guohao Lan; Manon Kok; Peter J. G. Teunissen; Wout Broere; Rudy L. J. Helmons; Javier Alonso–Mora; Christian C. J. M. Tiberius; Sandra Verhagen; Peter J. M. van Oosterom; Jochen  Lorenz Cremer; Dariu M. Gavrila; Justin Dauwels; Alireza Amiri-Simkooei; Aaron Yi Ding; Eberhard K. A. Gill</t>
+        </is>
+      </c>
+      <c r="AD42" s="4" t="inlineStr">
+        <is>
+          <t>1. Guido de Croon (Full / Senior Prof (Large Lab), h=44) | Fit=10.0/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.4/10 | Keywords=visual odometry, state estimation, pose estimation, visual inertial odometry, autonomous navigation, extended kalman filter | Paper=Self-Supervised Monocular Visual Drone Model Identification through Improved Occlusion Handling (2025)
+2. Heike Vallery (Full / Senior Prof (Large Lab), h=33) | Fit=10.0/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=8.3/10 | Keywords=factor graph optimization, robust localization, gnss sensor fusion, sensor fusion, trajectory estimation, state estimation | Paper=GNSS/Multisensor Fusion Using Continuous-Time Factor Graph Optimization for Robust Localization (2024)
+3. Christophe De Wagter (Associate / Established PI (High Fit), h=31) | Fit=9.7/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.3/10 | Keywords=visual odometry, state estimation, pose estimation, visual inertial odometry, extended kalman filter, kalman filter | Paper=Self-Supervised Monocular Visual Drone Model Identification through Improved Occlusion Handling (2025)
+4. Liangliang Nan (Associate / Established PI (High Fit), h=28) | Fit=9.3/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.0/10 | Keywords=visual localization, place recognition, pose estimation, point cloud registration, depth estimation, deep learning | Paper=CoPR: Toward Accurate Visual Localization With Continuous Place-Descriptor Regression (2023)
+5. Xucong Zhang (Associate / Established PI (High Fit), h=28) | Fit=9.2/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.9/10 | Keywords=event camera, depth estimation, object detection | Paper=Cooking Beyond Frames: A Stereo Event Camera Dataset in the Kitchen (2026)
+6. Holger Caesar (Associate / Established PI (High Fit), h=16) | Fit=8.9/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.8/10 | Keywords=multi-sensor fusion, gaussian splatting, sensor fusion, autonomous driving perception, autonomous vehicles, lidar camera fusion | Paper=GaussianCaR: Gaussian Splatting for Efficient Camera-Radar Fusion (2026)
+7. Julian F. P. Kooij (Associate / Established PI (High Fit), h=26) | Fit=9.1/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=visual localization, place recognition, pose estimation, lidar camera fusion, 3d object detection, object detection | Paper=CoPR: Toward Accurate Visual Localization With Continuous Place-Descriptor Regression (2023)
+8. Emmanuel Vander Poorten (Full / Senior Prof (Large Lab), h=31) | Fit=9.1/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=7.6/10 | Keywords=robust localization, sensor fusion, pose estimation, stereo vision | Paper=Fusion Framework for Coaxial Catheter Tracking (2023)
+9. Raj Thilak Rajan (Associate / Established PI (High Fit), h=17) | Fit=8.8/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=7.5/10 | Keywords=visual inertial odometry, autonomous navigation, autonomous vehicles | Paper=GPS-VIO Fusion with Online Rotational Calibration (2024)
+10. Marija Popović (Associate / Established PI (High Fit), h=22) | Fit=8.2/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.3/10 | Keywords=visual inertial odometry, state estimation, visual localization, pose estimation, robot localization, gaussian splatting | Paper=Perception-Aware Autonomous Exploration in Feature-Limited Environments (2026)
+11. Jan C. van Gemert (Full / Senior Prof (Large Lab), h=37) | Fit=8.3/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.3/10 | Keywords=event camera, depth estimation, object detection, deep learning, edge ai | Paper=Cooking Beyond Frames: A Stereo Event Camera Dataset in the Kitchen (2026)
+12. Coen C. de Visser (Full / Senior Prof (Large Lab), h=30) | Fit=8.4/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=7.2/10 | Keywords=visual inertial odometry, state estimation, event camera | Paper=Autonomous Quadrotor Flight Despite Rotor Failure With Onboard Vision Sensors: Frames vs. Event (2022)
+13. Michael Weinmann (Associate / Established PI (High Fit), h=24) | Fit=7.7/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.0/10 | Keywords=pose estimation, edge ai, object detection, jetson, depth estimation, tensorrt | Paper=6D Strawberry Pose Estimation: Real-time and Edge AI Solutions Using Purely Synthetic Training  (2026)
+14. Guohao Lan (Associate / Established PI (High Fit), h=22) | Fit=7.5/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=6.8/10 | Keywords=visual slam, pose estimation | Paper=DNN-based SLAM Tracking Error Online Estimation (2023)
+15. Manon Kok (Associate / Established PI (High Fit), h=21) | Fit=7.5/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=6.7/10 | Keywords=visual slam, state estimation, loop closure, trajectory estimation, extended kalman filter, kalman filter | Paper=Rao-Blackwellized particle smoothing for simultaneous localization and mapping (2024)
+16. Peter J. G. Teunissen (Full / Senior Prof (Large Lab), h=73) | Fit=6.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.2/10 | Keywords=gnss positioning, kalman filter | Paper=Correction: DIA-Estimator and Multidimensional Model Misspecifications: GNSS-based Positioning  (2026)
+17. Wout Broere (Full / Senior Prof (Large Lab), h=28) | Fit=6.3/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.1/10 | Keywords=autonomous navigation, 3d reconstruction, edge ai | Paper=Robotics and unmanned aerial vehicles for smart structural health monitoring: A systematic revi (2026)
+18. Rudy L. J. Helmons (Assistant Prof / Rising Star (Responsive), h=14) | Fit=6.5/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=6.0/10 | Keywords=extended kalman filter, kalman filter | Paper=An Extended Kalman Filter for Magnetic Field SLAM Using Gaussian Process Regression (2022)
+19. Javier Alonso–Mora (Full / Senior Prof (Large Lab), h=44) | Fit=6.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.9/10 | Keywords=loop closure, trajectory estimation, mobile robot navigation | Paper=Wi-Closure: Reliable and Efficient Search of Inter-robot Loop Closures Using Wireless Sensing (2023)
+20. Christian C. J. M. Tiberius (Full / Senior Prof (Large Lab), h=30) | Fit=6.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.9/10 | Keywords=gnss positioning | Paper=Correction: DIA-Estimator and Multidimensional Model Misspecifications: GNSS-based Positioning  (2026)
+21. Sandra Verhagen (Associate / Established PI (High Fit), h=30) | Fit=5.7/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.7/10 | Keywords=gnss positioning | Paper=The Delft School of Mathematical Geodesy—A Brief Review of the Contributions (2025)
+22. Peter J. M. van Oosterom (Full / Senior Prof (Large Lab), h=43) | Fit=4.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.1/10 | Keywords=visual slam, gnss positioning, gaussian splatting | Paper=Identification and Visualization of Unscanned Areas Within a Building Based on the Building’s O (2025)
+23. Jochen  Lorenz Cremer (Associate / Established PI (High Fit), h=17) | Fit=4.9/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.9/10 | Keywords=state estimation, deep learning | Paper=Deep Statistical Solver for Distribution System State Estimation (2023)
+24. Dariu M. Gavrila (Full / Senior Prof (Large Lab), h=49) | Fit=4.8/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.9/10 | Keywords=lidar camera fusion, 3d object detection, object detection | Paper=Multimodal Object Query Initialization for 3D Object Detection (2024)
+25. Justin Dauwels (Full / Senior Prof (Large Lab), h=47) | Fit=4.8/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=lidar camera fusion, autonomous vehicles, pose estimation, sensor fusion | Paper=PEM: Perception Error Model for Virtual Testing of Autonomous Vehicles (2023)
+26. Alireza Amiri-Simkooei (Full / Senior Prof (Large Lab), h=35) | Fit=4.2/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.6/10 | Keywords=gnss positioning | Paper=Multichannel Monte Carlo Singular Spectrum Analysis With Colored Noise Assessment: Application  (2025)
+27. Aaron Yi Ding (Full / Senior Prof (Large Lab), h=26) | Fit=3.6/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.2/10 | Keywords=edge ai, autonomous vehicles | Paper=A Survey on Approximate Edge AI for Energy Efficient Autonomous Driving Services (2023)
+28. Eberhard K. A. Gill (Full / Senior Prof (Large Lab), h=37) | Fit=3.6/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.2/10 | Keywords=gnss positioning | Paper=Snapshot GNSS receivers for low-effort, high-gain space situational awareness (2023)</t>
+        </is>
+      </c>
+      <c r="AE42" s="4" t="inlineStr">
+        <is>
+          <t>Guido de Croon: No homepage/funding evidence available
+Heike Vallery: No homepage/funding evidence available
+Christophe De Wagter: No homepage/funding evidence available
+Liangliang Nan: No homepage/funding evidence available
+Xucong Zhang: No homepage/funding evidence available
+Holger Caesar: No homepage/funding evidence available
+Julian F. P. Kooij: No homepage/funding evidence available
+Emmanuel Vander Poorten: No homepage/funding evidence available
+Raj Thilak Rajan: No homepage/funding evidence available
+Marija Popović: No homepage/funding evidence available
+Jan C. van Gemert: No homepage/funding evidence available
+Coen C. de Visser: No homepage/funding evidence available
+Michael Weinmann: No homepage/funding evidence available
+Guohao Lan: No homepage/funding evidence available
+Manon Kok: No homepage/funding evidence available
+Peter J. G. Teunissen: No homepage/funding evidence available
+Wout Broere: No homepage/funding evidence available
+Rudy L. J. Helmons: No homepage/funding evidence available
+Javier Alonso–Mora: No homepage/funding evidence available
+Christian C. J. M. Tiberius: No homepage/funding evidence available
+Sandra Verhagen: No homepage/funding evidence available
+Peter J. M. van Oosterom: No homepage/funding evidence available
+Jochen  Lorenz Cremer: No homepage/funding evidence available
+Dariu M. Gavrila: No homepage/funding evidence available
+Justin Dauwels: No homepage/funding evidence available
+Alireza Amiri-Simkooei: No homepage/funding evidence available
+Aaron Yi Ding: No homepage/funding evidence available
+Eberhard K. A. Gill: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Guido%20de%20Croon%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
@@ -5372,23 +5826,151 @@
           <t>Eindhoven University of Technology</t>
         </is>
       </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5024010116</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Gijs Dubbelman</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Correction: A Stixel-Based Stereo Perception for Multi-Robot Systems (2023)</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>I83019370</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit) (h=19)</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>robot perception, stereo vision, embedded systems, autonomous driving perception, semantic segmentation</t>
+        </is>
+      </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>7.42</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="Z43" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>6.72</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" s="4" t="inlineStr"/>
-      <c r="AE43" s="4" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gijs Dubbelman; H. J. Wörtche; Ömür Arslan; Gregor Kemper; Herman Bruyninckx; Elena Torta; René van de Molengraft; Aida Todri‐Sanial; Dip Goswami; Ruud J. G. van Sloun; Sander Stuijk; Marc C. W. Geilen; Decebal Constantin Mocanu; Pieter Pauwels; Mohsen Kaboli; M. S. Chong; Yiping Li; Elahe Arani; Bahram Zonooz; Peter H. N. de With; Fons van der Sommen</t>
+        </is>
+      </c>
+      <c r="AD43" s="4" t="inlineStr">
+        <is>
+          <t>1. Gijs Dubbelman (Associate / Established PI (High Fit), h=19) | Fit=8.1/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=7.1/10 | Keywords=robot perception, stereo vision, embedded systems, autonomous driving perception, semantic segmentation | Paper=Correction: A Stixel-Based Stereo Perception for Multi-Robot Systems (2023)
+2. H. J. Wörtche (Associate / Established PI (High Fit), h=30) | Fit=7.9/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.9/10 | Keywords=robot localization, pose estimation, learning-based localization, deep learning, embedded systems | Paper=A Machine Learning Approach to Robot Localization Using Fiducial Markers in RobotAtFactory 4.0  (2023)
+3. Ömür Arslan (Assistant Prof / Rising Star (Responsive), h=15) | Fit=7.3/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=6.6/10 | Keywords=autonomous navigation, mobile robot navigation, ros | Paper=Key-Scan-Based Mobile Robot Navigation: Integrated Mapping, Planning, and Control Using Graphs  (2025)
+4. Gregor Kemper (Associate / Established PI (High Fit), h=21) | Fit=6.9/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.5/10 | Keywords=gnss positioning, robot localization | Paper=Localization from Pseudoranges: Quadrics and Duality (2026)
+5. Herman Bruyninckx (Full / Senior Prof (Large Lab), h=43) | Fit=6.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.4/10 | Keywords=mobile robot navigation, robot localization, robot perception, stereo vision | Paper=Clutter-Resilient Autonomous Mobile Robot Navigation with Computationally Efficient Free-Space  (2023)
+6. Elena Torta (Assistant Prof / Rising Star (Responsive), h=14) | Fit=6.3/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.1/10 | Keywords=robot localization, mobile robot navigation, ros | Paper=Semantic-Enhanced Path Planning for Safety-Centric Indoor Robots Navigation (2024)
+7. René van de Molengraft (Full / Senior Prof (Large Lab), h=33) | Fit=6.2/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.0/10 | Keywords=multi-sensor fusion, sensor fusion, robot localization, mobile robot navigation, robot perception, ros | Paper=Situation-Aware Drivable Space Estimation for Automated Driving (2022)
+8. Aida Todri‐Sanial (Full / Senior Prof (Large Lab), h=25) | Fit=6.2/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=5.8/10 | Keywords=robot localization, mobile robot navigation, object detection, edge ai | Paper=SIFT-ONN: SIFT Feature Detection Algorithm Employing ONNs for Edge Detection (2023)
+9. Dip Goswami (Associate / Established PI (High Fit), h=24) | Fit=5.7/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.6/10 | Keywords=point cloud registration, event camera, deep learning | Paper=R3PM-Net: Real-time, Robust, Real-world Point Matching Network (2026)
+10. Ruud J. G. van Sloun (Full / Senior Prof (Large Lab), h=36) | Fit=5.6/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=5.4/10 | Keywords=state estimation, kalman filter, deep learning | Paper=KalmanNet: Neural Network Aided Kalman Filtering for Partially Known Dynamics (2022)
+11. Sander Stuijk (Full / Senior Prof (Large Lab), h=40) | Fit=5.3/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.4/10 | Keywords=depth estimation, hardware acceleration, embedded systems | Paper=A Flexible Multi-Core Hardware Architecture for Stereo-Based Depth Estimation CNNs (2025)
+12. Marc C. W. Geilen (Full / Senior Prof (Large Lab), h=36) | Fit=5.3/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.4/10 | Keywords=depth estimation, hardware acceleration, embedded systems | Paper=A Flexible Multi-Core Hardware Architecture for Stereo-Based Depth Estimation CNNs (2025)
+13. Decebal Constantin Mocanu (Associate / Established PI (High Fit), h=24) | Fit=5.7/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=5.3/10 | Keywords=multi-sensor fusion, sensor fusion | Paper=Situation-Aware Drivable Space Estimation for Automated Driving (2022)
+14. Pieter Pauwels (Full / Senior Prof (Large Lab), h=40) | Fit=5.4/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.3/10 | Keywords=mobile robot navigation, robot localization | Paper=Semantic Path Planning for Heterogeneous Robots from Building Digital Twin Data (2025)
+15. Mohsen Kaboli (Associate / Established PI (High Fit), h=21) | Fit=4.6/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.9/10 | Keywords=pose estimation | Paper=Shared visuo-tactile interactive perception for robust object pose estimation (2024)
+16. M. S. Chong (Associate / Established PI (High Fit), h=14) | Fit=4.3/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=state estimation | Paper=Resilient Nonlinear State Estimation Using the Median Operation for a Network of Droop-Controll (2024)
+17. Yiping Li (Full / Senior Prof (Large Lab), h=25) | Fit=4.2/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.6/10 | Keywords=pose estimation, deep learning | Paper=SurgRIPE challenge: Benchmark of surgical robot instrument pose estimation (2025)
+18. Elahe Arani (Associate / Established PI (High Fit), h=16) | Fit=4.1/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.4/10 | Keywords=depth estimation | Paper=Transformers in Unsupervised Structure-from-Motion (2023)
+19. Bahram Zonooz (Associate / Established PI (High Fit), h=15) | Fit=4.1/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.4/10 | Keywords=depth estimation | Paper=Transformers in Unsupervised Structure-from-Motion (2023)
+20. Peter H. N. de With (Full / Senior Prof (Large Lab), h=42) | Fit=3.9/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.3/10 | Keywords=3d reconstruction, deep learning, computer vision | Paper=Proceedings of the Workshop on 3D Geometry Generation for Scientific Computing (2024)
+21. Fons van der Sommen (Full / Senior Prof (Large Lab), h=28) | Fit=3.7/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.2/10 | Keywords=3d reconstruction, deep learning, computer vision | Paper=Proceedings of the Workshop on 3D Geometry Generation for Scientific Computing (2024)</t>
+        </is>
+      </c>
+      <c r="AE43" s="4" t="inlineStr">
+        <is>
+          <t>Gijs Dubbelman: No homepage/funding evidence available
+H. J. Wörtche: No homepage/funding evidence available
+Ömür Arslan: No homepage/funding evidence available
+Gregor Kemper: No homepage/funding evidence available
+Herman Bruyninckx: No homepage/funding evidence available
+Elena Torta: No homepage/funding evidence available
+René van de Molengraft: No homepage/funding evidence available
+Aida Todri‐Sanial: No homepage/funding evidence available
+Dip Goswami: No homepage/funding evidence available
+Ruud J. G. van Sloun: No homepage/funding evidence available
+Sander Stuijk: No homepage/funding evidence available
+Marc C. W. Geilen: No homepage/funding evidence available
+Decebal Constantin Mocanu: No homepage/funding evidence available
+Pieter Pauwels: No homepage/funding evidence available
+Mohsen Kaboli: No homepage/funding evidence available
+M. S. Chong: No homepage/funding evidence available
+Yiping Li: No homepage/funding evidence available
+Elahe Arani: No homepage/funding evidence available
+Bahram Zonooz: No homepage/funding evidence available
+Peter H. N. de With: No homepage/funding evidence available
+Fons van der Sommen: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22Gijs%20Dubbelman%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
@@ -7363,7 +7945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z414"/>
+  <dimension ref="A1:Z490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -51617,8 +52199,8140 @@
       </c>
       <c r="W414" s="4" t="inlineStr"/>
     </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>University of Tübingen</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Tübingen</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=937)</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>@uni-tuebingen.de</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G415" t="n">
+        <v>1</v>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>Andreas Geiger</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J415" t="n">
+        <v>90</v>
+      </c>
+      <c r="K415" t="n">
+        <v>66236</v>
+      </c>
+      <c r="L415" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="M415" t="n">
+        <v>10</v>
+      </c>
+      <c r="N415" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O415" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM; Deep Learning for Navigation &amp; Perception</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>gaussian splatting, depth estimation, 3d reconstruction, visual slam, pose estimation, 3d perception</t>
+        </is>
+      </c>
+      <c r="R415" t="n">
+        <v>12</v>
+      </c>
+      <c r="S415" t="n">
+        <v>204</v>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="U415" t="inlineStr">
+        <is>
+          <t>MVSplat: Efficient 3D Gaussian Splatting from Sparse Multi-view Images</t>
+        </is>
+      </c>
+      <c r="V415" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W415" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X415" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-tuebingen.de%20%22Andreas%20Geiger%22%20email</t>
+        </is>
+      </c>
+      <c r="Z415" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5016606943</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>University of Tübingen</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Tübingen</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=937)</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>@uni-tuebingen.de</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G416" t="n">
+        <v>2</v>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>Andreas Zell</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J416" t="n">
+        <v>58</v>
+      </c>
+      <c r="K416" t="n">
+        <v>12458</v>
+      </c>
+      <c r="L416" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="M416" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N416" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O416" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; State Estimation &amp; Factor Graphs; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>autonomous navigation, robot perception, depth estimation, deep learning, 3d reconstruction, pose estimation</t>
+        </is>
+      </c>
+      <c r="R416" t="n">
+        <v>4</v>
+      </c>
+      <c r="S416" t="n">
+        <v>93</v>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>Learning-Based Distance Estimation for 360° Single-Sensor Setups</t>
+        </is>
+      </c>
+      <c r="V416" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W416" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X416" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-tuebingen.de%20%22Andreas%20Zell%22%20email</t>
+        </is>
+      </c>
+      <c r="Z416" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5004958444</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>University of Tübingen</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Tübingen</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=937)</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>@uni-tuebingen.de</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G417" t="n">
+        <v>3</v>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>Gerard Pons‐Moll</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J417" t="n">
+        <v>57</v>
+      </c>
+      <c r="K417" t="n">
+        <v>20440</v>
+      </c>
+      <c r="L417" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="M417" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N417" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O417" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; 3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>point cloud registration, visual localization, visual slam</t>
+        </is>
+      </c>
+      <c r="R417" t="n">
+        <v>4</v>
+      </c>
+      <c r="S417" t="n">
+        <v>102</v>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>NICP: Neural ICP for 3D Human Registration at Scale</t>
+        </is>
+      </c>
+      <c r="V417" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W417" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X417" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-tuebingen.de%20%22Gerard%20Pons%E2%80%90Moll%22%20email</t>
+        </is>
+      </c>
+      <c r="Z417" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5076908763</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>University of Tübingen</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Tübingen</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=937)</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>@uni-tuebingen.de</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G418" t="n">
+        <v>4</v>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>Anpei Chen</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J418" t="n">
+        <v>19</v>
+      </c>
+      <c r="K418" t="n">
+        <v>4574</v>
+      </c>
+      <c r="L418" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="M418" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N418" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O418" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>gaussian splatting, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R418" t="n">
+        <v>1</v>
+      </c>
+      <c r="S418" t="n">
+        <v>51</v>
+      </c>
+      <c r="T418" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>ConeGS: Error-Guided Densification Using Pixel Cones for Improved Reconstruction with Fewer Primitives</t>
+        </is>
+      </c>
+      <c r="V418" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W418" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X418" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-tuebingen.de%20%22Anpei%20Chen%22%20email</t>
+        </is>
+      </c>
+      <c r="Z418" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5075572935</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>University of Tübingen</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Tübingen</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=937)</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>@uni-tuebingen.de</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G419" t="n">
+        <v>5</v>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Ziad M. Hafed</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J419" t="n">
+        <v>36</v>
+      </c>
+      <c r="K419" t="n">
+        <v>5019</v>
+      </c>
+      <c r="L419" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="M419" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N419" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O419" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>visual localization</t>
+        </is>
+      </c>
+      <c r="R419" t="n">
+        <v>2</v>
+      </c>
+      <c r="S419" t="n">
+        <v>61</v>
+      </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>Two-Dimensional Perisaccadic Visual Mislocalization in Rhesus Macaque Monkeys</t>
+        </is>
+      </c>
+      <c r="V419" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W419" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X419" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-tuebingen.de%20%22Ziad%20M.%20Hafed%22%20email</t>
+        </is>
+      </c>
+      <c r="Z419" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5053077408</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>University of Tübingen</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Tübingen</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=937)</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>@uni-tuebingen.de</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G420" t="n">
+        <v>6</v>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>Oliver Bringmann</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J420" t="n">
+        <v>28</v>
+      </c>
+      <c r="K420" t="n">
+        <v>3423</v>
+      </c>
+      <c r="L420" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="M420" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N420" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O420" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>autonomous vehicles, 3d object detection, object detection, semantic segmentation</t>
+        </is>
+      </c>
+      <c r="R420" t="n">
+        <v>1</v>
+      </c>
+      <c r="S420" t="n">
+        <v>104</v>
+      </c>
+      <c r="T420" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>Collective Perception Datasets for Autonomous Driving: A Comprehensive Review</t>
+        </is>
+      </c>
+      <c r="V420" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W420" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X420" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-tuebingen.de%20%22Oliver%20Bringmann%22%20email</t>
+        </is>
+      </c>
+      <c r="Z420" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5074802358</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>University of Erlangen-Nuremberg</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Erlangen</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=898)</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>@fau.de</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G421" t="n">
+        <v>1</v>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>Jörg E. Franke</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J421" t="n">
+        <v>38</v>
+      </c>
+      <c r="K421" t="n">
+        <v>9770</v>
+      </c>
+      <c r="L421" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="M421" t="n">
+        <v>10</v>
+      </c>
+      <c r="N421" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O421" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>pose estimation, point cloud registration, 3d reconstruction, robot perception, object detection</t>
+        </is>
+      </c>
+      <c r="R421" t="n">
+        <v>7</v>
+      </c>
+      <c r="S421" t="n">
+        <v>447</v>
+      </c>
+      <c r="T421" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>GeoHash3D: Robust and Efficient 6-DoF Pose Estimation from 3D Marker Sets</t>
+        </is>
+      </c>
+      <c r="V421" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W421" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X421" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Afau.de%20%22J%C3%B6rg%20E.%20Franke%22%20email</t>
+        </is>
+      </c>
+      <c r="Z421" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5059197069</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>University of Erlangen-Nuremberg</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Erlangen</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=898)</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>@fau.de</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G422" t="n">
+        <v>2</v>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>Andreas Bück</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J422" t="n">
+        <v>31</v>
+      </c>
+      <c r="K422" t="n">
+        <v>3097</v>
+      </c>
+      <c r="L422" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="M422" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N422" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O422" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>state estimation, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R422" t="n">
+        <v>1</v>
+      </c>
+      <c r="S422" t="n">
+        <v>82</v>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>2021-11-08</t>
+        </is>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>Multi-Rate Data Fusion for State and Parameter Estimation in (Bio-)Chemical Process Engineering</t>
+        </is>
+      </c>
+      <c r="V422" t="n">
+        <v>2021</v>
+      </c>
+      <c r="W422" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X422" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Afau.de%20%22Andreas%20B%C3%BCck%22%20email</t>
+        </is>
+      </c>
+      <c r="Z422" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5008350442</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>University of Erlangen-Nuremberg</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Erlangen</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=898)</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>@fau.de</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G423" t="n">
+        <v>3</v>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>Bernhard Egger</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J423" t="n">
+        <v>18</v>
+      </c>
+      <c r="K423" t="n">
+        <v>1770</v>
+      </c>
+      <c r="L423" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="M423" t="n">
+        <v>10</v>
+      </c>
+      <c r="N423" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O423" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>depth estimation, 3d reconstruction, semantic segmentation, autonomous vehicles, 3d object detection, object detection</t>
+        </is>
+      </c>
+      <c r="R423" t="n">
+        <v>4</v>
+      </c>
+      <c r="S423" t="n">
+        <v>95</v>
+      </c>
+      <c r="T423" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="U423" t="inlineStr">
+        <is>
+          <t>Gen3DSR: Generalizable 3D Scene Reconstruction Via Divide and Conquer From a Single View</t>
+        </is>
+      </c>
+      <c r="V423" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W423" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X423" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Afau.de%20%22Bernhard%20Egger%22%20email</t>
+        </is>
+      </c>
+      <c r="Z423" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5075603650</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>University of Erlangen-Nuremberg</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Erlangen</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=898)</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>@fau.de</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G424" t="n">
+        <v>4</v>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>Andreas Maier</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J424" t="n">
+        <v>65</v>
+      </c>
+      <c r="K424" t="n">
+        <v>21067</v>
+      </c>
+      <c r="L424" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="M424" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N424" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O424" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>point cloud registration</t>
+        </is>
+      </c>
+      <c r="R424" t="n">
+        <v>1</v>
+      </c>
+      <c r="S424" t="n">
+        <v>1064</v>
+      </c>
+      <c r="T424" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="U424" t="inlineStr">
+        <is>
+          <t>Abstract: Generation of Synthetic 3D Data using Simulated MR Examinations in Augmented Reality</t>
+        </is>
+      </c>
+      <c r="V424" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W424" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X424" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Afau.de%20%22Andreas%20Maier%22%20email</t>
+        </is>
+      </c>
+      <c r="Z424" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5101619735</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>University of Erlangen-Nuremberg</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Erlangen</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=898)</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>@fau.de</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G425" t="n">
+        <v>5</v>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>Knut Graichen</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J425" t="n">
+        <v>29</v>
+      </c>
+      <c r="K425" t="n">
+        <v>3548</v>
+      </c>
+      <c r="L425" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="M425" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N425" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O425" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>state estimation, kalman filter</t>
+        </is>
+      </c>
+      <c r="R425" t="n">
+        <v>1</v>
+      </c>
+      <c r="S425" t="n">
+        <v>124</v>
+      </c>
+      <c r="T425" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>Online Learning and Adaptation of Nonlinear Thermal Networks for Power Inverters</t>
+        </is>
+      </c>
+      <c r="V425" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W425" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X425" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Afau.de%20%22Knut%20Graichen%22%20email</t>
+        </is>
+      </c>
+      <c r="Z425" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5021957729</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>University of Erlangen-Nuremberg</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Erlangen</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=898)</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>@fau.de</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G426" t="n">
+        <v>6</v>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Philipp Beckerle</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J426" t="n">
+        <v>25</v>
+      </c>
+      <c r="K426" t="n">
+        <v>2957</v>
+      </c>
+      <c r="L426" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M426" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N426" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O426" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>pose estimation, deep learning, object detection</t>
+        </is>
+      </c>
+      <c r="R426" t="n">
+        <v>1</v>
+      </c>
+      <c r="S426" t="n">
+        <v>107</v>
+      </c>
+      <c r="T426" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>ASDF: Assembly State Detection Utilizing Late Fusion by Integrating 6D Pose Estimation</t>
+        </is>
+      </c>
+      <c r="V426" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W426" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X426" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Afau.de%20%22Philipp%20Beckerle%22%20email</t>
+        </is>
+      </c>
+      <c r="Z426" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5082242689</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>University of Erlangen-Nuremberg</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Erlangen</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=898)</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>@fau.de</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G427" t="n">
+        <v>7</v>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Martin Vossiek</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J427" t="n">
+        <v>35</v>
+      </c>
+      <c r="K427" t="n">
+        <v>5817</v>
+      </c>
+      <c r="L427" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="M427" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N427" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O427" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>trajectory estimation, autonomous vehicles, kalman filter</t>
+        </is>
+      </c>
+      <c r="R427" t="n">
+        <v>2</v>
+      </c>
+      <c r="S427" t="n">
+        <v>229</v>
+      </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="U427" t="inlineStr">
+        <is>
+          <t>Integrated Self-Contained Trajectory Estimation and Multistatic SAR Imaging in a Non-Static Uncoupled Bistatic Radar Network</t>
+        </is>
+      </c>
+      <c r="V427" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W427" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X427" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Afau.de%20%22Martin%20Vossiek%22%20email</t>
+        </is>
+      </c>
+      <c r="Z427" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5026943179</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>University of Erlangen-Nuremberg</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Erlangen</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=898)</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>@fau.de</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G428" t="n">
+        <v>8</v>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>Bernhard Kainz</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J428" t="n">
+        <v>49</v>
+      </c>
+      <c r="K428" t="n">
+        <v>16998</v>
+      </c>
+      <c r="L428" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="M428" t="n">
+        <v>10</v>
+      </c>
+      <c r="N428" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O428" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>pose estimation</t>
+        </is>
+      </c>
+      <c r="R428" t="n">
+        <v>1</v>
+      </c>
+      <c r="S428" t="n">
+        <v>178</v>
+      </c>
+      <c r="T428" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="U428" t="inlineStr">
+        <is>
+          <t>Multi-camera AR Guidance System for Surgical Instrument Handling and Assembly: Investigating Workload and Efficiency</t>
+        </is>
+      </c>
+      <c r="V428" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W428" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X428" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Afau.de%20%22Bernhard%20Kainz%22%20email</t>
+        </is>
+      </c>
+      <c r="Z428" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5078127596</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>University of Erlangen-Nuremberg</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Erlangen</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=898)</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>@fau.de</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G429" t="n">
+        <v>9</v>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>Franziska Mathis-Ullrich</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J429" t="n">
+        <v>22</v>
+      </c>
+      <c r="K429" t="n">
+        <v>1965</v>
+      </c>
+      <c r="L429" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="M429" t="n">
+        <v>10</v>
+      </c>
+      <c r="N429" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O429" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>sensor fusion, semantic segmentation, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R429" t="n">
+        <v>2</v>
+      </c>
+      <c r="S429" t="n">
+        <v>129</v>
+      </c>
+      <c r="T429" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="U429" t="inlineStr">
+        <is>
+          <t>Intraoperative fusion of models and data for robust distance sensing</t>
+        </is>
+      </c>
+      <c r="V429" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W429" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X429" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Afau.de%20%22Franziska%20Mathis-Ullrich%22%20email</t>
+        </is>
+      </c>
+      <c r="Z429" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5039110908</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>University of Erlangen-Nuremberg</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Erlangen</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=898)</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>@fau.de</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G430" t="n">
+        <v>10</v>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>Tobias Feigl</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J430" t="n">
+        <v>17</v>
+      </c>
+      <c r="K430" t="n">
+        <v>867</v>
+      </c>
+      <c r="L430" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="M430" t="n">
+        <v>10</v>
+      </c>
+      <c r="N430" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O430" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>gnss positioning</t>
+        </is>
+      </c>
+      <c r="R430" t="n">
+        <v>1</v>
+      </c>
+      <c r="S430" t="n">
+        <v>66</v>
+      </c>
+      <c r="T430" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="U430" t="inlineStr">
+        <is>
+          <t>Active Sensing with Meta-Reinforcement Learning for Emitter Localization from RF Observations</t>
+        </is>
+      </c>
+      <c r="V430" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W430" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X430" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Afau.de%20%22Tobias%20Feigl%22%20email</t>
+        </is>
+      </c>
+      <c r="Z430" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5015986195</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>University of Erlangen-Nuremberg</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Erlangen</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=898)</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>@fau.de</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G431" t="n">
+        <v>11</v>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Jörn Thielecke</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J431" t="n">
+        <v>18</v>
+      </c>
+      <c r="K431" t="n">
+        <v>1459</v>
+      </c>
+      <c r="L431" t="n">
+        <v>4</v>
+      </c>
+      <c r="M431" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="N431" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O431" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>visual slam</t>
+        </is>
+      </c>
+      <c r="R431" t="n">
+        <v>1</v>
+      </c>
+      <c r="S431" t="n">
+        <v>14</v>
+      </c>
+      <c r="T431" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="U431" t="inlineStr">
+        <is>
+          <t>Error Evaluation of Semantic VSLAM Algorithms for Smart Farming</t>
+        </is>
+      </c>
+      <c r="V431" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W431" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X431" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Afau.de%20%22J%C3%B6rn%20Thielecke%22%20email</t>
+        </is>
+      </c>
+      <c r="Z431" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5019918338</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>University of Bremen</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Bremen</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=488)</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>@uni-bremen.de</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G432" t="n">
+        <v>1</v>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>Kerstin Schill</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J432" t="n">
+        <v>18</v>
+      </c>
+      <c r="K432" t="n">
+        <v>1229</v>
+      </c>
+      <c r="L432" t="n">
+        <v>10</v>
+      </c>
+      <c r="M432" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N432" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O432" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, state estimation, kalman filter</t>
+        </is>
+      </c>
+      <c r="R432" t="n">
+        <v>1</v>
+      </c>
+      <c r="S432" t="n">
+        <v>16</v>
+      </c>
+      <c r="T432" t="inlineStr">
+        <is>
+          <t>2022-07-04</t>
+        </is>
+      </c>
+      <c r="U432" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Odometry aided by Speed and Steering Angle Measurements</t>
+        </is>
+      </c>
+      <c r="V432" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W432" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X432" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bremen.de%20%22Kerstin%20Schill%22%20email</t>
+        </is>
+      </c>
+      <c r="Z432" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5069823460</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>University of Bremen</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Bremen</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=488)</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>@uni-bremen.de</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G433" t="n">
+        <v>2</v>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>S. Patel</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J433" t="n">
+        <v>25</v>
+      </c>
+      <c r="K433" t="n">
+        <v>2022</v>
+      </c>
+      <c r="L433" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M433" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N433" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O433" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, sensor fusion, robust localization, extended kalman filter, kalman filter</t>
+        </is>
+      </c>
+      <c r="R433" t="n">
+        <v>1</v>
+      </c>
+      <c r="S433" t="n">
+        <v>18</v>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="U433" t="inlineStr">
+        <is>
+          <t>Indoor Localization for an Autonomous Model Car: A Marker-Based Multi-Sensor Fusion Framework</t>
+        </is>
+      </c>
+      <c r="V433" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W433" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X433" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bremen.de%20%22S.%20Patel%22%20email</t>
+        </is>
+      </c>
+      <c r="Z433" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5063519644</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>University of Bremen</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Bremen</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=488)</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>@uni-bremen.de</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G434" t="n">
+        <v>3</v>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Christof Büskens</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J434" t="n">
+        <v>18</v>
+      </c>
+      <c r="K434" t="n">
+        <v>1699</v>
+      </c>
+      <c r="L434" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M434" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N434" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O434" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, sensor fusion, robust localization, extended kalman filter, kalman filter</t>
+        </is>
+      </c>
+      <c r="R434" t="n">
+        <v>1</v>
+      </c>
+      <c r="S434" t="n">
+        <v>58</v>
+      </c>
+      <c r="T434" t="inlineStr">
+        <is>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="U434" t="inlineStr">
+        <is>
+          <t>Indoor Localization for an Autonomous Model Car: A Marker-Based Multi-Sensor Fusion Framework</t>
+        </is>
+      </c>
+      <c r="V434" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W434" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X434" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bremen.de%20%22Christof%20B%C3%BCskens%22%20email</t>
+        </is>
+      </c>
+      <c r="Z434" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5024184563</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>University of Bremen</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Bremen</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=488)</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>@uni-bremen.de</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G435" t="n">
+        <v>4</v>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>Michael Beetz</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J435" t="n">
+        <v>59</v>
+      </c>
+      <c r="K435" t="n">
+        <v>19635</v>
+      </c>
+      <c r="L435" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="M435" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N435" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O435" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>robot perception, pose estimation, computer vision, object detection, state estimation</t>
+        </is>
+      </c>
+      <c r="R435" t="n">
+        <v>3</v>
+      </c>
+      <c r="S435" t="n">
+        <v>91</v>
+      </c>
+      <c r="T435" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>An Open and Flexible Robot Perception Framework for Mobile Manipulation Tasks</t>
+        </is>
+      </c>
+      <c r="V435" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W435" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X435" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bremen.de%20%22Michael%20Beetz%22%20email</t>
+        </is>
+      </c>
+      <c r="Z435" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5003274224</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>University of Bremen</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Bremen</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=488)</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>@uni-bremen.de</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G436" t="n">
+        <v>5</v>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>Ralf Bachmayer</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J436" t="n">
+        <v>22</v>
+      </c>
+      <c r="K436" t="n">
+        <v>2262</v>
+      </c>
+      <c r="L436" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="M436" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N436" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O436" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>depth estimation, hardware acceleration, computer vision, fpga, embedded systems</t>
+        </is>
+      </c>
+      <c r="R436" t="n">
+        <v>1</v>
+      </c>
+      <c r="S436" t="n">
+        <v>29</v>
+      </c>
+      <c r="T436" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>Towards Energy-Optimized On-Board Computer Vision for Autonomous Underwater Vehicles</t>
+        </is>
+      </c>
+      <c r="V436" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W436" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X436" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bremen.de%20%22Ralf%20Bachmayer%22%20email</t>
+        </is>
+      </c>
+      <c r="Z436" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5009738217</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>University of Bremen</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Bremen</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=488)</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>@uni-bremen.de</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G437" t="n">
+        <v>6</v>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>Steffen Paul A</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J437" t="n">
+        <v>17</v>
+      </c>
+      <c r="K437" t="n">
+        <v>1590</v>
+      </c>
+      <c r="L437" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="M437" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N437" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O437" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>depth estimation, hardware acceleration, computer vision, fpga, embedded systems</t>
+        </is>
+      </c>
+      <c r="R437" t="n">
+        <v>1</v>
+      </c>
+      <c r="S437" t="n">
+        <v>33</v>
+      </c>
+      <c r="T437" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="U437" t="inlineStr">
+        <is>
+          <t>Towards Energy-Optimized On-Board Computer Vision for Autonomous Underwater Vehicles</t>
+        </is>
+      </c>
+      <c r="V437" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W437" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X437" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bremen.de%20%22Steffen%20Paul%20A%22%20email</t>
+        </is>
+      </c>
+      <c r="Z437" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5101959993</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>University of Bremen</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Bremen</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=488)</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>@uni-bremen.de</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G438" t="n">
+        <v>7</v>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>Hui Liu</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J438" t="n">
+        <v>32</v>
+      </c>
+      <c r="K438" t="n">
+        <v>4162</v>
+      </c>
+      <c r="L438" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="M438" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N438" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O438" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>autonomous navigation, deep learning, object detection, semantic segmentation</t>
+        </is>
+      </c>
+      <c r="R438" t="n">
+        <v>1</v>
+      </c>
+      <c r="S438" t="n">
+        <v>103</v>
+      </c>
+      <c r="T438" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>Integrated neural network framework for multi-object detection and recognition using UAV imagery</t>
+        </is>
+      </c>
+      <c r="V438" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W438" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X438" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bremen.de%20%22Hui%20Liu%22%20email</t>
+        </is>
+      </c>
+      <c r="Z438" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5021403424</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>University of Bremen</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Bremen</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=488)</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>@uni-bremen.de</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G439" t="n">
+        <v>8</v>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Nico Hochgeschwender</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J439" t="n">
+        <v>15</v>
+      </c>
+      <c r="K439" t="n">
+        <v>984</v>
+      </c>
+      <c r="L439" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="M439" t="n">
+        <v>10</v>
+      </c>
+      <c r="N439" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O439" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>robot localization, robot perception, mobile robot navigation</t>
+        </is>
+      </c>
+      <c r="R439" t="n">
+        <v>5</v>
+      </c>
+      <c r="S439" t="n">
+        <v>47</v>
+      </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>From Developer Needs to Domain-Specific Languages: Specifying Sceneries for Simulation-Based Validation of Mobile Robots</t>
+        </is>
+      </c>
+      <c r="V439" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W439" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X439" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bremen.de%20%22Nico%20Hochgeschwender%22%20email</t>
+        </is>
+      </c>
+      <c r="Z439" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5075287635</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>University of Bremen</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Bremen</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=488)</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>@uni-bremen.de</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G440" t="n">
+        <v>9</v>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>Gabriel Zachmann</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J440" t="n">
+        <v>26</v>
+      </c>
+      <c r="K440" t="n">
+        <v>3261</v>
+      </c>
+      <c r="L440" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="M440" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N440" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O440" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; Robotics &amp; Autonomous Navigation; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>pose estimation, deep learning, robot perception, point cloud registration</t>
+        </is>
+      </c>
+      <c r="R440" t="n">
+        <v>3</v>
+      </c>
+      <c r="S440" t="n">
+        <v>77</v>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>Recurrent multi-view 6DoF pose estimation for marker-less surgical tool tracking</t>
+        </is>
+      </c>
+      <c r="V440" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W440" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X440" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bremen.de%20%22Gabriel%20Zachmann%22%20email</t>
+        </is>
+      </c>
+      <c r="Z440" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5052869741</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>University of Bremen</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Bremen</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=488)</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>@uni-bremen.de</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Direct to PI / Chair (Cold Email Strong)</t>
+        </is>
+      </c>
+      <c r="G441" t="n">
+        <v>10</v>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>René Weller</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J441" t="n">
+        <v>15</v>
+      </c>
+      <c r="K441" t="n">
+        <v>696</v>
+      </c>
+      <c r="L441" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="M441" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N441" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O441" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>robot perception, point cloud registration</t>
+        </is>
+      </c>
+      <c r="R441" t="n">
+        <v>2</v>
+      </c>
+      <c r="S441" t="n">
+        <v>35</v>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>2022-11-28</t>
+        </is>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>NaivPhys4RP - Towards Human-like Robot Perception “Physical Reasoning based on Embodied Probabilistic Simulation”</t>
+        </is>
+      </c>
+      <c r="V441" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W441" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X441" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auni-bremen.de%20%22Ren%C3%A9%20Weller%22%20email</t>
+        </is>
+      </c>
+      <c r="Z441" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5018217148</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G442" t="n">
+        <v>1</v>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>Guido de Croon</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J442" t="n">
+        <v>44</v>
+      </c>
+      <c r="K442" t="n">
+        <v>7363</v>
+      </c>
+      <c r="L442" t="n">
+        <v>10</v>
+      </c>
+      <c r="M442" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N442" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O442" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>visual odometry, state estimation, pose estimation, visual inertial odometry, autonomous navigation, extended kalman filter</t>
+        </is>
+      </c>
+      <c r="R442" t="n">
+        <v>12</v>
+      </c>
+      <c r="S442" t="n">
+        <v>153</v>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>Self-Supervised Monocular Visual Drone Model Identification through Improved Occlusion Handling</t>
+        </is>
+      </c>
+      <c r="V442" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W442" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X442" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Guido%20de%20Croon%22%20email</t>
+        </is>
+      </c>
+      <c r="Z442" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5058902676</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G443" t="n">
+        <v>2</v>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>Heike Vallery</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J443" t="n">
+        <v>33</v>
+      </c>
+      <c r="K443" t="n">
+        <v>5096</v>
+      </c>
+      <c r="L443" t="n">
+        <v>10</v>
+      </c>
+      <c r="M443" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N443" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O443" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>factor graph optimization, robust localization, gnss sensor fusion, sensor fusion, trajectory estimation, state estimation</t>
+        </is>
+      </c>
+      <c r="R443" t="n">
+        <v>4</v>
+      </c>
+      <c r="S443" t="n">
+        <v>127</v>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>GNSS/Multisensor Fusion Using Continuous-Time Factor Graph Optimization for Robust Localization</t>
+        </is>
+      </c>
+      <c r="V443" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W443" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X443" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Heike%20Vallery%22%20email</t>
+        </is>
+      </c>
+      <c r="Z443" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5007760731</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G444" t="n">
+        <v>3</v>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>Christophe De Wagter</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J444" t="n">
+        <v>31</v>
+      </c>
+      <c r="K444" t="n">
+        <v>3808</v>
+      </c>
+      <c r="L444" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="M444" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N444" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O444" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>visual odometry, state estimation, pose estimation, visual inertial odometry, extended kalman filter, kalman filter</t>
+        </is>
+      </c>
+      <c r="R444" t="n">
+        <v>4</v>
+      </c>
+      <c r="S444" t="n">
+        <v>63</v>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>Self-Supervised Monocular Visual Drone Model Identification through Improved Occlusion Handling</t>
+        </is>
+      </c>
+      <c r="V444" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W444" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X444" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Christophe%20De%20Wagter%22%20email</t>
+        </is>
+      </c>
+      <c r="Z444" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5000649174</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G445" t="n">
+        <v>4</v>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>Liangliang Nan</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J445" t="n">
+        <v>28</v>
+      </c>
+      <c r="K445" t="n">
+        <v>2820</v>
+      </c>
+      <c r="L445" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="M445" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N445" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O445" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; 3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>visual localization, place recognition, pose estimation, point cloud registration, depth estimation, deep learning</t>
+        </is>
+      </c>
+      <c r="R445" t="n">
+        <v>11</v>
+      </c>
+      <c r="S445" t="n">
+        <v>99</v>
+      </c>
+      <c r="T445" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>CoPR: Toward Accurate Visual Localization With Continuous Place-Descriptor Regression</t>
+        </is>
+      </c>
+      <c r="V445" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W445" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X445" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Liangliang%20Nan%22%20email</t>
+        </is>
+      </c>
+      <c r="Z445" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5027616562</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G446" t="n">
+        <v>5</v>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>Xucong Zhang</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J446" t="n">
+        <v>28</v>
+      </c>
+      <c r="K446" t="n">
+        <v>5167</v>
+      </c>
+      <c r="L446" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="M446" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N446" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O446" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>event camera, depth estimation, object detection</t>
+        </is>
+      </c>
+      <c r="R446" t="n">
+        <v>1</v>
+      </c>
+      <c r="S446" t="n">
+        <v>50</v>
+      </c>
+      <c r="T446" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>Cooking Beyond Frames: A Stereo Event Camera Dataset in the Kitchen</t>
+        </is>
+      </c>
+      <c r="V446" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W446" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X446" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Xucong%20Zhang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z446" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5010012679</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G447" t="n">
+        <v>6</v>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>Holger Caesar</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J447" t="n">
+        <v>16</v>
+      </c>
+      <c r="K447" t="n">
+        <v>13966</v>
+      </c>
+      <c r="L447" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="M447" t="n">
+        <v>10</v>
+      </c>
+      <c r="N447" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O447" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; LiDAR &amp; Multimodal Sensor Fusion; Deep Learning for Navigation &amp; Perception</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, gaussian splatting, sensor fusion, autonomous driving perception, autonomous vehicles, lidar camera fusion</t>
+        </is>
+      </c>
+      <c r="R447" t="n">
+        <v>7</v>
+      </c>
+      <c r="S447" t="n">
+        <v>72</v>
+      </c>
+      <c r="T447" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>GaussianCaR: Gaussian Splatting for Efficient Camera-Radar Fusion</t>
+        </is>
+      </c>
+      <c r="V447" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W447" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X447" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Holger%20Caesar%22%20email</t>
+        </is>
+      </c>
+      <c r="Z447" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5001917215</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G448" t="n">
+        <v>7</v>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>Julian F. P. Kooij</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J448" t="n">
+        <v>26</v>
+      </c>
+      <c r="K448" t="n">
+        <v>2335</v>
+      </c>
+      <c r="L448" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="M448" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N448" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O448" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>visual localization, place recognition, pose estimation, lidar camera fusion, 3d object detection, object detection</t>
+        </is>
+      </c>
+      <c r="R448" t="n">
+        <v>5</v>
+      </c>
+      <c r="S448" t="n">
+        <v>51</v>
+      </c>
+      <c r="T448" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>CoPR: Toward Accurate Visual Localization With Continuous Place-Descriptor Regression</t>
+        </is>
+      </c>
+      <c r="V448" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W448" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X448" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Julian%20F.%20P.%20Kooij%22%20email</t>
+        </is>
+      </c>
+      <c r="Z448" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5074902093</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G449" t="n">
+        <v>8</v>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>Emmanuel Vander Poorten</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J449" t="n">
+        <v>31</v>
+      </c>
+      <c r="K449" t="n">
+        <v>3585</v>
+      </c>
+      <c r="L449" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="M449" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N449" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O449" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>robust localization, sensor fusion, pose estimation, stereo vision</t>
+        </is>
+      </c>
+      <c r="R449" t="n">
+        <v>1</v>
+      </c>
+      <c r="S449" t="n">
+        <v>167</v>
+      </c>
+      <c r="T449" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="U449" t="inlineStr">
+        <is>
+          <t>Fusion Framework for Coaxial Catheter Tracking</t>
+        </is>
+      </c>
+      <c r="V449" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W449" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X449" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Emmanuel%20Vander%20Poorten%22%20email</t>
+        </is>
+      </c>
+      <c r="Z449" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5068041103</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G450" t="n">
+        <v>9</v>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>Raj Thilak Rajan</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J450" t="n">
+        <v>17</v>
+      </c>
+      <c r="K450" t="n">
+        <v>1092</v>
+      </c>
+      <c r="L450" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="M450" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N450" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O450" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, autonomous navigation, autonomous vehicles</t>
+        </is>
+      </c>
+      <c r="R450" t="n">
+        <v>1</v>
+      </c>
+      <c r="S450" t="n">
+        <v>69</v>
+      </c>
+      <c r="T450" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="U450" t="inlineStr">
+        <is>
+          <t>GPS-VIO Fusion with Online Rotational Calibration</t>
+        </is>
+      </c>
+      <c r="V450" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W450" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X450" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Raj%20Thilak%20Rajan%22%20email</t>
+        </is>
+      </c>
+      <c r="Z450" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5043226807</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G451" t="n">
+        <v>10</v>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>Marija Popović</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J451" t="n">
+        <v>22</v>
+      </c>
+      <c r="K451" t="n">
+        <v>2262</v>
+      </c>
+      <c r="L451" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M451" t="n">
+        <v>10</v>
+      </c>
+      <c r="N451" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O451" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, state estimation, visual localization, pose estimation, robot localization, gaussian splatting</t>
+        </is>
+      </c>
+      <c r="R451" t="n">
+        <v>5</v>
+      </c>
+      <c r="S451" t="n">
+        <v>57</v>
+      </c>
+      <c r="T451" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>Perception-Aware Autonomous Exploration in Feature-Limited Environments</t>
+        </is>
+      </c>
+      <c r="V451" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W451" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X451" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Marija%20Popovi%C4%87%22%20email</t>
+        </is>
+      </c>
+      <c r="Z451" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5072802898</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G452" t="n">
+        <v>11</v>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>Jan C. van Gemert</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J452" t="n">
+        <v>37</v>
+      </c>
+      <c r="K452" t="n">
+        <v>6278</v>
+      </c>
+      <c r="L452" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="M452" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N452" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O452" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>event camera, depth estimation, object detection, deep learning, edge ai</t>
+        </is>
+      </c>
+      <c r="R452" t="n">
+        <v>3</v>
+      </c>
+      <c r="S452" t="n">
+        <v>146</v>
+      </c>
+      <c r="T452" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>Cooking Beyond Frames: A Stereo Event Camera Dataset in the Kitchen</t>
+        </is>
+      </c>
+      <c r="V452" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W452" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X452" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Jan%20C.%20van%20Gemert%22%20email</t>
+        </is>
+      </c>
+      <c r="Z452" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5077258803</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G453" t="n">
+        <v>12</v>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>Coen C. de Visser</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J453" t="n">
+        <v>30</v>
+      </c>
+      <c r="K453" t="n">
+        <v>2908</v>
+      </c>
+      <c r="L453" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="M453" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N453" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O453" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, state estimation, event camera</t>
+        </is>
+      </c>
+      <c r="R453" t="n">
+        <v>2</v>
+      </c>
+      <c r="S453" t="n">
+        <v>64</v>
+      </c>
+      <c r="T453" t="inlineStr">
+        <is>
+          <t>2024-01-04</t>
+        </is>
+      </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>Autonomous Quadrotor Flight Despite Rotor Failure With Onboard Vision Sensors: Frames vs. Events</t>
+        </is>
+      </c>
+      <c r="V453" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W453" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X453" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Coen%20C.%20de%20Visser%22%20email</t>
+        </is>
+      </c>
+      <c r="Z453" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5008760854</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G454" t="n">
+        <v>13</v>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>Michael Weinmann</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J454" t="n">
+        <v>24</v>
+      </c>
+      <c r="K454" t="n">
+        <v>1578</v>
+      </c>
+      <c r="L454" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="M454" t="n">
+        <v>10</v>
+      </c>
+      <c r="N454" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O454" t="n">
+        <v>7</v>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; LiDAR &amp; Multimodal Sensor Fusion; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>pose estimation, edge ai, object detection, jetson, depth estimation, tensorrt</t>
+        </is>
+      </c>
+      <c r="R454" t="n">
+        <v>6</v>
+      </c>
+      <c r="S454" t="n">
+        <v>67</v>
+      </c>
+      <c r="T454" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U454" t="inlineStr">
+        <is>
+          <t>6D Strawberry Pose Estimation: Real-time and Edge AI Solutions Using Purely Synthetic Training Data</t>
+        </is>
+      </c>
+      <c r="V454" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W454" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X454" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Michael%20Weinmann%22%20email</t>
+        </is>
+      </c>
+      <c r="Z454" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5017002784</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G455" t="n">
+        <v>14</v>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>Guohao Lan</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J455" t="n">
+        <v>22</v>
+      </c>
+      <c r="K455" t="n">
+        <v>2304</v>
+      </c>
+      <c r="L455" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="M455" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N455" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O455" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>visual slam, pose estimation</t>
+        </is>
+      </c>
+      <c r="R455" t="n">
+        <v>2</v>
+      </c>
+      <c r="S455" t="n">
+        <v>32</v>
+      </c>
+      <c r="T455" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="U455" t="inlineStr">
+        <is>
+          <t>DNN-based SLAM Tracking Error Online Estimation</t>
+        </is>
+      </c>
+      <c r="V455" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W455" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X455" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Guohao%20Lan%22%20email</t>
+        </is>
+      </c>
+      <c r="Z455" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5009415566</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G456" t="n">
+        <v>15</v>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>Manon Kok</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J456" t="n">
+        <v>21</v>
+      </c>
+      <c r="K456" t="n">
+        <v>2437</v>
+      </c>
+      <c r="L456" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="M456" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N456" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O456" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>visual slam, state estimation, loop closure, trajectory estimation, extended kalman filter, kalman filter</t>
+        </is>
+      </c>
+      <c r="R456" t="n">
+        <v>5</v>
+      </c>
+      <c r="S456" t="n">
+        <v>47</v>
+      </c>
+      <c r="T456" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="U456" t="inlineStr">
+        <is>
+          <t>Rao-Blackwellized particle smoothing for simultaneous localization and mapping</t>
+        </is>
+      </c>
+      <c r="V456" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W456" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X456" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Manon%20Kok%22%20email</t>
+        </is>
+      </c>
+      <c r="Z456" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5017416513</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G457" t="n">
+        <v>16</v>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>Peter J. G. Teunissen</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J457" t="n">
+        <v>73</v>
+      </c>
+      <c r="K457" t="n">
+        <v>21150</v>
+      </c>
+      <c r="L457" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="M457" t="n">
+        <v>10</v>
+      </c>
+      <c r="N457" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O457" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>gnss positioning, kalman filter</t>
+        </is>
+      </c>
+      <c r="R457" t="n">
+        <v>20</v>
+      </c>
+      <c r="S457" t="n">
+        <v>74</v>
+      </c>
+      <c r="T457" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="U457" t="inlineStr">
+        <is>
+          <t>Correction: DIA-Estimator and Multidimensional Model Misspecifications: GNSS-based Positioning Safety Analysis for UAVs</t>
+        </is>
+      </c>
+      <c r="V457" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W457" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X457" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Peter%20J.%20G.%20Teunissen%22%20email</t>
+        </is>
+      </c>
+      <c r="Z457" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5059663096</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G458" t="n">
+        <v>17</v>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>Wout Broere</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J458" t="n">
+        <v>28</v>
+      </c>
+      <c r="K458" t="n">
+        <v>2771</v>
+      </c>
+      <c r="L458" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="M458" t="n">
+        <v>10</v>
+      </c>
+      <c r="N458" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O458" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>autonomous navigation, 3d reconstruction, edge ai</t>
+        </is>
+      </c>
+      <c r="R458" t="n">
+        <v>1</v>
+      </c>
+      <c r="S458" t="n">
+        <v>51</v>
+      </c>
+      <c r="T458" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>Robotics and unmanned aerial vehicles for smart structural health monitoring: A systematic review</t>
+        </is>
+      </c>
+      <c r="V458" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W458" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X458" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Wout%20Broere%22%20email</t>
+        </is>
+      </c>
+      <c r="Z458" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5077837633</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G459" t="n">
+        <v>18</v>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>Rudy L. J. Helmons</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J459" t="n">
+        <v>14</v>
+      </c>
+      <c r="K459" t="n">
+        <v>542</v>
+      </c>
+      <c r="L459" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="M459" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N459" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O459" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>extended kalman filter, kalman filter</t>
+        </is>
+      </c>
+      <c r="R459" t="n">
+        <v>2</v>
+      </c>
+      <c r="S459" t="n">
+        <v>32</v>
+      </c>
+      <c r="T459" t="inlineStr">
+        <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="U459" t="inlineStr">
+        <is>
+          <t>An Extended Kalman Filter for Magnetic Field SLAM Using Gaussian Process Regression</t>
+        </is>
+      </c>
+      <c r="V459" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W459" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X459" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Rudy%20L.%20J.%20Helmons%22%20email</t>
+        </is>
+      </c>
+      <c r="Z459" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5038544106</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G460" t="n">
+        <v>19</v>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>Javier Alonso–Mora</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J460" t="n">
+        <v>44</v>
+      </c>
+      <c r="K460" t="n">
+        <v>9272</v>
+      </c>
+      <c r="L460" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="M460" t="n">
+        <v>10</v>
+      </c>
+      <c r="N460" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O460" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; State Estimation &amp; Factor Graphs; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>loop closure, trajectory estimation, mobile robot navigation</t>
+        </is>
+      </c>
+      <c r="R460" t="n">
+        <v>7</v>
+      </c>
+      <c r="S460" t="n">
+        <v>144</v>
+      </c>
+      <c r="T460" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="U460" t="inlineStr">
+        <is>
+          <t>Wi-Closure: Reliable and Efficient Search of Inter-robot Loop Closures Using Wireless Sensing</t>
+        </is>
+      </c>
+      <c r="V460" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W460" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X460" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Javier%20Alonso%E2%80%93Mora%22%20email</t>
+        </is>
+      </c>
+      <c r="Z460" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5013297671</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G461" t="n">
+        <v>20</v>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>Christian C. J. M. Tiberius</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J461" t="n">
+        <v>30</v>
+      </c>
+      <c r="K461" t="n">
+        <v>3527</v>
+      </c>
+      <c r="L461" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="M461" t="n">
+        <v>10</v>
+      </c>
+      <c r="N461" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O461" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>gnss positioning</t>
+        </is>
+      </c>
+      <c r="R461" t="n">
+        <v>9</v>
+      </c>
+      <c r="S461" t="n">
+        <v>35</v>
+      </c>
+      <c r="T461" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="U461" t="inlineStr">
+        <is>
+          <t>Correction: DIA-Estimator and Multidimensional Model Misspecifications: GNSS-based Positioning Safety Analysis for UAVs</t>
+        </is>
+      </c>
+      <c r="V461" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W461" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X461" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Christian%20C.%20J.%20M.%20Tiberius%22%20email</t>
+        </is>
+      </c>
+      <c r="Z461" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5039086149</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G462" t="n">
+        <v>21</v>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>Sandra Verhagen</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J462" t="n">
+        <v>30</v>
+      </c>
+      <c r="K462" t="n">
+        <v>2995</v>
+      </c>
+      <c r="L462" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="M462" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N462" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O462" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>gnss positioning</t>
+        </is>
+      </c>
+      <c r="R462" t="n">
+        <v>4</v>
+      </c>
+      <c r="S462" t="n">
+        <v>28</v>
+      </c>
+      <c r="T462" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U462" t="inlineStr">
+        <is>
+          <t>The Delft School of Mathematical Geodesy—A Brief Review of the Contributions</t>
+        </is>
+      </c>
+      <c r="V462" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W462" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X462" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Sandra%20Verhagen%22%20email</t>
+        </is>
+      </c>
+      <c r="Z462" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5042373941</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G463" t="n">
+        <v>22</v>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>Peter J. M. van Oosterom</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J463" t="n">
+        <v>43</v>
+      </c>
+      <c r="K463" t="n">
+        <v>8364</v>
+      </c>
+      <c r="L463" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="M463" t="n">
+        <v>10</v>
+      </c>
+      <c r="N463" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O463" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>visual slam, gnss positioning, gaussian splatting</t>
+        </is>
+      </c>
+      <c r="R463" t="n">
+        <v>3</v>
+      </c>
+      <c r="S463" t="n">
+        <v>97</v>
+      </c>
+      <c r="T463" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="U463" t="inlineStr">
+        <is>
+          <t>Identification and Visualization of Unscanned Areas Within a Building Based on the Building’s Outer Hull</t>
+        </is>
+      </c>
+      <c r="V463" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W463" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X463" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Peter%20J.%20M.%20van%20Oosterom%22%20email</t>
+        </is>
+      </c>
+      <c r="Z463" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5109972324</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G464" t="n">
+        <v>23</v>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>Jochen  Lorenz Cremer</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J464" t="n">
+        <v>17</v>
+      </c>
+      <c r="K464" t="n">
+        <v>1123</v>
+      </c>
+      <c r="L464" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="M464" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N464" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O464" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>state estimation, deep learning</t>
+        </is>
+      </c>
+      <c r="R464" t="n">
+        <v>1</v>
+      </c>
+      <c r="S464" t="n">
+        <v>99</v>
+      </c>
+      <c r="T464" t="inlineStr">
+        <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="U464" t="inlineStr">
+        <is>
+          <t>Deep Statistical Solver for Distribution System State Estimation</t>
+        </is>
+      </c>
+      <c r="V464" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W464" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X464" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Jochen%20%20Lorenz%20Cremer%22%20email</t>
+        </is>
+      </c>
+      <c r="Z464" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5112879194</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G465" t="n">
+        <v>24</v>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>Dariu M. Gavrila</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J465" t="n">
+        <v>49</v>
+      </c>
+      <c r="K465" t="n">
+        <v>13928</v>
+      </c>
+      <c r="L465" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="M465" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N465" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O465" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>lidar camera fusion, 3d object detection, object detection</t>
+        </is>
+      </c>
+      <c r="R465" t="n">
+        <v>2</v>
+      </c>
+      <c r="S465" t="n">
+        <v>38</v>
+      </c>
+      <c r="T465" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="U465" t="inlineStr">
+        <is>
+          <t>Multimodal Object Query Initialization for 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="V465" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W465" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X465" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Dariu%20M.%20Gavrila%22%20email</t>
+        </is>
+      </c>
+      <c r="Z465" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5085298812</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G466" t="n">
+        <v>25</v>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>Justin Dauwels</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J466" t="n">
+        <v>47</v>
+      </c>
+      <c r="K466" t="n">
+        <v>10763</v>
+      </c>
+      <c r="L466" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="M466" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N466" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O466" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; 3D Computer Vision &amp; Geometric Perception; Deep Learning for Navigation &amp; Perception</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>lidar camera fusion, autonomous vehicles, pose estimation, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R466" t="n">
+        <v>3</v>
+      </c>
+      <c r="S466" t="n">
+        <v>119</v>
+      </c>
+      <c r="T466" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="U466" t="inlineStr">
+        <is>
+          <t>PEM: Perception Error Model for Virtual Testing of Autonomous Vehicles</t>
+        </is>
+      </c>
+      <c r="V466" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W466" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X466" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Justin%20Dauwels%22%20email</t>
+        </is>
+      </c>
+      <c r="Z466" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5082613025</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G467" t="n">
+        <v>26</v>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>Alireza Amiri-Simkooei</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J467" t="n">
+        <v>35</v>
+      </c>
+      <c r="K467" t="n">
+        <v>3701</v>
+      </c>
+      <c r="L467" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="M467" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N467" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O467" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>gnss positioning</t>
+        </is>
+      </c>
+      <c r="R467" t="n">
+        <v>4</v>
+      </c>
+      <c r="S467" t="n">
+        <v>67</v>
+      </c>
+      <c r="T467" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="U467" t="inlineStr">
+        <is>
+          <t>Multichannel Monte Carlo Singular Spectrum Analysis With Colored Noise Assessment: Application to Greenland GNSS Vertical Displacement</t>
+        </is>
+      </c>
+      <c r="V467" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W467" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X467" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Alireza%20Amiri-Simkooei%22%20email</t>
+        </is>
+      </c>
+      <c r="Z467" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5029427002</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G468" t="n">
+        <v>27</v>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>Aaron Yi Ding</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J468" t="n">
+        <v>26</v>
+      </c>
+      <c r="K468" t="n">
+        <v>2924</v>
+      </c>
+      <c r="L468" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="M468" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N468" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O468" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception; Deep Learning for Navigation &amp; Perception</t>
+        </is>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>edge ai, autonomous vehicles</t>
+        </is>
+      </c>
+      <c r="R468" t="n">
+        <v>2</v>
+      </c>
+      <c r="S468" t="n">
+        <v>82</v>
+      </c>
+      <c r="T468" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="U468" t="inlineStr">
+        <is>
+          <t>A Survey on Approximate Edge AI for Energy Efficient Autonomous Driving Services</t>
+        </is>
+      </c>
+      <c r="V468" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W468" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X468" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Aaron%20Yi%20Ding%22%20email</t>
+        </is>
+      </c>
+      <c r="Z468" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5063593427</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>QS #47 (Top 15 Eng) | Tier S+ (Global Elite | h=810)</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G469" t="n">
+        <v>28</v>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>Eberhard K. A. Gill</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J469" t="n">
+        <v>37</v>
+      </c>
+      <c r="K469" t="n">
+        <v>7385</v>
+      </c>
+      <c r="L469" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="M469" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N469" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O469" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>gnss positioning</t>
+        </is>
+      </c>
+      <c r="R469" t="n">
+        <v>2</v>
+      </c>
+      <c r="S469" t="n">
+        <v>53</v>
+      </c>
+      <c r="T469" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="U469" t="inlineStr">
+        <is>
+          <t>Snapshot GNSS receivers for low-effort, high-gain space situational awareness</t>
+        </is>
+      </c>
+      <c r="V469" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W469" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X469" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atudelft.nl%20%22Eberhard%20K.%20A.%20Gill%22%20email</t>
+        </is>
+      </c>
+      <c r="Z469" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5069203558</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G470" t="n">
+        <v>1</v>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>Gijs Dubbelman</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J470" t="n">
+        <v>19</v>
+      </c>
+      <c r="K470" t="n">
+        <v>1248</v>
+      </c>
+      <c r="L470" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M470" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N470" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O470" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM; Deep Learning for Navigation &amp; Perception</t>
+        </is>
+      </c>
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t>robot perception, stereo vision, embedded systems, autonomous driving perception, semantic segmentation</t>
+        </is>
+      </c>
+      <c r="R470" t="n">
+        <v>3</v>
+      </c>
+      <c r="S470" t="n">
+        <v>60</v>
+      </c>
+      <c r="T470" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="U470" t="inlineStr">
+        <is>
+          <t>Correction: A Stixel-Based Stereo Perception for Multi-Robot Systems</t>
+        </is>
+      </c>
+      <c r="V470" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W470" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X470" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22Gijs%20Dubbelman%22%20email</t>
+        </is>
+      </c>
+      <c r="Z470" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5024010116</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G471" t="n">
+        <v>2</v>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>H. J. Wörtche</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J471" t="n">
+        <v>30</v>
+      </c>
+      <c r="K471" t="n">
+        <v>2950</v>
+      </c>
+      <c r="L471" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="M471" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N471" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O471" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>robot localization, pose estimation, learning-based localization, deep learning, embedded systems</t>
+        </is>
+      </c>
+      <c r="R471" t="n">
+        <v>3</v>
+      </c>
+      <c r="S471" t="n">
+        <v>25</v>
+      </c>
+      <c r="T471" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="U471" t="inlineStr">
+        <is>
+          <t>A Machine Learning Approach to Robot Localization Using Fiducial Markers in RobotAtFactory 4.0 Competition</t>
+        </is>
+      </c>
+      <c r="V471" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W471" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X471" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22H.%20J.%20W%C3%B6rtche%22%20email</t>
+        </is>
+      </c>
+      <c r="Z471" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5072096663</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G472" t="n">
+        <v>3</v>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>Ömür Arslan</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J472" t="n">
+        <v>15</v>
+      </c>
+      <c r="K472" t="n">
+        <v>852</v>
+      </c>
+      <c r="L472" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="M472" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N472" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O472" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>autonomous navigation, mobile robot navigation, ros</t>
+        </is>
+      </c>
+      <c r="R472" t="n">
+        <v>1</v>
+      </c>
+      <c r="S472" t="n">
+        <v>17</v>
+      </c>
+      <c r="T472" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="U472" t="inlineStr">
+        <is>
+          <t>Key-Scan-Based Mobile Robot Navigation: Integrated Mapping, Planning, and Control Using Graphs of Scan Regions</t>
+        </is>
+      </c>
+      <c r="V472" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W472" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X472" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22%C3%96m%C3%BCr%20Arslan%22%20email</t>
+        </is>
+      </c>
+      <c r="Z472" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5042096409</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G473" t="n">
+        <v>4</v>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>Gregor Kemper</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J473" t="n">
+        <v>21</v>
+      </c>
+      <c r="K473" t="n">
+        <v>1880</v>
+      </c>
+      <c r="L473" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="M473" t="n">
+        <v>10</v>
+      </c>
+      <c r="N473" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O473" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t>gnss positioning, robot localization</t>
+        </is>
+      </c>
+      <c r="R473" t="n">
+        <v>1</v>
+      </c>
+      <c r="S473" t="n">
+        <v>22</v>
+      </c>
+      <c r="T473" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="U473" t="inlineStr">
+        <is>
+          <t>Localization from Pseudoranges: Quadrics and Duality</t>
+        </is>
+      </c>
+      <c r="V473" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W473" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X473" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22Gregor%20Kemper%22%20email</t>
+        </is>
+      </c>
+      <c r="Z473" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5014902420</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G474" t="n">
+        <v>5</v>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>Herman Bruyninckx</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J474" t="n">
+        <v>43</v>
+      </c>
+      <c r="K474" t="n">
+        <v>8088</v>
+      </c>
+      <c r="L474" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="M474" t="n">
+        <v>10</v>
+      </c>
+      <c r="N474" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O474" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; LiDAR &amp; Multimodal Sensor Fusion; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>mobile robot navigation, robot localization, robot perception, stereo vision</t>
+        </is>
+      </c>
+      <c r="R474" t="n">
+        <v>7</v>
+      </c>
+      <c r="S474" t="n">
+        <v>80</v>
+      </c>
+      <c r="T474" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U474" t="inlineStr">
+        <is>
+          <t>Clutter-Resilient Autonomous Mobile Robot Navigation with Computationally Efficient Free-Space Features</t>
+        </is>
+      </c>
+      <c r="V474" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W474" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X474" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22Herman%20Bruyninckx%22%20email</t>
+        </is>
+      </c>
+      <c r="Z474" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5009116988</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G475" t="n">
+        <v>6</v>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>Elena Torta</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J475" t="n">
+        <v>14</v>
+      </c>
+      <c r="K475" t="n">
+        <v>959</v>
+      </c>
+      <c r="L475" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="M475" t="n">
+        <v>10</v>
+      </c>
+      <c r="N475" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O475" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>robot localization, mobile robot navigation, ros</t>
+        </is>
+      </c>
+      <c r="R475" t="n">
+        <v>9</v>
+      </c>
+      <c r="S475" t="n">
+        <v>38</v>
+      </c>
+      <c r="T475" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="U475" t="inlineStr">
+        <is>
+          <t>Semantic-Enhanced Path Planning for Safety-Centric Indoor Robots Navigation</t>
+        </is>
+      </c>
+      <c r="V475" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W475" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X475" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22Elena%20Torta%22%20email</t>
+        </is>
+      </c>
+      <c r="Z475" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5069500372</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G476" t="n">
+        <v>7</v>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>René van de Molengraft</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J476" t="n">
+        <v>33</v>
+      </c>
+      <c r="K476" t="n">
+        <v>5327</v>
+      </c>
+      <c r="L476" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="M476" t="n">
+        <v>10</v>
+      </c>
+      <c r="N476" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O476" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; LiDAR &amp; Multimodal Sensor Fusion; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, sensor fusion, robot localization, mobile robot navigation, robot perception, ros</t>
+        </is>
+      </c>
+      <c r="R476" t="n">
+        <v>6</v>
+      </c>
+      <c r="S476" t="n">
+        <v>61</v>
+      </c>
+      <c r="T476" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="U476" t="inlineStr">
+        <is>
+          <t>Situation-Aware Drivable Space Estimation for Automated Driving</t>
+        </is>
+      </c>
+      <c r="V476" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W476" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X476" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22Ren%C3%A9%20van%20de%20Molengraft%22%20email</t>
+        </is>
+      </c>
+      <c r="Z476" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5033596147</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G477" t="n">
+        <v>8</v>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>Aida Todri‐Sanial</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J477" t="n">
+        <v>25</v>
+      </c>
+      <c r="K477" t="n">
+        <v>2658</v>
+      </c>
+      <c r="L477" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="M477" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N477" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O477" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>robot localization, mobile robot navigation, object detection, edge ai</t>
+        </is>
+      </c>
+      <c r="R477" t="n">
+        <v>2</v>
+      </c>
+      <c r="S477" t="n">
+        <v>167</v>
+      </c>
+      <c r="T477" t="inlineStr">
+        <is>
+          <t>2024-02-15</t>
+        </is>
+      </c>
+      <c r="U477" t="inlineStr">
+        <is>
+          <t>SIFT-ONN: SIFT Feature Detection Algorithm Employing ONNs for Edge Detection</t>
+        </is>
+      </c>
+      <c r="V477" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W477" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X477" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22Aida%20Todri%E2%80%90Sanial%22%20email</t>
+        </is>
+      </c>
+      <c r="Z477" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5022136174</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G478" t="n">
+        <v>9</v>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>Dip Goswami</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J478" t="n">
+        <v>24</v>
+      </c>
+      <c r="K478" t="n">
+        <v>1758</v>
+      </c>
+      <c r="L478" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="M478" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N478" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O478" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>point cloud registration, event camera, deep learning</t>
+        </is>
+      </c>
+      <c r="R478" t="n">
+        <v>1</v>
+      </c>
+      <c r="S478" t="n">
+        <v>35</v>
+      </c>
+      <c r="T478" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="U478" t="inlineStr">
+        <is>
+          <t>R3PM-Net: Real-time, Robust, Real-world Point Matching Network</t>
+        </is>
+      </c>
+      <c r="V478" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W478" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X478" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22Dip%20Goswami%22%20email</t>
+        </is>
+      </c>
+      <c r="Z478" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5049989469</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G479" t="n">
+        <v>10</v>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>Ruud J. G. van Sloun</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J479" t="n">
+        <v>36</v>
+      </c>
+      <c r="K479" t="n">
+        <v>6016</v>
+      </c>
+      <c r="L479" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="M479" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N479" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O479" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>state estimation, kalman filter, deep learning</t>
+        </is>
+      </c>
+      <c r="R479" t="n">
+        <v>3</v>
+      </c>
+      <c r="S479" t="n">
+        <v>168</v>
+      </c>
+      <c r="T479" t="inlineStr">
+        <is>
+          <t>2023-12-22</t>
+        </is>
+      </c>
+      <c r="U479" t="inlineStr">
+        <is>
+          <t>KalmanNet: Neural Network Aided Kalman Filtering for Partially Known Dynamics</t>
+        </is>
+      </c>
+      <c r="V479" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W479" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X479" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22Ruud%20J.%20G.%20van%20Sloun%22%20email</t>
+        </is>
+      </c>
+      <c r="Z479" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5042985821</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G480" t="n">
+        <v>11</v>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>Sander Stuijk</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J480" t="n">
+        <v>40</v>
+      </c>
+      <c r="K480" t="n">
+        <v>7154</v>
+      </c>
+      <c r="L480" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="M480" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N480" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O480" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>depth estimation, hardware acceleration, embedded systems</t>
+        </is>
+      </c>
+      <c r="R480" t="n">
+        <v>1</v>
+      </c>
+      <c r="S480" t="n">
+        <v>59</v>
+      </c>
+      <c r="T480" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="U480" t="inlineStr">
+        <is>
+          <t>A Flexible Multi-Core Hardware Architecture for Stereo-Based Depth Estimation CNNs</t>
+        </is>
+      </c>
+      <c r="V480" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W480" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X480" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22Sander%20Stuijk%22%20email</t>
+        </is>
+      </c>
+      <c r="Z480" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5032436846</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G481" t="n">
+        <v>12</v>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>Marc C. W. Geilen</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J481" t="n">
+        <v>36</v>
+      </c>
+      <c r="K481" t="n">
+        <v>4579</v>
+      </c>
+      <c r="L481" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="M481" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N481" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O481" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>depth estimation, hardware acceleration, embedded systems</t>
+        </is>
+      </c>
+      <c r="R481" t="n">
+        <v>1</v>
+      </c>
+      <c r="S481" t="n">
+        <v>31</v>
+      </c>
+      <c r="T481" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="U481" t="inlineStr">
+        <is>
+          <t>A Flexible Multi-Core Hardware Architecture for Stereo-Based Depth Estimation CNNs</t>
+        </is>
+      </c>
+      <c r="V481" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W481" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X481" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22Marc%20C.%20W.%20Geilen%22%20email</t>
+        </is>
+      </c>
+      <c r="Z481" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5063550119</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G482" t="n">
+        <v>13</v>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>Decebal Constantin Mocanu</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J482" t="n">
+        <v>24</v>
+      </c>
+      <c r="K482" t="n">
+        <v>2269</v>
+      </c>
+      <c r="L482" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="M482" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N482" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O482" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R482" t="n">
+        <v>1</v>
+      </c>
+      <c r="S482" t="n">
+        <v>74</v>
+      </c>
+      <c r="T482" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="U482" t="inlineStr">
+        <is>
+          <t>Situation-Aware Drivable Space Estimation for Automated Driving</t>
+        </is>
+      </c>
+      <c r="V482" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W482" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X482" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22Decebal%20Constantin%20Mocanu%22%20email</t>
+        </is>
+      </c>
+      <c r="Z482" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5011045254</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G483" t="n">
+        <v>14</v>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>Pieter Pauwels</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J483" t="n">
+        <v>40</v>
+      </c>
+      <c r="K483" t="n">
+        <v>6236</v>
+      </c>
+      <c r="L483" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="M483" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N483" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O483" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>mobile robot navigation, robot localization</t>
+        </is>
+      </c>
+      <c r="R483" t="n">
+        <v>4</v>
+      </c>
+      <c r="S483" t="n">
+        <v>107</v>
+      </c>
+      <c r="T483" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="U483" t="inlineStr">
+        <is>
+          <t>Semantic Path Planning for Heterogeneous Robots from Building Digital Twin Data</t>
+        </is>
+      </c>
+      <c r="V483" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W483" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X483" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22Pieter%20Pauwels%22%20email</t>
+        </is>
+      </c>
+      <c r="Z483" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5086041678</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G484" t="n">
+        <v>15</v>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>Mohsen Kaboli</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J484" t="n">
+        <v>21</v>
+      </c>
+      <c r="K484" t="n">
+        <v>2185</v>
+      </c>
+      <c r="L484" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="M484" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N484" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O484" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>pose estimation</t>
+        </is>
+      </c>
+      <c r="R484" t="n">
+        <v>1</v>
+      </c>
+      <c r="S484" t="n">
+        <v>26</v>
+      </c>
+      <c r="T484" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="U484" t="inlineStr">
+        <is>
+          <t>Shared visuo-tactile interactive perception for robust object pose estimation</t>
+        </is>
+      </c>
+      <c r="V484" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W484" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X484" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22Mohsen%20Kaboli%22%20email</t>
+        </is>
+      </c>
+      <c r="Z484" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5030520581</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G485" t="n">
+        <v>16</v>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>M. S. Chong</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J485" t="n">
+        <v>14</v>
+      </c>
+      <c r="K485" t="n">
+        <v>909</v>
+      </c>
+      <c r="L485" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="M485" t="n">
+        <v>10</v>
+      </c>
+      <c r="N485" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O485" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>state estimation</t>
+        </is>
+      </c>
+      <c r="R485" t="n">
+        <v>2</v>
+      </c>
+      <c r="S485" t="n">
+        <v>38</v>
+      </c>
+      <c r="T485" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="U485" t="inlineStr">
+        <is>
+          <t>Resilient Nonlinear State Estimation Using the Median Operation for a Network of Droop-Controlled Power Inverters</t>
+        </is>
+      </c>
+      <c r="V485" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W485" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X485" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22M.%20S.%20Chong%22%20email</t>
+        </is>
+      </c>
+      <c r="Z485" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5083231405</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G486" t="n">
+        <v>17</v>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>Yiping Li</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J486" t="n">
+        <v>25</v>
+      </c>
+      <c r="K486" t="n">
+        <v>2328</v>
+      </c>
+      <c r="L486" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M486" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N486" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O486" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q486" t="inlineStr">
+        <is>
+          <t>pose estimation, deep learning</t>
+        </is>
+      </c>
+      <c r="R486" t="n">
+        <v>1</v>
+      </c>
+      <c r="S486" t="n">
+        <v>80</v>
+      </c>
+      <c r="T486" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="U486" t="inlineStr">
+        <is>
+          <t>SurgRIPE challenge: Benchmark of surgical robot instrument pose estimation</t>
+        </is>
+      </c>
+      <c r="V486" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W486" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X486" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22Yiping%20Li%22%20email</t>
+        </is>
+      </c>
+      <c r="Z486" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5070772177</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G487" t="n">
+        <v>18</v>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>Elahe Arani</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J487" t="n">
+        <v>16</v>
+      </c>
+      <c r="K487" t="n">
+        <v>826</v>
+      </c>
+      <c r="L487" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M487" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N487" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O487" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q487" t="inlineStr">
+        <is>
+          <t>depth estimation</t>
+        </is>
+      </c>
+      <c r="R487" t="n">
+        <v>2</v>
+      </c>
+      <c r="S487" t="n">
+        <v>64</v>
+      </c>
+      <c r="T487" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="U487" t="inlineStr">
+        <is>
+          <t>Transformers in Unsupervised Structure-from-Motion</t>
+        </is>
+      </c>
+      <c r="V487" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W487" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X487" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22Elahe%20Arani%22%20email</t>
+        </is>
+      </c>
+      <c r="Z487" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5047435371</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G488" t="n">
+        <v>19</v>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>Bahram Zonooz</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J488" t="n">
+        <v>15</v>
+      </c>
+      <c r="K488" t="n">
+        <v>680</v>
+      </c>
+      <c r="L488" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M488" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N488" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O488" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q488" t="inlineStr">
+        <is>
+          <t>depth estimation</t>
+        </is>
+      </c>
+      <c r="R488" t="n">
+        <v>2</v>
+      </c>
+      <c r="S488" t="n">
+        <v>59</v>
+      </c>
+      <c r="T488" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="U488" t="inlineStr">
+        <is>
+          <t>Transformers in Unsupervised Structure-from-Motion</t>
+        </is>
+      </c>
+      <c r="V488" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W488" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X488" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22Bahram%20Zonooz%22%20email</t>
+        </is>
+      </c>
+      <c r="Z488" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5028650455</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G489" t="n">
+        <v>20</v>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>Peter H. N. de With</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J489" t="n">
+        <v>42</v>
+      </c>
+      <c r="K489" t="n">
+        <v>9191</v>
+      </c>
+      <c r="L489" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="M489" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N489" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O489" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q489" t="inlineStr">
+        <is>
+          <t>3d reconstruction, deep learning, computer vision</t>
+        </is>
+      </c>
+      <c r="R489" t="n">
+        <v>2</v>
+      </c>
+      <c r="S489" t="n">
+        <v>243</v>
+      </c>
+      <c r="T489" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="U489" t="inlineStr">
+        <is>
+          <t>Proceedings of the Workshop on 3D Geometry Generation for Scientific Computing</t>
+        </is>
+      </c>
+      <c r="V489" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W489" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X489" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22Peter%20H.%20N.%20de%20With%22%20email</t>
+        </is>
+      </c>
+      <c r="Z489" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5029008213</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>QS #136 (Strong Robotics) | Tier S+ (Global Elite | h=666)</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>@tue.nl</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G490" t="n">
+        <v>21</v>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>Fons van der Sommen</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J490" t="n">
+        <v>28</v>
+      </c>
+      <c r="K490" t="n">
+        <v>3577</v>
+      </c>
+      <c r="L490" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="M490" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N490" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O490" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>3d reconstruction, deep learning, computer vision</t>
+        </is>
+      </c>
+      <c r="R490" t="n">
+        <v>1</v>
+      </c>
+      <c r="S490" t="n">
+        <v>201</v>
+      </c>
+      <c r="T490" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="U490" t="inlineStr">
+        <is>
+          <t>Proceedings of the Workshop on 3D Geometry Generation for Scientific Computing</t>
+        </is>
+      </c>
+      <c r="V490" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W490" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X490" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Atue.nl%20%22Fons%20van%20der%20Sommen%22%20email</t>
+        </is>
+      </c>
+      <c r="Z490" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5075677746</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z414"/>
+  <autoFilter ref="A1:Z490"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AG$127</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Z$490</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Z$523</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -5978,23 +5978,147 @@
           <t>University of Twente</t>
         </is>
       </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>QS #233 (Strong Robotics) | Tier S+ (Global Elite | h=628)</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5086428184</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>George Vosselman A</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Multi-sensor Fusion SLAM from the Nadir View for UAV Localization and Mapping (2025)</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>@utwente.nl</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>I94624287</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=60)</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, sensor fusion, factor graph optimization, state estimation, visual inertial odometry, visual odometry</t>
+        </is>
+      </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>9.57</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="Z44" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>8.18</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD44" s="4" t="inlineStr"/>
-      <c r="AE44" s="4" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>George Vosselman A; Francesco Nex; Ville Lehtola; Bashar Saleem Abbas Alsadik; Françoise J. Siepel; Antonio Franchi; Nicola Strisciuglio; Ivo A. M. J. Broeders; Jelmer M. Wolterink; Massimo Sartori; Maurice van Keulen; Hao Cheng; Norman Kerle; Sander Oude Elberink; Stefano Stramigioli; Mannes Poel; Christoph Brüne; Paul Havinga; Marco J.G. Bekooij</t>
+        </is>
+      </c>
+      <c r="AD44" s="4" t="inlineStr">
+        <is>
+          <t>1. George Vosselman A (Full / Senior Prof (Large Lab), h=60) | Fit=10.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.5/10 | Keywords=multi-sensor fusion, sensor fusion, factor graph optimization, state estimation, visual inertial odometry, visual odometry | Paper=Multi-sensor Fusion SLAM from the Nadir View for UAV Localization and Mapping (2025)
+2. Francesco Nex (Full / Senior Prof (Large Lab), h=38) | Fit=10.0/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.4/10 | Keywords=multi-sensor fusion, sensor fusion, factor graph optimization, state estimation, visual inertial odometry, visual odometry | Paper=Multi-sensor Fusion SLAM from the Nadir View for UAV Localization and Mapping (2025)
+3. Ville Lehtola (Associate / Established PI (High Fit), h=19) | Fit=9.4/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.1/10 | Keywords=lidar inertial odometry, extended kalman filter, kalman filter, semantic segmentation, 3d reconstruction, multi-sensor fusion | Paper=Gaussian or Plane? Both: Semantic-Driven Voxel Representation for LiDAR–Inertial Odometry (2025)
+4. Bashar Saleem Abbas Alsadik (Associate / Established PI (High Fit), h=15) | Fit=9.4/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.1/10 | Keywords=visual slam, lidar slam, robot localization, autonomous navigation, deep learning, depth estimation | Paper=The Simultaneous Localization and Mapping (SLAM)-An Overview (2021)
+5. Françoise J. Siepel (Associate / Established PI (High Fit), h=16) | Fit=9.1/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.8/10 | Keywords=visual slam, pose estimation, depth estimation, robust localization, deep learning, object detection | Paper=Integration of Visual SLAM in Robot-Assisted Minimally Invasive Surgery: Advances, Challenges,  (2024)
+6. Antonio Franchi (Full / Senior Prof (Large Lab), h=55) | Fit=8.9/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=visual inertial odometry, pose estimation, object detection, visual localization, state estimation, kalman filter | Paper=Multi-Agent Visual-Inertial Localization for Integrated Aerial Systems With Loose Fusion of Odo (2024)
+7. Nicola Strisciuglio (Associate / Established PI (High Fit), h=24) | Fit=7.7/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.8/10 | Keywords=place recognition, visual localization, computer vision | Paper=Data-Efficient Large Scale Place Recognition with Graded Similarity Supervision (2023)
+8. Ivo A. M. J. Broeders (Full / Senior Prof (Large Lab), h=51) | Fit=6.8/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.2/10 | Keywords=pose estimation, depth estimation, 3d reconstruction, object detection | Paper=NeRF-OR: neural radiance fields for operating room scene reconstruction from sparse-view RGB-D  (2024)
+9. Jelmer M. Wolterink (Full / Senior Prof (Large Lab), h=34) | Fit=6.8/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.2/10 | Keywords=pose estimation, depth estimation, 3d reconstruction, object detection | Paper=NeRF-OR: neural radiance fields for operating room scene reconstruction from sparse-view RGB-D  (2024)
+10. Massimo Sartori (Full / Senior Prof (Large Lab), h=33) | Fit=6.3/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.1/10 | Keywords=pose estimation, point cloud registration | Paper=Navigation-guided a-mode ultrasound system for reliable non-invasive 3D bone pose estimation (2026)
+11. Maurice van Keulen (Full / Senior Prof (Large Lab), h=20) | Fit=6.3/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=6.1/10 | Keywords=gaussian splatting, 3d reconstruction | Paper=Evaluating 3D Reconstruction: A Side-by-Side Comparison of NeRF and Gaussian Splatting in Indoo (2026)
+12. Hao Cheng (Associate / Established PI (High Fit), h=28) | Fit=5.8/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.7/10 | Keywords=sensor fusion, pose estimation, gaussian splatting | Paper=DVLO4D: Deep Visual-Lidar Odometry with Sparse Spatial-Temporal Fusion (2025)
+13. Norman Kerle (Full / Senior Prof (Large Lab), h=55) | Fit=5.9/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=5.6/10 | Keywords=autonomous navigation, depth estimation, computer vision, loop closure | Paper=End-to-End Nano-Drone Obstacle Avoidance for Indoor Exploration (2024)
+14. Sander Oude Elberink (Full / Senior Prof (Large Lab), h=33) | Fit=5.8/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.6/10 | Keywords=sensor fusion, pose estimation, 3d reconstruction | Paper=DVLO4D: Deep Visual-Lidar Odometry with Sparse Spatial-Temporal Fusion (2025)
+15. Stefano Stramigioli (Full / Senior Prof (Large Lab), h=51) | Fit=5.1/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=4.9/10 | Keywords=autonomous navigation | Paper=Towards Autonomous Pipeline Inspection with Hierarchical Reinforcement Learning (2022)
+16. Mannes Poel (Full / Senior Prof (Large Lab), h=31) | Fit=5.1/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=4.9/10 | Keywords=autonomous navigation | Paper=Towards Autonomous Pipeline Inspection with Hierarchical Reinforcement Learning (2022)
+17. Christoph Brüne (Associate / Established PI (High Fit), h=24) | Fit=5.1/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=4.9/10 | Keywords=autonomous navigation | Paper=Towards Autonomous Pipeline Inspection with Hierarchical Reinforcement Learning (2022)
+18. Paul Havinga (Full / Senior Prof (Large Lab), h=53) | Fit=4.7/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.9/10 | Keywords=inertial navigation | Paper=iMoT: Inertial Motion Transformer for Inertial Navigation (2025)
+19. Marco J.G. Bekooij (Associate / Established PI (High Fit), h=22) | Fit=4.3/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=4.4/10 | Keywords=robust localization, object detection, semantic segmentation | Paper=Weakly Supervised Semantic Segmentation for Range-Doppler Maps (2022)</t>
+        </is>
+      </c>
+      <c r="AE44" s="4" t="inlineStr">
+        <is>
+          <t>George Vosselman A: No homepage/funding evidence available
+Francesco Nex: No homepage/funding evidence available
+Ville Lehtola: No homepage/funding evidence available
+Bashar Saleem Abbas Alsadik: No homepage/funding evidence available
+Françoise J. Siepel: No homepage/funding evidence available
+Antonio Franchi: No homepage/funding evidence available
+Nicola Strisciuglio: No homepage/funding evidence available
+Ivo A. M. J. Broeders: No homepage/funding evidence available
+Jelmer M. Wolterink: No homepage/funding evidence available
+Massimo Sartori: No homepage/funding evidence available
+Maurice van Keulen: No homepage/funding evidence available
+Hao Cheng: No homepage/funding evidence available
+Norman Kerle: No homepage/funding evidence available
+Sander Oude Elberink: No homepage/funding evidence available
+Stefano Stramigioli: No homepage/funding evidence available
+Mannes Poel: No homepage/funding evidence available
+Christoph Brüne: No homepage/funding evidence available
+Paul Havinga: No homepage/funding evidence available
+Marco J.G. Bekooij: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Autwente.nl%20%22George%20Vosselman%20A%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
@@ -6002,23 +6126,123 @@
           <t>University of Amsterdam</t>
         </is>
       </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>QS #55 | Tier S+ (Global Elite | h=1213)</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100631506</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sirui Wang</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>DFSVO: Detection-Free Stereo Visual Odometry for underwater localization and mapping (2026)</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>@uva.nl</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>I887064364</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit) (h=15)</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>visual odometry</t>
+        </is>
+      </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>7.47</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Z45" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" s="4" t="inlineStr"/>
-      <c r="AE45" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Sirui Wang; Shaodi You; Martin R. Oswald; Theo Gevers; Arnoud Visser; Somaya Ben Allouch; Sezer Karaoğlu</t>
+        </is>
+      </c>
+      <c r="AD45" s="4" t="inlineStr">
+        <is>
+          <t>1. Sirui Wang (Associate / Established PI (High Fit), h=15) | Fit=9.9/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.4/10 | Keywords=visual odometry | Paper=DFSVO: Detection-Free Stereo Visual Odometry for underwater localization and mapping (2026)
+2. Shaodi You (Associate / Established PI (High Fit), h=31) | Fit=8.6/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.6/10 | Keywords=visual slam, depth estimation, pose estimation, computer vision | Paper=Atlantis++: Enabling Underwater Depth Estimation with Stable Diffusion and Beyond (2026)
+3. Martin R. Oswald (Full / Senior Prof (Large Lab), h=31) | Fit=6.9/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.5/10 | Keywords=point cloud registration, gaussian splatting, place recognition, robot perception, object detection, visual slam | Paper=Splat-LOAM: Gaussian Splatting LiDAR Odometry and Mapping (2025)
+4. Theo Gevers (Full / Senior Prof (Large Lab), h=56) | Fit=6.0/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.8/10 | Keywords=loop closure, gaussian splatting, computer vision, pose estimation | Paper=MAGiC-SLAM: Multi-Agent Gaussian Globally Consistent SLAM (2025)
+5. Arnoud Visser (Full / Senior Prof (Large Lab), h=23) | Fit=5.9/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.7/10 | Keywords=pose estimation | Paper=Position and Altitude of the Nao Camera Head from Two Points on the Soccer Field Plus the Gravi (2025)
+6. Somaya Ben Allouch (Associate / Established PI (High Fit), h=28) | Fit=5.5/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.5/10 | Keywords=robot perception | Paper=Robot Social Skills: Influencing Children’s Performance and Robot Perception Through a Robot Ma (2026)
+7. Sezer Karaoğlu (Associate / Established PI (High Fit), h=18) | Fit=4.5/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=4.9/10 | Keywords=pose estimation, computer vision, gaussian splatting | Paper=3D human pose estimation and action recognition using fisheye cameras: A survey and benchmark (2025)</t>
+        </is>
+      </c>
+      <c r="AE45" s="4" t="inlineStr">
+        <is>
+          <t>Sirui Wang: No homepage/funding evidence available
+Shaodi You: No homepage/funding evidence available
+Martin R. Oswald: No homepage/funding evidence available
+Theo Gevers: No homepage/funding evidence available
+Arnoud Visser: No homepage/funding evidence available
+Somaya Ben Allouch: No homepage/funding evidence available
+Sezer Karaoğlu: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auva.nl%20%22Sirui%20Wang%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
@@ -6026,23 +6250,117 @@
           <t>Vrije Universiteit Amsterdam</t>
         </is>
       </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1011)</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5079556921</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Ivano Malavolta</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Tuning ROS 2 for Energy-Efficient Navigation: Empirical Insights from Costmap 2D Configurations (2026)</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>@vu.nl</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>I865915315</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=35)</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>autonomous navigation, mobile robot navigation, ros, ros2</t>
+        </is>
+      </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>9.35</v>
       </c>
       <c r="Z46" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>5.31</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" s="4" t="inlineStr"/>
-      <c r="AE46" s="4" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ivano Malavolta; Koen V. Hindriks; Jeroen C. J. Koelemeij; Stefan Schlobach A</t>
+        </is>
+      </c>
+      <c r="AD46" s="4" t="inlineStr">
+        <is>
+          <t>1. Ivano Malavolta (Full / Senior Prof (Large Lab), h=35) | Fit=6.6/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.3/10 | Keywords=autonomous navigation, mobile robot navigation, ros, ros2 | Paper=Tuning ROS 2 for Energy-Efficient Navigation: Empirical Insights from Costmap 2D Configurations (2026)
+2. Koen V. Hindriks (Full / Senior Prof (Large Lab), h=39) | Fit=5.3/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.4/10 | Keywords=robot perception | Paper=Robot Social Skills: Influencing Children’s Performance and Robot Perception Through a Robot Ma (2026)
+3. Jeroen C. J. Koelemeij (Associate / Established PI (High Fit), h=23) | Fit=5.4/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=5.2/10 | Keywords=gnss positioning | Paper=A hybrid optical–wireless network for decimetre-level terrestrial positioning (2022)
+4. Stefan Schlobach A (Full / Senior Prof (Large Lab), h=26) | Fit=3.9/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.4/10 | Keywords=robot perception | Paper=Advancing Robotic Perception with Perceived-Entity Linking (2024)</t>
+        </is>
+      </c>
+      <c r="AE46" s="4" t="inlineStr">
+        <is>
+          <t>Ivano Malavolta: No homepage/funding evidence available
+Koen V. Hindriks: No homepage/funding evidence available
+Jeroen C. J. Koelemeij: No homepage/funding evidence available
+Stefan Schlobach A: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Avu.nl%20%22Ivano%20Malavolta%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="B47" t="inlineStr">
@@ -6050,28 +6368,153 @@
           <t>Radboud University</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>QS #242 | Tier S+ (Global Elite | h=1140)</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5030520581</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Mohsen Kaboli</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>GMCR: Graph-based Maximum Consensus Estimation for Point Cloud Registration (2023)</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Nijmegen</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>@ru.nl</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>I145872427</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit) (h=21)</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>point cloud registration, pose estimation, sensor calibration, semantic segmentation</t>
+        </is>
+      </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="Z47" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" s="4" t="inlineStr"/>
-      <c r="AE47" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Mohsen Kaboli; Serge Thill</t>
+        </is>
+      </c>
+      <c r="AD47" s="4" t="inlineStr">
+        <is>
+          <t>1. Mohsen Kaboli (Associate / Established PI (High Fit), h=21) | Fit=8.9/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=7.5/10 | Keywords=point cloud registration, pose estimation, sensor calibration, semantic segmentation | Paper=GMCR: Graph-based Maximum Consensus Estimation for Point Cloud Registration (2023)
+2. Serge Thill (Full / Senior Prof (Large Lab), h=23) | Fit=4.3/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.5/10 | Keywords=pose estimation, deep learning | Paper=Towards Robot-Assisted Data Generation with Minimal User Interaction for Autonomously Training  (2023)</t>
+        </is>
+      </c>
+      <c r="AE47" s="4" t="inlineStr">
+        <is>
+          <t>Mohsen Kaboli: No homepage/funding evidence available
+Serge Thill: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aru.nl%20%22Mohsen%20Kaboli%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
           <t>Leiden University</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=923)</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Leiden</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>@leiden.edu</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>I121797337</t>
         </is>
       </c>
       <c r="X48" t="n">
@@ -7945,7 +8388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z490"/>
+  <dimension ref="A1:Z523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -60331,8 +60774,3489 @@
         </is>
       </c>
     </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>QS #233 (Strong Robotics) | Tier S+ (Global Elite | h=628)</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>@utwente.nl</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G491" t="n">
+        <v>1</v>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>George Vosselman A</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J491" t="n">
+        <v>60</v>
+      </c>
+      <c r="K491" t="n">
+        <v>14160</v>
+      </c>
+      <c r="L491" t="n">
+        <v>10</v>
+      </c>
+      <c r="M491" t="n">
+        <v>10</v>
+      </c>
+      <c r="N491" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O491" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Visual-Inertial Navigation &amp; SLAM; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, sensor fusion, factor graph optimization, state estimation, visual inertial odometry, visual odometry</t>
+        </is>
+      </c>
+      <c r="R491" t="n">
+        <v>9</v>
+      </c>
+      <c r="S491" t="n">
+        <v>67</v>
+      </c>
+      <c r="T491" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="U491" t="inlineStr">
+        <is>
+          <t>Multi-sensor Fusion SLAM from the Nadir View for UAV Localization and Mapping</t>
+        </is>
+      </c>
+      <c r="V491" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W491" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X491" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Autwente.nl%20%22George%20Vosselman%20A%22%20email</t>
+        </is>
+      </c>
+      <c r="Z491" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5086428184</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>QS #233 (Strong Robotics) | Tier S+ (Global Elite | h=628)</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>@utwente.nl</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G492" t="n">
+        <v>2</v>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>Francesco Nex</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J492" t="n">
+        <v>38</v>
+      </c>
+      <c r="K492" t="n">
+        <v>9513</v>
+      </c>
+      <c r="L492" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="M492" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N492" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O492" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, sensor fusion, factor graph optimization, state estimation, visual inertial odometry, visual odometry</t>
+        </is>
+      </c>
+      <c r="R492" t="n">
+        <v>20</v>
+      </c>
+      <c r="S492" t="n">
+        <v>73</v>
+      </c>
+      <c r="T492" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="U492" t="inlineStr">
+        <is>
+          <t>Multi-sensor Fusion SLAM from the Nadir View for UAV Localization and Mapping</t>
+        </is>
+      </c>
+      <c r="V492" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W492" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X492" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Autwente.nl%20%22Francesco%20Nex%22%20email</t>
+        </is>
+      </c>
+      <c r="Z492" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5013633154</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>QS #233 (Strong Robotics) | Tier S+ (Global Elite | h=628)</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>@utwente.nl</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G493" t="n">
+        <v>3</v>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>Ville Lehtola</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J493" t="n">
+        <v>19</v>
+      </c>
+      <c r="K493" t="n">
+        <v>1565</v>
+      </c>
+      <c r="L493" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="M493" t="n">
+        <v>10</v>
+      </c>
+      <c r="N493" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O493" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; State Estimation &amp; Factor Graphs; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>lidar inertial odometry, extended kalman filter, kalman filter, semantic segmentation, 3d reconstruction, multi-sensor fusion</t>
+        </is>
+      </c>
+      <c r="R493" t="n">
+        <v>6</v>
+      </c>
+      <c r="S493" t="n">
+        <v>25</v>
+      </c>
+      <c r="T493" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="U493" t="inlineStr">
+        <is>
+          <t>Gaussian or Plane? Both: Semantic-Driven Voxel Representation for LiDAR–Inertial Odometry</t>
+        </is>
+      </c>
+      <c r="V493" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W493" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X493" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Autwente.nl%20%22Ville%20Lehtola%22%20email</t>
+        </is>
+      </c>
+      <c r="Z493" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5025807163</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>QS #233 (Strong Robotics) | Tier S+ (Global Elite | h=628)</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>@utwente.nl</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G494" t="n">
+        <v>4</v>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>Bashar Saleem Abbas Alsadik</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J494" t="n">
+        <v>15</v>
+      </c>
+      <c r="K494" t="n">
+        <v>634</v>
+      </c>
+      <c r="L494" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="M494" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N494" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O494" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q494" t="inlineStr">
+        <is>
+          <t>visual slam, lidar slam, robot localization, autonomous navigation, deep learning, depth estimation</t>
+        </is>
+      </c>
+      <c r="R494" t="n">
+        <v>6</v>
+      </c>
+      <c r="S494" t="n">
+        <v>30</v>
+      </c>
+      <c r="T494" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="U494" t="inlineStr">
+        <is>
+          <t>The Simultaneous Localization and Mapping (SLAM)-An Overview</t>
+        </is>
+      </c>
+      <c r="V494" t="n">
+        <v>2021</v>
+      </c>
+      <c r="W494" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X494" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Autwente.nl%20%22Bashar%20Saleem%20Abbas%20Alsadik%22%20email</t>
+        </is>
+      </c>
+      <c r="Z494" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5052229489</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>QS #233 (Strong Robotics) | Tier S+ (Global Elite | h=628)</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>@utwente.nl</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G495" t="n">
+        <v>5</v>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>Françoise J. Siepel</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J495" t="n">
+        <v>16</v>
+      </c>
+      <c r="K495" t="n">
+        <v>957</v>
+      </c>
+      <c r="L495" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="M495" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N495" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O495" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; State Estimation &amp; Factor Graphs; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q495" t="inlineStr">
+        <is>
+          <t>visual slam, pose estimation, depth estimation, robust localization, deep learning, object detection</t>
+        </is>
+      </c>
+      <c r="R495" t="n">
+        <v>3</v>
+      </c>
+      <c r="S495" t="n">
+        <v>34</v>
+      </c>
+      <c r="T495" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="U495" t="inlineStr">
+        <is>
+          <t>Integration of Visual SLAM in Robot-Assisted Minimally Invasive Surgery: Advances, Challenges, and Solutions</t>
+        </is>
+      </c>
+      <c r="V495" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W495" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X495" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Autwente.nl%20%22Fran%C3%A7oise%20J.%20Siepel%22%20email</t>
+        </is>
+      </c>
+      <c r="Z495" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5053182111</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>QS #233 (Strong Robotics) | Tier S+ (Global Elite | h=628)</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>@utwente.nl</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G496" t="n">
+        <v>6</v>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>Antonio Franchi</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J496" t="n">
+        <v>55</v>
+      </c>
+      <c r="K496" t="n">
+        <v>9657</v>
+      </c>
+      <c r="L496" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="M496" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N496" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O496" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q496" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, pose estimation, object detection, visual localization, state estimation, kalman filter</t>
+        </is>
+      </c>
+      <c r="R496" t="n">
+        <v>5</v>
+      </c>
+      <c r="S496" t="n">
+        <v>112</v>
+      </c>
+      <c r="T496" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="U496" t="inlineStr">
+        <is>
+          <t>Multi-Agent Visual-Inertial Localization for Integrated Aerial Systems With Loose Fusion of Odometry and Kinematics</t>
+        </is>
+      </c>
+      <c r="V496" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W496" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X496" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Autwente.nl%20%22Antonio%20Franchi%22%20email</t>
+        </is>
+      </c>
+      <c r="Z496" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5001771133</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>QS #233 (Strong Robotics) | Tier S+ (Global Elite | h=628)</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>@utwente.nl</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G497" t="n">
+        <v>7</v>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>Nicola Strisciuglio</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J497" t="n">
+        <v>24</v>
+      </c>
+      <c r="K497" t="n">
+        <v>2303</v>
+      </c>
+      <c r="L497" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="M497" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N497" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O497" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q497" t="inlineStr">
+        <is>
+          <t>place recognition, visual localization, computer vision</t>
+        </is>
+      </c>
+      <c r="R497" t="n">
+        <v>2</v>
+      </c>
+      <c r="S497" t="n">
+        <v>49</v>
+      </c>
+      <c r="T497" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="U497" t="inlineStr">
+        <is>
+          <t>Data-Efficient Large Scale Place Recognition with Graded Similarity Supervision</t>
+        </is>
+      </c>
+      <c r="V497" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W497" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X497" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Autwente.nl%20%22Nicola%20Strisciuglio%22%20email</t>
+        </is>
+      </c>
+      <c r="Z497" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5067565879</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>QS #233 (Strong Robotics) | Tier S+ (Global Elite | h=628)</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>@utwente.nl</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G498" t="n">
+        <v>8</v>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>Ivo A. M. J. Broeders</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J498" t="n">
+        <v>51</v>
+      </c>
+      <c r="K498" t="n">
+        <v>8172</v>
+      </c>
+      <c r="L498" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="M498" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N498" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O498" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>pose estimation, depth estimation, 3d reconstruction, object detection</t>
+        </is>
+      </c>
+      <c r="R498" t="n">
+        <v>1</v>
+      </c>
+      <c r="S498" t="n">
+        <v>47</v>
+      </c>
+      <c r="T498" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="U498" t="inlineStr">
+        <is>
+          <t>NeRF-OR: neural radiance fields for operating room scene reconstruction from sparse-view RGB-D videos</t>
+        </is>
+      </c>
+      <c r="V498" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W498" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X498" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Autwente.nl%20%22Ivo%20A.%20M.%20J.%20Broeders%22%20email</t>
+        </is>
+      </c>
+      <c r="Z498" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5052055692</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>QS #233 (Strong Robotics) | Tier S+ (Global Elite | h=628)</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>@utwente.nl</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G499" t="n">
+        <v>9</v>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>Jelmer M. Wolterink</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J499" t="n">
+        <v>34</v>
+      </c>
+      <c r="K499" t="n">
+        <v>8913</v>
+      </c>
+      <c r="L499" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="M499" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N499" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O499" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>pose estimation, depth estimation, 3d reconstruction, object detection</t>
+        </is>
+      </c>
+      <c r="R499" t="n">
+        <v>1</v>
+      </c>
+      <c r="S499" t="n">
+        <v>145</v>
+      </c>
+      <c r="T499" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="U499" t="inlineStr">
+        <is>
+          <t>NeRF-OR: neural radiance fields for operating room scene reconstruction from sparse-view RGB-D videos</t>
+        </is>
+      </c>
+      <c r="V499" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W499" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X499" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Autwente.nl%20%22Jelmer%20M.%20Wolterink%22%20email</t>
+        </is>
+      </c>
+      <c r="Z499" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5028639654</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>QS #233 (Strong Robotics) | Tier S+ (Global Elite | h=628)</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>@utwente.nl</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G500" t="n">
+        <v>10</v>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>Massimo Sartori</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J500" t="n">
+        <v>33</v>
+      </c>
+      <c r="K500" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L500" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="M500" t="n">
+        <v>10</v>
+      </c>
+      <c r="N500" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O500" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t>pose estimation, point cloud registration</t>
+        </is>
+      </c>
+      <c r="R500" t="n">
+        <v>1</v>
+      </c>
+      <c r="S500" t="n">
+        <v>140</v>
+      </c>
+      <c r="T500" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="U500" t="inlineStr">
+        <is>
+          <t>Navigation-guided a-mode ultrasound system for reliable non-invasive 3D bone pose estimation</t>
+        </is>
+      </c>
+      <c r="V500" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W500" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X500" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Autwente.nl%20%22Massimo%20Sartori%22%20email</t>
+        </is>
+      </c>
+      <c r="Z500" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5083381101</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>QS #233 (Strong Robotics) | Tier S+ (Global Elite | h=628)</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>@utwente.nl</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G501" t="n">
+        <v>11</v>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>Maurice van Keulen</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J501" t="n">
+        <v>20</v>
+      </c>
+      <c r="K501" t="n">
+        <v>2625</v>
+      </c>
+      <c r="L501" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="M501" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N501" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O501" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; 3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>gaussian splatting, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R501" t="n">
+        <v>4</v>
+      </c>
+      <c r="S501" t="n">
+        <v>50</v>
+      </c>
+      <c r="T501" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="U501" t="inlineStr">
+        <is>
+          <t>Evaluating 3D Reconstruction: A Side-by-Side Comparison of NeRF and Gaussian Splatting in Indoor and Outdoor Environments</t>
+        </is>
+      </c>
+      <c r="V501" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W501" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X501" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Autwente.nl%20%22Maurice%20van%20Keulen%22%20email</t>
+        </is>
+      </c>
+      <c r="Z501" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5062035687</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>QS #233 (Strong Robotics) | Tier S+ (Global Elite | h=628)</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>@utwente.nl</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G502" t="n">
+        <v>12</v>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>Hao Cheng</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J502" t="n">
+        <v>28</v>
+      </c>
+      <c r="K502" t="n">
+        <v>2731</v>
+      </c>
+      <c r="L502" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="M502" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N502" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O502" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q502" t="inlineStr">
+        <is>
+          <t>sensor fusion, pose estimation, gaussian splatting</t>
+        </is>
+      </c>
+      <c r="R502" t="n">
+        <v>3</v>
+      </c>
+      <c r="S502" t="n">
+        <v>128</v>
+      </c>
+      <c r="T502" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="U502" t="inlineStr">
+        <is>
+          <t>DVLO4D: Deep Visual-Lidar Odometry with Sparse Spatial-Temporal Fusion</t>
+        </is>
+      </c>
+      <c r="V502" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W502" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X502" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Autwente.nl%20%22Hao%20Cheng%22%20email</t>
+        </is>
+      </c>
+      <c r="Z502" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100406787</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>QS #233 (Strong Robotics) | Tier S+ (Global Elite | h=628)</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>@utwente.nl</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G503" t="n">
+        <v>13</v>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>Norman Kerle</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J503" t="n">
+        <v>55</v>
+      </c>
+      <c r="K503" t="n">
+        <v>10644</v>
+      </c>
+      <c r="L503" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="M503" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N503" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O503" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>autonomous navigation, depth estimation, computer vision, loop closure</t>
+        </is>
+      </c>
+      <c r="R503" t="n">
+        <v>3</v>
+      </c>
+      <c r="S503" t="n">
+        <v>27</v>
+      </c>
+      <c r="T503" t="inlineStr">
+        <is>
+          <t>2024-01-24</t>
+        </is>
+      </c>
+      <c r="U503" t="inlineStr">
+        <is>
+          <t>End-to-End Nano-Drone Obstacle Avoidance for Indoor Exploration</t>
+        </is>
+      </c>
+      <c r="V503" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W503" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X503" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Autwente.nl%20%22Norman%20Kerle%22%20email</t>
+        </is>
+      </c>
+      <c r="Z503" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5014462963</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>QS #233 (Strong Robotics) | Tier S+ (Global Elite | h=628)</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>@utwente.nl</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G504" t="n">
+        <v>14</v>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>Sander Oude Elberink</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J504" t="n">
+        <v>33</v>
+      </c>
+      <c r="K504" t="n">
+        <v>4990</v>
+      </c>
+      <c r="L504" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="M504" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N504" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O504" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t>sensor fusion, pose estimation, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R504" t="n">
+        <v>2</v>
+      </c>
+      <c r="S504" t="n">
+        <v>42</v>
+      </c>
+      <c r="T504" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="U504" t="inlineStr">
+        <is>
+          <t>DVLO4D: Deep Visual-Lidar Odometry with Sparse Spatial-Temporal Fusion</t>
+        </is>
+      </c>
+      <c r="V504" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W504" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X504" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Autwente.nl%20%22Sander%20Oude%20Elberink%22%20email</t>
+        </is>
+      </c>
+      <c r="Z504" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5059990087</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>QS #233 (Strong Robotics) | Tier S+ (Global Elite | h=628)</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>@utwente.nl</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G505" t="n">
+        <v>15</v>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>Stefano Stramigioli</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J505" t="n">
+        <v>51</v>
+      </c>
+      <c r="K505" t="n">
+        <v>11704</v>
+      </c>
+      <c r="L505" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="M505" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N505" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O505" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>autonomous navigation</t>
+        </is>
+      </c>
+      <c r="R505" t="n">
+        <v>1</v>
+      </c>
+      <c r="S505" t="n">
+        <v>112</v>
+      </c>
+      <c r="T505" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="U505" t="inlineStr">
+        <is>
+          <t>Towards Autonomous Pipeline Inspection with Hierarchical Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="V505" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W505" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X505" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Autwente.nl%20%22Stefano%20Stramigioli%22%20email</t>
+        </is>
+      </c>
+      <c r="Z505" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5047812798</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>QS #233 (Strong Robotics) | Tier S+ (Global Elite | h=628)</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>@utwente.nl</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G506" t="n">
+        <v>16</v>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>Mannes Poel</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J506" t="n">
+        <v>31</v>
+      </c>
+      <c r="K506" t="n">
+        <v>3435</v>
+      </c>
+      <c r="L506" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="M506" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N506" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O506" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q506" t="inlineStr">
+        <is>
+          <t>autonomous navigation</t>
+        </is>
+      </c>
+      <c r="R506" t="n">
+        <v>1</v>
+      </c>
+      <c r="S506" t="n">
+        <v>28</v>
+      </c>
+      <c r="T506" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="U506" t="inlineStr">
+        <is>
+          <t>Towards Autonomous Pipeline Inspection with Hierarchical Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="V506" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W506" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X506" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Autwente.nl%20%22Mannes%20Poel%22%20email</t>
+        </is>
+      </c>
+      <c r="Z506" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5046610258</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>QS #233 (Strong Robotics) | Tier S+ (Global Elite | h=628)</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>@utwente.nl</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G507" t="n">
+        <v>17</v>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>Christoph Brüne</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J507" t="n">
+        <v>24</v>
+      </c>
+      <c r="K507" t="n">
+        <v>1716</v>
+      </c>
+      <c r="L507" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="M507" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N507" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O507" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q507" t="inlineStr">
+        <is>
+          <t>autonomous navigation</t>
+        </is>
+      </c>
+      <c r="R507" t="n">
+        <v>1</v>
+      </c>
+      <c r="S507" t="n">
+        <v>67</v>
+      </c>
+      <c r="T507" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="U507" t="inlineStr">
+        <is>
+          <t>Towards Autonomous Pipeline Inspection with Hierarchical Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="V507" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W507" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X507" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Autwente.nl%20%22Christoph%20Br%C3%BCne%22%20email</t>
+        </is>
+      </c>
+      <c r="Z507" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5078725649</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>QS #233 (Strong Robotics) | Tier S+ (Global Elite | h=628)</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>@utwente.nl</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G508" t="n">
+        <v>18</v>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>Paul Havinga</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J508" t="n">
+        <v>53</v>
+      </c>
+      <c r="K508" t="n">
+        <v>12538</v>
+      </c>
+      <c r="L508" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="M508" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N508" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O508" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q508" t="inlineStr">
+        <is>
+          <t>inertial navigation</t>
+        </is>
+      </c>
+      <c r="R508" t="n">
+        <v>1</v>
+      </c>
+      <c r="S508" t="n">
+        <v>51</v>
+      </c>
+      <c r="T508" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="U508" t="inlineStr">
+        <is>
+          <t>iMoT: Inertial Motion Transformer for Inertial Navigation</t>
+        </is>
+      </c>
+      <c r="V508" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W508" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X508" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Autwente.nl%20%22Paul%20Havinga%22%20email</t>
+        </is>
+      </c>
+      <c r="Z508" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5067566830</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>QS #233 (Strong Robotics) | Tier S+ (Global Elite | h=628)</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>@utwente.nl</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G509" t="n">
+        <v>19</v>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>Marco J.G. Bekooij</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J509" t="n">
+        <v>22</v>
+      </c>
+      <c r="K509" t="n">
+        <v>1950</v>
+      </c>
+      <c r="L509" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="M509" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N509" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O509" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q509" t="inlineStr">
+        <is>
+          <t>robust localization, object detection, semantic segmentation</t>
+        </is>
+      </c>
+      <c r="R509" t="n">
+        <v>1</v>
+      </c>
+      <c r="S509" t="n">
+        <v>16</v>
+      </c>
+      <c r="T509" t="inlineStr">
+        <is>
+          <t>2022-04-05</t>
+        </is>
+      </c>
+      <c r="U509" t="inlineStr">
+        <is>
+          <t>Weakly Supervised Semantic Segmentation for Range-Doppler Maps</t>
+        </is>
+      </c>
+      <c r="V509" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W509" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X509" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Autwente.nl%20%22Marco%20J.G.%20Bekooij%22%20email</t>
+        </is>
+      </c>
+      <c r="Z509" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5111443523</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>University of Amsterdam</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>QS #55 | Tier S+ (Global Elite | h=1213)</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>@uva.nl</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G510" t="n">
+        <v>1</v>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>Sirui Wang</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J510" t="n">
+        <v>15</v>
+      </c>
+      <c r="K510" t="n">
+        <v>1094</v>
+      </c>
+      <c r="L510" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="M510" t="n">
+        <v>10</v>
+      </c>
+      <c r="N510" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O510" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q510" t="inlineStr">
+        <is>
+          <t>visual odometry</t>
+        </is>
+      </c>
+      <c r="R510" t="n">
+        <v>1</v>
+      </c>
+      <c r="S510" t="n">
+        <v>58</v>
+      </c>
+      <c r="T510" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="U510" t="inlineStr">
+        <is>
+          <t>DFSVO: Detection-Free Stereo Visual Odometry for underwater localization and mapping</t>
+        </is>
+      </c>
+      <c r="V510" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W510" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X510" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auva.nl%20%22Sirui%20Wang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z510" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100631506</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>University of Amsterdam</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>QS #55 | Tier S+ (Global Elite | h=1213)</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>@uva.nl</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G511" t="n">
+        <v>2</v>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>Shaodi You</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J511" t="n">
+        <v>31</v>
+      </c>
+      <c r="K511" t="n">
+        <v>4353</v>
+      </c>
+      <c r="L511" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="M511" t="n">
+        <v>10</v>
+      </c>
+      <c r="N511" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O511" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>visual slam, depth estimation, pose estimation, computer vision</t>
+        </is>
+      </c>
+      <c r="R511" t="n">
+        <v>2</v>
+      </c>
+      <c r="S511" t="n">
+        <v>59</v>
+      </c>
+      <c r="T511" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="U511" t="inlineStr">
+        <is>
+          <t>Atlantis++: Enabling Underwater Depth Estimation with Stable Diffusion and Beyond</t>
+        </is>
+      </c>
+      <c r="V511" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W511" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X511" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auva.nl%20%22Shaodi%20You%22%20email</t>
+        </is>
+      </c>
+      <c r="Z511" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5003277535</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>University of Amsterdam</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>QS #55 | Tier S+ (Global Elite | h=1213)</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>@uva.nl</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G512" t="n">
+        <v>3</v>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>Martin R. Oswald</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J512" t="n">
+        <v>31</v>
+      </c>
+      <c r="K512" t="n">
+        <v>3676</v>
+      </c>
+      <c r="L512" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="M512" t="n">
+        <v>10</v>
+      </c>
+      <c r="N512" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O512" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>point cloud registration, gaussian splatting, place recognition, robot perception, object detection, visual slam</t>
+        </is>
+      </c>
+      <c r="R512" t="n">
+        <v>10</v>
+      </c>
+      <c r="S512" t="n">
+        <v>99</v>
+      </c>
+      <c r="T512" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="U512" t="inlineStr">
+        <is>
+          <t>Splat-LOAM: Gaussian Splatting LiDAR Odometry and Mapping</t>
+        </is>
+      </c>
+      <c r="V512" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W512" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X512" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auva.nl%20%22Martin%20R.%20Oswald%22%20email</t>
+        </is>
+      </c>
+      <c r="Z512" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5040640817</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>University of Amsterdam</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>QS #55 | Tier S+ (Global Elite | h=1213)</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>@uva.nl</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G513" t="n">
+        <v>4</v>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>Theo Gevers</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J513" t="n">
+        <v>56</v>
+      </c>
+      <c r="K513" t="n">
+        <v>20850</v>
+      </c>
+      <c r="L513" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="M513" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N513" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O513" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; LiDAR &amp; Multimodal Sensor Fusion; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t>loop closure, gaussian splatting, computer vision, pose estimation</t>
+        </is>
+      </c>
+      <c r="R513" t="n">
+        <v>3</v>
+      </c>
+      <c r="S513" t="n">
+        <v>96</v>
+      </c>
+      <c r="T513" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U513" t="inlineStr">
+        <is>
+          <t>MAGiC-SLAM: Multi-Agent Gaussian Globally Consistent SLAM</t>
+        </is>
+      </c>
+      <c r="V513" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W513" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X513" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auva.nl%20%22Theo%20Gevers%22%20email</t>
+        </is>
+      </c>
+      <c r="Z513" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5040169071</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>University of Amsterdam</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>QS #55 | Tier S+ (Global Elite | h=1213)</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>@uva.nl</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G514" t="n">
+        <v>5</v>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>Arnoud Visser</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J514" t="n">
+        <v>23</v>
+      </c>
+      <c r="K514" t="n">
+        <v>1383</v>
+      </c>
+      <c r="L514" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="M514" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N514" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O514" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>pose estimation</t>
+        </is>
+      </c>
+      <c r="R514" t="n">
+        <v>1</v>
+      </c>
+      <c r="S514" t="n">
+        <v>17</v>
+      </c>
+      <c r="T514" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="U514" t="inlineStr">
+        <is>
+          <t>Position and Altitude of the Nao Camera Head from Two Points on the Soccer Field Plus the Gravitational Direction</t>
+        </is>
+      </c>
+      <c r="V514" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W514" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X514" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auva.nl%20%22Arnoud%20Visser%22%20email</t>
+        </is>
+      </c>
+      <c r="Z514" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5085420075</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>University of Amsterdam</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>QS #55 | Tier S+ (Global Elite | h=1213)</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>@uva.nl</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G515" t="n">
+        <v>6</v>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>Somaya Ben Allouch</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J515" t="n">
+        <v>28</v>
+      </c>
+      <c r="K515" t="n">
+        <v>3187</v>
+      </c>
+      <c r="L515" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="M515" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N515" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O515" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q515" t="inlineStr">
+        <is>
+          <t>robot perception</t>
+        </is>
+      </c>
+      <c r="R515" t="n">
+        <v>1</v>
+      </c>
+      <c r="S515" t="n">
+        <v>64</v>
+      </c>
+      <c r="T515" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U515" t="inlineStr">
+        <is>
+          <t>Robot Social Skills: Influencing Children’s Performance and Robot Perception Through a Robot Math Tutor’s Scaffolding and Personalization</t>
+        </is>
+      </c>
+      <c r="V515" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W515" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X515" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auva.nl%20%22Somaya%20Ben%20Allouch%22%20email</t>
+        </is>
+      </c>
+      <c r="Z515" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5057289735</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>University of Amsterdam</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>QS #55 | Tier S+ (Global Elite | h=1213)</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>@uva.nl</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G516" t="n">
+        <v>7</v>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>Sezer Karaoğlu</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J516" t="n">
+        <v>18</v>
+      </c>
+      <c r="K516" t="n">
+        <v>975</v>
+      </c>
+      <c r="L516" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="M516" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N516" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O516" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q516" t="inlineStr">
+        <is>
+          <t>pose estimation, computer vision, gaussian splatting</t>
+        </is>
+      </c>
+      <c r="R516" t="n">
+        <v>2</v>
+      </c>
+      <c r="S516" t="n">
+        <v>50</v>
+      </c>
+      <c r="T516" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U516" t="inlineStr">
+        <is>
+          <t>3D human pose estimation and action recognition using fisheye cameras: A survey and benchmark</t>
+        </is>
+      </c>
+      <c r="V516" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W516" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X516" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auva.nl%20%22Sezer%20Karao%C4%9Flu%22%20email</t>
+        </is>
+      </c>
+      <c r="Z516" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5015057235</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Vrije Universiteit Amsterdam</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1011)</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>@vu.nl</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G517" t="n">
+        <v>1</v>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>Ivano Malavolta</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J517" t="n">
+        <v>35</v>
+      </c>
+      <c r="K517" t="n">
+        <v>4384</v>
+      </c>
+      <c r="L517" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="M517" t="n">
+        <v>10</v>
+      </c>
+      <c r="N517" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O517" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Embedded AI &amp; Real-Time Edge Robotics; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q517" t="inlineStr">
+        <is>
+          <t>autonomous navigation, mobile robot navigation, ros, ros2</t>
+        </is>
+      </c>
+      <c r="R517" t="n">
+        <v>2</v>
+      </c>
+      <c r="S517" t="n">
+        <v>99</v>
+      </c>
+      <c r="T517" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U517" t="inlineStr">
+        <is>
+          <t>Tuning ROS 2 for Energy-Efficient Navigation: Empirical Insights from Costmap 2D Configurations</t>
+        </is>
+      </c>
+      <c r="V517" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W517" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X517" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Avu.nl%20%22Ivano%20Malavolta%22%20email</t>
+        </is>
+      </c>
+      <c r="Z517" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5079556921</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Vrije Universiteit Amsterdam</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1011)</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>@vu.nl</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G518" t="n">
+        <v>2</v>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>Koen V. Hindriks</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J518" t="n">
+        <v>39</v>
+      </c>
+      <c r="K518" t="n">
+        <v>6496</v>
+      </c>
+      <c r="L518" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="M518" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N518" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O518" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q518" t="inlineStr">
+        <is>
+          <t>robot perception</t>
+        </is>
+      </c>
+      <c r="R518" t="n">
+        <v>1</v>
+      </c>
+      <c r="S518" t="n">
+        <v>122</v>
+      </c>
+      <c r="T518" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U518" t="inlineStr">
+        <is>
+          <t>Robot Social Skills: Influencing Children’s Performance and Robot Perception Through a Robot Math Tutor’s Scaffolding and Personalization</t>
+        </is>
+      </c>
+      <c r="V518" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W518" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X518" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Avu.nl%20%22Koen%20V.%20Hindriks%22%20email</t>
+        </is>
+      </c>
+      <c r="Z518" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5071518251</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Vrije Universiteit Amsterdam</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1011)</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>@vu.nl</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G519" t="n">
+        <v>3</v>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>Jeroen C. J. Koelemeij</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J519" t="n">
+        <v>23</v>
+      </c>
+      <c r="K519" t="n">
+        <v>3112</v>
+      </c>
+      <c r="L519" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M519" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N519" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O519" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q519" t="inlineStr">
+        <is>
+          <t>gnss positioning</t>
+        </is>
+      </c>
+      <c r="R519" t="n">
+        <v>1</v>
+      </c>
+      <c r="S519" t="n">
+        <v>21</v>
+      </c>
+      <c r="T519" t="inlineStr">
+        <is>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="U519" t="inlineStr">
+        <is>
+          <t>A hybrid optical–wireless network for decimetre-level terrestrial positioning</t>
+        </is>
+      </c>
+      <c r="V519" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W519" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X519" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Avu.nl%20%22Jeroen%20C.%20J.%20Koelemeij%22%20email</t>
+        </is>
+      </c>
+      <c r="Z519" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5013718580</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Vrije Universiteit Amsterdam</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1011)</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>@vu.nl</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G520" t="n">
+        <v>4</v>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>Stefan Schlobach A</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J520" t="n">
+        <v>26</v>
+      </c>
+      <c r="K520" t="n">
+        <v>3498</v>
+      </c>
+      <c r="L520" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M520" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N520" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O520" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q520" t="inlineStr">
+        <is>
+          <t>robot perception</t>
+        </is>
+      </c>
+      <c r="R520" t="n">
+        <v>2</v>
+      </c>
+      <c r="S520" t="n">
+        <v>43</v>
+      </c>
+      <c r="T520" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="U520" t="inlineStr">
+        <is>
+          <t>Advancing Robotic Perception with Perceived-Entity Linking</t>
+        </is>
+      </c>
+      <c r="V520" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W520" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X520" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Avu.nl%20%22Stefan%20Schlobach%20A%22%20email</t>
+        </is>
+      </c>
+      <c r="Z520" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5075365612</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Radboud University</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Nijmegen</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>QS #242 | Tier S+ (Global Elite | h=1140)</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>@ru.nl</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G521" t="n">
+        <v>1</v>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>Mohsen Kaboli</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J521" t="n">
+        <v>21</v>
+      </c>
+      <c r="K521" t="n">
+        <v>2186</v>
+      </c>
+      <c r="L521" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="M521" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N521" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O521" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q521" t="inlineStr">
+        <is>
+          <t>point cloud registration, pose estimation, sensor calibration, semantic segmentation</t>
+        </is>
+      </c>
+      <c r="R521" t="n">
+        <v>3</v>
+      </c>
+      <c r="S521" t="n">
+        <v>26</v>
+      </c>
+      <c r="T521" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="U521" t="inlineStr">
+        <is>
+          <t>GMCR: Graph-based Maximum Consensus Estimation for Point Cloud Registration</t>
+        </is>
+      </c>
+      <c r="V521" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W521" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X521" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aru.nl%20%22Mohsen%20Kaboli%22%20email</t>
+        </is>
+      </c>
+      <c r="Z521" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5030520581</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Radboud University</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Nijmegen</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>QS #242 | Tier S+ (Global Elite | h=1140)</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>@ru.nl</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G522" t="n">
+        <v>2</v>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>Serge Thill</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J522" t="n">
+        <v>23</v>
+      </c>
+      <c r="K522" t="n">
+        <v>2173</v>
+      </c>
+      <c r="L522" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="M522" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N522" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O522" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q522" t="inlineStr">
+        <is>
+          <t>pose estimation, deep learning</t>
+        </is>
+      </c>
+      <c r="R522" t="n">
+        <v>1</v>
+      </c>
+      <c r="S522" t="n">
+        <v>61</v>
+      </c>
+      <c r="T522" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="U522" t="inlineStr">
+        <is>
+          <t>Towards Robot-Assisted Data Generation with Minimal User Interaction for Autonomously Training 6D Pose Estimation in Operational Environments</t>
+        </is>
+      </c>
+      <c r="V522" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W522" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X522" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aru.nl%20%22Serge%20Thill%22%20email</t>
+        </is>
+      </c>
+      <c r="Z522" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5081506012</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Leiden University</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Leiden</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=923)</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>@leiden.edu</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="J523" t="n">
+        <v>0</v>
+      </c>
+      <c r="K523" t="n">
+        <v>0</v>
+      </c>
+      <c r="L523" t="n">
+        <v>0</v>
+      </c>
+      <c r="M523" t="n">
+        <v>0</v>
+      </c>
+      <c r="N523" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O523" t="n">
+        <v>0</v>
+      </c>
+      <c r="R523" t="n">
+        <v>0</v>
+      </c>
+      <c r="S523" t="n">
+        <v>0</v>
+      </c>
+      <c r="W523" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z490"/>
+  <autoFilter ref="A1:Z523"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AG$127</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Z$523</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Z$582</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -6541,23 +6541,127 @@
           <t>University of Groningen</t>
         </is>
       </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1373)</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5021403340</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Ming Cao</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Robust simultaneous UWB-anchor calibration and robot localization for emergency situations (2025)</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>@rug.nl</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>I169381384</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=57)</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>robot localization, factor graph optimization, pose estimation, 3d reconstruction, robot perception</t>
+        </is>
+      </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>6.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>9.41</v>
       </c>
       <c r="Z49" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" s="4" t="inlineStr"/>
-      <c r="AE49" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ming Cao; Nicolai Petkov; Hamidreza Kasaei; Bin-Bin Hu; Kailai Li; Sarthak Misra; Weijia Yao; Frans W. Cornelissen; Joost Heutink</t>
+        </is>
+      </c>
+      <c r="AD49" s="4" t="inlineStr">
+        <is>
+          <t>1. Ming Cao (Full / Senior Prof (Large Lab), h=57) | Fit=8.9/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=robot localization, factor graph optimization, pose estimation, 3d reconstruction, robot perception | Paper=Robust simultaneous UWB-anchor calibration and robot localization for emergency situations (2025)
+2. Nicolai Petkov (Full / Senior Prof (Large Lab), h=37) | Fit=7.3/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.5/10 | Keywords=place recognition, visual localization, computer vision | Paper=Data-Efficient Large Scale Place Recognition with Graded Similarity Supervision (2023)
+3. Hamidreza Kasaei (Associate / Established PI (High Fit), h=18) | Fit=4.7/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.0/10 | Keywords=pose estimation, deep learning, robot perception, computer vision, 3d reconstruction | Paper=MORE: simultaneous multi-view 3D object recognition and pose estimation (2023)
+4. Bin-Bin Hu (Assistant Prof / Rising Star (Responsive), h=17) | Fit=4.7/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.9/10 | Keywords=trajectory estimation, kalman filter | Paper=Decentralized Model-Free Monitoring of Multi-UAV-Multi-USV Systems Using Sparse Data and Bayesi (2025)
+5. Kailai Li (Assistant Prof / Rising Star (Responsive), h=14) | Fit=4.5/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=state estimation | Paper=On Embedding B-Splines in Recursive State Estimation (2025)
+6. Sarthak Misra (Full / Senior Prof (Large Lab), h=54) | Fit=4.7/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=robot localization, object detection | Paper=Towards Localization of Miniaturized Medical Robots With Microwaves (2024)
+7. Weijia Yao (Associate / Established PI (High Fit), h=16) | Fit=4.0/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.3/10 | Keywords=mobile robot navigation | Paper=A Singularity-Free Guiding Vector Field for Robot Navigation (2023)
+8. Frans W. Cornelissen (Full / Senior Prof (Large Lab), h=39) | Fit=3.6/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.1/10 | Keywords=visual odometry | Paper=ACE-DNV: Automatic classification of gaze events in dynamic natural viewing (2024)
+9. Joost Heutink (Full / Senior Prof (Large Lab), h=17) | Fit=3.6/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.1/10 | Keywords=visual odometry | Paper=ACE-DNV: Automatic classification of gaze events in dynamic natural viewing (2024)</t>
+        </is>
+      </c>
+      <c r="AE49" s="4" t="inlineStr">
+        <is>
+          <t>Ming Cao: No homepage/funding evidence available
+Nicolai Petkov: No homepage/funding evidence available
+Hamidreza Kasaei: No homepage/funding evidence available
+Bin-Bin Hu: No homepage/funding evidence available
+Kailai Li: No homepage/funding evidence available
+Sarthak Misra: No homepage/funding evidence available
+Weijia Yao: No homepage/funding evidence available
+Frans W. Cornelissen: No homepage/funding evidence available
+Joost Heutink: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arug.nl%20%22Ming%20Cao%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="B50" t="inlineStr">
@@ -6565,28 +6669,157 @@
           <t>Utrecht University</t>
         </is>
       </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1156)</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5076613413</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Peter Vangorp</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>The Impact of the Number of k-Means Clusters on 3D Point Cloud Registration (2024)</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>@uu.nl</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>I193662353</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive) (h=14)</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>point cloud registration, autonomous navigation, 3d reconstruction</t>
+        </is>
+      </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="Z50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" s="4" t="inlineStr"/>
-      <c r="AE50" s="4" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Peter Vangorp; Qi Bi; Surya Gayet; Nathan Van der Stoep</t>
+        </is>
+      </c>
+      <c r="AD50" s="4" t="inlineStr">
+        <is>
+          <t>1. Peter Vangorp (Assistant Prof / Rising Star (Responsive), h=14) | Fit=8.7/10 | Activity=8.2/10 | Funding=0.0/10 | Overall=7.3/10 | Keywords=point cloud registration, autonomous navigation, 3d reconstruction | Paper=The Impact of the Number of k-Means Clusters on 3D Point Cloud Registration (2024)
+2. Qi Bi (Associate / Established PI (High Fit), h=24) | Fit=5.1/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.2/10 | Keywords=gaussian splatting | Paper=AtlantisGS: Underwater Sparse-View Scene Reconstruction via Gaussian Splatting (2025)
+3. Surya Gayet (Full / Senior Prof (Large Lab), h=19) | Fit=4.3/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.6/10 | Keywords=visual localization | Paper=Using hearing and vision for motion prediction, motion perception, and localization. (2025)
+4. Nathan Van der Stoep (Associate / Established PI (High Fit), h=20) | Fit=4.0/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.5/10 | Keywords=visual localization | Paper=Using hearing and vision for motion prediction, motion perception, and localization. (2025)</t>
+        </is>
+      </c>
+      <c r="AE50" s="4" t="inlineStr">
+        <is>
+          <t>Peter Vangorp: No homepage/funding evidence available
+Qi Bi: No homepage/funding evidence available
+Surya Gayet: No homepage/funding evidence available
+Nathan Van der Stoep: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auu.nl%20%22Peter%20Vangorp%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
           <t>Maastricht University</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=874)</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Maastricht</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>@maastrichtuniversity.nl</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>I34352273</t>
         </is>
       </c>
       <c r="X51" t="n">
@@ -6632,23 +6865,163 @@
           <t>ETH Zürich</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5083003222</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Roland Siegwart</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>When Your State Estimator Has Lost The Plot: Detecting Estimator Failures Via Spectral Analysis (2026)</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>I35440088</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=127)</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, lidar inertial odometry, state estimation, multi-sensor fusion, point cloud registration, sensor fusion</t>
+        </is>
+      </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z53" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" s="4" t="inlineStr"/>
-      <c r="AE53" s="4" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Roland Siegwart; Marc Pollefeys; Marco Hutter; Margarita Chli; Stefan Leutenegger; Dániel Baráth; Michael Pantic; César Cadena; Zihan Zhu; Helen Oleynikova; Benedikt S. Soja; Boyang Sun; Luca Benini C; Lionel Ott; Daniele Palossi; Michele Magno; Danda Pani Paudel; Andreas M. Kunz; Ming Li; Giacomo Indiveri; Othmar Frey; Konrad Schindler; Siyu Tang; Luc Van Gool; Markus Rothacher; Laura Crocetti; Andreas Wieser</t>
+        </is>
+      </c>
+      <c r="AD53" s="4" t="inlineStr">
+        <is>
+          <t>1. Roland Siegwart (Full / Senior Prof (Large Lab), h=127) | Fit=10.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.5/10 | Keywords=visual inertial odometry, lidar inertial odometry, state estimation, multi-sensor fusion, point cloud registration, sensor fusion | Paper=When Your State Estimator Has Lost The Plot: Detecting Estimator Failures Via Spectral Analysis (2026)
+2. Marc Pollefeys (Full / Senior Prof (Large Lab), h=112) | Fit=10.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.5/10 | Keywords=visual-inertial slam, gaussian splatting, loop closure, pose estimation, 3d reconstruction, robot localization | Paper=VIGS-SLAM: Visual Inertial Gaussian Splatting SLAM (2026)
+3. Marco Hutter (Full / Senior Prof (Large Lab), h=84) | Fit=10.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.5/10 | Keywords=robot localization, multi-sensor fusion, sensor fusion, state estimation, place recognition, pose estimation | Paper=TRaIL-Odom: Tightly Coupled Continuous Time Radar-IMU-LiDAR Odometry With Adaptive Doppler Weig (2026)
+4. Margarita Chli (Full / Senior Prof (Large Lab), h=40) | Fit=10.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.5/10 | Keywords=lidar inertial odometry, sensor fusion, mobile robot navigation, loop closure, lidar slam, place recognition | Paper=EllipseLIO: Adaptive LiDAR Inertial Odometry With an Ellipsoid Representation (2026)
+5. Stefan Leutenegger (Full / Senior Prof (Large Lab), h=40) | Fit=10.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.5/10 | Keywords=visual-inertial slam, visual odometry, state estimation, multi-sensor fusion, autonomous navigation, sensor fusion | Paper=AERO-VIS: Asynchronous Event-Based Real-Time Onboard Visual-Inertial SLAM (2026)
+6. Dániel Baráth (Associate / Established PI (High Fit), h=24) | Fit=10.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.5/10 | Keywords=visual-inertial slam, gaussian splatting, loop closure, pose estimation, 3d reconstruction, visual localization | Paper=VIGS-SLAM: Visual Inertial Gaussian Splatting SLAM (2026)
+7. Michael Pantic (Assistant Prof / Rising Star (Responsive), h=12) | Fit=10.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.5/10 | Keywords=visual inertial odometry, lidar inertial odometry, state estimation, multi-sensor fusion, sensor fusion, field robotics | Paper=When Your State Estimator Has Lost The Plot: Detecting Estimator Failures Via Spectral Analysis (2026)
+8. César Cadena (Full / Senior Prof (Large Lab), h=44) | Fit=10.0/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.4/10 | Keywords=robot localization, state estimation, sensor fusion, lidar inertial odometry, multi-sensor fusion, point cloud registration | Paper=Holistic Fusion: Task- and Setup-Agnostic Robot Localization and State Estimation With Factor G (2026)
+9. Zihan Zhu (Associate / Established PI (High Fit), h=23) | Fit=9.8/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.3/10 | Keywords=visual-inertial slam, gaussian splatting, loop closure, pose estimation, 3d reconstruction, visual slam | Paper=VIGS-SLAM: Visual Inertial Gaussian Splatting SLAM (2026)
+10. Helen Oleynikova (Associate / Established PI (High Fit), h=22) | Fit=9.9/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=8.2/10 | Keywords=lidar inertial odometry, multi-sensor fusion, point cloud registration, sensor fusion, extended kalman filter, kalman filter | Paper=COIN-LIO: Complementary Intensity-Augmented LiDAR Inertial Odometry (2024)
+11. Benedikt S. Soja (Full / Senior Prof (Large Lab), h=22) | Fit=9.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.2/10 | Keywords=factor graph optimization, visual odometry, gnss positioning, visual inertial odometry, extended kalman filter, kalman filter | Paper=Smartphone-based Vision/MEMS-IMU/GNSS tightly coupled seamless positioning using factor graph o (2024)
+12. Boyang Sun (Associate / Established PI (High Fit), h=19) | Fit=9.4/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.2/10 | Keywords=loop closure, visual slam, trajectory estimation, mobile robot navigation, 3d reconstruction, visual localization | Paper=Loop Closure From Two Views: Revisiting PGO for Scalable Trajectory Estimation Through Monocula (2026)
+13. Luca Benini C (Full / Senior Prof (Large Lab), h=112) | Fit=9.2/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.9/10 | Keywords=visual inertial odometry, hardware acceleration, embedded systems, gnss positioning, sensor fusion, computer vision | Paper=Low Latency Visual Inertial Odometry With On-Sensor Accelerated Optical Flow for Resource-Const (2024)
+14. Lionel Ott (Associate / Established PI (High Fit), h=23) | Fit=9.5/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=7.9/10 | Keywords=multi-sensor fusion, sensor fusion, state estimation, robot localization, pose estimation, 3d computer vision | Paper=To Fuse or Not to Fuse: Measuring Consistency in Multi-sensor Fusion for Aerial Robots (2024)
+15. Daniele Palossi (Associate / Established PI (High Fit), h=17) | Fit=9.0/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.8/10 | Keywords=multi-sensor fusion, sensor fusion, pose estimation, deep learning, visual odometry | Paper=Fusing Multi-sensor Input with State Information on TinyML Brains for Autonomous Nano-drones (2024)
+16. Michele Magno (Full / Senior Prof (Large Lab), h=48) | Fit=8.9/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=visual inertial odometry, hardware acceleration, embedded systems, gnss positioning, sensor fusion, computer vision | Paper=Low Latency Visual Inertial Odometry With On-Sensor Accelerated Optical Flow for Resource-Const (2024)
+17. Danda Pani Paudel (Full / Senior Prof (Large Lab), h=28) | Fit=9.2/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=visual odometry, pose estimation, stereo vision, ros, visual localization | Paper=Stereo Orientation Prior for UAV Robust and Accurate Visual Odometry (2022)
+18. Andreas M. Kunz (Full / Senior Prof (Large Lab), h=27) | Fit=9.1/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=visual inertial odometry, place recognition | Paper=DVIO - Distributed Visual-Inertial Odometry in a Multi-user Environment (2024)
+19. Ming Li (Assistant Prof / Rising Star (Responsive), h=15) | Fit=8.8/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.7/10 | Keywords=visual localization, autonomous navigation, deep learning | Paper=Localization Based on End-to-End Learning Methods (2026)
+20. Giacomo Indiveri (Full / Senior Prof (Large Lab), h=62) | Fit=8.8/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=7.5/10 | Keywords=visual odometry, robot localization, robot perception | Paper=Visual odometry with neuromorphic resonator networks (2024)
+21. Othmar Frey (Associate / Established PI (High Fit), h=19) | Fit=9.0/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=7.5/10 | Keywords=gnss ins integration, gnss positioning, inertial navigation | Paper=Assessing the Impact of Positioning Errors in Car-Borne Repeat-Pass SAR Interferometry With a C (2022)
+22. Konrad Schindler (Full / Senior Prof (Large Lab), h=79) | Fit=8.5/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=7.4/10 | Keywords=loop closure, point cloud registration, gaussian splatting, 3d reconstruction, sensor fusion, depth estimation | Paper=LoopSplat: Loop Closure by Registering 3D Gaussian Splats (2025)
+23. Siyu Tang (Full / Senior Prof (Large Lab), h=42) | Fit=8.3/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.3/10 | Keywords=gaussian splatting, 3d reconstruction | Paper=DeGauss: Dynamic-Static Decomposition with Gaussian Splatting for Distractor-Free 3D Reconstruc (2025)
+24. Luc Van Gool (Full / Senior Prof (Large Lab), h=189) | Fit=8.2/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.2/10 | Keywords=visual odometry, depth estimation, 3d perception, visual slam, point cloud registration, object detection | Paper=Replay-Based Online Adaptation for Unsupervised Deep Visual Odometry (2023)
+25. Markus Rothacher (Full / Senior Prof (Large Lab), h=51) | Fit=7.6/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.7/10 | Keywords=gnss positioning, extended kalman filter, kalman filter, sensor fusion | Paper=A Cloud-native Approach for Processing of Crowdsourced GNSS Observations and Machine Learning a (2024)
+26. Laura Crocetti (Associate / Established PI (High Fit), h=10) | Fit=7.3/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=6.6/10 | Keywords=gnss positioning, extended kalman filter, kalman filter | Paper=A Cloud-native Approach for Processing of Crowdsourced GNSS Observations and Machine Learning a (2024)
+27. Andreas Wieser (Full / Senior Prof (Large Lab), h=22) | Fit=5.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.8/10 | Keywords=point cloud registration, deep learning, sensor fusion, depth estimation | Paper=Cross-modal feature fusion for robust point cloud registration with ambiguous geometry (2025)</t>
+        </is>
+      </c>
+      <c r="AE53" s="4" t="inlineStr">
+        <is>
+          <t>Roland Siegwart: No homepage/funding evidence available
+Marc Pollefeys: No homepage/funding evidence available
+Marco Hutter: No homepage/funding evidence available
+Margarita Chli: No homepage/funding evidence available
+Stefan Leutenegger: No homepage/funding evidence available
+Dániel Baráth: No homepage/funding evidence available
+Michael Pantic: No homepage/funding evidence available
+César Cadena: No homepage/funding evidence available
+Zihan Zhu: No homepage/funding evidence available
+Helen Oleynikova: No homepage/funding evidence available
+Benedikt S. Soja: No homepage/funding evidence available
+Boyang Sun: No homepage/funding evidence available
+Luca Benini C: No homepage/funding evidence available
+Lionel Ott: No homepage/funding evidence available
+Daniele Palossi: No homepage/funding evidence available
+Michele Magno: No homepage/funding evidence available
+Danda Pani Paudel: No homepage/funding evidence available
+Andreas M. Kunz: No homepage/funding evidence available
+Ming Li: No homepage/funding evidence available
+Giacomo Indiveri: No homepage/funding evidence available
+Othmar Frey: No homepage/funding evidence available
+Konrad Schindler: No homepage/funding evidence available
+Siyu Tang: No homepage/funding evidence available
+Luc Van Gool: No homepage/funding evidence available
+Markus Rothacher: No homepage/funding evidence available
+Laura Crocetti: No homepage/funding evidence available
+Andreas Wieser: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Roland%20Siegwart%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="B54" t="inlineStr">
@@ -6656,23 +7029,145 @@
           <t>EPFL</t>
         </is>
       </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>QS #26 | Tier S+ (Global Elite | h=1194)</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5033612355</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Jan Škaloud</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Extraction of Image-to-Lidar Correspondences and their Impact on Optimal Sensor Fusion (2026)</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>@epfl.ch</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>I5124864</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=28)</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>sensor fusion, factor graph optimization, gnss ins integration, lidar camera fusion, multi-sensor fusion, inertial navigation</t>
+        </is>
+      </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Z54" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>7.48</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" s="4" t="inlineStr"/>
-      <c r="AE54" s="4" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Jan Škaloud; Mathieu Salzmann; Alcherio Martinoli; Olga Fink; Alexandre Alahi; Shaojie Shen; Auke Jan Ijspeert; Brigitte M. Jolles; Dario Floreano; Jean‐Yves Le Boudec; Mario Paolone; Amir Zamir; Yves Weinand; Pascal Frossard B; Paolo Perona; Katrin Beyer; Alexander Mathis; Touradj Ebrahimi</t>
+        </is>
+      </c>
+      <c r="AD54" s="4" t="inlineStr">
+        <is>
+          <t>1. Jan Škaloud (Full / Senior Prof (Large Lab), h=28) | Fit=9.8/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=8.4/10 | Keywords=sensor fusion, factor graph optimization, gnss ins integration, lidar camera fusion, multi-sensor fusion, inertial navigation | Paper=Extraction of Image-to-Lidar Correspondences and their Impact on Optimal Sensor Fusion (2026)
+2. Mathieu Salzmann (Full / Senior Prof (Large Lab), h=65) | Fit=9.2/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.9/10 | Keywords=point cloud registration, pose estimation, 3d reconstruction | Paper=Learning-Based Point Cloud Registration for 6D Object Pose Estimation in the Real World (2022)
+3. Alcherio Martinoli (Full / Senior Prof (Large Lab), h=47) | Fit=8.4/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.5/10 | Keywords=robust localization, state estimation, sensor calibration | Paper=Robust Localization for Multi-robot Formations: An Experimental Evaluation of an Extended GM-PH (2022)
+4. Olga Fink (Full / Senior Prof (Large Lab), h=36) | Fit=8.2/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.3/10 | Keywords=3d reconstruction, pose estimation, gaussian splatting | Paper=SEAR: Simple and Efficient Adaptation of Visual Geometric Transformers for Unpaired RGB-Thermal (2026)
+5. Alexandre Alahi (Full / Senior Prof (Large Lab), h=47) | Fit=6.9/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=6.3/10 | Keywords=point cloud registration, pose estimation, depth estimation, ros, jetson | Paper=Real-Time Localization for Closed-Loop Control of Assistive Furniture (2023)
+6. Shaojie Shen (Full / Senior Prof (Large Lab), h=64) | Fit=6.6/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.3/10 | Keywords=autonomous navigation, depth estimation, ros | Paper=SwarmNxt: Open-source Software-Hardware Platform for Fast and Agile Aerial Swarms (2026)
+7. Auke Jan Ijspeert (Full / Senior Prof (Large Lab), h=76) | Fit=6.7/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.2/10 | Keywords=point cloud registration, pose estimation, field robotics | Paper=Real-Time Localization for Closed-Loop Control of Assistive Furniture (2023)
+8. Brigitte M. Jolles (Full / Senior Prof (Large Lab), h=37) | Fit=6.2/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.0/10 | Keywords=visual inertial odometry, pose estimation | Paper=Spatiotemporal gait analysis using video from a moving observer (2026)
+9. Dario Floreano (Full / Senior Prof (Large Lab), h=85) | Fit=6.0/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.9/10 | Keywords=autonomous navigation, depth estimation, ros | Paper=SwarmNxt: Open-source Software-Hardware Platform for Fast and Agile Aerial Swarms (2026)
+10. Jean‐Yves Le Boudec (Full / Senior Prof (Large Lab), h=70) | Fit=6.4/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=5.8/10 | Keywords=state estimation, kalman filter | Paper=Static and recursive PMU-based state estimation processes for transmission and distribution pow (2022)
+11. Mario Paolone (Full / Senior Prof (Large Lab), h=62) | Fit=6.4/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=5.8/10 | Keywords=state estimation, kalman filter | Paper=Static and recursive PMU-based state estimation processes for transmission and distribution pow (2022)
+12. Amir Zamir (Full / Senior Prof (Large Lab), h=32) | Fit=6.2/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=5.8/10 | Keywords=visual odometry | Paper=Modality-invariant Visual Odometry for Embodied Vision (2023)
+13. Yves Weinand (Full / Senior Prof (Large Lab), h=21) | Fit=6.0/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=5.7/10 | Keywords=pose estimation, 3d reconstruction | Paper=TSLAM: a tag-based object-centered monocular navigation system for augmented manual woodworking (2024)
+14. Pascal Frossard B (Full / Senior Prof (Large Lab), h=61) | Fit=5.8/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=5.5/10 | Keywords=3d perception, autonomous driving perception, 3d object detection, object detection | Paper=IS-Fusion: Instance-Scene Collaborative Fusion for Multimodal 3D Object Detection (2024)
+15. Paolo Perona (Full / Senior Prof (Large Lab), h=28) | Fit=5.2/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=5.2/10 | Keywords=gnss positioning, depth estimation | Paper=Performance and accuracy of cross‐section tracking methods for hydromorphological habitat asses (2024)
+16. Katrin Beyer (Full / Senior Prof (Large Lab), h=44) | Fit=4.7/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=point cloud registration, 3d reconstruction | Paper=Image-based geometric digital twinning for stone masonry elements (2022)
+17. Alexander Mathis (Associate / Established PI (High Fit), h=30) | Fit=4.4/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.7/10 | Keywords=pose estimation, computer vision | Paper=HOISDF: Constraining 3D Hand-Object Pose Estimation with Global Signed Distance Fields (2024)
+18. Touradj Ebrahimi (Full / Senior Prof (Large Lab), h=69) | Fit=4.2/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.5/10 | Keywords=event camera, computer vision, embedded systems | Paper=Evaluation of the impact of lossy compression on event camera-based computer vision tasks (2023)</t>
+        </is>
+      </c>
+      <c r="AE54" s="4" t="inlineStr">
+        <is>
+          <t>Jan Škaloud: No homepage/funding evidence available
+Mathieu Salzmann: No homepage/funding evidence available
+Alcherio Martinoli: No homepage/funding evidence available
+Olga Fink: No homepage/funding evidence available
+Alexandre Alahi: No homepage/funding evidence available
+Shaojie Shen: No homepage/funding evidence available
+Auke Jan Ijspeert: No homepage/funding evidence available
+Brigitte M. Jolles: No homepage/funding evidence available
+Dario Floreano: No homepage/funding evidence available
+Jean‐Yves Le Boudec: No homepage/funding evidence available
+Mario Paolone: No homepage/funding evidence available
+Amir Zamir: No homepage/funding evidence available
+Yves Weinand: No homepage/funding evidence available
+Pascal Frossard B: No homepage/funding evidence available
+Paolo Perona: No homepage/funding evidence available
+Katrin Beyer: No homepage/funding evidence available
+Alexander Mathis: No homepage/funding evidence available
+Touradj Ebrahimi: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aepfl.ch%20%22Jan%20%C5%A0kaloud%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="B55" t="inlineStr">
@@ -8388,7 +8883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z523"/>
+  <dimension ref="A1:Z582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -64255,8 +64750,6271 @@
       </c>
       <c r="W523" s="4" t="inlineStr"/>
     </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>University of Groningen</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1373)</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>@rug.nl</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G524" t="n">
+        <v>1</v>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>Ming Cao</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J524" t="n">
+        <v>57</v>
+      </c>
+      <c r="K524" t="n">
+        <v>15523</v>
+      </c>
+      <c r="L524" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="M524" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N524" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O524" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; Robotics &amp; Autonomous Navigation; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q524" t="inlineStr">
+        <is>
+          <t>robot localization, factor graph optimization, pose estimation, 3d reconstruction, robot perception</t>
+        </is>
+      </c>
+      <c r="R524" t="n">
+        <v>5</v>
+      </c>
+      <c r="S524" t="n">
+        <v>198</v>
+      </c>
+      <c r="T524" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U524" t="inlineStr">
+        <is>
+          <t>Robust simultaneous UWB-anchor calibration and robot localization for emergency situations</t>
+        </is>
+      </c>
+      <c r="V524" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W524" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X524" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arug.nl%20%22Ming%20Cao%22%20email</t>
+        </is>
+      </c>
+      <c r="Z524" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5021403340</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>University of Groningen</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1373)</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>@rug.nl</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G525" t="n">
+        <v>2</v>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>Nicolai Petkov</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J525" t="n">
+        <v>37</v>
+      </c>
+      <c r="K525" t="n">
+        <v>6759</v>
+      </c>
+      <c r="L525" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="M525" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N525" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O525" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q525" t="inlineStr">
+        <is>
+          <t>place recognition, visual localization, computer vision</t>
+        </is>
+      </c>
+      <c r="R525" t="n">
+        <v>3</v>
+      </c>
+      <c r="S525" t="n">
+        <v>31</v>
+      </c>
+      <c r="T525" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="U525" t="inlineStr">
+        <is>
+          <t>Data-Efficient Large Scale Place Recognition with Graded Similarity Supervision</t>
+        </is>
+      </c>
+      <c r="V525" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W525" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X525" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arug.nl%20%22Nicolai%20Petkov%22%20email</t>
+        </is>
+      </c>
+      <c r="Z525" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5065962800</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>University of Groningen</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1373)</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>@rug.nl</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G526" t="n">
+        <v>3</v>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>Hamidreza Kasaei</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J526" t="n">
+        <v>18</v>
+      </c>
+      <c r="K526" t="n">
+        <v>1186</v>
+      </c>
+      <c r="L526" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="M526" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N526" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O526" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q526" t="inlineStr">
+        <is>
+          <t>pose estimation, deep learning, robot perception, computer vision, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R526" t="n">
+        <v>7</v>
+      </c>
+      <c r="S526" t="n">
+        <v>56</v>
+      </c>
+      <c r="T526" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U526" t="inlineStr">
+        <is>
+          <t>MORE: simultaneous multi-view 3D object recognition and pose estimation</t>
+        </is>
+      </c>
+      <c r="V526" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W526" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X526" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arug.nl%20%22Hamidreza%20Kasaei%22%20email</t>
+        </is>
+      </c>
+      <c r="Z526" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5008655688</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>University of Groningen</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1373)</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>@rug.nl</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G527" t="n">
+        <v>4</v>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>Bin-Bin Hu</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J527" t="n">
+        <v>17</v>
+      </c>
+      <c r="K527" t="n">
+        <v>1033</v>
+      </c>
+      <c r="L527" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="M527" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N527" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O527" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q527" t="inlineStr">
+        <is>
+          <t>trajectory estimation, kalman filter</t>
+        </is>
+      </c>
+      <c r="R527" t="n">
+        <v>1</v>
+      </c>
+      <c r="S527" t="n">
+        <v>48</v>
+      </c>
+      <c r="T527" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="U527" t="inlineStr">
+        <is>
+          <t>Decentralized Model-Free Monitoring of Multi-UAV-Multi-USV Systems Using Sparse Data and Bayesian Learning</t>
+        </is>
+      </c>
+      <c r="V527" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W527" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X527" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arug.nl%20%22Bin-Bin%20Hu%22%20email</t>
+        </is>
+      </c>
+      <c r="Z527" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5084566965</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>University of Groningen</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1373)</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>@rug.nl</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G528" t="n">
+        <v>5</v>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>Kailai Li</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J528" t="n">
+        <v>14</v>
+      </c>
+      <c r="K528" t="n">
+        <v>538</v>
+      </c>
+      <c r="L528" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="M528" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N528" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O528" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Visual-Inertial Navigation &amp; SLAM; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q528" t="inlineStr">
+        <is>
+          <t>state estimation</t>
+        </is>
+      </c>
+      <c r="R528" t="n">
+        <v>2</v>
+      </c>
+      <c r="S528" t="n">
+        <v>30</v>
+      </c>
+      <c r="T528" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="U528" t="inlineStr">
+        <is>
+          <t>On Embedding B-Splines in Recursive State Estimation</t>
+        </is>
+      </c>
+      <c r="V528" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W528" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X528" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arug.nl%20%22Kailai%20Li%22%20email</t>
+        </is>
+      </c>
+      <c r="Z528" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5063845462</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>University of Groningen</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1373)</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>@rug.nl</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G529" t="n">
+        <v>6</v>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>Sarthak Misra</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J529" t="n">
+        <v>54</v>
+      </c>
+      <c r="K529" t="n">
+        <v>10156</v>
+      </c>
+      <c r="L529" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="M529" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N529" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O529" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q529" t="inlineStr">
+        <is>
+          <t>robot localization, object detection</t>
+        </is>
+      </c>
+      <c r="R529" t="n">
+        <v>1</v>
+      </c>
+      <c r="S529" t="n">
+        <v>105</v>
+      </c>
+      <c r="T529" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="U529" t="inlineStr">
+        <is>
+          <t>Towards Localization of Miniaturized Medical Robots With Microwaves</t>
+        </is>
+      </c>
+      <c r="V529" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W529" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X529" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arug.nl%20%22Sarthak%20Misra%22%20email</t>
+        </is>
+      </c>
+      <c r="Z529" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5050730423</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>University of Groningen</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1373)</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>@rug.nl</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G530" t="n">
+        <v>7</v>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>Weijia Yao</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J530" t="n">
+        <v>16</v>
+      </c>
+      <c r="K530" t="n">
+        <v>800</v>
+      </c>
+      <c r="L530" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="M530" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N530" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O530" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q530" t="inlineStr">
+        <is>
+          <t>mobile robot navigation</t>
+        </is>
+      </c>
+      <c r="R530" t="n">
+        <v>1</v>
+      </c>
+      <c r="S530" t="n">
+        <v>62</v>
+      </c>
+      <c r="T530" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="U530" t="inlineStr">
+        <is>
+          <t>A Singularity-Free Guiding Vector Field for Robot Navigation</t>
+        </is>
+      </c>
+      <c r="V530" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W530" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X530" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arug.nl%20%22Weijia%20Yao%22%20email</t>
+        </is>
+      </c>
+      <c r="Z530" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5041756875</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>University of Groningen</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1373)</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>@rug.nl</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G531" t="n">
+        <v>8</v>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>Frans W. Cornelissen</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J531" t="n">
+        <v>39</v>
+      </c>
+      <c r="K531" t="n">
+        <v>6582</v>
+      </c>
+      <c r="L531" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M531" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N531" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O531" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q531" t="inlineStr">
+        <is>
+          <t>visual odometry</t>
+        </is>
+      </c>
+      <c r="R531" t="n">
+        <v>1</v>
+      </c>
+      <c r="S531" t="n">
+        <v>56</v>
+      </c>
+      <c r="T531" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="U531" t="inlineStr">
+        <is>
+          <t>ACE-DNV: Automatic classification of gaze events in dynamic natural viewing</t>
+        </is>
+      </c>
+      <c r="V531" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W531" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X531" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arug.nl%20%22Frans%20W.%20Cornelissen%22%20email</t>
+        </is>
+      </c>
+      <c r="Z531" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5055183223</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>University of Groningen</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1373)</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>@rug.nl</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G532" t="n">
+        <v>9</v>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>Joost Heutink</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J532" t="n">
+        <v>17</v>
+      </c>
+      <c r="K532" t="n">
+        <v>988</v>
+      </c>
+      <c r="L532" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M532" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N532" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O532" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="P532" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q532" t="inlineStr">
+        <is>
+          <t>visual odometry</t>
+        </is>
+      </c>
+      <c r="R532" t="n">
+        <v>1</v>
+      </c>
+      <c r="S532" t="n">
+        <v>65</v>
+      </c>
+      <c r="T532" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="U532" t="inlineStr">
+        <is>
+          <t>ACE-DNV: Automatic classification of gaze events in dynamic natural viewing</t>
+        </is>
+      </c>
+      <c r="V532" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W532" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X532" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Arug.nl%20%22Joost%20Heutink%22%20email</t>
+        </is>
+      </c>
+      <c r="Z532" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5091551401</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Utrecht University</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1156)</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>@uu.nl</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G533" t="n">
+        <v>1</v>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>Peter Vangorp</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J533" t="n">
+        <v>14</v>
+      </c>
+      <c r="K533" t="n">
+        <v>693</v>
+      </c>
+      <c r="L533" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="M533" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="N533" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O533" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q533" t="inlineStr">
+        <is>
+          <t>point cloud registration, autonomous navigation, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R533" t="n">
+        <v>1</v>
+      </c>
+      <c r="S533" t="n">
+        <v>10</v>
+      </c>
+      <c r="T533" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="U533" t="inlineStr">
+        <is>
+          <t>The Impact of the Number of k-Means Clusters on 3D Point Cloud Registration</t>
+        </is>
+      </c>
+      <c r="V533" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W533" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X533" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auu.nl%20%22Peter%20Vangorp%22%20email</t>
+        </is>
+      </c>
+      <c r="Z533" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5076613413</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Utrecht University</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1156)</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>@uu.nl</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G534" t="n">
+        <v>2</v>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>Qi Bi</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J534" t="n">
+        <v>24</v>
+      </c>
+      <c r="K534" t="n">
+        <v>2195</v>
+      </c>
+      <c r="L534" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="M534" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N534" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O534" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q534" t="inlineStr">
+        <is>
+          <t>gaussian splatting</t>
+        </is>
+      </c>
+      <c r="R534" t="n">
+        <v>1</v>
+      </c>
+      <c r="S534" t="n">
+        <v>77</v>
+      </c>
+      <c r="T534" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="U534" t="inlineStr">
+        <is>
+          <t>AtlantisGS: Underwater Sparse-View Scene Reconstruction via Gaussian Splatting</t>
+        </is>
+      </c>
+      <c r="V534" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W534" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X534" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auu.nl%20%22Qi%20Bi%22%20email</t>
+        </is>
+      </c>
+      <c r="Z534" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5035415308</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Utrecht University</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1156)</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>@uu.nl</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G535" t="n">
+        <v>3</v>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>Surya Gayet</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J535" t="n">
+        <v>19</v>
+      </c>
+      <c r="K535" t="n">
+        <v>1328</v>
+      </c>
+      <c r="L535" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="M535" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N535" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O535" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q535" t="inlineStr">
+        <is>
+          <t>visual localization</t>
+        </is>
+      </c>
+      <c r="R535" t="n">
+        <v>4</v>
+      </c>
+      <c r="S535" t="n">
+        <v>108</v>
+      </c>
+      <c r="T535" t="inlineStr">
+        <is>
+          <t>2025-01-27</t>
+        </is>
+      </c>
+      <c r="U535" t="inlineStr">
+        <is>
+          <t>Using hearing and vision for motion prediction, motion perception, and localization.</t>
+        </is>
+      </c>
+      <c r="V535" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W535" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X535" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auu.nl%20%22Surya%20Gayet%22%20email</t>
+        </is>
+      </c>
+      <c r="Z535" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5005424667</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Utrecht University</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=1156)</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>@uu.nl</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="G536" t="n">
+        <v>4</v>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>Nathan Van der Stoep</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J536" t="n">
+        <v>20</v>
+      </c>
+      <c r="K536" t="n">
+        <v>918</v>
+      </c>
+      <c r="L536" t="n">
+        <v>4</v>
+      </c>
+      <c r="M536" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N536" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O536" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q536" t="inlineStr">
+        <is>
+          <t>visual localization</t>
+        </is>
+      </c>
+      <c r="R536" t="n">
+        <v>3</v>
+      </c>
+      <c r="S536" t="n">
+        <v>32</v>
+      </c>
+      <c r="T536" t="inlineStr">
+        <is>
+          <t>2025-01-27</t>
+        </is>
+      </c>
+      <c r="U536" t="inlineStr">
+        <is>
+          <t>Using hearing and vision for motion prediction, motion perception, and localization.</t>
+        </is>
+      </c>
+      <c r="V536" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W536" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X536" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Auu.nl%20%22Nathan%20Van%20der%20Stoep%22%20email</t>
+        </is>
+      </c>
+      <c r="Z536" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5085035611</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Maastricht University</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Maastricht</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=874)</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>@maastrichtuniversity.nl</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Vacancy-based (Job Portal + Contact PI)</t>
+        </is>
+      </c>
+      <c r="J537" t="n">
+        <v>0</v>
+      </c>
+      <c r="K537" t="n">
+        <v>0</v>
+      </c>
+      <c r="L537" t="n">
+        <v>0</v>
+      </c>
+      <c r="M537" t="n">
+        <v>0</v>
+      </c>
+      <c r="N537" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O537" t="n">
+        <v>0</v>
+      </c>
+      <c r="R537" t="n">
+        <v>0</v>
+      </c>
+      <c r="S537" t="n">
+        <v>0</v>
+      </c>
+      <c r="W537" s="4" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G538" t="n">
+        <v>1</v>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>Roland Siegwart</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J538" t="n">
+        <v>127</v>
+      </c>
+      <c r="K538" t="n">
+        <v>72607</v>
+      </c>
+      <c r="L538" t="n">
+        <v>10</v>
+      </c>
+      <c r="M538" t="n">
+        <v>10</v>
+      </c>
+      <c r="N538" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O538" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q538" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, lidar inertial odometry, state estimation, multi-sensor fusion, point cloud registration, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R538" t="n">
+        <v>25</v>
+      </c>
+      <c r="S538" t="n">
+        <v>276</v>
+      </c>
+      <c r="T538" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U538" t="inlineStr">
+        <is>
+          <t>When Your State Estimator Has Lost The Plot: Detecting Estimator Failures Via Spectral Analysis</t>
+        </is>
+      </c>
+      <c r="V538" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W538" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X538" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Roland%20Siegwart%22%20email</t>
+        </is>
+      </c>
+      <c r="Z538" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5083003222</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G539" t="n">
+        <v>2</v>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>Marc Pollefeys</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J539" t="n">
+        <v>112</v>
+      </c>
+      <c r="K539" t="n">
+        <v>53189</v>
+      </c>
+      <c r="L539" t="n">
+        <v>10</v>
+      </c>
+      <c r="M539" t="n">
+        <v>10</v>
+      </c>
+      <c r="N539" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O539" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q539" t="inlineStr">
+        <is>
+          <t>visual-inertial slam, gaussian splatting, loop closure, pose estimation, 3d reconstruction, robot localization</t>
+        </is>
+      </c>
+      <c r="R539" t="n">
+        <v>54</v>
+      </c>
+      <c r="S539" t="n">
+        <v>5065</v>
+      </c>
+      <c r="T539" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U539" t="inlineStr">
+        <is>
+          <t>VIGS-SLAM: Visual Inertial Gaussian Splatting SLAM</t>
+        </is>
+      </c>
+      <c r="V539" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W539" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X539" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Marc%20Pollefeys%22%20email</t>
+        </is>
+      </c>
+      <c r="Z539" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5021908609</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G540" t="n">
+        <v>3</v>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>Marco Hutter</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J540" t="n">
+        <v>84</v>
+      </c>
+      <c r="K540" t="n">
+        <v>26496</v>
+      </c>
+      <c r="L540" t="n">
+        <v>10</v>
+      </c>
+      <c r="M540" t="n">
+        <v>10</v>
+      </c>
+      <c r="N540" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O540" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P540" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; LiDAR &amp; Multimodal Sensor Fusion; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q540" t="inlineStr">
+        <is>
+          <t>robot localization, multi-sensor fusion, sensor fusion, state estimation, place recognition, pose estimation</t>
+        </is>
+      </c>
+      <c r="R540" t="n">
+        <v>18</v>
+      </c>
+      <c r="S540" t="n">
+        <v>453</v>
+      </c>
+      <c r="T540" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="U540" t="inlineStr">
+        <is>
+          <t>TRaIL-Odom: Tightly Coupled Continuous Time Radar-IMU-LiDAR Odometry With Adaptive Doppler Weighting</t>
+        </is>
+      </c>
+      <c r="V540" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W540" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X540" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Marco%20Hutter%22%20email</t>
+        </is>
+      </c>
+      <c r="Z540" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5044258783</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G541" t="n">
+        <v>4</v>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>Margarita Chli</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J541" t="n">
+        <v>40</v>
+      </c>
+      <c r="K541" t="n">
+        <v>10127</v>
+      </c>
+      <c r="L541" t="n">
+        <v>10</v>
+      </c>
+      <c r="M541" t="n">
+        <v>10</v>
+      </c>
+      <c r="N541" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O541" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q541" t="inlineStr">
+        <is>
+          <t>lidar inertial odometry, sensor fusion, mobile robot navigation, loop closure, lidar slam, place recognition</t>
+        </is>
+      </c>
+      <c r="R541" t="n">
+        <v>4</v>
+      </c>
+      <c r="S541" t="n">
+        <v>44</v>
+      </c>
+      <c r="T541" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="U541" t="inlineStr">
+        <is>
+          <t>EllipseLIO: Adaptive LiDAR Inertial Odometry With an Ellipsoid Representation</t>
+        </is>
+      </c>
+      <c r="V541" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W541" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X541" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Margarita%20Chli%22%20email</t>
+        </is>
+      </c>
+      <c r="Z541" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5055582765</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G542" t="n">
+        <v>5</v>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>Stefan Leutenegger</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J542" t="n">
+        <v>40</v>
+      </c>
+      <c r="K542" t="n">
+        <v>17942</v>
+      </c>
+      <c r="L542" t="n">
+        <v>10</v>
+      </c>
+      <c r="M542" t="n">
+        <v>10</v>
+      </c>
+      <c r="N542" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O542" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P542" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q542" t="inlineStr">
+        <is>
+          <t>visual-inertial slam, visual odometry, state estimation, multi-sensor fusion, autonomous navigation, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R542" t="n">
+        <v>3</v>
+      </c>
+      <c r="S542" t="n">
+        <v>85</v>
+      </c>
+      <c r="T542" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="U542" t="inlineStr">
+        <is>
+          <t>AERO-VIS: Asynchronous Event-Based Real-Time Onboard Visual-Inertial SLAM</t>
+        </is>
+      </c>
+      <c r="V542" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W542" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X542" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Stefan%20Leutenegger%22%20email</t>
+        </is>
+      </c>
+      <c r="Z542" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5006726091</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G543" t="n">
+        <v>6</v>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>Dániel Baráth</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J543" t="n">
+        <v>24</v>
+      </c>
+      <c r="K543" t="n">
+        <v>2925</v>
+      </c>
+      <c r="L543" t="n">
+        <v>10</v>
+      </c>
+      <c r="M543" t="n">
+        <v>10</v>
+      </c>
+      <c r="N543" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O543" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q543" t="inlineStr">
+        <is>
+          <t>visual-inertial slam, gaussian splatting, loop closure, pose estimation, 3d reconstruction, visual localization</t>
+        </is>
+      </c>
+      <c r="R543" t="n">
+        <v>9</v>
+      </c>
+      <c r="S543" t="n">
+        <v>102</v>
+      </c>
+      <c r="T543" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="U543" t="inlineStr">
+        <is>
+          <t>VIGS-SLAM: Visual Inertial Gaussian Splatting SLAM</t>
+        </is>
+      </c>
+      <c r="V543" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W543" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X543" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22D%C3%A1niel%20Bar%C3%A1th%22%20email</t>
+        </is>
+      </c>
+      <c r="Z543" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5016636021</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G544" t="n">
+        <v>7</v>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>Michael Pantic</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J544" t="n">
+        <v>12</v>
+      </c>
+      <c r="K544" t="n">
+        <v>1004</v>
+      </c>
+      <c r="L544" t="n">
+        <v>10</v>
+      </c>
+      <c r="M544" t="n">
+        <v>10</v>
+      </c>
+      <c r="N544" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O544" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Deep Learning for Navigation &amp; Perception; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q544" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, lidar inertial odometry, state estimation, multi-sensor fusion, sensor fusion, field robotics</t>
+        </is>
+      </c>
+      <c r="R544" t="n">
+        <v>6</v>
+      </c>
+      <c r="S544" t="n">
+        <v>41</v>
+      </c>
+      <c r="T544" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U544" t="inlineStr">
+        <is>
+          <t>When Your State Estimator Has Lost The Plot: Detecting Estimator Failures Via Spectral Analysis</t>
+        </is>
+      </c>
+      <c r="V544" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W544" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X544" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Michael%20Pantic%22%20email</t>
+        </is>
+      </c>
+      <c r="Z544" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5032693392</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G545" t="n">
+        <v>8</v>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>César Cadena</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J545" t="n">
+        <v>44</v>
+      </c>
+      <c r="K545" t="n">
+        <v>14195</v>
+      </c>
+      <c r="L545" t="n">
+        <v>10</v>
+      </c>
+      <c r="M545" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N545" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O545" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q545" t="inlineStr">
+        <is>
+          <t>robot localization, state estimation, sensor fusion, lidar inertial odometry, multi-sensor fusion, point cloud registration</t>
+        </is>
+      </c>
+      <c r="R545" t="n">
+        <v>16</v>
+      </c>
+      <c r="S545" t="n">
+        <v>130</v>
+      </c>
+      <c r="T545" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="U545" t="inlineStr">
+        <is>
+          <t>Holistic Fusion: Task- and Setup-Agnostic Robot Localization and State Estimation With Factor Graphs</t>
+        </is>
+      </c>
+      <c r="V545" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W545" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X545" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22C%C3%A9sar%20Cadena%22%20email</t>
+        </is>
+      </c>
+      <c r="Z545" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5063529163</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G546" t="n">
+        <v>9</v>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>Zihan Zhu</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J546" t="n">
+        <v>23</v>
+      </c>
+      <c r="K546" t="n">
+        <v>2671</v>
+      </c>
+      <c r="L546" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="M546" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N546" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O546" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="P546" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q546" t="inlineStr">
+        <is>
+          <t>visual-inertial slam, gaussian splatting, loop closure, pose estimation, 3d reconstruction, visual slam</t>
+        </is>
+      </c>
+      <c r="R546" t="n">
+        <v>2</v>
+      </c>
+      <c r="S546" t="n">
+        <v>68</v>
+      </c>
+      <c r="T546" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U546" t="inlineStr">
+        <is>
+          <t>VIGS-SLAM: Visual Inertial Gaussian Splatting SLAM</t>
+        </is>
+      </c>
+      <c r="V546" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W546" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X546" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Zihan%20Zhu%22%20email</t>
+        </is>
+      </c>
+      <c r="Z546" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5103244203</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G547" t="n">
+        <v>10</v>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>Helen Oleynikova</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J547" t="n">
+        <v>22</v>
+      </c>
+      <c r="K547" t="n">
+        <v>3418</v>
+      </c>
+      <c r="L547" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="M547" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N547" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O547" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P547" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Deep Learning for Navigation &amp; Perception; Embedded AI &amp; Real-Time Edge Robotics</t>
+        </is>
+      </c>
+      <c r="Q547" t="inlineStr">
+        <is>
+          <t>lidar inertial odometry, multi-sensor fusion, point cloud registration, sensor fusion, extended kalman filter, kalman filter</t>
+        </is>
+      </c>
+      <c r="R547" t="n">
+        <v>5</v>
+      </c>
+      <c r="S547" t="n">
+        <v>26</v>
+      </c>
+      <c r="T547" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="U547" t="inlineStr">
+        <is>
+          <t>COIN-LIO: Complementary Intensity-Augmented LiDAR Inertial Odometry</t>
+        </is>
+      </c>
+      <c r="V547" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W547" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X547" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Helen%20Oleynikova%22%20email</t>
+        </is>
+      </c>
+      <c r="Z547" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5050090757</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G548" t="n">
+        <v>11</v>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>Benedikt S. Soja</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J548" t="n">
+        <v>22</v>
+      </c>
+      <c r="K548" t="n">
+        <v>1831</v>
+      </c>
+      <c r="L548" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="M548" t="n">
+        <v>10</v>
+      </c>
+      <c r="N548" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O548" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="P548" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q548" t="inlineStr">
+        <is>
+          <t>factor graph optimization, visual odometry, gnss positioning, visual inertial odometry, extended kalman filter, kalman filter</t>
+        </is>
+      </c>
+      <c r="R548" t="n">
+        <v>19</v>
+      </c>
+      <c r="S548" t="n">
+        <v>356</v>
+      </c>
+      <c r="T548" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="U548" t="inlineStr">
+        <is>
+          <t>Smartphone-based Vision/MEMS-IMU/GNSS tightly coupled seamless positioning using factor graph optimization</t>
+        </is>
+      </c>
+      <c r="V548" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W548" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X548" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Benedikt%20S.%20Soja%22%20email</t>
+        </is>
+      </c>
+      <c r="Z548" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5046082471</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G549" t="n">
+        <v>12</v>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>Boyang Sun</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J549" t="n">
+        <v>19</v>
+      </c>
+      <c r="K549" t="n">
+        <v>1193</v>
+      </c>
+      <c r="L549" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="M549" t="n">
+        <v>10</v>
+      </c>
+      <c r="N549" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O549" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="P549" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q549" t="inlineStr">
+        <is>
+          <t>loop closure, visual slam, trajectory estimation, mobile robot navigation, 3d reconstruction, visual localization</t>
+        </is>
+      </c>
+      <c r="R549" t="n">
+        <v>5</v>
+      </c>
+      <c r="S549" t="n">
+        <v>46</v>
+      </c>
+      <c r="T549" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U549" t="inlineStr">
+        <is>
+          <t>Loop Closure From Two Views: Revisiting PGO for Scalable Trajectory Estimation Through Monocular Priors</t>
+        </is>
+      </c>
+      <c r="V549" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W549" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X549" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Boyang%20Sun%22%20email</t>
+        </is>
+      </c>
+      <c r="Z549" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5101951314</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G550" t="n">
+        <v>13</v>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>Luca Benini C</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J550" t="n">
+        <v>112</v>
+      </c>
+      <c r="K550" t="n">
+        <v>62308</v>
+      </c>
+      <c r="L550" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="M550" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N550" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O550" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="P550" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q550" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, hardware acceleration, embedded systems, gnss positioning, sensor fusion, computer vision</t>
+        </is>
+      </c>
+      <c r="R550" t="n">
+        <v>5</v>
+      </c>
+      <c r="S550" t="n">
+        <v>665</v>
+      </c>
+      <c r="T550" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="U550" t="inlineStr">
+        <is>
+          <t>Low Latency Visual Inertial Odometry With On-Sensor Accelerated Optical Flow for Resource-Constrained UAVs</t>
+        </is>
+      </c>
+      <c r="V550" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W550" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X550" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Luca%20Benini%20C%22%20email</t>
+        </is>
+      </c>
+      <c r="Z550" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5003234972</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G551" t="n">
+        <v>14</v>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>Lionel Ott</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J551" t="n">
+        <v>23</v>
+      </c>
+      <c r="K551" t="n">
+        <v>6323</v>
+      </c>
+      <c r="L551" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="M551" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N551" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O551" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Deep Learning for Navigation &amp; Perception; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q551" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, sensor fusion, state estimation, robot localization, pose estimation, 3d computer vision</t>
+        </is>
+      </c>
+      <c r="R551" t="n">
+        <v>14</v>
+      </c>
+      <c r="S551" t="n">
+        <v>70</v>
+      </c>
+      <c r="T551" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="U551" t="inlineStr">
+        <is>
+          <t>To Fuse or Not to Fuse: Measuring Consistency in Multi-sensor Fusion for Aerial Robots</t>
+        </is>
+      </c>
+      <c r="V551" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W551" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X551" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Lionel%20Ott%22%20email</t>
+        </is>
+      </c>
+      <c r="Z551" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5033725695</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G552" t="n">
+        <v>15</v>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>Daniele Palossi</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J552" t="n">
+        <v>17</v>
+      </c>
+      <c r="K552" t="n">
+        <v>999</v>
+      </c>
+      <c r="L552" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="M552" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N552" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O552" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="P552" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q552" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, sensor fusion, pose estimation, deep learning, visual odometry</t>
+        </is>
+      </c>
+      <c r="R552" t="n">
+        <v>2</v>
+      </c>
+      <c r="S552" t="n">
+        <v>86</v>
+      </c>
+      <c r="T552" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="U552" t="inlineStr">
+        <is>
+          <t>Fusing Multi-sensor Input with State Information on TinyML Brains for Autonomous Nano-drones</t>
+        </is>
+      </c>
+      <c r="V552" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W552" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X552" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Daniele%20Palossi%22%20email</t>
+        </is>
+      </c>
+      <c r="Z552" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5061890705</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G553" t="n">
+        <v>16</v>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>Michele Magno</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J553" t="n">
+        <v>48</v>
+      </c>
+      <c r="K553" t="n">
+        <v>8685</v>
+      </c>
+      <c r="L553" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="M553" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N553" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O553" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; GNSS &amp; Robust Localization; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q553" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, hardware acceleration, embedded systems, gnss positioning, sensor fusion, computer vision</t>
+        </is>
+      </c>
+      <c r="R553" t="n">
+        <v>6</v>
+      </c>
+      <c r="S553" t="n">
+        <v>369</v>
+      </c>
+      <c r="T553" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="U553" t="inlineStr">
+        <is>
+          <t>Low Latency Visual Inertial Odometry With On-Sensor Accelerated Optical Flow for Resource-Constrained UAVs</t>
+        </is>
+      </c>
+      <c r="V553" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W553" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X553" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Michele%20Magno%22%20email</t>
+        </is>
+      </c>
+      <c r="Z553" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5066423975</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G554" t="n">
+        <v>17</v>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>Danda Pani Paudel</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J554" t="n">
+        <v>28</v>
+      </c>
+      <c r="K554" t="n">
+        <v>3303</v>
+      </c>
+      <c r="L554" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="M554" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N554" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O554" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="P554" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q554" t="inlineStr">
+        <is>
+          <t>visual odometry, pose estimation, stereo vision, ros, visual localization</t>
+        </is>
+      </c>
+      <c r="R554" t="n">
+        <v>3</v>
+      </c>
+      <c r="S554" t="n">
+        <v>198</v>
+      </c>
+      <c r="T554" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="U554" t="inlineStr">
+        <is>
+          <t>Stereo Orientation Prior for UAV Robust and Accurate Visual Odometry</t>
+        </is>
+      </c>
+      <c r="V554" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W554" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X554" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Danda%20Pani%20Paudel%22%20email</t>
+        </is>
+      </c>
+      <c r="Z554" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5050696776</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G555" t="n">
+        <v>18</v>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>Andreas M. Kunz</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J555" t="n">
+        <v>27</v>
+      </c>
+      <c r="K555" t="n">
+        <v>3152</v>
+      </c>
+      <c r="L555" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="M555" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N555" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O555" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="P555" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q555" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, place recognition</t>
+        </is>
+      </c>
+      <c r="R555" t="n">
+        <v>1</v>
+      </c>
+      <c r="S555" t="n">
+        <v>57</v>
+      </c>
+      <c r="T555" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="U555" t="inlineStr">
+        <is>
+          <t>DVIO - Distributed Visual-Inertial Odometry in a Multi-user Environment</t>
+        </is>
+      </c>
+      <c r="V555" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W555" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X555" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Andreas%20M.%20Kunz%22%20email</t>
+        </is>
+      </c>
+      <c r="Z555" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5006637184</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G556" t="n">
+        <v>19</v>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>Ming Li</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J556" t="n">
+        <v>15</v>
+      </c>
+      <c r="K556" t="n">
+        <v>598</v>
+      </c>
+      <c r="L556" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="M556" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N556" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O556" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="P556" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q556" t="inlineStr">
+        <is>
+          <t>visual localization, autonomous navigation, deep learning</t>
+        </is>
+      </c>
+      <c r="R556" t="n">
+        <v>3</v>
+      </c>
+      <c r="S556" t="n">
+        <v>36</v>
+      </c>
+      <c r="T556" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U556" t="inlineStr">
+        <is>
+          <t>Localization Based on End-to-End Learning Methods</t>
+        </is>
+      </c>
+      <c r="V556" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W556" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X556" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Ming%20Li%22%20email</t>
+        </is>
+      </c>
+      <c r="Z556" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100351375</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G557" t="n">
+        <v>20</v>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>Giacomo Indiveri</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J557" t="n">
+        <v>62</v>
+      </c>
+      <c r="K557" t="n">
+        <v>19589</v>
+      </c>
+      <c r="L557" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="M557" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N557" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O557" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="P557" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q557" t="inlineStr">
+        <is>
+          <t>visual odometry, robot localization, robot perception</t>
+        </is>
+      </c>
+      <c r="R557" t="n">
+        <v>2</v>
+      </c>
+      <c r="S557" t="n">
+        <v>311</v>
+      </c>
+      <c r="T557" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="U557" t="inlineStr">
+        <is>
+          <t>Visual odometry with neuromorphic resonator networks</t>
+        </is>
+      </c>
+      <c r="V557" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W557" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X557" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Giacomo%20Indiveri%22%20email</t>
+        </is>
+      </c>
+      <c r="Z557" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5060241952</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G558" t="n">
+        <v>21</v>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>Othmar Frey</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J558" t="n">
+        <v>19</v>
+      </c>
+      <c r="K558" t="n">
+        <v>1772</v>
+      </c>
+      <c r="L558" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="M558" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N558" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O558" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q558" t="inlineStr">
+        <is>
+          <t>gnss ins integration, gnss positioning, inertial navigation</t>
+        </is>
+      </c>
+      <c r="R558" t="n">
+        <v>1</v>
+      </c>
+      <c r="S558" t="n">
+        <v>55</v>
+      </c>
+      <c r="T558" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="U558" t="inlineStr">
+        <is>
+          <t>Assessing the Impact of Positioning Errors in Car-Borne Repeat-Pass SAR Interferometry With a Controlled Rail-Based Experiment</t>
+        </is>
+      </c>
+      <c r="V558" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W558" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X558" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Othmar%20Frey%22%20email</t>
+        </is>
+      </c>
+      <c r="Z558" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5062774484</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G559" t="n">
+        <v>22</v>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>Konrad Schindler</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J559" t="n">
+        <v>79</v>
+      </c>
+      <c r="K559" t="n">
+        <v>31671</v>
+      </c>
+      <c r="L559" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="M559" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N559" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O559" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; GNSS &amp; Robust Localization; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q559" t="inlineStr">
+        <is>
+          <t>loop closure, point cloud registration, gaussian splatting, 3d reconstruction, sensor fusion, depth estimation</t>
+        </is>
+      </c>
+      <c r="R559" t="n">
+        <v>8</v>
+      </c>
+      <c r="S559" t="n">
+        <v>359</v>
+      </c>
+      <c r="T559" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="U559" t="inlineStr">
+        <is>
+          <t>LoopSplat: Loop Closure by Registering 3D Gaussian Splats</t>
+        </is>
+      </c>
+      <c r="V559" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W559" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X559" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Konrad%20Schindler%22%20email</t>
+        </is>
+      </c>
+      <c r="Z559" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5005404030</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G560" t="n">
+        <v>23</v>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>Siyu Tang</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J560" t="n">
+        <v>42</v>
+      </c>
+      <c r="K560" t="n">
+        <v>7979</v>
+      </c>
+      <c r="L560" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="M560" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N560" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O560" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="P560" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q560" t="inlineStr">
+        <is>
+          <t>gaussian splatting, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R560" t="n">
+        <v>3</v>
+      </c>
+      <c r="S560" t="n">
+        <v>122</v>
+      </c>
+      <c r="T560" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="U560" t="inlineStr">
+        <is>
+          <t>DeGauss: Dynamic-Static Decomposition with Gaussian Splatting for Distractor-Free 3D Reconstruction</t>
+        </is>
+      </c>
+      <c r="V560" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W560" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X560" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Siyu%20Tang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z560" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5056265728</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G561" t="n">
+        <v>24</v>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>Luc Van Gool</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J561" t="n">
+        <v>189</v>
+      </c>
+      <c r="K561" t="n">
+        <v>200483</v>
+      </c>
+      <c r="L561" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="M561" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N561" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O561" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="P561" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q561" t="inlineStr">
+        <is>
+          <t>visual odometry, depth estimation, 3d perception, visual slam, point cloud registration, object detection</t>
+        </is>
+      </c>
+      <c r="R561" t="n">
+        <v>8</v>
+      </c>
+      <c r="S561" t="n">
+        <v>631</v>
+      </c>
+      <c r="T561" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="U561" t="inlineStr">
+        <is>
+          <t>Replay-Based Online Adaptation for Unsupervised Deep Visual Odometry</t>
+        </is>
+      </c>
+      <c r="V561" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W561" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X561" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Luc%20Van%20Gool%22%20email</t>
+        </is>
+      </c>
+      <c r="Z561" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5001254143</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G562" t="n">
+        <v>25</v>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>Markus Rothacher</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J562" t="n">
+        <v>51</v>
+      </c>
+      <c r="K562" t="n">
+        <v>9624</v>
+      </c>
+      <c r="L562" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="M562" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N562" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O562" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="P562" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q562" t="inlineStr">
+        <is>
+          <t>gnss positioning, extended kalman filter, kalman filter, sensor fusion</t>
+        </is>
+      </c>
+      <c r="R562" t="n">
+        <v>7</v>
+      </c>
+      <c r="S562" t="n">
+        <v>100</v>
+      </c>
+      <c r="T562" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="U562" t="inlineStr">
+        <is>
+          <t>A Cloud-native Approach for Processing of Crowdsourced GNSS Observations and Machine Learning at Scale: A Case Study from the CAMALIOT Project</t>
+        </is>
+      </c>
+      <c r="V562" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W562" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X562" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Markus%20Rothacher%22%20email</t>
+        </is>
+      </c>
+      <c r="Z562" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5004202455</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G563" t="n">
+        <v>26</v>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>Laura Crocetti</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J563" t="n">
+        <v>10</v>
+      </c>
+      <c r="K563" t="n">
+        <v>374</v>
+      </c>
+      <c r="L563" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="M563" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N563" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O563" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="P563" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q563" t="inlineStr">
+        <is>
+          <t>gnss positioning, extended kalman filter, kalman filter</t>
+        </is>
+      </c>
+      <c r="R563" t="n">
+        <v>4</v>
+      </c>
+      <c r="S563" t="n">
+        <v>71</v>
+      </c>
+      <c r="T563" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="U563" t="inlineStr">
+        <is>
+          <t>A Cloud-native Approach for Processing of Crowdsourced GNSS Observations and Machine Learning at Scale: A Case Study from the CAMALIOT Project</t>
+        </is>
+      </c>
+      <c r="V563" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W563" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X563" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Laura%20Crocetti%22%20email</t>
+        </is>
+      </c>
+      <c r="Z563" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5018722846</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>ETH Zürich</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>QS #7 | Tier S+ (Global Elite | h=1285)</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>@ethz.ch</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G564" t="n">
+        <v>27</v>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>Andreas Wieser</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J564" t="n">
+        <v>22</v>
+      </c>
+      <c r="K564" t="n">
+        <v>3316</v>
+      </c>
+      <c r="L564" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="M564" t="n">
+        <v>10</v>
+      </c>
+      <c r="N564" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O564" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q564" t="inlineStr">
+        <is>
+          <t>point cloud registration, deep learning, sensor fusion, depth estimation</t>
+        </is>
+      </c>
+      <c r="R564" t="n">
+        <v>5</v>
+      </c>
+      <c r="S564" t="n">
+        <v>112</v>
+      </c>
+      <c r="T564" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="U564" t="inlineStr">
+        <is>
+          <t>Cross-modal feature fusion for robust point cloud registration with ambiguous geometry</t>
+        </is>
+      </c>
+      <c r="V564" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W564" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X564" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aethz.ch%20%22Andreas%20Wieser%22%20email</t>
+        </is>
+      </c>
+      <c r="Z564" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5034901004</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>QS #26 | Tier S+ (Global Elite | h=1194)</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>@epfl.ch</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G565" t="n">
+        <v>1</v>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>Jan Škaloud</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J565" t="n">
+        <v>28</v>
+      </c>
+      <c r="K565" t="n">
+        <v>2875</v>
+      </c>
+      <c r="L565" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="M565" t="n">
+        <v>10</v>
+      </c>
+      <c r="N565" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O565" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="P565" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; State Estimation &amp; Factor Graphs; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q565" t="inlineStr">
+        <is>
+          <t>sensor fusion, factor graph optimization, gnss ins integration, lidar camera fusion, multi-sensor fusion, inertial navigation</t>
+        </is>
+      </c>
+      <c r="R565" t="n">
+        <v>12</v>
+      </c>
+      <c r="S565" t="n">
+        <v>51</v>
+      </c>
+      <c r="T565" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="U565" t="inlineStr">
+        <is>
+          <t>Extraction of Image-to-Lidar Correspondences and their Impact on Optimal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="V565" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W565" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X565" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aepfl.ch%20%22Jan%20%C5%A0kaloud%22%20email</t>
+        </is>
+      </c>
+      <c r="Z565" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5033612355</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>QS #26 | Tier S+ (Global Elite | h=1194)</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>@epfl.ch</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G566" t="n">
+        <v>2</v>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>Mathieu Salzmann</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J566" t="n">
+        <v>65</v>
+      </c>
+      <c r="K566" t="n">
+        <v>16116</v>
+      </c>
+      <c r="L566" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="M566" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N566" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O566" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="P566" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; State Estimation &amp; Factor Graphs; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q566" t="inlineStr">
+        <is>
+          <t>point cloud registration, pose estimation, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R566" t="n">
+        <v>18</v>
+      </c>
+      <c r="S566" t="n">
+        <v>190</v>
+      </c>
+      <c r="T566" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="U566" t="inlineStr">
+        <is>
+          <t>Learning-Based Point Cloud Registration for 6D Object Pose Estimation in the Real World</t>
+        </is>
+      </c>
+      <c r="V566" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W566" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X566" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aepfl.ch%20%22Mathieu%20Salzmann%22%20email</t>
+        </is>
+      </c>
+      <c r="Z566" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5049300388</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>QS #26 | Tier S+ (Global Elite | h=1194)</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>@epfl.ch</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G567" t="n">
+        <v>3</v>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>Alcherio Martinoli</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J567" t="n">
+        <v>47</v>
+      </c>
+      <c r="K567" t="n">
+        <v>9552</v>
+      </c>
+      <c r="L567" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="M567" t="n">
+        <v>10</v>
+      </c>
+      <c r="N567" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O567" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="P567" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q567" t="inlineStr">
+        <is>
+          <t>robust localization, state estimation, sensor calibration</t>
+        </is>
+      </c>
+      <c r="R567" t="n">
+        <v>5</v>
+      </c>
+      <c r="S567" t="n">
+        <v>34</v>
+      </c>
+      <c r="T567" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U567" t="inlineStr">
+        <is>
+          <t>Robust Localization for Multi-robot Formations: An Experimental Evaluation of an Extended GM-PHD Filter</t>
+        </is>
+      </c>
+      <c r="V567" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W567" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X567" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aepfl.ch%20%22Alcherio%20Martinoli%22%20email</t>
+        </is>
+      </c>
+      <c r="Z567" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5080713076</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>QS #26 | Tier S+ (Global Elite | h=1194)</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>@epfl.ch</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G568" t="n">
+        <v>4</v>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>Olga Fink</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J568" t="n">
+        <v>36</v>
+      </c>
+      <c r="K568" t="n">
+        <v>6691</v>
+      </c>
+      <c r="L568" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="M568" t="n">
+        <v>10</v>
+      </c>
+      <c r="N568" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O568" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="P568" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q568" t="inlineStr">
+        <is>
+          <t>3d reconstruction, pose estimation, gaussian splatting</t>
+        </is>
+      </c>
+      <c r="R568" t="n">
+        <v>3</v>
+      </c>
+      <c r="S568" t="n">
+        <v>234</v>
+      </c>
+      <c r="T568" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="U568" t="inlineStr">
+        <is>
+          <t>SEAR: Simple and Efficient Adaptation of Visual Geometric Transformers for Unpaired RGB-Thermal 3D Reconstruction</t>
+        </is>
+      </c>
+      <c r="V568" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W568" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X568" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aepfl.ch%20%22Olga%20Fink%22%20email</t>
+        </is>
+      </c>
+      <c r="Z568" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5079637160</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>QS #26 | Tier S+ (Global Elite | h=1194)</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>@epfl.ch</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G569" t="n">
+        <v>5</v>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>Alexandre Alahi</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J569" t="n">
+        <v>47</v>
+      </c>
+      <c r="K569" t="n">
+        <v>29040</v>
+      </c>
+      <c r="L569" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="M569" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N569" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O569" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="P569" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; 3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q569" t="inlineStr">
+        <is>
+          <t>point cloud registration, pose estimation, depth estimation, ros, jetson</t>
+        </is>
+      </c>
+      <c r="R569" t="n">
+        <v>4</v>
+      </c>
+      <c r="S569" t="n">
+        <v>185</v>
+      </c>
+      <c r="T569" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="U569" t="inlineStr">
+        <is>
+          <t>Real-Time Localization for Closed-Loop Control of Assistive Furniture</t>
+        </is>
+      </c>
+      <c r="V569" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W569" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X569" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aepfl.ch%20%22Alexandre%20Alahi%22%20email</t>
+        </is>
+      </c>
+      <c r="Z569" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5068504559</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>QS #26 | Tier S+ (Global Elite | h=1194)</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>@epfl.ch</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G570" t="n">
+        <v>6</v>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>Shaojie Shen</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J570" t="n">
+        <v>64</v>
+      </c>
+      <c r="K570" t="n">
+        <v>19329</v>
+      </c>
+      <c r="L570" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="M570" t="n">
+        <v>10</v>
+      </c>
+      <c r="N570" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O570" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="P570" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q570" t="inlineStr">
+        <is>
+          <t>autonomous navigation, depth estimation, ros</t>
+        </is>
+      </c>
+      <c r="R570" t="n">
+        <v>1</v>
+      </c>
+      <c r="S570" t="n">
+        <v>147</v>
+      </c>
+      <c r="T570" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="U570" t="inlineStr">
+        <is>
+          <t>SwarmNxt: Open-source Software-Hardware Platform for Fast and Agile Aerial Swarms</t>
+        </is>
+      </c>
+      <c r="V570" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W570" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X570" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aepfl.ch%20%22Shaojie%20Shen%22%20email</t>
+        </is>
+      </c>
+      <c r="Z570" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5001947944</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>QS #26 | Tier S+ (Global Elite | h=1194)</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>@epfl.ch</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G571" t="n">
+        <v>7</v>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>Auke Jan Ijspeert</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J571" t="n">
+        <v>76</v>
+      </c>
+      <c r="K571" t="n">
+        <v>25428</v>
+      </c>
+      <c r="L571" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="M571" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N571" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O571" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="P571" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q571" t="inlineStr">
+        <is>
+          <t>point cloud registration, pose estimation, field robotics</t>
+        </is>
+      </c>
+      <c r="R571" t="n">
+        <v>2</v>
+      </c>
+      <c r="S571" t="n">
+        <v>133</v>
+      </c>
+      <c r="T571" t="inlineStr">
+        <is>
+          <t>2023-12-06</t>
+        </is>
+      </c>
+      <c r="U571" t="inlineStr">
+        <is>
+          <t>Real-Time Localization for Closed-Loop Control of Assistive Furniture</t>
+        </is>
+      </c>
+      <c r="V571" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W571" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X571" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aepfl.ch%20%22Auke%20Jan%20Ijspeert%22%20email</t>
+        </is>
+      </c>
+      <c r="Z571" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5069603317</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>QS #26 | Tier S+ (Global Elite | h=1194)</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>@epfl.ch</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G572" t="n">
+        <v>8</v>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>Brigitte M. Jolles</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J572" t="n">
+        <v>37</v>
+      </c>
+      <c r="K572" t="n">
+        <v>4989</v>
+      </c>
+      <c r="L572" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="M572" t="n">
+        <v>10</v>
+      </c>
+      <c r="N572" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O572" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="P572" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q572" t="inlineStr">
+        <is>
+          <t>visual inertial odometry, pose estimation</t>
+        </is>
+      </c>
+      <c r="R572" t="n">
+        <v>1</v>
+      </c>
+      <c r="S572" t="n">
+        <v>50</v>
+      </c>
+      <c r="T572" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="U572" t="inlineStr">
+        <is>
+          <t>Spatiotemporal gait analysis using video from a moving observer</t>
+        </is>
+      </c>
+      <c r="V572" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W572" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X572" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aepfl.ch%20%22Brigitte%20M.%20Jolles%22%20email</t>
+        </is>
+      </c>
+      <c r="Z572" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5061492442</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>QS #26 | Tier S+ (Global Elite | h=1194)</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>@epfl.ch</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G573" t="n">
+        <v>9</v>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>Dario Floreano</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J573" t="n">
+        <v>85</v>
+      </c>
+      <c r="K573" t="n">
+        <v>30990</v>
+      </c>
+      <c r="L573" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="M573" t="n">
+        <v>10</v>
+      </c>
+      <c r="N573" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O573" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q573" t="inlineStr">
+        <is>
+          <t>autonomous navigation, depth estimation, ros</t>
+        </is>
+      </c>
+      <c r="R573" t="n">
+        <v>2</v>
+      </c>
+      <c r="S573" t="n">
+        <v>104</v>
+      </c>
+      <c r="T573" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="U573" t="inlineStr">
+        <is>
+          <t>SwarmNxt: Open-source Software-Hardware Platform for Fast and Agile Aerial Swarms</t>
+        </is>
+      </c>
+      <c r="V573" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W573" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X573" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aepfl.ch%20%22Dario%20Floreano%22%20email</t>
+        </is>
+      </c>
+      <c r="Z573" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5059369445</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>QS #26 | Tier S+ (Global Elite | h=1194)</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>@epfl.ch</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G574" t="n">
+        <v>10</v>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>Jean‐Yves Le Boudec</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J574" t="n">
+        <v>70</v>
+      </c>
+      <c r="K574" t="n">
+        <v>24967</v>
+      </c>
+      <c r="L574" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="M574" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N574" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O574" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q574" t="inlineStr">
+        <is>
+          <t>state estimation, kalman filter</t>
+        </is>
+      </c>
+      <c r="R574" t="n">
+        <v>1</v>
+      </c>
+      <c r="S574" t="n">
+        <v>36</v>
+      </c>
+      <c r="T574" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="U574" t="inlineStr">
+        <is>
+          <t>Static and recursive PMU-based state estimation processes for transmission and distribution power grids</t>
+        </is>
+      </c>
+      <c r="V574" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W574" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X574" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aepfl.ch%20%22Jean%E2%80%90Yves%20Le%20Boudec%22%20email</t>
+        </is>
+      </c>
+      <c r="Z574" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5041322972</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>QS #26 | Tier S+ (Global Elite | h=1194)</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>@epfl.ch</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G575" t="n">
+        <v>11</v>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>Mario Paolone</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J575" t="n">
+        <v>62</v>
+      </c>
+      <c r="K575" t="n">
+        <v>15738</v>
+      </c>
+      <c r="L575" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="M575" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N575" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O575" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q575" t="inlineStr">
+        <is>
+          <t>state estimation, kalman filter</t>
+        </is>
+      </c>
+      <c r="R575" t="n">
+        <v>1</v>
+      </c>
+      <c r="S575" t="n">
+        <v>175</v>
+      </c>
+      <c r="T575" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="U575" t="inlineStr">
+        <is>
+          <t>Static and recursive PMU-based state estimation processes for transmission and distribution power grids</t>
+        </is>
+      </c>
+      <c r="V575" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W575" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X575" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aepfl.ch%20%22Mario%20Paolone%22%20email</t>
+        </is>
+      </c>
+      <c r="Z575" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5050504092</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>QS #26 | Tier S+ (Global Elite | h=1194)</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>@epfl.ch</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G576" t="n">
+        <v>12</v>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>Amir Zamir</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J576" t="n">
+        <v>32</v>
+      </c>
+      <c r="K576" t="n">
+        <v>15492</v>
+      </c>
+      <c r="L576" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="M576" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N576" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O576" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q576" t="inlineStr">
+        <is>
+          <t>visual odometry</t>
+        </is>
+      </c>
+      <c r="R576" t="n">
+        <v>1</v>
+      </c>
+      <c r="S576" t="n">
+        <v>36</v>
+      </c>
+      <c r="T576" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="U576" t="inlineStr">
+        <is>
+          <t>Modality-invariant Visual Odometry for Embodied Vision</t>
+        </is>
+      </c>
+      <c r="V576" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W576" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X576" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aepfl.ch%20%22Amir%20Zamir%22%20email</t>
+        </is>
+      </c>
+      <c r="Z576" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5023178110</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>QS #26 | Tier S+ (Global Elite | h=1194)</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>@epfl.ch</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G577" t="n">
+        <v>13</v>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>Yves Weinand</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J577" t="n">
+        <v>21</v>
+      </c>
+      <c r="K577" t="n">
+        <v>1403</v>
+      </c>
+      <c r="L577" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="M577" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N577" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O577" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; State Estimation &amp; Factor Graphs; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q577" t="inlineStr">
+        <is>
+          <t>pose estimation, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R577" t="n">
+        <v>3</v>
+      </c>
+      <c r="S577" t="n">
+        <v>49</v>
+      </c>
+      <c r="T577" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="U577" t="inlineStr">
+        <is>
+          <t>TSLAM: a tag-based object-centered monocular navigation system for augmented manual woodworking</t>
+        </is>
+      </c>
+      <c r="V577" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W577" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X577" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aepfl.ch%20%22Yves%20Weinand%22%20email</t>
+        </is>
+      </c>
+      <c r="Z577" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5034853783</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>QS #26 | Tier S+ (Global Elite | h=1194)</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>@epfl.ch</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G578" t="n">
+        <v>14</v>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>Pascal Frossard B</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J578" t="n">
+        <v>61</v>
+      </c>
+      <c r="K578" t="n">
+        <v>29028</v>
+      </c>
+      <c r="L578" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="M578" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N578" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O578" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q578" t="inlineStr">
+        <is>
+          <t>3d perception, autonomous driving perception, 3d object detection, object detection</t>
+        </is>
+      </c>
+      <c r="R578" t="n">
+        <v>1</v>
+      </c>
+      <c r="S578" t="n">
+        <v>188</v>
+      </c>
+      <c r="T578" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="U578" t="inlineStr">
+        <is>
+          <t>IS-Fusion: Instance-Scene Collaborative Fusion for Multimodal 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="V578" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W578" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X578" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aepfl.ch%20%22Pascal%20Frossard%20B%22%20email</t>
+        </is>
+      </c>
+      <c r="Z578" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5000947076</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>QS #26 | Tier S+ (Global Elite | h=1194)</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>@epfl.ch</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G579" t="n">
+        <v>15</v>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>Paolo Perona</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J579" t="n">
+        <v>28</v>
+      </c>
+      <c r="K579" t="n">
+        <v>2777</v>
+      </c>
+      <c r="L579" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="M579" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N579" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O579" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q579" t="inlineStr">
+        <is>
+          <t>gnss positioning, depth estimation</t>
+        </is>
+      </c>
+      <c r="R579" t="n">
+        <v>1</v>
+      </c>
+      <c r="S579" t="n">
+        <v>69</v>
+      </c>
+      <c r="T579" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="U579" t="inlineStr">
+        <is>
+          <t>Performance and accuracy of cross‐section tracking methods for hydromorphological habitat assessment in wadable rivers with sparse canopy conditions</t>
+        </is>
+      </c>
+      <c r="V579" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W579" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X579" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aepfl.ch%20%22Paolo%20Perona%22%20email</t>
+        </is>
+      </c>
+      <c r="Z579" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5086428243</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>QS #26 | Tier S+ (Global Elite | h=1194)</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>@epfl.ch</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G580" t="n">
+        <v>16</v>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>Katrin Beyer</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J580" t="n">
+        <v>44</v>
+      </c>
+      <c r="K580" t="n">
+        <v>5603</v>
+      </c>
+      <c r="L580" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M580" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N580" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O580" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q580" t="inlineStr">
+        <is>
+          <t>point cloud registration, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R580" t="n">
+        <v>2</v>
+      </c>
+      <c r="S580" t="n">
+        <v>159</v>
+      </c>
+      <c r="T580" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="U580" t="inlineStr">
+        <is>
+          <t>Image-based geometric digital twinning for stone masonry elements</t>
+        </is>
+      </c>
+      <c r="V580" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W580" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X580" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aepfl.ch%20%22Katrin%20Beyer%22%20email</t>
+        </is>
+      </c>
+      <c r="Z580" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5069185743</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>QS #26 | Tier S+ (Global Elite | h=1194)</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>@epfl.ch</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G581" t="n">
+        <v>17</v>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>Alexander Mathis</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J581" t="n">
+        <v>30</v>
+      </c>
+      <c r="K581" t="n">
+        <v>11578</v>
+      </c>
+      <c r="L581" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="M581" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N581" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O581" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="P581" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q581" t="inlineStr">
+        <is>
+          <t>pose estimation, computer vision</t>
+        </is>
+      </c>
+      <c r="R581" t="n">
+        <v>2</v>
+      </c>
+      <c r="S581" t="n">
+        <v>92</v>
+      </c>
+      <c r="T581" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="U581" t="inlineStr">
+        <is>
+          <t>HOISDF: Constraining 3D Hand-Object Pose Estimation with Global Signed Distance Fields</t>
+        </is>
+      </c>
+      <c r="V581" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W581" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X581" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aepfl.ch%20%22Alexander%20Mathis%22%20email</t>
+        </is>
+      </c>
+      <c r="Z581" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5013861606</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>QS #26 | Tier S+ (Global Elite | h=1194)</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>@epfl.ch</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Direct to PI + Formal Portal (Employee Contract)</t>
+        </is>
+      </c>
+      <c r="G582" t="n">
+        <v>18</v>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>Touradj Ebrahimi</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J582" t="n">
+        <v>69</v>
+      </c>
+      <c r="K582" t="n">
+        <v>26899</v>
+      </c>
+      <c r="L582" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="M582" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N582" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O582" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="P582" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q582" t="inlineStr">
+        <is>
+          <t>event camera, computer vision, embedded systems</t>
+        </is>
+      </c>
+      <c r="R582" t="n">
+        <v>1</v>
+      </c>
+      <c r="S582" t="n">
+        <v>117</v>
+      </c>
+      <c r="T582" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="U582" t="inlineStr">
+        <is>
+          <t>Evaluation of the impact of lossy compression on event camera-based computer vision tasks</t>
+        </is>
+      </c>
+      <c r="V582" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W582" s="4" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X582" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aepfl.ch%20%22Touradj%20Ebrahimi%22%20email</t>
+        </is>
+      </c>
+      <c r="Z582" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5082188773</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z523"/>
+  <autoFilter ref="A1:Z582"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AG$142</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Z$612</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faculty Results'!$A$1:$Z$647</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -3992,23 +3992,129 @@
           <t>University of Liverpool</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=983)</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5019906827</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Chenguang Yang</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Development of vision–based SLAM: from traditional methods to multimodal fusion (2024)</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>@liverpool.ac.uk</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>I146655781</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=82)</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>visual slam, multi-sensor fusion, sensor fusion, pose estimation, field robotics, deep learning</t>
+        </is>
+      </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>9.43</v>
       </c>
       <c r="Z28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>7.39</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" s="2" t="inlineStr"/>
-      <c r="AE28" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Chenguang Yang; Jeremy S. Smith; Miguel López‐Benítez; Guangliang Cheng; Yutao Yue; Ángel F. García‐Fernández; Simon R. Maskell; Baoru Huang; Andrew Ian Cooper; Jason F. Ralph</t>
+        </is>
+      </c>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>1. Chenguang Yang (Full / Senior Prof (Large Lab), h=82) | Fit=9.9/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.4/10 | Keywords=visual slam, multi-sensor fusion, sensor fusion, pose estimation, field robotics, deep learning | Paper=Development of vision–based SLAM: from traditional methods to multimodal fusion (2024)
+2. Jeremy S. Smith (Full / Senior Prof (Large Lab), h=27) | Fit=9.8/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.3/10 | Keywords=lidar slam, multi-sensor fusion, sensor fusion, extended kalman filter, kalman filter, autonomous navigation | Paper=EKF-Based Fusion of Wi-Fi/LiDAR/IMU for Indoor Localization and Navigation (2025)
+3. Miguel López‐Benítez (Full / Senior Prof (Large Lab), h=29) | Fit=9.5/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=8.1/10 | Keywords=state estimation, factor graph optimization, kalman filter, sensor fusion, depth estimation, deep learning | Paper=Enabling Cooperative Autonomy in UUV Clusters: A Survey of Robust State Estimation and Informat (2025)
+4. Guangliang Cheng (Associate / Established PI (High Fit), h=24) | Fit=6.6/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=6.2/10 | Keywords=visual localization, autonomous driving perception, deep learning | Paper=PointLIBERO: Unlocking Spatial Awareness in VLAs With a Novel 3-D Dataset and a Lightweight Fra (2026)
+5. Yutao Yue (Full / Senior Prof (Large Lab), h=16) | Fit=6.5/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=5.9/10 | Keywords=sensor fusion, autonomous vehicles, deep learning, object detection, semantic segmentation, depth estimation | Paper=Radar-Camera Fusion for Object Detection and Semantic Segmentation in Autonomous Driving: A Com (2023)
+6. Ángel F. García‐Fernández (Full / Senior Prof (Large Lab), h=32) | Fit=6.1/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.8/10 | Keywords=trajectory estimation, state estimation, kalman filter, object detection | Paper=Notch power detector for multiple vehicle trajectory estimation with distributed acoustic sensi (2025)
+7. Simon R. Maskell (Full / Senior Prof (Large Lab), h=28) | Fit=6.0/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=5.7/10 | Keywords=trajectory estimation, inertial navigation | Paper=Notch power detector for multiple vehicle trajectory estimation with distributed acoustic sensi (2025)
+8. Baoru Huang (Associate / Established PI (High Fit), h=16) | Fit=4.4/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=point cloud registration, robot perception | Paper=A Robust Point Cloud Registration Method Using Geometrical Information and Probabilistic Models (2026)
+9. Andrew Ian Cooper (Full / Senior Prof (Large Lab), h=138) | Fit=4.3/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=4.7/10 | Keywords=robot localization | Paper=Localization, inspection, and reasoning (LIRA) module for autonomous workflows in self-driving  (2025)
+10. Jason F. Ralph (Full / Senior Prof (Large Lab), h=21) | Fit=3.7/10 | Activity=8.1/10 | Funding=0.0/10 | Overall=4.0/10 | Keywords=inertial navigation | Paper=Cold atom inertial sensors for navigation applications (2022)</t>
+        </is>
+      </c>
+      <c r="AE28" s="2" t="inlineStr">
+        <is>
+          <t>Chenguang Yang: No homepage/funding evidence available
+Jeremy S. Smith: No homepage/funding evidence available
+Miguel López‐Benítez: No homepage/funding evidence available
+Guangliang Cheng: No homepage/funding evidence available
+Yutao Yue: No homepage/funding evidence available
+Ángel F. García‐Fernández: No homepage/funding evidence available
+Simon R. Maskell: No homepage/funding evidence available
+Baoru Huang: No homepage/funding evidence available
+Andrew Ian Cooper: No homepage/funding evidence available
+Jason F. Ralph: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aliverpool.ac.uk%20%22Chenguang%20Yang%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="X29" t="n">
@@ -4035,23 +4141,121 @@
           <t>Brunel University of London</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=514)</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5091804294</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hamid Bahai</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>A Critical Review of Deep Learning-Based Multi-Sensor Fusion Techniques (2022)</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>@brunel.ac.uk</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>I59433898</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit) (h=24)</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, sensor fusion, depth estimation, deep learning</t>
+        </is>
+      </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>8.41</v>
       </c>
       <c r="Z30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" s="2" t="inlineStr"/>
-      <c r="AE30" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hamid Bahai; Kezhi Wang; Paresh M Date; M. Nazmul Huda; Zidong Wang; Mingfeng Wang</t>
+        </is>
+      </c>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>1. Hamid Bahai (Associate / Established PI (High Fit), h=24) | Fit=9.6/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=8.0/10 | Keywords=multi-sensor fusion, sensor fusion, depth estimation, deep learning | Paper=A Critical Review of Deep Learning-Based Multi-Sensor Fusion Techniques (2022)
+2. Kezhi Wang (Full / Senior Prof (Large Lab), h=57) | Fit=6.1/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.0/10 | Keywords=multi-sensor fusion, sensor fusion, robust localization | Paper=Point Cloud for Wireless Communications: A Comprehensive Survey on Fundamentals, Techniques, an (2026)
+3. Paresh M Date (Associate / Established PI (High Fit), h=20) | Fit=6.8/10 | Activity=7.4/10 | Funding=0.0/10 | Overall=5.9/10 | Keywords=state estimation, extended kalman filter, kalman filter | Paper=Gaussian Filtering for Simultaneously Occurring Delayed and Missing Measurements (2022)
+4. M. Nazmul Huda (Assistant Prof / Rising Star (Responsive), h=12) | Fit=6.8/10 | Activity=7.2/10 | Funding=0.0/10 | Overall=5.9/10 | Keywords=robot localization, pose estimation, autonomous vehicles | Paper=Evaluation of SLAM Algorithms for Search and Rescue Applications (2023)
+5. Zidong Wang (Full / Senior Prof (Large Lab), h=151) | Fit=5.4/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=5.3/10 | Keywords=state estimation | Paper=Composite Disturbance Filtering: A Novel State Estimation Scheme for Systems With Multisource,  (2023)
+6. Mingfeng Wang (Associate / Established PI (High Fit), h=19) | Fit=4.4/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=4.7/10 | Keywords=visual localization, 3d reconstruction | Paper=A 2-stage vision-based localization methodology for efficient automatic charging of electric ve (2025)</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="inlineStr">
+        <is>
+          <t>Hamid Bahai: No homepage/funding evidence available
+Kezhi Wang: No homepage/funding evidence available
+Paresh M Date: No homepage/funding evidence available
+M. Nazmul Huda: No homepage/funding evidence available
+Zidong Wang: No homepage/funding evidence available
+Mingfeng Wang: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abrunel.ac.uk%20%22Hamid%20Bahai%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
@@ -4059,23 +4263,125 @@
           <t>Durham University</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=718)</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5114375483</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Clive Roberts</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>A High-Order Extended Kalman Filtering-Enabled Nonlinear State Estimation Method for High-Speed Trains Considering Multiple Operating Phases (2025)</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>@dur.ac.uk</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>I190082696</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=48)</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>state estimation, extended kalman filter, kalman filter</t>
+        </is>
+      </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>6.41</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>9.48</v>
       </c>
       <c r="Z31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="2" t="inlineStr"/>
-      <c r="AE31" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Clive Roberts; Jon Gluyas; Toby P. Breckon; Yixin Sun; Hubert P. H. Shum; Jiaxu Liu; Farshad Arvin; Amir Atapour–Abarghouei</t>
+        </is>
+      </c>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>1. Clive Roberts (Full / Senior Prof (Large Lab), h=48) | Fit=8.6/10 | Activity=9.2/10 | Funding=0.0/10 | Overall=7.4/10 | Keywords=state estimation, extended kalman filter, kalman filter | Paper=A High-Order Extended Kalman Filtering-Enabled Nonlinear State Estimation Method for High-Speed (2025)
+2. Jon Gluyas (Full / Senior Prof (Large Lab), h=38) | Fit=6.6/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=6.0/10 | Keywords=gnss positioning, mobile robot navigation | Paper=First navigation with wireless muometric navigation system (MuWNS) in indoor and underground en (2023)
+3. Toby P. Breckon (Full / Senior Prof (Large Lab), h=46) | Fit=5.9/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.9/10 | Keywords=lidar camera fusion, autonomous driving perception, semantic segmentation, sensor fusion, mobile robot navigation, deep learning | Paper=KD360-VoxelBEV: LiDAR and 360-degree Camera Cross Modality Knowledge Distillation for Bird’s-Ey (2026)
+4. Yixin Sun (Assistant Prof / Rising Star (Responsive), h=16) | Fit=5.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=5.5/10 | Keywords=lidar camera fusion, autonomous driving perception, sensor fusion, mobile robot navigation, deep learning | Paper=KD360-VoxelBEV: LiDAR and 360-degree Camera Cross Modality Knowledge Distillation for Bird’s-Ey (2026)
+5. Hubert P. H. Shum (Full / Senior Prof (Large Lab), h=32) | Fit=5.5/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.5/10 | Keywords=lidar camera fusion, autonomous driving perception, semantic segmentation | Paper=KD360-VoxelBEV: LiDAR and 360-degree Camera Cross Modality Knowledge Distillation for Bird’s-Ey (2026)
+6. Jiaxu Liu (Full / Senior Prof (Large Lab), h=34) | Fit=5.2/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.3/10 | Keywords=lidar camera fusion, autonomous driving perception | Paper=KD360-VoxelBEV: LiDAR and 360-degree Camera Cross Modality Knowledge Distillation for Bird’s-Ey (2026)
+7. Farshad Arvin (Full / Senior Prof (Large Lab), h=35) | Fit=4.8/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=pose estimation, visual localization | Paper=Real Time Fiducial Marker Localisation System with Full 6 DOF Pose Estimation (2023)
+8. Amir Atapour–Abarghouei (Associate / Established PI (High Fit), h=20) | Fit=4.2/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=4.7/10 | Keywords=sensor fusion, mobile robot navigation, deep learning | Paper=Dur360BEV: A Real-World 360-Degree Single Camera Dataset and Benchmark for Bird-Eye View Mappin (2025)</t>
+        </is>
+      </c>
+      <c r="AE31" s="2" t="inlineStr">
+        <is>
+          <t>Clive Roberts: No homepage/funding evidence available
+Jon Gluyas: No homepage/funding evidence available
+Toby P. Breckon: No homepage/funding evidence available
+Yixin Sun: No homepage/funding evidence available
+Hubert P. H. Shum: No homepage/funding evidence available
+Jiaxu Liu: No homepage/funding evidence available
+Farshad Arvin: No homepage/funding evidence available
+Amir Atapour–Abarghouei: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Adur.ac.uk%20%22Clive%20Roberts%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
@@ -4083,23 +4389,119 @@
           <t>University of York</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=779)</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5086288842</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>William A. P. Smith</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Self-supervised Relative Pose with Homography Model-fitting in the Loop (2023)</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>@york.ac.uk</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>I52099693</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=31)</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>visual odometry, pose estimation, depth estimation, semantic segmentation</t>
+        </is>
+      </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>9.41</v>
       </c>
       <c r="Z32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>5.89</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="2" t="inlineStr"/>
-      <c r="AE32" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>William A. P. Smith; Mark Andrew Post; Jim Woodcock; Kanapathippillai Cumanan; Joanna Hodge</t>
+        </is>
+      </c>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>1. William A. P. Smith (Full / Senior Prof (Large Lab), h=31) | Fit=8.5/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=7.5/10 | Keywords=visual odometry, pose estimation, depth estimation, semantic segmentation | Paper=Self-supervised Relative Pose with Homography Model-fitting in the Loop (2023)
+2. Mark Andrew Post (Associate / Established PI (High Fit), h=12) | Fit=6.6/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.3/10 | Keywords=visual slam, mobile robot navigation | Paper=StrucLine-SLAM: A Lightweight and Fully Geometric SLAM System for Structure-Dominant Environmen (2026)
+3. Jim Woodcock (Full / Senior Prof (Large Lab), h=38) | Fit=6.5/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=6.0/10 | Keywords=robot localization | Paper=Uncertainty and Probabilistic UTP (2024)
+4. Kanapathippillai Cumanan (Full / Senior Prof (Large Lab), h=38) | Fit=4.7/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=5.0/10 | Keywords=robust localization | Paper=SRLoc: WiFi Fingerprint Localization Method Against Adversarial Attacks Based on Diffusion-Insp (2026)
+5. Joanna Hodge (Associate / Established PI (High Fit), h=20) | Fit=4.5/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=4.6/10 | Keywords=robot localization | Paper=Sensors and Data in Mobile Robotics for Localisation (2023)</t>
+        </is>
+      </c>
+      <c r="AE32" s="2" t="inlineStr">
+        <is>
+          <t>William A. P. Smith: No homepage/funding evidence available
+Mark Andrew Post: No homepage/funding evidence available
+Jim Woodcock: No homepage/funding evidence available
+Kanapathippillai Cumanan: No homepage/funding evidence available
+Joanna Hodge: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ayork.ac.uk%20%22William%20A.%20P.%20Smith%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
@@ -4107,23 +4509,121 @@
           <t>Lancaster University</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=693)</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5000898945</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>David Cheneler</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Manifold-Constrained Visual Odometry for Soft Worm-Inspired Robots in Pipe-Inspection Tasks (2026)</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>@lancaster.ac.uk</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>I67415387</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab) (h=17)</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>visual odometry, state estimation</t>
+        </is>
+      </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>7.62</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" s="2" t="inlineStr"/>
-      <c r="AE33" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>David Cheneler; Stephen David Monk; Hossein Rahmani; Zhengxin Yu; Qiang Ni; Allahyar Montazeri</t>
+        </is>
+      </c>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>1. David Cheneler (Full / Senior Prof (Large Lab), h=17) | Fit=8.5/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.5/10 | Keywords=visual odometry, state estimation | Paper=Manifold-Constrained Visual Odometry for Soft Worm-Inspired Robots in Pipe-Inspection Tasks (2026)
+2. Stephen David Monk (Assistant Prof / Rising Star (Responsive), h=14) | Fit=8.5/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=7.5/10 | Keywords=visual odometry, state estimation | Paper=Manifold-Constrained Visual Odometry for Soft Worm-Inspired Robots in Pipe-Inspection Tasks (2026)
+3. Hossein Rahmani (Associate / Established PI (High Fit), h=27) | Fit=7.2/10 | Activity=9.7/10 | Funding=0.0/10 | Overall=6.6/10 | Keywords=pose estimation, deep learning | Paper=Deep Learning-Based Object Pose Estimation: A Comprehensive Survey (2026)
+4. Zhengxin Yu (Assistant Prof / Rising Star (Responsive), h=14) | Fit=7.2/10 | Activity=8.5/10 | Funding=0.0/10 | Overall=6.4/10 | Keywords=visual odometry, pose estimation | Paper=Federated Meta Learning for Visual Navigation in GPS-denied Urban Airspace (2023)
+5. Qiang Ni (Full / Senior Prof (Large Lab), h=65) | Fit=6.7/10 | Activity=10.0/10 | Funding=0.0/10 | Overall=6.4/10 | Keywords=inertial navigation, trajectory estimation | Paper=Tracking Large-scale Shared Bikes with Inertial Motion Learning in GNSS Blocked Environments (2026)
+6. Allahyar Montazeri (Full / Senior Prof (Large Lab), h=22) | Fit=4.6/10 | Activity=8.9/10 | Funding=0.0/10 | Overall=4.8/10 | Keywords=robot localization | Paper=Simultaneous localization and mapping in a multi-robot system in a dynamic environment with unk (2024)</t>
+        </is>
+      </c>
+      <c r="AE33" s="2" t="inlineStr">
+        <is>
+          <t>David Cheneler: No homepage/funding evidence available
+Stephen David Monk: No homepage/funding evidence available
+Hossein Rahmani: No homepage/funding evidence available
+Zhengxin Yu: No homepage/funding evidence available
+Qiang Ni: No homepage/funding evidence available
+Allahyar Montazeri: No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Alancaster.ac.uk%20%22David%20Cheneler%22%20email</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="X34" t="n">
@@ -9653,7 +10153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z612"/>
+  <dimension ref="A1:Z647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="3" min="1" max="1"/>
@@ -74943,8 +75443,3753 @@
         </is>
       </c>
     </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>University of Liverpool</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=983)</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>@liverpool.ac.uk</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G613" t="n">
+        <v>1</v>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>Chenguang Yang</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J613" t="n">
+        <v>82</v>
+      </c>
+      <c r="K613" t="n">
+        <v>25935</v>
+      </c>
+      <c r="L613" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="M613" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N613" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O613" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="P613" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q613" t="inlineStr">
+        <is>
+          <t>visual slam, multi-sensor fusion, sensor fusion, pose estimation, field robotics, deep learning</t>
+        </is>
+      </c>
+      <c r="R613" t="n">
+        <v>8</v>
+      </c>
+      <c r="S613" t="n">
+        <v>464</v>
+      </c>
+      <c r="T613" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U613" t="inlineStr">
+        <is>
+          <t>Development of vision–based SLAM: from traditional methods to multimodal fusion</t>
+        </is>
+      </c>
+      <c r="V613" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W613" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X613" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aliverpool.ac.uk%20%22Chenguang%20Yang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z613" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5019906827</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>University of Liverpool</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=983)</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>@liverpool.ac.uk</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G614" t="n">
+        <v>2</v>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>Jeremy S. Smith</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J614" t="n">
+        <v>27</v>
+      </c>
+      <c r="K614" t="n">
+        <v>3020</v>
+      </c>
+      <c r="L614" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="M614" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N614" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O614" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="P614" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; 3D Computer Vision &amp; Geometric Perception; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q614" t="inlineStr">
+        <is>
+          <t>lidar slam, multi-sensor fusion, sensor fusion, extended kalman filter, kalman filter, autonomous navigation</t>
+        </is>
+      </c>
+      <c r="R614" t="n">
+        <v>4</v>
+      </c>
+      <c r="S614" t="n">
+        <v>58</v>
+      </c>
+      <c r="T614" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="U614" t="inlineStr">
+        <is>
+          <t>EKF-Based Fusion of Wi-Fi/LiDAR/IMU for Indoor Localization and Navigation</t>
+        </is>
+      </c>
+      <c r="V614" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W614" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X614" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aliverpool.ac.uk%20%22Jeremy%20S.%20Smith%22%20email</t>
+        </is>
+      </c>
+      <c r="Z614" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5003757015</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>University of Liverpool</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=983)</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>@liverpool.ac.uk</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G615" t="n">
+        <v>3</v>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>Miguel López‐Benítez</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J615" t="n">
+        <v>29</v>
+      </c>
+      <c r="K615" t="n">
+        <v>3855</v>
+      </c>
+      <c r="L615" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="M615" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N615" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O615" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="P615" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; GNSS &amp; Robust Localization; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q615" t="inlineStr">
+        <is>
+          <t>state estimation, factor graph optimization, kalman filter, sensor fusion, depth estimation, deep learning</t>
+        </is>
+      </c>
+      <c r="R615" t="n">
+        <v>4</v>
+      </c>
+      <c r="S615" t="n">
+        <v>86</v>
+      </c>
+      <c r="T615" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="U615" t="inlineStr">
+        <is>
+          <t>Enabling Cooperative Autonomy in UUV Clusters: A Survey of Robust State Estimation and Information Fusion Techniques</t>
+        </is>
+      </c>
+      <c r="V615" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W615" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X615" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aliverpool.ac.uk%20%22Miguel%20L%C3%B3pez%E2%80%90Ben%C3%ADtez%22%20email</t>
+        </is>
+      </c>
+      <c r="Z615" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5050222424</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>University of Liverpool</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=983)</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>@liverpool.ac.uk</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G616" t="n">
+        <v>4</v>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>Guangliang Cheng</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J616" t="n">
+        <v>24</v>
+      </c>
+      <c r="K616" t="n">
+        <v>2807</v>
+      </c>
+      <c r="L616" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="M616" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N616" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O616" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="P616" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Deep Learning for Navigation &amp; Perception; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q616" t="inlineStr">
+        <is>
+          <t>visual localization, autonomous driving perception, deep learning</t>
+        </is>
+      </c>
+      <c r="R616" t="n">
+        <v>2</v>
+      </c>
+      <c r="S616" t="n">
+        <v>73</v>
+      </c>
+      <c r="T616" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U616" t="inlineStr">
+        <is>
+          <t>PointLIBERO: Unlocking Spatial Awareness in VLAs With a Novel 3-D Dataset and a Lightweight Framework</t>
+        </is>
+      </c>
+      <c r="V616" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W616" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X616" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aliverpool.ac.uk%20%22Guangliang%20Cheng%22%20email</t>
+        </is>
+      </c>
+      <c r="Z616" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5045854934</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>University of Liverpool</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=983)</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>@liverpool.ac.uk</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G617" t="n">
+        <v>5</v>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>Yutao Yue</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J617" t="n">
+        <v>16</v>
+      </c>
+      <c r="K617" t="n">
+        <v>1309</v>
+      </c>
+      <c r="L617" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="M617" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N617" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O617" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="P617" t="inlineStr">
+        <is>
+          <t>Deep Learning for Navigation &amp; Perception; LiDAR &amp; Multimodal Sensor Fusion; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q617" t="inlineStr">
+        <is>
+          <t>sensor fusion, autonomous vehicles, deep learning, object detection, semantic segmentation, depth estimation</t>
+        </is>
+      </c>
+      <c r="R617" t="n">
+        <v>2</v>
+      </c>
+      <c r="S617" t="n">
+        <v>187</v>
+      </c>
+      <c r="T617" t="inlineStr">
+        <is>
+          <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="U617" t="inlineStr">
+        <is>
+          <t>Radar-Camera Fusion for Object Detection and Semantic Segmentation in Autonomous Driving: A Comprehensive Review</t>
+        </is>
+      </c>
+      <c r="V617" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W617" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X617" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aliverpool.ac.uk%20%22Yutao%20Yue%22%20email</t>
+        </is>
+      </c>
+      <c r="Z617" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5052861384</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>University of Liverpool</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=983)</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>@liverpool.ac.uk</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G618" t="n">
+        <v>6</v>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>Ángel F. García‐Fernández</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J618" t="n">
+        <v>32</v>
+      </c>
+      <c r="K618" t="n">
+        <v>3934</v>
+      </c>
+      <c r="L618" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="M618" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N618" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O618" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="P618" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q618" t="inlineStr">
+        <is>
+          <t>trajectory estimation, state estimation, kalman filter, object detection</t>
+        </is>
+      </c>
+      <c r="R618" t="n">
+        <v>10</v>
+      </c>
+      <c r="S618" t="n">
+        <v>106</v>
+      </c>
+      <c r="T618" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="U618" t="inlineStr">
+        <is>
+          <t>Notch power detector for multiple vehicle trajectory estimation with distributed acoustic sensing</t>
+        </is>
+      </c>
+      <c r="V618" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W618" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X618" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aliverpool.ac.uk%20%22%C3%81ngel%20F.%20Garc%C3%ADa%E2%80%90Fern%C3%A1ndez%22%20email</t>
+        </is>
+      </c>
+      <c r="Z618" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5049418113</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>University of Liverpool</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=983)</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>@liverpool.ac.uk</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G619" t="n">
+        <v>7</v>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>Simon R. Maskell</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J619" t="n">
+        <v>28</v>
+      </c>
+      <c r="K619" t="n">
+        <v>15128</v>
+      </c>
+      <c r="L619" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="M619" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N619" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O619" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="P619" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q619" t="inlineStr">
+        <is>
+          <t>trajectory estimation, inertial navigation</t>
+        </is>
+      </c>
+      <c r="R619" t="n">
+        <v>3</v>
+      </c>
+      <c r="S619" t="n">
+        <v>115</v>
+      </c>
+      <c r="T619" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="U619" t="inlineStr">
+        <is>
+          <t>Notch power detector for multiple vehicle trajectory estimation with distributed acoustic sensing</t>
+        </is>
+      </c>
+      <c r="V619" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W619" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X619" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aliverpool.ac.uk%20%22Simon%20R.%20Maskell%22%20email</t>
+        </is>
+      </c>
+      <c r="Z619" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5083636287</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>University of Liverpool</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=983)</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>@liverpool.ac.uk</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G620" t="n">
+        <v>8</v>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>Baoru Huang</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J620" t="n">
+        <v>16</v>
+      </c>
+      <c r="K620" t="n">
+        <v>660</v>
+      </c>
+      <c r="L620" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="M620" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N620" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O620" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="P620" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q620" t="inlineStr">
+        <is>
+          <t>point cloud registration, robot perception</t>
+        </is>
+      </c>
+      <c r="R620" t="n">
+        <v>3</v>
+      </c>
+      <c r="S620" t="n">
+        <v>90</v>
+      </c>
+      <c r="T620" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U620" t="inlineStr">
+        <is>
+          <t>A Robust Point Cloud Registration Method Using Geometrical Information and Probabilistic Models for Robot-Assisted Bronchoscopy Navigation</t>
+        </is>
+      </c>
+      <c r="V620" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W620" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X620" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aliverpool.ac.uk%20%22Baoru%20Huang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z620" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5045614046</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>University of Liverpool</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=983)</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>@liverpool.ac.uk</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G621" t="n">
+        <v>9</v>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>Andrew Ian Cooper</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J621" t="n">
+        <v>138</v>
+      </c>
+      <c r="K621" t="n">
+        <v>65270</v>
+      </c>
+      <c r="L621" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="M621" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N621" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O621" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P621" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q621" t="inlineStr">
+        <is>
+          <t>robot localization</t>
+        </is>
+      </c>
+      <c r="R621" t="n">
+        <v>1</v>
+      </c>
+      <c r="S621" t="n">
+        <v>206</v>
+      </c>
+      <c r="T621" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="U621" t="inlineStr">
+        <is>
+          <t>Localization, inspection, and reasoning (LIRA) module for autonomous workflows in self-driving laboratories</t>
+        </is>
+      </c>
+      <c r="V621" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W621" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X621" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aliverpool.ac.uk%20%22Andrew%20Ian%20Cooper%22%20email</t>
+        </is>
+      </c>
+      <c r="Z621" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5060033823</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>University of Liverpool</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=983)</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>@liverpool.ac.uk</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G622" t="n">
+        <v>10</v>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>Jason F. Ralph</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J622" t="n">
+        <v>21</v>
+      </c>
+      <c r="K622" t="n">
+        <v>1565</v>
+      </c>
+      <c r="L622" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="M622" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N622" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O622" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="P622" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q622" t="inlineStr">
+        <is>
+          <t>inertial navigation</t>
+        </is>
+      </c>
+      <c r="R622" t="n">
+        <v>1</v>
+      </c>
+      <c r="S622" t="n">
+        <v>35</v>
+      </c>
+      <c r="T622" t="inlineStr">
+        <is>
+          <t>2022-10-03</t>
+        </is>
+      </c>
+      <c r="U622" t="inlineStr">
+        <is>
+          <t>Cold atom inertial sensors for navigation applications</t>
+        </is>
+      </c>
+      <c r="V622" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W622" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X622" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Aliverpool.ac.uk%20%22Jason%20F.%20Ralph%22%20email</t>
+        </is>
+      </c>
+      <c r="Z622" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5088124267</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Brunel University of London</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=514)</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>@brunel.ac.uk</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G623" t="n">
+        <v>1</v>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>Hamid Bahai</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J623" t="n">
+        <v>24</v>
+      </c>
+      <c r="K623" t="n">
+        <v>1877</v>
+      </c>
+      <c r="L623" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="M623" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N623" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O623" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="P623" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q623" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, sensor fusion, depth estimation, deep learning</t>
+        </is>
+      </c>
+      <c r="R623" t="n">
+        <v>1</v>
+      </c>
+      <c r="S623" t="n">
+        <v>24</v>
+      </c>
+      <c r="T623" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="U623" t="inlineStr">
+        <is>
+          <t>A Critical Review of Deep Learning-Based Multi-Sensor Fusion Techniques</t>
+        </is>
+      </c>
+      <c r="V623" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W623" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X623" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abrunel.ac.uk%20%22Hamid%20Bahai%22%20email</t>
+        </is>
+      </c>
+      <c r="Z623" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5091804294</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Brunel University of London</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=514)</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>@brunel.ac.uk</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G624" t="n">
+        <v>2</v>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>Kezhi Wang</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J624" t="n">
+        <v>57</v>
+      </c>
+      <c r="K624" t="n">
+        <v>15452</v>
+      </c>
+      <c r="L624" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="M624" t="n">
+        <v>10</v>
+      </c>
+      <c r="N624" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O624" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="P624" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization; 3D Computer Vision &amp; Geometric Perception; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q624" t="inlineStr">
+        <is>
+          <t>multi-sensor fusion, sensor fusion, robust localization</t>
+        </is>
+      </c>
+      <c r="R624" t="n">
+        <v>4</v>
+      </c>
+      <c r="S624" t="n">
+        <v>230</v>
+      </c>
+      <c r="T624" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="U624" t="inlineStr">
+        <is>
+          <t>Point Cloud for Wireless Communications: A Comprehensive Survey on Fundamentals, Techniques, and Applications</t>
+        </is>
+      </c>
+      <c r="V624" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W624" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X624" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abrunel.ac.uk%20%22Kezhi%20Wang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z624" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5022523766</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>Brunel University of London</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=514)</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>@brunel.ac.uk</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G625" t="n">
+        <v>3</v>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>Paresh M Date</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J625" t="n">
+        <v>20</v>
+      </c>
+      <c r="K625" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L625" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="M625" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="N625" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O625" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="P625" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q625" t="inlineStr">
+        <is>
+          <t>state estimation, extended kalman filter, kalman filter</t>
+        </is>
+      </c>
+      <c r="R625" t="n">
+        <v>2</v>
+      </c>
+      <c r="S625" t="n">
+        <v>12</v>
+      </c>
+      <c r="T625" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="U625" t="inlineStr">
+        <is>
+          <t>Gaussian Filtering for Simultaneously Occurring Delayed and Missing Measurements</t>
+        </is>
+      </c>
+      <c r="V625" t="n">
+        <v>2022</v>
+      </c>
+      <c r="W625" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X625" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abrunel.ac.uk%20%22Paresh%20M%20Date%22%20email</t>
+        </is>
+      </c>
+      <c r="Z625" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5009805193</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>Brunel University of London</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=514)</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>@brunel.ac.uk</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G626" t="n">
+        <v>4</v>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>M. Nazmul Huda</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J626" t="n">
+        <v>12</v>
+      </c>
+      <c r="K626" t="n">
+        <v>573</v>
+      </c>
+      <c r="L626" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="M626" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="N626" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O626" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="P626" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q626" t="inlineStr">
+        <is>
+          <t>robot localization, pose estimation, autonomous vehicles</t>
+        </is>
+      </c>
+      <c r="R626" t="n">
+        <v>2</v>
+      </c>
+      <c r="S626" t="n">
+        <v>7</v>
+      </c>
+      <c r="T626" t="inlineStr">
+        <is>
+          <t>2023-04-13</t>
+        </is>
+      </c>
+      <c r="U626" t="inlineStr">
+        <is>
+          <t>Evaluation of SLAM Algorithms for Search and Rescue Applications</t>
+        </is>
+      </c>
+      <c r="V626" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W626" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X626" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abrunel.ac.uk%20%22M.%20Nazmul%20Huda%22%20email</t>
+        </is>
+      </c>
+      <c r="Z626" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5089610698</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Brunel University of London</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=514)</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>@brunel.ac.uk</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G627" t="n">
+        <v>5</v>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>Zidong Wang</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J627" t="n">
+        <v>151</v>
+      </c>
+      <c r="K627" t="n">
+        <v>84253</v>
+      </c>
+      <c r="L627" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="M627" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N627" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O627" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="P627" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation; State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q627" t="inlineStr">
+        <is>
+          <t>state estimation</t>
+        </is>
+      </c>
+      <c r="R627" t="n">
+        <v>6</v>
+      </c>
+      <c r="S627" t="n">
+        <v>650</v>
+      </c>
+      <c r="T627" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="U627" t="inlineStr">
+        <is>
+          <t>Composite Disturbance Filtering: A Novel State Estimation Scheme for Systems With Multisource, Heterogeneous, and Isomeric Disturbances</t>
+        </is>
+      </c>
+      <c r="V627" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W627" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X627" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abrunel.ac.uk%20%22Zidong%20Wang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z627" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100699858</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>Brunel University of London</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Tier S (Top 100 Research | h=514)</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>@brunel.ac.uk</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G628" t="n">
+        <v>6</v>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>Mingfeng Wang</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J628" t="n">
+        <v>19</v>
+      </c>
+      <c r="K628" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L628" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="M628" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N628" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O628" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="P628" t="inlineStr">
+        <is>
+          <t>3D Computer Vision &amp; Geometric Perception; Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q628" t="inlineStr">
+        <is>
+          <t>visual localization, 3d reconstruction</t>
+        </is>
+      </c>
+      <c r="R628" t="n">
+        <v>2</v>
+      </c>
+      <c r="S628" t="n">
+        <v>73</v>
+      </c>
+      <c r="T628" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="U628" t="inlineStr">
+        <is>
+          <t>A 2-stage vision-based localization methodology for efficient automatic charging of electric vehicles in uncertain environments</t>
+        </is>
+      </c>
+      <c r="V628" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W628" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X628" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Abrunel.ac.uk%20%22Mingfeng%20Wang%22%20email</t>
+        </is>
+      </c>
+      <c r="Z628" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100698753</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Durham University</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=718)</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>@dur.ac.uk</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G629" t="n">
+        <v>1</v>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>Clive Roberts</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J629" t="n">
+        <v>48</v>
+      </c>
+      <c r="K629" t="n">
+        <v>8394</v>
+      </c>
+      <c r="L629" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="M629" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="N629" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O629" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="P629" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q629" t="inlineStr">
+        <is>
+          <t>state estimation, extended kalman filter, kalman filter</t>
+        </is>
+      </c>
+      <c r="R629" t="n">
+        <v>1</v>
+      </c>
+      <c r="S629" t="n">
+        <v>82</v>
+      </c>
+      <c r="T629" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="U629" t="inlineStr">
+        <is>
+          <t>A High-Order Extended Kalman Filtering-Enabled Nonlinear State Estimation Method for High-Speed Trains Considering Multiple Operating Phases</t>
+        </is>
+      </c>
+      <c r="V629" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W629" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X629" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Adur.ac.uk%20%22Clive%20Roberts%22%20email</t>
+        </is>
+      </c>
+      <c r="Z629" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5114375483</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Durham University</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=718)</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>@dur.ac.uk</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G630" t="n">
+        <v>2</v>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>Jon Gluyas</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J630" t="n">
+        <v>38</v>
+      </c>
+      <c r="K630" t="n">
+        <v>5872</v>
+      </c>
+      <c r="L630" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="M630" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N630" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O630" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="P630" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q630" t="inlineStr">
+        <is>
+          <t>gnss positioning, mobile robot navigation</t>
+        </is>
+      </c>
+      <c r="R630" t="n">
+        <v>1</v>
+      </c>
+      <c r="S630" t="n">
+        <v>96</v>
+      </c>
+      <c r="T630" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="U630" t="inlineStr">
+        <is>
+          <t>First navigation with wireless muometric navigation system (MuWNS) in indoor and underground environments</t>
+        </is>
+      </c>
+      <c r="V630" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W630" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X630" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Adur.ac.uk%20%22Jon%20Gluyas%22%20email</t>
+        </is>
+      </c>
+      <c r="Z630" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5024338561</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Durham University</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=718)</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>@dur.ac.uk</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G631" t="n">
+        <v>3</v>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>Toby P. Breckon</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J631" t="n">
+        <v>46</v>
+      </c>
+      <c r="K631" t="n">
+        <v>8765</v>
+      </c>
+      <c r="L631" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="M631" t="n">
+        <v>10</v>
+      </c>
+      <c r="N631" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O631" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="P631" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q631" t="inlineStr">
+        <is>
+          <t>lidar camera fusion, autonomous driving perception, semantic segmentation, sensor fusion, mobile robot navigation, deep learning</t>
+        </is>
+      </c>
+      <c r="R631" t="n">
+        <v>5</v>
+      </c>
+      <c r="S631" t="n">
+        <v>77</v>
+      </c>
+      <c r="T631" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U631" t="inlineStr">
+        <is>
+          <t>KD360-VoxelBEV: LiDAR and 360-degree Camera Cross Modality Knowledge Distillation for Bird’s-Eye-View Segmentation</t>
+        </is>
+      </c>
+      <c r="V631" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W631" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X631" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Adur.ac.uk%20%22Toby%20P.%20Breckon%22%20email</t>
+        </is>
+      </c>
+      <c r="Z631" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5045115593</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Durham University</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=718)</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>@dur.ac.uk</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G632" t="n">
+        <v>4</v>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>Yixin Sun</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J632" t="n">
+        <v>16</v>
+      </c>
+      <c r="K632" t="n">
+        <v>842</v>
+      </c>
+      <c r="L632" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="M632" t="n">
+        <v>10</v>
+      </c>
+      <c r="N632" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O632" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="P632" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q632" t="inlineStr">
+        <is>
+          <t>lidar camera fusion, autonomous driving perception, sensor fusion, mobile robot navigation, deep learning</t>
+        </is>
+      </c>
+      <c r="R632" t="n">
+        <v>3</v>
+      </c>
+      <c r="S632" t="n">
+        <v>37</v>
+      </c>
+      <c r="T632" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U632" t="inlineStr">
+        <is>
+          <t>KD360-VoxelBEV: LiDAR and 360-degree Camera Cross Modality Knowledge Distillation for Bird’s-Eye-View Segmentation</t>
+        </is>
+      </c>
+      <c r="V632" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W632" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X632" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Adur.ac.uk%20%22Yixin%20Sun%22%20email</t>
+        </is>
+      </c>
+      <c r="Z632" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5026356718</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Durham University</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=718)</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>@dur.ac.uk</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G633" t="n">
+        <v>5</v>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>Hubert P. H. Shum</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J633" t="n">
+        <v>32</v>
+      </c>
+      <c r="K633" t="n">
+        <v>4299</v>
+      </c>
+      <c r="L633" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="M633" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N633" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O633" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="P633" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q633" t="inlineStr">
+        <is>
+          <t>lidar camera fusion, autonomous driving perception, semantic segmentation</t>
+        </is>
+      </c>
+      <c r="R633" t="n">
+        <v>2</v>
+      </c>
+      <c r="S633" t="n">
+        <v>135</v>
+      </c>
+      <c r="T633" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="U633" t="inlineStr">
+        <is>
+          <t>KD360-VoxelBEV: LiDAR and 360-degree Camera Cross Modality Knowledge Distillation for Bird’s-Eye-View Segmentation</t>
+        </is>
+      </c>
+      <c r="V633" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W633" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X633" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Adur.ac.uk%20%22Hubert%20P.%20H.%20Shum%22%20email</t>
+        </is>
+      </c>
+      <c r="Z633" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5038258635</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>Durham University</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=718)</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>@dur.ac.uk</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G634" t="n">
+        <v>6</v>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>Jiaxu Liu</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J634" t="n">
+        <v>34</v>
+      </c>
+      <c r="K634" t="n">
+        <v>4125</v>
+      </c>
+      <c r="L634" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="M634" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N634" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O634" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="P634" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q634" t="inlineStr">
+        <is>
+          <t>lidar camera fusion, autonomous driving perception</t>
+        </is>
+      </c>
+      <c r="R634" t="n">
+        <v>1</v>
+      </c>
+      <c r="S634" t="n">
+        <v>165</v>
+      </c>
+      <c r="T634" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="U634" t="inlineStr">
+        <is>
+          <t>KD360-VoxelBEV: LiDAR and 360-degree Camera Cross Modality Knowledge Distillation for Bird’s-Eye-View Segmentation</t>
+        </is>
+      </c>
+      <c r="V634" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W634" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X634" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Adur.ac.uk%20%22Jiaxu%20Liu%22%20email</t>
+        </is>
+      </c>
+      <c r="Z634" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5038889450</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>Durham University</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=718)</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>@dur.ac.uk</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G635" t="n">
+        <v>7</v>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>Farshad Arvin</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J635" t="n">
+        <v>35</v>
+      </c>
+      <c r="K635" t="n">
+        <v>4136</v>
+      </c>
+      <c r="L635" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="M635" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N635" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O635" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P635" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation; 3D Computer Vision &amp; Geometric Perception</t>
+        </is>
+      </c>
+      <c r="Q635" t="inlineStr">
+        <is>
+          <t>pose estimation, visual localization</t>
+        </is>
+      </c>
+      <c r="R635" t="n">
+        <v>2</v>
+      </c>
+      <c r="S635" t="n">
+        <v>167</v>
+      </c>
+      <c r="T635" t="inlineStr">
+        <is>
+          <t>2023-03-15</t>
+        </is>
+      </c>
+      <c r="U635" t="inlineStr">
+        <is>
+          <t>Real Time Fiducial Marker Localisation System with Full 6 DOF Pose Estimation</t>
+        </is>
+      </c>
+      <c r="V635" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W635" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X635" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Adur.ac.uk%20%22Farshad%20Arvin%22%20email</t>
+        </is>
+      </c>
+      <c r="Z635" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5005614248</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Durham University</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=718)</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>@dur.ac.uk</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G636" t="n">
+        <v>8</v>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>Amir Atapour–Abarghouei</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J636" t="n">
+        <v>20</v>
+      </c>
+      <c r="K636" t="n">
+        <v>2450</v>
+      </c>
+      <c r="L636" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="M636" t="n">
+        <v>10</v>
+      </c>
+      <c r="N636" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O636" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="P636" t="inlineStr">
+        <is>
+          <t>LiDAR &amp; Multimodal Sensor Fusion; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q636" t="inlineStr">
+        <is>
+          <t>sensor fusion, mobile robot navigation, deep learning</t>
+        </is>
+      </c>
+      <c r="R636" t="n">
+        <v>2</v>
+      </c>
+      <c r="S636" t="n">
+        <v>46</v>
+      </c>
+      <c r="T636" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U636" t="inlineStr">
+        <is>
+          <t>Dur360BEV: A Real-World 360-Degree Single Camera Dataset and Benchmark for Bird-Eye View Mapping in Autonomous Driving</t>
+        </is>
+      </c>
+      <c r="V636" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W636" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X636" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Adur.ac.uk%20%22Amir%20Atapour%E2%80%93Abarghouei%22%20email</t>
+        </is>
+      </c>
+      <c r="Z636" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5013030358</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>University of York</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=779)</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>@york.ac.uk</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G637" t="n">
+        <v>1</v>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>William A. P. Smith</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J637" t="n">
+        <v>31</v>
+      </c>
+      <c r="K637" t="n">
+        <v>3771</v>
+      </c>
+      <c r="L637" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="M637" t="n">
+        <v>10</v>
+      </c>
+      <c r="N637" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O637" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="P637" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; 3D Computer Vision &amp; Geometric Perception; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q637" t="inlineStr">
+        <is>
+          <t>visual odometry, pose estimation, depth estimation, semantic segmentation</t>
+        </is>
+      </c>
+      <c r="R637" t="n">
+        <v>3</v>
+      </c>
+      <c r="S637" t="n">
+        <v>38</v>
+      </c>
+      <c r="T637" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="U637" t="inlineStr">
+        <is>
+          <t>Self-supervised Relative Pose with Homography Model-fitting in the Loop</t>
+        </is>
+      </c>
+      <c r="V637" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W637" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X637" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ayork.ac.uk%20%22William%20A.%20P.%20Smith%22%20email</t>
+        </is>
+      </c>
+      <c r="Z637" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5086288842</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>University of York</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=779)</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>@york.ac.uk</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G638" t="n">
+        <v>2</v>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>Mark Andrew Post</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J638" t="n">
+        <v>12</v>
+      </c>
+      <c r="K638" t="n">
+        <v>612</v>
+      </c>
+      <c r="L638" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="M638" t="n">
+        <v>10</v>
+      </c>
+      <c r="N638" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O638" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="P638" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM; Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q638" t="inlineStr">
+        <is>
+          <t>visual slam, mobile robot navigation</t>
+        </is>
+      </c>
+      <c r="R638" t="n">
+        <v>3</v>
+      </c>
+      <c r="S638" t="n">
+        <v>22</v>
+      </c>
+      <c r="T638" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="U638" t="inlineStr">
+        <is>
+          <t>StrucLine-SLAM: A Lightweight and Fully Geometric SLAM System for Structure-Dominant Environments</t>
+        </is>
+      </c>
+      <c r="V638" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W638" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X638" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ayork.ac.uk%20%22Mark%20Andrew%20Post%22%20email</t>
+        </is>
+      </c>
+      <c r="Z638" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5086888932</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>University of York</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=779)</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>@york.ac.uk</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G639" t="n">
+        <v>3</v>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>Jim Woodcock</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J639" t="n">
+        <v>38</v>
+      </c>
+      <c r="K639" t="n">
+        <v>6880</v>
+      </c>
+      <c r="L639" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="M639" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N639" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O639" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="P639" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q639" t="inlineStr">
+        <is>
+          <t>robot localization</t>
+        </is>
+      </c>
+      <c r="R639" t="n">
+        <v>2</v>
+      </c>
+      <c r="S639" t="n">
+        <v>71</v>
+      </c>
+      <c r="T639" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="U639" t="inlineStr">
+        <is>
+          <t>Uncertainty and Probabilistic UTP</t>
+        </is>
+      </c>
+      <c r="V639" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W639" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X639" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ayork.ac.uk%20%22Jim%20Woodcock%22%20email</t>
+        </is>
+      </c>
+      <c r="Z639" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5006626759</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>University of York</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=779)</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>@york.ac.uk</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G640" t="n">
+        <v>4</v>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>Kanapathippillai Cumanan</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J640" t="n">
+        <v>38</v>
+      </c>
+      <c r="K640" t="n">
+        <v>4824</v>
+      </c>
+      <c r="L640" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="M640" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N640" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O640" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="P640" t="inlineStr">
+        <is>
+          <t>GNSS &amp; Robust Localization</t>
+        </is>
+      </c>
+      <c r="Q640" t="inlineStr">
+        <is>
+          <t>robust localization</t>
+        </is>
+      </c>
+      <c r="R640" t="n">
+        <v>1</v>
+      </c>
+      <c r="S640" t="n">
+        <v>71</v>
+      </c>
+      <c r="T640" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U640" t="inlineStr">
+        <is>
+          <t>SRLoc: WiFi Fingerprint Localization Method Against Adversarial Attacks Based on Diffusion-Inspired Model</t>
+        </is>
+      </c>
+      <c r="V640" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W640" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X640" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ayork.ac.uk%20%22Kanapathippillai%20Cumanan%22%20email</t>
+        </is>
+      </c>
+      <c r="Z640" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5067366238</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>University of York</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=779)</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>@york.ac.uk</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G641" t="n">
+        <v>5</v>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>Joanna Hodge</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J641" t="n">
+        <v>20</v>
+      </c>
+      <c r="K641" t="n">
+        <v>5584</v>
+      </c>
+      <c r="L641" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="M641" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N641" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O641" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="P641" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q641" t="inlineStr">
+        <is>
+          <t>robot localization</t>
+        </is>
+      </c>
+      <c r="R641" t="n">
+        <v>1</v>
+      </c>
+      <c r="S641" t="n">
+        <v>30</v>
+      </c>
+      <c r="T641" t="inlineStr">
+        <is>
+          <t>2023-01-20</t>
+        </is>
+      </c>
+      <c r="U641" t="inlineStr">
+        <is>
+          <t>Sensors and Data in Mobile Robotics for Localisation</t>
+        </is>
+      </c>
+      <c r="V641" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W641" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X641" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Ayork.ac.uk%20%22Joanna%20Hodge%22%20email</t>
+        </is>
+      </c>
+      <c r="Z641" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5024373546</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Lancaster University</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=693)</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>@lancaster.ac.uk</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G642" t="n">
+        <v>1</v>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>David Cheneler</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J642" t="n">
+        <v>17</v>
+      </c>
+      <c r="K642" t="n">
+        <v>1182</v>
+      </c>
+      <c r="L642" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M642" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N642" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O642" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="P642" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q642" t="inlineStr">
+        <is>
+          <t>visual odometry, state estimation</t>
+        </is>
+      </c>
+      <c r="R642" t="n">
+        <v>1</v>
+      </c>
+      <c r="S642" t="n">
+        <v>55</v>
+      </c>
+      <c r="T642" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U642" t="inlineStr">
+        <is>
+          <t>Manifold-Constrained Visual Odometry for Soft Worm-Inspired Robots in Pipe-Inspection Tasks</t>
+        </is>
+      </c>
+      <c r="V642" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W642" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X642" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Alancaster.ac.uk%20%22David%20Cheneler%22%20email</t>
+        </is>
+      </c>
+      <c r="Z642" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5000898945</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Lancaster University</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=693)</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>@lancaster.ac.uk</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G643" t="n">
+        <v>2</v>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>Stephen David Monk</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J643" t="n">
+        <v>14</v>
+      </c>
+      <c r="K643" t="n">
+        <v>874</v>
+      </c>
+      <c r="L643" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M643" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N643" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O643" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="P643" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q643" t="inlineStr">
+        <is>
+          <t>visual odometry, state estimation</t>
+        </is>
+      </c>
+      <c r="R643" t="n">
+        <v>1</v>
+      </c>
+      <c r="S643" t="n">
+        <v>16</v>
+      </c>
+      <c r="T643" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U643" t="inlineStr">
+        <is>
+          <t>Manifold-Constrained Visual Odometry for Soft Worm-Inspired Robots in Pipe-Inspection Tasks</t>
+        </is>
+      </c>
+      <c r="V643" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W643" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X643" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Alancaster.ac.uk%20%22Stephen%20David%20Monk%22%20email</t>
+        </is>
+      </c>
+      <c r="Z643" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5037791572</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>Lancaster University</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=693)</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>@lancaster.ac.uk</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G644" t="n">
+        <v>3</v>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>Hossein Rahmani</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>Associate / Established PI (High Fit)</t>
+        </is>
+      </c>
+      <c r="J644" t="n">
+        <v>27</v>
+      </c>
+      <c r="K644" t="n">
+        <v>4245</v>
+      </c>
+      <c r="L644" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="M644" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N644" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O644" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="P644" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs; 3D Computer Vision &amp; Geometric Perception; LiDAR &amp; Multimodal Sensor Fusion</t>
+        </is>
+      </c>
+      <c r="Q644" t="inlineStr">
+        <is>
+          <t>pose estimation, deep learning</t>
+        </is>
+      </c>
+      <c r="R644" t="n">
+        <v>1</v>
+      </c>
+      <c r="S644" t="n">
+        <v>59</v>
+      </c>
+      <c r="T644" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="U644" t="inlineStr">
+        <is>
+          <t>Deep Learning-Based Object Pose Estimation: A Comprehensive Survey</t>
+        </is>
+      </c>
+      <c r="V644" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W644" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X644" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Alancaster.ac.uk%20%22Hossein%20Rahmani%22%20email</t>
+        </is>
+      </c>
+      <c r="Z644" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5101524297</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Lancaster University</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=693)</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>@lancaster.ac.uk</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G645" t="n">
+        <v>4</v>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>Zhengxin Yu</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>Assistant Prof / Rising Star (Responsive)</t>
+        </is>
+      </c>
+      <c r="J645" t="n">
+        <v>14</v>
+      </c>
+      <c r="K645" t="n">
+        <v>938</v>
+      </c>
+      <c r="L645" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="M645" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="N645" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O645" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="P645" t="inlineStr">
+        <is>
+          <t>Visual-Inertial Navigation &amp; SLAM</t>
+        </is>
+      </c>
+      <c r="Q645" t="inlineStr">
+        <is>
+          <t>visual odometry, pose estimation</t>
+        </is>
+      </c>
+      <c r="R645" t="n">
+        <v>1</v>
+      </c>
+      <c r="S645" t="n">
+        <v>36</v>
+      </c>
+      <c r="T645" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="U645" t="inlineStr">
+        <is>
+          <t>Federated Meta Learning for Visual Navigation in GPS-denied Urban Airspace</t>
+        </is>
+      </c>
+      <c r="V645" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W645" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X645" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Alancaster.ac.uk%20%22Zhengxin%20Yu%22%20email</t>
+        </is>
+      </c>
+      <c r="Z645" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5061566111</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Lancaster University</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=693)</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>@lancaster.ac.uk</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G646" t="n">
+        <v>5</v>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>Qiang Ni</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J646" t="n">
+        <v>65</v>
+      </c>
+      <c r="K646" t="n">
+        <v>14991</v>
+      </c>
+      <c r="L646" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="M646" t="n">
+        <v>10</v>
+      </c>
+      <c r="N646" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O646" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="P646" t="inlineStr">
+        <is>
+          <t>State Estimation &amp; Factor Graphs</t>
+        </is>
+      </c>
+      <c r="Q646" t="inlineStr">
+        <is>
+          <t>inertial navigation, trajectory estimation</t>
+        </is>
+      </c>
+      <c r="R646" t="n">
+        <v>1</v>
+      </c>
+      <c r="S646" t="n">
+        <v>122</v>
+      </c>
+      <c r="T646" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="U646" t="inlineStr">
+        <is>
+          <t>Tracking Large-scale Shared Bikes with Inertial Motion Learning in GNSS Blocked Environments</t>
+        </is>
+      </c>
+      <c r="V646" t="n">
+        <v>2026</v>
+      </c>
+      <c r="W646" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X646" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Alancaster.ac.uk%20%22Qiang%20Ni%22%20email</t>
+        </is>
+      </c>
+      <c r="Z646" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5069951778</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Lancaster University</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Tier S+ (Global Elite | h=693)</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>@lancaster.ac.uk</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>Studentship / CDT + Contact PI (Check Intl Funding)</t>
+        </is>
+      </c>
+      <c r="G647" t="n">
+        <v>6</v>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>Allahyar Montazeri</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>Full / Senior Prof (Large Lab)</t>
+        </is>
+      </c>
+      <c r="J647" t="n">
+        <v>22</v>
+      </c>
+      <c r="K647" t="n">
+        <v>1359</v>
+      </c>
+      <c r="L647" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="M647" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="N647" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O647" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="P647" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Autonomous Navigation</t>
+        </is>
+      </c>
+      <c r="Q647" t="inlineStr">
+        <is>
+          <t>robot localization</t>
+        </is>
+      </c>
+      <c r="R647" t="n">
+        <v>1</v>
+      </c>
+      <c r="S647" t="n">
+        <v>63</v>
+      </c>
+      <c r="T647" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
+        </is>
+      </c>
+      <c r="U647" t="inlineStr">
+        <is>
+          <t>Simultaneous localization and mapping in a multi-robot system in a dynamic environment with unknown initial correspondence</t>
+        </is>
+      </c>
+      <c r="V647" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W647" s="2" t="inlineStr">
+        <is>
+          <t>No homepage/funding evidence available</t>
+        </is>
+      </c>
+      <c r="X647" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=site%3Alancaster.ac.uk%20%22Allahyar%20Montazeri%22%20email</t>
+        </is>
+      </c>
+      <c r="Z647" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5001180960</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z612"/>
+  <autoFilter ref="A1:Z647"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>